--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>590768242688</v>
+        <v>587993186304</v>
       </c>
       <c r="G7" t="n">
-        <v>59.18</v>
+        <v>58.9</v>
       </c>
       <c r="H7" t="n">
-        <v>36.97</v>
+        <v>36.8</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1363,16 +1363,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>24.1</v>
+        <v>26.3</v>
       </c>
       <c r="S7" t="n">
-        <v>61.9</v>
+        <v>62.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,37 +1386,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1532.8</v>
+        <v>1525.6</v>
       </c>
       <c r="X7" t="n">
-        <v>17.4</v>
+        <v>16.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.86</v>
+        <v>33.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.65</v>
+        <v>60.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>128.36</v>
+        <v>127.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.69</v>
+        <v>32.49</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.11</v>
+        <v>38.1</v>
       </c>
       <c r="AD7" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.7841</v>
+        <v>1291.6401</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.339</v>
+        <v>1052.303</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>24.1</v>
+        <v>26.3</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>587993186304</v>
+        <v>587222351872</v>
       </c>
       <c r="G7" t="n">
-        <v>58.9</v>
+        <v>58.83</v>
       </c>
       <c r="H7" t="n">
-        <v>36.8</v>
+        <v>36.75</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1363,16 +1363,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="S7" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,22 +1386,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1525.6</v>
+        <v>1523.6</v>
       </c>
       <c r="X7" t="n">
-        <v>16.85</v>
+        <v>16.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.23</v>
+        <v>33.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.89</v>
+        <v>60.68</v>
       </c>
       <c r="AA7" t="n">
-        <v>127.28</v>
+        <v>126.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.49</v>
+        <v>32.43</v>
       </c>
       <c r="AC7" t="n">
         <v>38.1</v>
@@ -1413,10 +1413,10 @@
         <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6401</v>
+        <v>1291.6001</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.303</v>
+        <v>1052.293</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>587222351872</v>
+        <v>587607769088</v>
       </c>
       <c r="G7" t="n">
-        <v>58.83</v>
+        <v>58.86</v>
       </c>
       <c r="H7" t="n">
-        <v>36.75</v>
+        <v>36.77</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1369,7 +1369,7 @@
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>26.9</v>
+        <v>26.5</v>
       </c>
       <c r="S7" t="n">
         <v>62.2</v>
@@ -1386,22 +1386,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1523.6</v>
+        <v>1524.8</v>
       </c>
       <c r="X7" t="n">
-        <v>16.7</v>
+        <v>16.79</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.06</v>
+        <v>33.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.68</v>
+        <v>60.81</v>
       </c>
       <c r="AA7" t="n">
-        <v>126.98</v>
+        <v>127.16</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="AC7" t="n">
         <v>38.1</v>
@@ -1413,10 +1413,10 @@
         <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6001</v>
+        <v>1291.6241</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.293</v>
+        <v>1052.299</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>26.9</v>
+        <v>26.5</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>587607769088</v>
+        <v>587838980096</v>
       </c>
       <c r="G7" t="n">
-        <v>58.86</v>
+        <v>58.89</v>
       </c>
       <c r="H7" t="n">
-        <v>36.77</v>
+        <v>36.79</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1363,16 +1363,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="S7" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,22 +1386,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1524.8</v>
+        <v>1525.2</v>
       </c>
       <c r="X7" t="n">
-        <v>16.79</v>
+        <v>16.82</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.16</v>
+        <v>33.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.81</v>
+        <v>60.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>127.16</v>
+        <v>127.22</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.47</v>
+        <v>32.48</v>
       </c>
       <c r="AC7" t="n">
         <v>38.1</v>
@@ -1413,10 +1413,10 @@
         <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6241</v>
+        <v>1291.6321</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.299</v>
+        <v>1052.301</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>587838980096</v>
+        <v>587607769088</v>
       </c>
       <c r="G7" t="n">
-        <v>58.89</v>
+        <v>58.86</v>
       </c>
       <c r="H7" t="n">
-        <v>36.79</v>
+        <v>36.77</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1363,16 +1363,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="S7" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,22 +1386,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1525.2</v>
+        <v>1524.6</v>
       </c>
       <c r="X7" t="n">
-        <v>16.82</v>
+        <v>16.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.2</v>
+        <v>33.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.85</v>
+        <v>60.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>127.22</v>
+        <v>127.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.48</v>
+        <v>32.46</v>
       </c>
       <c r="AC7" t="n">
         <v>38.1</v>
@@ -1413,10 +1413,10 @@
         <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6321</v>
+        <v>1291.6201</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.301</v>
+        <v>1052.298</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:BC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,6 +614,81 @@
       </c>
       <c r="AN1" t="inlineStr">
         <is>
+          <t>Supporto 20D</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Supporto 60D</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Resistenza 20D</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Resistenza 60D</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Distanza MA50 %</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Distanza MA200 %</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Entry Zone</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Risk Flag</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Trigger Monitoraggio</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Priority Score</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Azione Suggerita</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Scenario Base</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Scenario Positivo</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Scenario Negativo</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Azione Pratica</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>Area</t>
         </is>
       </c>
@@ -750,7 +825,68 @@
       <c r="AM2" t="n">
         <v>751</v>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AN2" t="n">
+        <v>358.7757</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>273.3367</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>402.3797</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>402.3797</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Monitor / partial entry only</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Medium-high risk</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
+      </c>
+      <c r="AW2" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.1%.</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>USA / Internet</t>
         </is>
@@ -888,7 +1024,68 @@
       <c r="AM3" t="n">
         <v>751</v>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AN3" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>164.9777</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>235.4656</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>235.4656</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Monitor / partial entry only</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>High risk</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
+      </c>
+      <c r="AW3" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>NVDA: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>USA / Semiconductors</t>
         </is>
@@ -1026,7 +1223,68 @@
       <c r="AM4" t="n">
         <v>751</v>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AN4" t="n">
+        <v>292.68</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>246.403</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>Monitor / partial entry only</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Medium-high risk</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
+      </c>
+      <c r="AW4" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>AAPL: scenario base Accumulate Carefully, score 73.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.9%.</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>USA / Technology</t>
         </is>
@@ -1162,7 +1420,68 @@
       <c r="AM5" t="n">
         <v>751</v>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AN5" t="n">
+        <v>245.22</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>199.34</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>274</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>274.99</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>Monitor / partial entry only</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Medium-high risk</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
+      </c>
+      <c r="AW5" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>AMZN: scenario base Hold / Monitor, score 66.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 199.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
         <is>
           <t>USA / Consumer &amp; Cloud</t>
         </is>
@@ -1300,7 +1619,68 @@
       <c r="AM6" t="n">
         <v>751</v>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AN6" t="n">
+        <v>404.3343</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>355.9989</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>460.52</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>460.52</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Monitor / partial entry only</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Medium-high risk</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
+      </c>
+      <c r="AW6" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>MSFT: scenario base Hold / Monitor, score 65.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
         <is>
           <t>USA / Technology</t>
         </is>
@@ -1333,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>587607769088</v>
+        <v>590305689600</v>
       </c>
       <c r="G7" t="n">
-        <v>58.86</v>
+        <v>59.14</v>
       </c>
       <c r="H7" t="n">
-        <v>36.77</v>
+        <v>36.94</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1363,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>26.6</v>
+        <v>24.5</v>
       </c>
       <c r="S7" t="n">
-        <v>62.2</v>
+        <v>61.9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1524.6</v>
+        <v>1531.6</v>
       </c>
       <c r="X7" t="n">
-        <v>16.77</v>
+        <v>17.31</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.14</v>
+        <v>33.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.78</v>
+        <v>61.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>127.13</v>
+        <v>128.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.46</v>
+        <v>32.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.1</v>
+        <v>38.11</v>
       </c>
       <c r="AD7" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6201</v>
+        <v>1291.7601</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.298</v>
+        <v>1052.333</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1433,12 +1813,73 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>26.6</v>
+        <v>24.5</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AN7" t="n">
+        <v>1249</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1109.5466</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1531.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1531.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>Extended - wait pullback</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>High risk</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>prezzo 18.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+        </is>
+      </c>
+      <c r="AW7" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ASML.AS: scenario base Hold / Monitor, score 61.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.6%.</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 1531.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
         <is>
           <t>Europe / Semiconductors</t>
         </is>
@@ -1576,7 +2017,68 @@
       <c r="AM8" t="n">
         <v>751</v>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AN8" t="n">
+        <v>585.39</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>525.72</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>635.29</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>688.55</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-11.43</v>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>Wait for trend repair</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>High risk</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>prezzo 5.6% sotto MA50: attendere recupero</t>
+        </is>
+      </c>
+      <c r="AW8" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
         <is>
           <t>USA / Social &amp; AI</t>
         </is>
@@ -1712,7 +2214,68 @@
       <c r="AM9" t="n">
         <v>751</v>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AN9" t="n">
+        <v>391</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>Monitor / partial entry only</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>High risk</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
+        </is>
+      </c>
+      <c r="AW9" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ridurre size / solo monitoraggio</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>TSLA: scenario base High Risk, score 41.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.3%.</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
         <is>
           <t>USA / EV</t>
         </is>
@@ -1810,7 +2373,56 @@
       <c r="AM10" t="n">
         <v>0</v>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>Dati prezzo insufficienti.</t>
+        </is>
+      </c>
+      <c r="AW10" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Evitare per ora</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Azione pratica: non trasformare lo score in ordine automatico; usa watchlist, alert prezzo, controllo news/trimestrali e dimensione posizione.</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>Italy / Semiconductors</t>
         </is>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>590305689600</v>
+        <v>588147326976</v>
       </c>
       <c r="G7" t="n">
-        <v>59.14</v>
+        <v>58.92</v>
       </c>
       <c r="H7" t="n">
-        <v>36.94</v>
+        <v>36.81</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1743,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>24.5</v>
+        <v>26.2</v>
       </c>
       <c r="S7" t="n">
-        <v>61.9</v>
+        <v>62.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1531.6</v>
+        <v>1526</v>
       </c>
       <c r="X7" t="n">
-        <v>17.31</v>
+        <v>16.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.76</v>
+        <v>33.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.52</v>
+        <v>60.93</v>
       </c>
       <c r="AA7" t="n">
-        <v>128.18</v>
+        <v>127.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.66</v>
+        <v>32.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.11</v>
+        <v>38.1</v>
       </c>
       <c r="AD7" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.7601</v>
+        <v>1291.6481</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.333</v>
+        <v>1052.305</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>24.5</v>
+        <v>26.2</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>
@@ -1825,16 +1825,16 @@
         <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>1531.6</v>
+        <v>1526</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1531.6</v>
+        <v>1526</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.57</v>
+        <v>18.14</v>
       </c>
       <c r="AS7" t="n">
-        <v>45.54</v>
+        <v>45.01</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 18.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 18.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>18.9</v>
+        <v>20.2</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 61.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.1%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1531.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1526.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>588147326976</v>
+        <v>587376492544</v>
       </c>
       <c r="G7" t="n">
-        <v>58.92</v>
+        <v>58.84</v>
       </c>
       <c r="H7" t="n">
-        <v>36.81</v>
+        <v>36.76</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1743,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="S7" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,22 +1766,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="X7" t="n">
-        <v>16.88</v>
+        <v>16.73</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.27</v>
+        <v>33.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.93</v>
+        <v>60.72</v>
       </c>
       <c r="AA7" t="n">
-        <v>127.34</v>
+        <v>127.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.5</v>
+        <v>32.44</v>
       </c>
       <c r="AC7" t="n">
         <v>38.1</v>
@@ -1793,10 +1793,10 @@
         <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6481</v>
+        <v>1291.6081</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.305</v>
+        <v>1052.295</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>
@@ -1825,16 +1825,16 @@
         <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.14</v>
+        <v>17.99</v>
       </c>
       <c r="AS7" t="n">
-        <v>45.01</v>
+        <v>44.83</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 18.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 18.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.1%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1526.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1524.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>587376492544</v>
+        <v>588841156608</v>
       </c>
       <c r="G7" t="n">
-        <v>58.84</v>
+        <v>58.99</v>
       </c>
       <c r="H7" t="n">
-        <v>36.76</v>
+        <v>36.85</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1743,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>26.8</v>
+        <v>25.6</v>
       </c>
       <c r="S7" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,22 +1766,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1524</v>
+        <v>1527.8</v>
       </c>
       <c r="X7" t="n">
-        <v>16.73</v>
+        <v>17.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.09</v>
+        <v>33.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.72</v>
+        <v>61.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>127.04</v>
+        <v>127.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.44</v>
+        <v>32.55</v>
       </c>
       <c r="AC7" t="n">
         <v>38.1</v>
@@ -1793,10 +1793,10 @@
         <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6081</v>
+        <v>1291.6841</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.295</v>
+        <v>1052.314</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>26.8</v>
+        <v>25.6</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>
@@ -1825,16 +1825,16 @@
         <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>1524</v>
+        <v>1527.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1524</v>
+        <v>1527.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>17.99</v>
+        <v>18.28</v>
       </c>
       <c r="AS7" t="n">
-        <v>44.83</v>
+        <v>45.18</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 18.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 18.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>20.7</v>
+        <v>19.8</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.3%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1524.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1527.80 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>588841156608</v>
+        <v>588224397312</v>
       </c>
       <c r="G7" t="n">
-        <v>58.99</v>
+        <v>58.93</v>
       </c>
       <c r="H7" t="n">
-        <v>36.85</v>
+        <v>36.81</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1743,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="Q7" t="n">
         <v>18.5</v>
       </c>
       <c r="R7" t="n">
-        <v>25.6</v>
+        <v>26.1</v>
       </c>
       <c r="S7" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,22 +1766,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1527.8</v>
+        <v>1526.2</v>
       </c>
       <c r="X7" t="n">
-        <v>17.02</v>
+        <v>16.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.42</v>
+        <v>33.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.12</v>
+        <v>60.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>127.61</v>
+        <v>127.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.55</v>
+        <v>32.51</v>
       </c>
       <c r="AC7" t="n">
         <v>38.1</v>
@@ -1793,10 +1793,10 @@
         <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6841</v>
+        <v>1291.6521</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.314</v>
+        <v>1052.306</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>25.6</v>
+        <v>26.1</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>
@@ -1825,16 +1825,16 @@
         <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>1527.8</v>
+        <v>1526.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1527.8</v>
+        <v>1526.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.28</v>
+        <v>18.16</v>
       </c>
       <c r="AS7" t="n">
-        <v>45.18</v>
+        <v>45.03</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 18.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 18.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.3%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1527.80 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1526.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4430541881344</v>
+        <v>4431456239616</v>
       </c>
       <c r="G2" t="n">
-        <v>27.69</v>
+        <v>27.7</v>
       </c>
       <c r="H2" t="n">
-        <v>25.12</v>
+        <v>25.13</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -773,25 +773,25 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>363.31</v>
+        <v>363.385</v>
       </c>
       <c r="X2" t="n">
-        <v>-8.66</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.66</v>
+        <v>18.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.61</v>
+        <v>13.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>116.86</v>
+        <v>110.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.56</v>
+        <v>44.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.73</v>
+        <v>29.71</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
@@ -800,10 +800,10 @@
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>355.9417</v>
+        <v>357.7259</v>
       </c>
       <c r="AG2" t="n">
-        <v>304.4693</v>
+        <v>305.2903</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>82.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
         <v>358.7757</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.07</v>
+        <v>1.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.33</v>
+        <v>19.03</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.1%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5053469425664</v>
+        <v>4988072886272</v>
       </c>
       <c r="G3" t="n">
-        <v>31.95</v>
+        <v>31.54</v>
       </c>
       <c r="H3" t="n">
-        <v>16.45</v>
+        <v>16.24</v>
       </c>
       <c r="I3" t="n">
         <v>62.97</v>
@@ -946,10 +946,10 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>90.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>14.1</v>
@@ -958,7 +958,7 @@
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>74.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>208.64</v>
+        <v>205.94</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.24</v>
+        <v>-4.19</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.37</v>
+        <v>11.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.91</v>
+        <v>13.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>49.25</v>
+        <v>45.52</v>
       </c>
       <c r="AB3" t="n">
-        <v>76.01000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>46.98</v>
+        <v>46.96</v>
       </c>
       <c r="AD3" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>203.972</v>
+        <v>204.7443</v>
       </c>
       <c r="AG3" t="n">
-        <v>188.512</v>
+        <v>188.668</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>90.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>14.1</v>
@@ -1022,7 +1022,7 @@
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>205.1</v>
@@ -1037,10 +1037,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.29</v>
+        <v>0.57</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.68</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>58.1</v>
+        <v>56.7</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 73.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4428825362432</v>
+        <v>4307581140992</v>
       </c>
       <c r="G4" t="n">
-        <v>36.51</v>
+        <v>35.51</v>
       </c>
       <c r="H4" t="n">
-        <v>31.38</v>
+        <v>30.52</v>
       </c>
       <c r="I4" t="n">
         <v>27.15</v>
@@ -1145,19 +1145,19 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>89.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>43.4</v>
       </c>
       <c r="Q4" t="n">
         <v>42.2</v>
       </c>
       <c r="R4" t="n">
-        <v>71.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>73.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>301.54</v>
+        <v>293.285</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.14</v>
+        <v>12.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.62</v>
+        <v>5.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>50.89</v>
+        <v>44.39</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.25</v>
+        <v>18.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>25.91</v>
+        <v>25.94</v>
       </c>
       <c r="AD4" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>282.0628</v>
+        <v>282.9571</v>
       </c>
       <c r="AG4" t="n">
-        <v>265.1448</v>
+        <v>265.4899</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>89.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AK4" t="n">
         <v>42.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>71.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>292.68</v>
+        <v>293.285</v>
       </c>
       <c r="AO4" t="n">
         <v>246.403</v>
@@ -1236,10 +1236,10 @@
         <v>315.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.91</v>
+        <v>3.65</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.73</v>
+        <v>10.47</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>70.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 73.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2637858340864</v>
+        <v>2633039347712</v>
       </c>
       <c r="G5" t="n">
-        <v>31.64</v>
+        <v>31.58</v>
       </c>
       <c r="H5" t="n">
-        <v>24.86</v>
+        <v>24.82</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>79.5</v>
+        <v>77.5</v>
       </c>
       <c r="P5" t="n">
-        <v>55.9</v>
+        <v>56.1</v>
       </c>
       <c r="Q5" t="n">
         <v>38.1</v>
       </c>
       <c r="R5" t="n">
-        <v>75.8</v>
+        <v>75</v>
       </c>
       <c r="S5" t="n">
-        <v>66.8</v>
+        <v>66.3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>245.22</v>
+        <v>244.772</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.57</v>
+        <v>-10.23</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.86</v>
+        <v>14.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.03</v>
+        <v>6.64</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.95</v>
+        <v>14.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.9</v>
+        <v>25.79</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.99</v>
+        <v>30.97</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>251.9112</v>
+        <v>252.8198</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.2354</v>
+        <v>232.3495</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,19 +1409,19 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>79.5</v>
+        <v>77.5</v>
       </c>
       <c r="AK5" t="n">
         <v>38.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>75.8</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>245.22</v>
+        <v>244.772</v>
       </c>
       <c r="AO5" t="n">
         <v>199.34</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-2.66</v>
+        <v>-3.18</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.59</v>
+        <v>5.35</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>66.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.2%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3058583732224</v>
+        <v>3020624494592</v>
       </c>
       <c r="G6" t="n">
-        <v>24.51</v>
+        <v>24.2</v>
       </c>
       <c r="H6" t="n">
-        <v>21.29</v>
+        <v>21.02</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1541,19 +1541,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>39.9</v>
+        <v>38.1</v>
       </c>
       <c r="P6" t="n">
-        <v>69.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>44.1</v>
       </c>
       <c r="R6" t="n">
-        <v>78.2</v>
+        <v>74.2</v>
       </c>
       <c r="S6" t="n">
-        <v>65.5</v>
+        <v>63.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,27 +1562,27 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>411.74</v>
+        <v>406.635</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.93</v>
+        <v>-1.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.79</v>
+        <v>0.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>-13.99</v>
+        <v>-15.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>-11.26</v>
+        <v>-12.86</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.91</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>23.97</v>
@@ -1591,33 +1591,33 @@
         <v>-33.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AF6" t="n">
-        <v>408.6026</v>
+        <v>409.6153</v>
       </c>
       <c r="AG6" t="n">
-        <v>453.9891</v>
+        <v>453.517</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>39.9</v>
+        <v>38.1</v>
       </c>
       <c r="AK6" t="n">
         <v>44.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>78.2</v>
+        <v>74.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
         <v>404.3343</v>
@@ -1632,14 +1632,14 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.77</v>
+        <v>-0.73</v>
       </c>
       <c r="AS6" t="n">
-        <v>-9.31</v>
+        <v>-10.34</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>61.6</v>
+        <v>59.6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 65.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>588224397312</v>
+        <v>593466163200</v>
       </c>
       <c r="G7" t="n">
-        <v>58.93</v>
+        <v>59.45</v>
       </c>
       <c r="H7" t="n">
-        <v>36.81</v>
+        <v>37.14</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1743,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="R7" t="n">
-        <v>26.1</v>
+        <v>22</v>
       </c>
       <c r="S7" t="n">
-        <v>62.1</v>
+        <v>61.6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1526.2</v>
+        <v>1539.8</v>
       </c>
       <c r="X7" t="n">
-        <v>16.9</v>
+        <v>17.94</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.28</v>
+        <v>34.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.95</v>
+        <v>62.39</v>
       </c>
       <c r="AA7" t="n">
-        <v>127.37</v>
+        <v>129.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.51</v>
+        <v>32.89</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.1</v>
+        <v>38.11</v>
       </c>
       <c r="AD7" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.6521</v>
+        <v>1291.9241</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.306</v>
+        <v>1052.374</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AL7" t="n">
-        <v>26.1</v>
+        <v>22</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>
@@ -1825,16 +1825,16 @@
         <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>1526.2</v>
+        <v>1539.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1526.2</v>
+        <v>1539.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.16</v>
+        <v>19.19</v>
       </c>
       <c r="AS7" t="n">
-        <v>45.03</v>
+        <v>46.32</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 18.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 19.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>20.2</v>
+        <v>17</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 61.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1526.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1539.80 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1485967589376</v>
+        <v>1505462714368</v>
       </c>
       <c r="G8" t="n">
-        <v>21.28</v>
+        <v>21.56</v>
       </c>
       <c r="H8" t="n">
-        <v>16.19</v>
+        <v>16.4</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1942,16 +1942,16 @@
         <v>26.3</v>
       </c>
       <c r="P8" t="n">
-        <v>80.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="Q8" t="n">
         <v>29.1</v>
       </c>
       <c r="R8" t="n">
-        <v>66.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>585.39</v>
+        <v>593.12</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.09</v>
+        <v>-2.71</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.5</v>
+        <v>-9.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11.36</v>
+        <v>-11.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>-14.23</v>
+        <v>-14.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>30.82</v>
+        <v>31.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.3</v>
+        <v>36.28</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AF8" t="n">
-        <v>620.2773999999999</v>
+        <v>621.6254</v>
       </c>
       <c r="AG8" t="n">
-        <v>660.9453</v>
+        <v>660.2241</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
         <v>29.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>66.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
         <v>585.39</v>
@@ -2030,10 +2030,10 @@
         <v>688.55</v>
       </c>
       <c r="AR8" t="n">
-        <v>-5.62</v>
+        <v>-4.59</v>
       </c>
       <c r="AS8" t="n">
-        <v>-11.43</v>
+        <v>-10.16</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 5.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1535903268864</v>
+        <v>1498928119808</v>
       </c>
       <c r="G9" t="n">
-        <v>371.77</v>
+        <v>362.82</v>
       </c>
       <c r="H9" t="n">
-        <v>163.28</v>
+        <v>159.35</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>58.5</v>
+        <v>51.4</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>78.2</v>
       </c>
       <c r="S9" t="n">
-        <v>41.3</v>
+        <v>39.5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>408.95</v>
+        <v>399.105</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-6.83</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.58</v>
+        <v>-0.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>-10.03</v>
+        <v>-12.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>43.64</v>
+        <v>35.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>18.86</v>
+        <v>17.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>57.95</v>
+        <v>57.93</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>396.0254</v>
+        <v>396.7709</v>
       </c>
       <c r="AG9" t="n">
-        <v>414.5671</v>
+        <v>414.9621</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>58.5</v>
+        <v>51.4</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>78.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN9" t="n">
         <v>391</v>
@@ -2227,10 +2227,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.26</v>
+        <v>0.59</v>
       </c>
       <c r="AS9" t="n">
-        <v>-1.35</v>
+        <v>-3.82</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>34.9</v>
+        <v>33</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 41.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.3%.</t>
+          <t>TSLA: scenario base High Risk, score 39.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4431456239616</v>
+        <v>4396578766848</v>
       </c>
       <c r="G2" t="n">
-        <v>27.7</v>
+        <v>27.48</v>
       </c>
       <c r="H2" t="n">
-        <v>25.13</v>
+        <v>24.93</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,7 +750,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>60.1</v>
+        <v>60.7</v>
       </c>
       <c r="Q2" t="n">
         <v>40.5</v>
@@ -759,7 +759,7 @@
         <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>363.385</v>
+        <v>360.55</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.279999999999999</v>
+        <v>-9.99</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.42</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.33</v>
+        <v>12.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.08</v>
+        <v>108.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.5</v>
+        <v>44.12</v>
       </c>
       <c r="AC2" t="n">
         <v>29.71</v>
@@ -797,13 +797,13 @@
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>357.7259</v>
+        <v>357.6692</v>
       </c>
       <c r="AG2" t="n">
-        <v>305.2903</v>
+        <v>305.2761</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.58</v>
+        <v>0.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.03</v>
+        <v>18.1</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4988072886272</v>
+        <v>4282539048960</v>
       </c>
       <c r="G3" t="n">
-        <v>31.54</v>
+        <v>35.3</v>
       </c>
       <c r="H3" t="n">
-        <v>16.24</v>
+        <v>30.34</v>
       </c>
       <c r="I3" t="n">
-        <v>62.97</v>
+        <v>27.15</v>
       </c>
       <c r="J3" t="n">
-        <v>114.29</v>
+        <v>141.47</v>
       </c>
       <c r="K3" t="n">
-        <v>85.2</v>
+        <v>16.6</v>
       </c>
       <c r="L3" t="n">
-        <v>6.55</v>
+        <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>85.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>68.40000000000001</v>
+        <v>43.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.1</v>
+        <v>42.2</v>
       </c>
       <c r="R3" t="n">
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>73.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,42 +967,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>205.94</v>
+        <v>291.56</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.19</v>
+        <v>-0.51</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.59</v>
+        <v>11.88</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.04</v>
+        <v>4.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>45.52</v>
+        <v>43.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>75.11</v>
+        <v>17.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>46.96</v>
+        <v>25.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>204.7443</v>
+        <v>282.9226</v>
       </c>
       <c r="AG3" t="n">
-        <v>188.668</v>
+        <v>265.4813</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.1</v>
+        <v>42.2</v>
       </c>
       <c r="AL3" t="n">
         <v>82.8</v>
@@ -1025,22 +1025,22 @@
         <v>752</v>
       </c>
       <c r="AN3" t="n">
-        <v>205.1</v>
+        <v>291.56</v>
       </c>
       <c r="AO3" t="n">
-        <v>164.9777</v>
+        <v>246.403</v>
       </c>
       <c r="AP3" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.57</v>
+        <v>3.05</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>56.7</v>
+        <v>71.8</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 73.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4307581140992</v>
+        <v>4926793580544</v>
       </c>
       <c r="G4" t="n">
-        <v>35.51</v>
+        <v>31.15</v>
       </c>
       <c r="H4" t="n">
-        <v>30.52</v>
+        <v>16.04</v>
       </c>
       <c r="I4" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="J4" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="K4" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L4" t="n">
-        <v>79.55</v>
+        <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>81.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="P4" t="n">
-        <v>43.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>42.2</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>78.8</v>
       </c>
       <c r="S4" t="n">
-        <v>73</v>
+        <v>71.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,80 +1166,80 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>293.285</v>
+        <v>203.42</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08</v>
+        <v>-5.36</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.55</v>
+        <v>10.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.4</v>
+        <v>11.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.39</v>
+        <v>43.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.11</v>
+        <v>74.39</v>
       </c>
       <c r="AC4" t="n">
-        <v>25.94</v>
+        <v>46.98</v>
       </c>
       <c r="AD4" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.7</v>
+        <v>1.58</v>
       </c>
       <c r="AF4" t="n">
-        <v>282.9571</v>
+        <v>204.6939</v>
       </c>
       <c r="AG4" t="n">
-        <v>265.4899</v>
+        <v>188.6554</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>42.2</v>
+        <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>78.8</v>
       </c>
       <c r="AM4" t="n">
         <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>293.285</v>
+        <v>203.42</v>
       </c>
       <c r="AO4" t="n">
-        <v>246.403</v>
+        <v>164.9777</v>
       </c>
       <c r="AP4" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AQ4" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.65</v>
+        <v>-0.62</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.47</v>
+        <v>7.83</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>72.2</v>
+        <v>54.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.6%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2633039347712</v>
+        <v>2609943674880</v>
       </c>
       <c r="G5" t="n">
-        <v>31.58</v>
+        <v>31.31</v>
       </c>
       <c r="H5" t="n">
-        <v>24.82</v>
+        <v>24.6</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>77.5</v>
+        <v>75.3</v>
       </c>
       <c r="P5" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="Q5" t="n">
         <v>38.1</v>
       </c>
       <c r="R5" t="n">
-        <v>75</v>
+        <v>73.7</v>
       </c>
       <c r="S5" t="n">
-        <v>66.3</v>
+        <v>65.7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>244.772</v>
+        <v>242.64</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.23</v>
+        <v>-11.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.2</v>
+        <v>13.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.64</v>
+        <v>5.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.61</v>
+        <v>13.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.79</v>
+        <v>25.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.97</v>
+        <v>30.98</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>252.8198</v>
+        <v>252.7772</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.3495</v>
+        <v>232.3388</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,19 +1409,19 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>77.5</v>
+        <v>75.3</v>
       </c>
       <c r="AK5" t="n">
         <v>38.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>73.7</v>
       </c>
       <c r="AM5" t="n">
         <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>244.772</v>
+        <v>242.64</v>
       </c>
       <c r="AO5" t="n">
         <v>199.34</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.18</v>
+        <v>-4.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.35</v>
+        <v>4.43</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>65.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.0%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3020624494592</v>
+        <v>2997522006016</v>
       </c>
       <c r="G6" t="n">
-        <v>24.2</v>
+        <v>24.02</v>
       </c>
       <c r="H6" t="n">
-        <v>21.02</v>
+        <v>20.86</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1541,19 +1541,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>38.1</v>
+        <v>36.5</v>
       </c>
       <c r="P6" t="n">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="Q6" t="n">
         <v>44.1</v>
       </c>
       <c r="R6" t="n">
-        <v>74.2</v>
+        <v>73</v>
       </c>
       <c r="S6" t="n">
-        <v>63.8</v>
+        <v>63.4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>406.635</v>
+        <v>403.54</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.83</v>
+        <v>-2.58</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.43</v>
+        <v>-0.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>-15.46</v>
+        <v>-16.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>-12.86</v>
+        <v>-13.52</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.97</v>
+        <v>23.98</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AF6" t="n">
-        <v>409.6153</v>
+        <v>409.5534</v>
       </c>
       <c r="AG6" t="n">
-        <v>453.517</v>
+        <v>453.5015</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,19 +1608,19 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>38.1</v>
+        <v>36.5</v>
       </c>
       <c r="AK6" t="n">
         <v>44.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>74.2</v>
+        <v>73</v>
       </c>
       <c r="AM6" t="n">
         <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>404.3343</v>
+        <v>403.54</v>
       </c>
       <c r="AO6" t="n">
         <v>355.9989</v>
@@ -1632,10 +1632,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.73</v>
+        <v>-1.47</v>
       </c>
       <c r="AS6" t="n">
-        <v>-10.34</v>
+        <v>-11.02</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.7%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>593466163200</v>
+        <v>595316113408</v>
       </c>
       <c r="G7" t="n">
-        <v>59.45</v>
+        <v>59.64</v>
       </c>
       <c r="H7" t="n">
-        <v>37.14</v>
+        <v>37.26</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1743,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="Q7" t="n">
         <v>18.4</v>
       </c>
       <c r="R7" t="n">
-        <v>22</v>
+        <v>20.6</v>
       </c>
       <c r="S7" t="n">
-        <v>61.6</v>
+        <v>61.4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1539.8</v>
+        <v>1544.6</v>
       </c>
       <c r="X7" t="n">
-        <v>17.94</v>
+        <v>18.31</v>
       </c>
       <c r="Y7" t="n">
-        <v>34.47</v>
+        <v>34.89</v>
       </c>
       <c r="Z7" t="n">
-        <v>62.39</v>
+        <v>62.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>129.4</v>
+        <v>130.11</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.89</v>
+        <v>33.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.11</v>
+        <v>38.12</v>
       </c>
       <c r="AD7" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>1291.9241</v>
+        <v>1292.0201</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.374</v>
+        <v>1052.398</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>18.4</v>
       </c>
       <c r="AL7" t="n">
-        <v>22</v>
+        <v>20.6</v>
       </c>
       <c r="AM7" t="n">
         <v>765</v>
@@ -1825,16 +1825,16 @@
         <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>1539.8</v>
+        <v>1544.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1539.8</v>
+        <v>1544.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.19</v>
+        <v>19.55</v>
       </c>
       <c r="AS7" t="n">
-        <v>46.32</v>
+        <v>46.77</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 19.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 19.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>15.9</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 61.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 61.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.6%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1539.80 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1544.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1505462714368</v>
+        <v>1493659025408</v>
       </c>
       <c r="G8" t="n">
-        <v>21.56</v>
+        <v>21.39</v>
       </c>
       <c r="H8" t="n">
-        <v>16.4</v>
+        <v>16.27</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>26.3</v>
+        <v>24.7</v>
       </c>
       <c r="P8" t="n">
-        <v>79.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>29.1</v>
       </c>
       <c r="R8" t="n">
-        <v>68.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="S8" t="n">
-        <v>59.5</v>
+        <v>59</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>593.12</v>
+        <v>588.42</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.71</v>
+        <v>-3.48</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.24</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11.78</v>
+        <v>-12.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>-14.73</v>
+        <v>-15.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>31.35</v>
+        <v>31</v>
       </c>
       <c r="AC8" t="n">
         <v>36.28</v>
@@ -1989,13 +1989,13 @@
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>621.6254</v>
+        <v>621.5314</v>
       </c>
       <c r="AG8" t="n">
-        <v>660.2241</v>
+        <v>660.2005</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26.3</v>
+        <v>24.7</v>
       </c>
       <c r="AK8" t="n">
         <v>29.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>68.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
@@ -2030,10 +2030,10 @@
         <v>688.55</v>
       </c>
       <c r="AR8" t="n">
-        <v>-4.59</v>
+        <v>-5.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>-10.16</v>
+        <v>-10.87</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>40.2</v>
+        <v>39.4</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2100,174 +2100,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1498928119808</v>
-      </c>
-      <c r="G9" t="n">
-        <v>362.82</v>
-      </c>
-      <c r="H9" t="n">
-        <v>159.35</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>51.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>399.105</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-6.83</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-12.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>57.93</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>396.7709</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>414.9621</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>51.4</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL9" t="n">
         <v>0</v>
       </c>
-      <c r="AL9" t="n">
-        <v>78.2</v>
-      </c>
       <c r="AM9" t="n">
-        <v>752</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>391</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>343.25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-3.82</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>33</v>
+        <v>32.3</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 39.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2277,19 +2227,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2297,124 +2247,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1480543830016</v>
+      </c>
+      <c r="G10" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="H10" t="n">
+        <v>157.39</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>50</v>
-      </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>394.16</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-7.98</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-13.37</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>396.672</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>414.9374</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>100</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>74.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+        <v>752</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>391</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-5</v>
+      </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>32.3</v>
+        <v>30.7</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 37.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.6%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4396578766848</v>
+        <v>4442127073280</v>
       </c>
       <c r="G2" t="n">
-        <v>27.48</v>
+        <v>27.76</v>
       </c>
       <c r="H2" t="n">
-        <v>24.93</v>
+        <v>25.18</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,7 +750,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>60.7</v>
+        <v>60</v>
       </c>
       <c r="Q2" t="n">
         <v>40.5</v>
@@ -759,7 +759,7 @@
         <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,25 +773,25 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>360.55</v>
+        <v>364.26</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.99</v>
+        <v>-9.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>18.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.45</v>
+        <v>13.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.44</v>
+        <v>110.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.12</v>
+        <v>44.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.71</v>
+        <v>29.72</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
@@ -800,10 +800,10 @@
         <v>1.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>357.6692</v>
+        <v>357.7434</v>
       </c>
       <c r="AG2" t="n">
-        <v>305.2761</v>
+        <v>305.2947</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>82.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AN2" t="n">
         <v>358.7757</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.8</v>
+        <v>1.82</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.1</v>
+        <v>19.31</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.8%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4282539048960</v>
+        <v>5042570002432</v>
       </c>
       <c r="G3" t="n">
-        <v>35.3</v>
+        <v>31.88</v>
       </c>
       <c r="H3" t="n">
-        <v>30.34</v>
+        <v>16.42</v>
       </c>
       <c r="I3" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="J3" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="K3" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L3" t="n">
-        <v>79.55</v>
+        <v>6.55</v>
       </c>
       <c r="M3" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>80.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="P3" t="n">
-        <v>43.8</v>
+        <v>67.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.2</v>
+        <v>14.1</v>
       </c>
       <c r="R3" t="n">
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>72.7</v>
+        <v>74.2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,42 +967,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>291.56</v>
+        <v>208.19</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.51</v>
+        <v>-3.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.88</v>
+        <v>12.81</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.78</v>
+        <v>14.27</v>
       </c>
       <c r="AA3" t="n">
-        <v>43.54</v>
+        <v>47.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.88</v>
+        <v>74.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>25.96</v>
+        <v>46.97</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="AF3" t="n">
-        <v>282.9226</v>
+        <v>204.7893</v>
       </c>
       <c r="AG3" t="n">
-        <v>265.4813</v>
+        <v>188.6792</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,34 +1013,34 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>80.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>42.2</v>
+        <v>14.1</v>
       </c>
       <c r="AL3" t="n">
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AN3" t="n">
-        <v>291.56</v>
+        <v>205.1</v>
       </c>
       <c r="AO3" t="n">
-        <v>246.403</v>
+        <v>164.9777</v>
       </c>
       <c r="AP3" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AQ3" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.05</v>
+        <v>1.66</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.82</v>
+        <v>10.34</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>71.8</v>
+        <v>57.5</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.0%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.7%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4926793580544</v>
+        <v>4267410980864</v>
       </c>
       <c r="G4" t="n">
-        <v>31.15</v>
+        <v>35.18</v>
       </c>
       <c r="H4" t="n">
-        <v>16.04</v>
+        <v>30.23</v>
       </c>
       <c r="I4" t="n">
-        <v>62.97</v>
+        <v>27.15</v>
       </c>
       <c r="J4" t="n">
-        <v>114.29</v>
+        <v>141.47</v>
       </c>
       <c r="K4" t="n">
-        <v>85.2</v>
+        <v>16.6</v>
       </c>
       <c r="L4" t="n">
-        <v>6.55</v>
+        <v>79.55</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>82.2</v>
+        <v>79.5</v>
       </c>
       <c r="P4" t="n">
-        <v>69.09999999999999</v>
+        <v>44.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>42.1</v>
       </c>
       <c r="R4" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,80 +1166,80 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>203.42</v>
+        <v>290.55</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.36</v>
+        <v>-0.85</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.23</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.65</v>
+        <v>4.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>43.74</v>
+        <v>43.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>74.39</v>
+        <v>17.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.98</v>
+        <v>25.98</v>
       </c>
       <c r="AD4" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.58</v>
+        <v>0.66</v>
       </c>
       <c r="AF4" t="n">
-        <v>204.6939</v>
+        <v>282.9024</v>
       </c>
       <c r="AG4" t="n">
-        <v>188.6554</v>
+        <v>265.4762</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>82.2</v>
+        <v>79.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.1</v>
+        <v>42.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AN4" t="n">
-        <v>203.42</v>
+        <v>290.55</v>
       </c>
       <c r="AO4" t="n">
-        <v>164.9777</v>
+        <v>246.403</v>
       </c>
       <c r="AP4" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.62</v>
+        <v>2.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.83</v>
+        <v>9.44</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>54.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2609943674880</v>
+        <v>2626778562560</v>
       </c>
       <c r="G5" t="n">
-        <v>31.31</v>
+        <v>31.51</v>
       </c>
       <c r="H5" t="n">
-        <v>24.6</v>
+        <v>24.77</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>75.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>56.7</v>
+        <v>56.2</v>
       </c>
       <c r="Q5" t="n">
         <v>38.1</v>
       </c>
       <c r="R5" t="n">
-        <v>73.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>65.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>242.64</v>
+        <v>244.19</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.02</v>
+        <v>-10.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.21</v>
+        <v>13.93</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.71</v>
+        <v>6.39</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.61</v>
+        <v>14.34</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.42</v>
+        <v>24.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.98</v>
+        <v>30.96</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>252.7772</v>
+        <v>252.8082</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.3388</v>
+        <v>232.3466</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,19 +1409,19 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>75.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AK5" t="n">
         <v>38.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>73.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AN5" t="n">
-        <v>242.64</v>
+        <v>244.19</v>
       </c>
       <c r="AO5" t="n">
         <v>199.34</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.01</v>
+        <v>-3.41</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.43</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 4.0% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2997522006016</v>
+        <v>2996704903168</v>
       </c>
       <c r="G6" t="n">
-        <v>24.02</v>
+        <v>24.01</v>
       </c>
       <c r="H6" t="n">
         <v>20.86</v>
@@ -1541,7 +1541,7 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="P6" t="n">
         <v>70.5</v>
@@ -1553,7 +1553,7 @@
         <v>73</v>
       </c>
       <c r="S6" t="n">
-        <v>63.4</v>
+        <v>63.3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>403.54</v>
+        <v>403.41</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.58</v>
+        <v>-2.61</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>-16.11</v>
+        <v>-16.13</v>
       </c>
       <c r="AA6" t="n">
-        <v>-13.52</v>
+        <v>-13.55</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.17</v>
+        <v>7.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.98</v>
+        <v>23.99</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="AF6" t="n">
-        <v>409.5534</v>
+        <v>409.5508</v>
       </c>
       <c r="AG6" t="n">
-        <v>453.5015</v>
+        <v>453.5009</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="AK6" t="n">
         <v>44.1</v>
@@ -1617,10 +1617,10 @@
         <v>73</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AN6" t="n">
-        <v>403.54</v>
+        <v>403.41</v>
       </c>
       <c r="AO6" t="n">
         <v>355.9989</v>
@@ -1632,10 +1632,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.47</v>
+        <v>-1.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>-11.02</v>
+        <v>-11.05</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>595316113408</v>
+        <v>581364023296</v>
       </c>
       <c r="G7" t="n">
-        <v>59.64</v>
+        <v>58.24</v>
       </c>
       <c r="H7" t="n">
-        <v>37.26</v>
+        <v>36.38</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1743,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>11.1</v>
+        <v>12.3</v>
       </c>
       <c r="Q7" t="n">
         <v>18.4</v>
       </c>
       <c r="R7" t="n">
-        <v>20.6</v>
+        <v>27.1</v>
       </c>
       <c r="S7" t="n">
-        <v>61.4</v>
+        <v>62.3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1544.6</v>
+        <v>1514.6</v>
       </c>
       <c r="X7" t="n">
-        <v>18.31</v>
+        <v>14.79</v>
       </c>
       <c r="Y7" t="n">
-        <v>34.89</v>
+        <v>32.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>62.89</v>
+        <v>58.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>130.11</v>
+        <v>121.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>33.03</v>
+        <v>32.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.12</v>
+        <v>38.13</v>
       </c>
       <c r="AD7" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1292.0201</v>
+        <v>1284.3927</v>
       </c>
       <c r="AG7" t="n">
-        <v>1052.398</v>
+        <v>1047.8913</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         <v>18.4</v>
       </c>
       <c r="AL7" t="n">
-        <v>20.6</v>
+        <v>27.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AN7" t="n">
         <v>1249</v>
@@ -1825,16 +1825,16 @@
         <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>1544.6</v>
+        <v>1514.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1544.6</v>
+        <v>1514.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.55</v>
+        <v>17.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>46.77</v>
+        <v>44.54</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 19.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 17.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>15.9</v>
+        <v>20.9</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 61.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.9%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1544.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1514.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1493659025408</v>
+        <v>1483936890880</v>
       </c>
       <c r="G8" t="n">
-        <v>21.39</v>
+        <v>21.25</v>
       </c>
       <c r="H8" t="n">
-        <v>16.27</v>
+        <v>16.17</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>24.7</v>
+        <v>23.4</v>
       </c>
       <c r="P8" t="n">
-        <v>80.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>29.1</v>
       </c>
       <c r="R8" t="n">
-        <v>67.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>58.7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>588.42</v>
+        <v>584.59</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.48</v>
+        <v>-4.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.960000000000001</v>
+        <v>-10.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>-12.48</v>
+        <v>-13.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>-15.4</v>
+        <v>-15.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>31</v>
+        <v>29.76</v>
       </c>
       <c r="AC8" t="n">
         <v>36.28</v>
@@ -1989,13 +1989,13 @@
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>621.5314</v>
+        <v>621.4548</v>
       </c>
       <c r="AG8" t="n">
-        <v>660.2005</v>
+        <v>660.1814000000001</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,19 +2006,19 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24.7</v>
+        <v>23.4</v>
       </c>
       <c r="AK8" t="n">
         <v>29.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>67.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AN8" t="n">
-        <v>585.39</v>
+        <v>584.59</v>
       </c>
       <c r="AO8" t="n">
         <v>525.72</v>
@@ -2030,10 +2030,10 @@
         <v>688.55</v>
       </c>
       <c r="AR8" t="n">
-        <v>-5.33</v>
+        <v>-5.93</v>
       </c>
       <c r="AS8" t="n">
-        <v>-10.87</v>
+        <v>-11.45</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>39.4</v>
+        <v>38.9</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
+          <t>META: scenario base Hold / Monitor, score 58.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.9%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1480543830016</v>
+        <v>1489820450816</v>
       </c>
       <c r="G10" t="n">
-        <v>358.37</v>
+        <v>360.62</v>
       </c>
       <c r="H10" t="n">
-        <v>157.39</v>
+        <v>157.88</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="S10" t="n">
-        <v>37.4</v>
+        <v>37.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>394.16</v>
+        <v>396.68</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.98</v>
+        <v>-7.39</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.27</v>
+        <v>-0.64</v>
       </c>
       <c r="Z10" t="n">
-        <v>-13.37</v>
+        <v>-12.82</v>
       </c>
       <c r="AA10" t="n">
-        <v>33.55</v>
+        <v>34.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>17.37</v>
+        <v>16.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>57.96</v>
+        <v>57.97</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AF10" t="n">
-        <v>396.672</v>
+        <v>396.7224</v>
       </c>
       <c r="AG10" t="n">
-        <v>414.9374</v>
+        <v>414.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="AM10" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AN10" t="n">
         <v>391</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.62</v>
+        <v>-0.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>-5</v>
+        <v>-4.4</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 37.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.6%.</t>
+          <t>TSLA: scenario base High Risk, score 37.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.0%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4442127073280</v>
+        <v>4346030850048</v>
       </c>
       <c r="G2" t="n">
-        <v>27.76</v>
+        <v>27.18</v>
       </c>
       <c r="H2" t="n">
-        <v>25.18</v>
+        <v>24.64</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>61.4</v>
       </c>
       <c r="Q2" t="n">
         <v>40.5</v>
       </c>
       <c r="R2" t="n">
-        <v>82.8</v>
+        <v>78.5</v>
       </c>
       <c r="S2" t="n">
-        <v>80.2</v>
+        <v>79</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,45 +773,45 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>364.26</v>
+        <v>356.38</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.06</v>
+        <v>-8.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.71</v>
+        <v>15.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.6</v>
+        <v>13.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.58</v>
+        <v>102.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.13</v>
+        <v>43.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.72</v>
+        <v>29.73</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>357.7434</v>
+        <v>359.4043</v>
       </c>
       <c r="AG2" t="n">
-        <v>305.2947</v>
+        <v>306.049</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>100</v>
@@ -820,13 +820,13 @@
         <v>40.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>82.8</v>
+        <v>78.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
-        <v>358.7757</v>
+        <v>356.38</v>
       </c>
       <c r="AO2" t="n">
         <v>273.3367</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.82</v>
+        <v>-0.84</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.31</v>
+        <v>16.45</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>77.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.8%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 79.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5042570002432</v>
+        <v>4282539048960</v>
       </c>
       <c r="G3" t="n">
-        <v>31.88</v>
+        <v>35.34</v>
       </c>
       <c r="H3" t="n">
-        <v>16.42</v>
+        <v>30.39</v>
       </c>
       <c r="I3" t="n">
-        <v>62.97</v>
+        <v>27.15</v>
       </c>
       <c r="J3" t="n">
-        <v>114.29</v>
+        <v>141.47</v>
       </c>
       <c r="K3" t="n">
-        <v>85.2</v>
+        <v>16.6</v>
       </c>
       <c r="L3" t="n">
-        <v>6.55</v>
+        <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>88.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>67.7</v>
+        <v>43.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.1</v>
+        <v>42.2</v>
       </c>
       <c r="R3" t="n">
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>74.2</v>
+        <v>72.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,42 +967,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>208.19</v>
+        <v>291.58</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.14</v>
+        <v>-0.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.81</v>
+        <v>11.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.27</v>
+        <v>5.12</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.11</v>
+        <v>45.31</v>
       </c>
       <c r="AB3" t="n">
-        <v>74.81</v>
+        <v>17.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>46.97</v>
+        <v>25.97</v>
       </c>
       <c r="AD3" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.59</v>
+        <v>0.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>204.7893</v>
+        <v>283.8059</v>
       </c>
       <c r="AG3" t="n">
-        <v>188.6792</v>
+        <v>265.7985</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,34 +1013,34 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>88.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.1</v>
+        <v>42.2</v>
       </c>
       <c r="AL3" t="n">
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
-        <v>205.1</v>
+        <v>290.55</v>
       </c>
       <c r="AO3" t="n">
-        <v>164.9777</v>
+        <v>246.403</v>
       </c>
       <c r="AP3" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.66</v>
+        <v>2.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.34</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>57.5</v>
+        <v>72</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.7%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4267410980864</v>
+        <v>4854372630528</v>
       </c>
       <c r="G4" t="n">
-        <v>35.18</v>
+        <v>30.65</v>
       </c>
       <c r="H4" t="n">
-        <v>30.23</v>
+        <v>15.75</v>
       </c>
       <c r="I4" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="J4" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="K4" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L4" t="n">
-        <v>79.55</v>
+        <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>79.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>44.1</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>42.1</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>76</v>
       </c>
       <c r="S4" t="n">
-        <v>72.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,80 +1166,80 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>290.55</v>
+        <v>200.42</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.85</v>
+        <v>-8.56</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>7.86</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.42</v>
+        <v>8.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>43.05</v>
+        <v>40.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.16</v>
+        <v>72.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>25.98</v>
+        <v>47</v>
       </c>
       <c r="AD4" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.66</v>
+        <v>1.54</v>
       </c>
       <c r="AF4" t="n">
-        <v>282.9024</v>
+        <v>205.4982</v>
       </c>
       <c r="AG4" t="n">
-        <v>265.4762</v>
+        <v>188.7925</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>79.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>42.1</v>
+        <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>76</v>
       </c>
       <c r="AM4" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>290.55</v>
+        <v>200.42</v>
       </c>
       <c r="AO4" t="n">
-        <v>246.403</v>
+        <v>164.9777</v>
       </c>
       <c r="AP4" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AQ4" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.7</v>
+        <v>-2.47</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.44</v>
+        <v>6.16</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>71.59999999999999</v>
+        <v>52</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.7%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 69.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2626778562560</v>
+        <v>2560192151552</v>
       </c>
       <c r="G5" t="n">
-        <v>31.51</v>
+        <v>30.83</v>
       </c>
       <c r="H5" t="n">
-        <v>24.77</v>
+        <v>24.14</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>76.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="P5" t="n">
-        <v>56.2</v>
+        <v>57.9</v>
       </c>
       <c r="Q5" t="n">
         <v>38.1</v>
       </c>
       <c r="R5" t="n">
-        <v>74.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>66.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>244.19</v>
+        <v>238</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.45</v>
+        <v>-11.52</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.93</v>
+        <v>11.92</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.39</v>
+        <v>4.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.34</v>
+        <v>9.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.67</v>
+        <v>23.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.96</v>
+        <v>30.98</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="AF5" t="n">
-        <v>252.8082</v>
+        <v>253.5492</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.3466</v>
+        <v>232.3924</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,19 +1409,19 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>76.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="AK5" t="n">
         <v>38.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>74.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>244.19</v>
+        <v>238</v>
       </c>
       <c r="AO5" t="n">
         <v>199.34</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.41</v>
+        <v>-6.13</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>2.41</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 6.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>65.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 64.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1510,50 +1510,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2996704903168</v>
+        <v>580901470208</v>
       </c>
       <c r="G6" t="n">
-        <v>24.01</v>
+        <v>58.44</v>
       </c>
       <c r="H6" t="n">
-        <v>20.86</v>
+        <v>36.33</v>
       </c>
       <c r="I6" t="n">
-        <v>39.34</v>
+        <v>29.71</v>
       </c>
       <c r="J6" t="n">
-        <v>34.01</v>
+        <v>52.24</v>
       </c>
       <c r="K6" t="n">
-        <v>18.3</v>
+        <v>13.2</v>
       </c>
       <c r="L6" t="n">
-        <v>30.27</v>
+        <v>12.99</v>
       </c>
       <c r="M6" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>36.4</v>
+        <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>70.5</v>
+        <v>12.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>44.1</v>
+        <v>18.4</v>
       </c>
       <c r="R6" t="n">
-        <v>73</v>
+        <v>31.5</v>
       </c>
       <c r="S6" t="n">
-        <v>63.3</v>
+        <v>62.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,98 +1562,98 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>403.41</v>
+        <v>1508.4</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.61</v>
+        <v>15.53</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.36</v>
+        <v>31.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>-16.13</v>
+        <v>59.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>-13.55</v>
+        <v>124.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.61</v>
+        <v>31.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.99</v>
+        <v>38.13</v>
       </c>
       <c r="AD6" t="n">
-        <v>-33.91</v>
+        <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.32</v>
+        <v>0.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>409.5508</v>
+        <v>1291.2961</v>
       </c>
       <c r="AG6" t="n">
-        <v>453.5009</v>
+        <v>1052.217</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.4</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>44.1</v>
+        <v>18.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>73</v>
+        <v>31.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="AN6" t="n">
-        <v>403.41</v>
+        <v>1249</v>
       </c>
       <c r="AO6" t="n">
-        <v>355.9989</v>
+        <v>1109.5466</v>
       </c>
       <c r="AP6" t="n">
-        <v>460.52</v>
+        <v>1514.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>460.52</v>
+        <v>1514.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.5</v>
+        <v>16.81</v>
       </c>
       <c r="AS6" t="n">
-        <v>-11.05</v>
+        <v>43.35</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 16.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>58.8</v>
+        <v>24.2</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.8%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1514.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1709,47 +1709,47 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>581364023296</v>
+        <v>2951762673664</v>
       </c>
       <c r="G7" t="n">
-        <v>58.24</v>
+        <v>23.68</v>
       </c>
       <c r="H7" t="n">
-        <v>36.38</v>
+        <v>20.49</v>
       </c>
       <c r="I7" t="n">
-        <v>29.71</v>
+        <v>39.34</v>
       </c>
       <c r="J7" t="n">
-        <v>52.24</v>
+        <v>34.01</v>
       </c>
       <c r="K7" t="n">
-        <v>13.2</v>
+        <v>18.3</v>
       </c>
       <c r="L7" t="n">
-        <v>12.99</v>
+        <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>32.6</v>
       </c>
       <c r="P7" t="n">
-        <v>12.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.4</v>
+        <v>44.1</v>
       </c>
       <c r="R7" t="n">
-        <v>27.1</v>
+        <v>70.5</v>
       </c>
       <c r="S7" t="n">
         <v>62.3</v>
@@ -1761,98 +1761,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1514.6</v>
+        <v>397.36</v>
       </c>
       <c r="X7" t="n">
-        <v>14.79</v>
+        <v>-3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>32.34</v>
+        <v>-1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>58.78</v>
+        <v>-18.71</v>
       </c>
       <c r="AA7" t="n">
-        <v>121.2</v>
+        <v>-15.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.22</v>
+        <v>7.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.13</v>
+        <v>23.99</v>
       </c>
       <c r="AD7" t="n">
-        <v>-44.77</v>
+        <v>-33.91</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.85</v>
+        <v>0.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>1284.3927</v>
+        <v>410.3343</v>
       </c>
       <c r="AG7" t="n">
-        <v>1047.8913</v>
+        <v>452.9675</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>100</v>
+        <v>32.6</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.4</v>
+        <v>44.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>27.1</v>
+        <v>70.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
-        <v>1249</v>
+        <v>397.36</v>
       </c>
       <c r="AO7" t="n">
-        <v>1109.5466</v>
+        <v>355.9989</v>
       </c>
       <c r="AP7" t="n">
-        <v>1514.6</v>
+        <v>460.52</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1514.6</v>
+        <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>17.92</v>
+        <v>-3.16</v>
       </c>
       <c r="AS7" t="n">
-        <v>44.54</v>
+        <v>-12.28</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 17.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>20.9</v>
+        <v>57.2</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.9%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1514.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1483936890880</v>
+        <v>1449388933120</v>
       </c>
       <c r="G8" t="n">
-        <v>21.25</v>
+        <v>20.78</v>
       </c>
       <c r="H8" t="n">
-        <v>16.17</v>
+        <v>15.79</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>23.4</v>
+        <v>19.3</v>
       </c>
       <c r="P8" t="n">
-        <v>80.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="Q8" t="n">
         <v>29.1</v>
       </c>
       <c r="R8" t="n">
-        <v>66.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="S8" t="n">
-        <v>58.7</v>
+        <v>57.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>584.59</v>
+        <v>570.98</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.11</v>
+        <v>-4.66</v>
       </c>
       <c r="Y8" t="n">
-        <v>-10.55</v>
+        <v>-12.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.05</v>
+        <v>-14.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>-15.95</v>
+        <v>-17.48</v>
       </c>
       <c r="AB8" t="n">
-        <v>29.76</v>
+        <v>28.7</v>
       </c>
       <c r="AC8" t="n">
         <v>36.28</v>
@@ -1989,13 +1989,13 @@
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>621.4548</v>
+        <v>622.1468</v>
       </c>
       <c r="AG8" t="n">
-        <v>660.1814000000001</v>
+        <v>659.2712</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,19 +2006,19 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23.4</v>
+        <v>19.3</v>
       </c>
       <c r="AK8" t="n">
         <v>29.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>66.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
-        <v>584.59</v>
+        <v>570.98</v>
       </c>
       <c r="AO8" t="n">
         <v>525.72</v>
@@ -2030,10 +2030,10 @@
         <v>688.55</v>
       </c>
       <c r="AR8" t="n">
-        <v>-5.93</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>-11.45</v>
+        <v>-13.39</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 5.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>38.9</v>
+        <v>36.9</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 58.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.9%.</t>
+          <t>META: scenario base Hold / Monitor, score 57.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.2%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1489820450816</v>
+        <v>1433146621952</v>
       </c>
       <c r="G10" t="n">
-        <v>360.62</v>
+        <v>356.63</v>
       </c>
       <c r="H10" t="n">
-        <v>157.88</v>
+        <v>152.64</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>75.2</v>
+        <v>69.3</v>
       </c>
       <c r="S10" t="n">
-        <v>37.9</v>
+        <v>34.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>396.68</v>
+        <v>381.59</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.39</v>
+        <v>-14.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.64</v>
+        <v>-6.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>-12.82</v>
+        <v>-13.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>34.4</v>
+        <v>23.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.78</v>
+        <v>15.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>57.97</v>
+        <v>57.98</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>396.7224</v>
+        <v>397.2486</v>
       </c>
       <c r="AG10" t="n">
-        <v>414.95</v>
+        <v>415.1579</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,19 +2350,19 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>75.2</v>
+        <v>69.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN10" t="n">
-        <v>391</v>
+        <v>381.59</v>
       </c>
       <c r="AO10" t="n">
         <v>343.25</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.01</v>
+        <v>-3.94</v>
       </c>
       <c r="AS10" t="n">
-        <v>-4.4</v>
+        <v>-8.09</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>31.4</v>
+        <v>26.7</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 37.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.0%.</t>
+          <t>TSLA: scenario base High Risk, score 34.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.9%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4346030850048</v>
+        <v>4362981605376</v>
       </c>
       <c r="G2" t="n">
-        <v>27.18</v>
+        <v>27.29</v>
       </c>
       <c r="H2" t="n">
-        <v>24.64</v>
+        <v>24.71</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -741,7 +741,7 @@
         <v>20.03</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,7 +750,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>61.4</v>
+        <v>61.2</v>
       </c>
       <c r="Q2" t="n">
         <v>40.5</v>
@@ -773,25 +773,25 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>356.38</v>
+        <v>357.77</v>
       </c>
       <c r="X2" t="n">
-        <v>-8.25</v>
+        <v>-7.58</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.51</v>
+        <v>17.93</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.75</v>
+        <v>12.98</v>
       </c>
       <c r="AA2" t="n">
-        <v>102.96</v>
+        <v>100.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.01</v>
+        <v>43.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.73</v>
+        <v>29.71</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
@@ -800,10 +800,10 @@
         <v>1.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>359.4043</v>
+        <v>360.8119</v>
       </c>
       <c r="AG2" t="n">
-        <v>306.049</v>
+        <v>306.7984</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>78.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
         <v>356.38</v>
@@ -832,7 +832,7 @@
         <v>273.3367</v>
       </c>
       <c r="AP2" t="n">
-        <v>402.3797</v>
+        <v>400.8306</v>
       </c>
       <c r="AQ2" t="n">
         <v>402.3797</v>
@@ -841,7 +841,7 @@
         <v>-0.84</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.45</v>
+        <v>16.61</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4282539048960</v>
+        <v>4342023192576</v>
       </c>
       <c r="G3" t="n">
-        <v>35.34</v>
+        <v>35.83</v>
       </c>
       <c r="H3" t="n">
-        <v>30.39</v>
+        <v>30.81</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -946,10 +946,10 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>81.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="P3" t="n">
-        <v>43.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q3" t="n">
         <v>42.2</v>
@@ -958,7 +958,7 @@
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>72.8</v>
+        <v>74.3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>291.58</v>
+        <v>295.63</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.38</v>
+        <v>0.28</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.9</v>
+        <v>15.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.12</v>
+        <v>6.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>45.31</v>
+        <v>46.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.27</v>
+        <v>17.79</v>
       </c>
       <c r="AC3" t="n">
-        <v>25.97</v>
+        <v>25.96</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>283.8059</v>
+        <v>284.6474</v>
       </c>
       <c r="AG3" t="n">
-        <v>265.7985</v>
+        <v>266.1441</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>81.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="AK3" t="n">
         <v>42.2</v>
@@ -1022,7 +1022,7 @@
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
         <v>290.55</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.74</v>
+        <v>3.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.699999999999999</v>
+        <v>11.08</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>72</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.7%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4854372630528</v>
+        <v>4962156281856</v>
       </c>
       <c r="G4" t="n">
-        <v>30.65</v>
+        <v>31.37</v>
       </c>
       <c r="H4" t="n">
-        <v>15.75</v>
+        <v>16.1</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>76.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="P4" t="n">
-        <v>70.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="Q4" t="n">
         <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>76</v>
+        <v>78.8</v>
       </c>
       <c r="S4" t="n">
-        <v>69.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>200.42</v>
+        <v>204.87</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.56</v>
+        <v>-7.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.86</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.15</v>
+        <v>10.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>40.71</v>
+        <v>42.51</v>
       </c>
       <c r="AB4" t="n">
-        <v>72.47</v>
+        <v>73.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>47</v>
+        <v>46.98</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>205.4982</v>
+        <v>206.1116</v>
       </c>
       <c r="AG4" t="n">
-        <v>188.7925</v>
+        <v>188.919</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,16 +1212,16 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>76.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="AK4" t="n">
         <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>76</v>
+        <v>78.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN4" t="n">
         <v>200.42</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2.47</v>
+        <v>-0.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.16</v>
+        <v>8.44</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 69.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.6%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2560192151552</v>
+        <v>2597949538304</v>
       </c>
       <c r="G5" t="n">
-        <v>30.83</v>
+        <v>32.12</v>
       </c>
       <c r="H5" t="n">
-        <v>24.14</v>
+        <v>24.49</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>72</v>
+        <v>77.7</v>
       </c>
       <c r="P5" t="n">
-        <v>57.9</v>
+        <v>55.9</v>
       </c>
       <c r="Q5" t="n">
         <v>38.1</v>
       </c>
       <c r="R5" t="n">
-        <v>70.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="S5" t="n">
-        <v>64.8</v>
+        <v>66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>238</v>
+        <v>241.51</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.52</v>
+        <v>-9.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.92</v>
+        <v>15.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.9</v>
+        <v>5.96</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.69</v>
+        <v>10.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.57</v>
+        <v>24.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.98</v>
+        <v>30.97</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>253.5492</v>
+        <v>254.214</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.3924</v>
+        <v>232.4602</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,16 +1409,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>72</v>
+        <v>77.7</v>
       </c>
       <c r="AK5" t="n">
         <v>38.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>70.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
         <v>238</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-6.13</v>
+        <v>-5</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.41</v>
+        <v>3.89</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 6.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>63.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 64.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.1%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>580901470208</v>
+        <v>607418253312</v>
       </c>
       <c r="G6" t="n">
-        <v>58.44</v>
+        <v>60.8</v>
       </c>
       <c r="H6" t="n">
-        <v>36.33</v>
+        <v>37.99</v>
       </c>
       <c r="I6" t="n">
         <v>29.71</v>
@@ -1544,16 +1544,16 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>12.4</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="R6" t="n">
-        <v>31.5</v>
+        <v>34.5</v>
       </c>
       <c r="S6" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,25 +1567,25 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1508.4</v>
+        <v>1507.2</v>
       </c>
       <c r="X6" t="n">
-        <v>15.53</v>
+        <v>19.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>31.73</v>
+        <v>25.88</v>
       </c>
       <c r="Z6" t="n">
-        <v>59.08</v>
+        <v>57.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>124.72</v>
+        <v>128.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>31.72</v>
+        <v>31.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>38.13</v>
+        <v>38.1</v>
       </c>
       <c r="AD6" t="n">
         <v>-44.77</v>
@@ -1594,10 +1594,10 @@
         <v>0.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>1291.2961</v>
+        <v>1298.5627</v>
       </c>
       <c r="AG6" t="n">
-        <v>1052.217</v>
+        <v>1056.5172</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>31.5</v>
+        <v>34.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AN6" t="n">
         <v>1249</v>
@@ -1632,10 +1632,10 @@
         <v>1514.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.81</v>
+        <v>16.07</v>
       </c>
       <c r="AS6" t="n">
-        <v>43.35</v>
+        <v>42.66</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1649,11 +1649,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 16.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 16.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>24.2</v>
+        <v>26.2</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.8%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.1%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2951762673664</v>
+        <v>2899615154176</v>
       </c>
       <c r="G7" t="n">
-        <v>23.68</v>
+        <v>23.22</v>
       </c>
       <c r="H7" t="n">
-        <v>20.49</v>
+        <v>20.18</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1734,25 +1734,25 @@
         <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>32.6</v>
+        <v>30</v>
       </c>
       <c r="P7" t="n">
-        <v>71.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>44.1</v>
       </c>
       <c r="R7" t="n">
-        <v>70.5</v>
+        <v>67.8</v>
       </c>
       <c r="S7" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,22 +1766,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>397.36</v>
+        <v>390.34</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.5</v>
+        <v>-4.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.64</v>
+        <v>-2.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>-18.71</v>
+        <v>-20.31</v>
       </c>
       <c r="AA7" t="n">
-        <v>-15.28</v>
+        <v>-16.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.06</v>
+        <v>6.41</v>
       </c>
       <c r="AC7" t="n">
         <v>23.99</v>
@@ -1790,13 +1790,13 @@
         <v>-33.91</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AF7" t="n">
-        <v>410.3343</v>
+        <v>410.7537</v>
       </c>
       <c r="AG7" t="n">
-        <v>452.9675</v>
+        <v>452.4137</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,19 +1807,19 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32.6</v>
+        <v>30</v>
       </c>
       <c r="AK7" t="n">
         <v>44.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>70.5</v>
+        <v>67.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
-        <v>397.36</v>
+        <v>390.34</v>
       </c>
       <c r="AO7" t="n">
         <v>355.9989</v>
@@ -1831,10 +1831,10 @@
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-3.16</v>
+        <v>-4.97</v>
       </c>
       <c r="AS7" t="n">
-        <v>-12.28</v>
+        <v>-13.72</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>57.2</v>
+        <v>55.8</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.2%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1449388933120</v>
+        <v>1442915942400</v>
       </c>
       <c r="G8" t="n">
-        <v>20.78</v>
+        <v>20.66</v>
       </c>
       <c r="H8" t="n">
-        <v>15.79</v>
+        <v>15.72</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1933,25 +1933,25 @@
         <v>35.61</v>
       </c>
       <c r="M8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>19.3</v>
+        <v>22.1</v>
       </c>
       <c r="P8" t="n">
-        <v>81.5</v>
+        <v>81.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="R8" t="n">
-        <v>62.9</v>
+        <v>62.3</v>
       </c>
       <c r="S8" t="n">
-        <v>57.5</v>
+        <v>58.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>570.98</v>
+        <v>568.4299999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.66</v>
+        <v>-5.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>-12.73</v>
+        <v>-10.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>-14.23</v>
+        <v>-13.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>-17.48</v>
+        <v>-18.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>28.7</v>
+        <v>28.46</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.28</v>
+        <v>36.26</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>622.1468</v>
+        <v>622.0728</v>
       </c>
       <c r="AG8" t="n">
-        <v>659.2712</v>
+        <v>658.3557</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,19 +2006,19 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19.3</v>
+        <v>22.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>62.9</v>
+        <v>62.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
-        <v>570.98</v>
+        <v>568.4299999999999</v>
       </c>
       <c r="AO8" t="n">
         <v>525.72</v>
@@ -2030,10 +2030,10 @@
         <v>688.55</v>
       </c>
       <c r="AR8" t="n">
-        <v>-8.220000000000001</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>-13.39</v>
+        <v>-13.66</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 8.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>36.9</v>
+        <v>37.5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 57.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 58.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2100,124 +2100,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>1499097071616</v>
+      </c>
+      <c r="G9" t="n">
+        <v>359.59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>159.54</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>50</v>
-      </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>399.15</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-7.91</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>397.7966</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>415.4206</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="AK9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>100</v>
-      </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>78.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+        <v>753</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>443.3</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-3.92</v>
+      </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>32.3</v>
+        <v>32.9</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 39.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2227,19 +2277,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2247,174 +2297,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1433146621952</v>
-      </c>
-      <c r="G10" t="n">
-        <v>356.63</v>
-      </c>
-      <c r="H10" t="n">
-        <v>152.64</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>381.59</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-14.25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-6.43</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-13.19</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>57.98</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>397.2486</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>415.1579</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>35</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL10" t="n">
         <v>0</v>
       </c>
-      <c r="AL10" t="n">
-        <v>69.3</v>
-      </c>
       <c r="AM10" t="n">
-        <v>752</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>381.59</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>343.25</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-3.94</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-8.09</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>26.7</v>
+        <v>32.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 34.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.9%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4362981605376</v>
+        <v>4386274148352</v>
       </c>
       <c r="G2" t="n">
-        <v>27.29</v>
+        <v>27.48</v>
       </c>
       <c r="H2" t="n">
-        <v>24.71</v>
+        <v>24.84</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>61.2</v>
+        <v>60.8</v>
       </c>
       <c r="Q2" t="n">
         <v>40.5</v>
       </c>
       <c r="R2" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="S2" t="n">
         <v>79</v>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>357.77</v>
+        <v>359.68</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.58</v>
+        <v>-10.61</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.93</v>
+        <v>19.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.98</v>
+        <v>12.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>100.89</v>
+        <v>103.39</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.12</v>
+        <v>43.31</v>
       </c>
       <c r="AC2" t="n">
         <v>29.71</v>
@@ -797,13 +797,13 @@
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AF2" t="n">
-        <v>360.8119</v>
+        <v>362.0613</v>
       </c>
       <c r="AG2" t="n">
-        <v>306.7984</v>
+        <v>307.5641</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>40.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="AM2" t="n">
         <v>753</v>
@@ -832,16 +832,16 @@
         <v>273.3367</v>
       </c>
       <c r="AP2" t="n">
-        <v>400.8306</v>
+        <v>396.7031</v>
       </c>
       <c r="AQ2" t="n">
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.84</v>
+        <v>-0.66</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.61</v>
+        <v>16.94</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>76.2</v>
+        <v>76.3</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 79.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 79.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4342023192576</v>
+        <v>4275929874432</v>
       </c>
       <c r="G3" t="n">
-        <v>35.83</v>
+        <v>35.29</v>
       </c>
       <c r="H3" t="n">
-        <v>30.81</v>
+        <v>30.34</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>42.6</v>
+        <v>43.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="R3" t="n">
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>74.3</v>
+        <v>74.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>295.63</v>
+        <v>291.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0.28</v>
+        <v>-2.59</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.7</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.85</v>
+        <v>4.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.45</v>
+        <v>47.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.79</v>
+        <v>17.29</v>
       </c>
       <c r="AC3" t="n">
-        <v>25.96</v>
+        <v>25.97</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>284.6474</v>
+        <v>285.3621</v>
       </c>
       <c r="AG3" t="n">
-        <v>266.1441</v>
+        <v>266.4564</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="AL3" t="n">
         <v>82.8</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.86</v>
+        <v>2.02</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.08</v>
+        <v>9.26</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4962156281856</v>
+        <v>4969906831360</v>
       </c>
       <c r="G4" t="n">
         <v>31.37</v>
       </c>
       <c r="H4" t="n">
-        <v>16.1</v>
+        <v>16.12</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>84</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="S4" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>204.87</v>
+        <v>205.19</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.1</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>13.97</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.89</v>
+        <v>11.79</v>
       </c>
       <c r="AA4" t="n">
-        <v>42.51</v>
+        <v>43.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>73.62</v>
+        <v>71.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.98</v>
+        <v>46.93</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AF4" t="n">
-        <v>206.1116</v>
+        <v>206.7045</v>
       </c>
       <c r="AG4" t="n">
-        <v>188.919</v>
+        <v>189.0373</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,13 +1212,13 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>84</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="AM4" t="n">
         <v>753</v>
@@ -1230,16 +1230,16 @@
         <v>164.9777</v>
       </c>
       <c r="AP4" t="n">
-        <v>235.4656</v>
+        <v>225.0577</v>
       </c>
       <c r="AQ4" t="n">
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.6</v>
+        <v>-0.73</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.44</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>54.8</v>
+        <v>55.7</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 72.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2597949538304</v>
+        <v>2566108479488</v>
       </c>
       <c r="G5" t="n">
-        <v>32.12</v>
+        <v>31.26</v>
       </c>
       <c r="H5" t="n">
-        <v>24.49</v>
+        <v>24.19</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>77.7</v>
+        <v>75.5</v>
       </c>
       <c r="P5" t="n">
-        <v>55.9</v>
+        <v>57.3</v>
       </c>
       <c r="Q5" t="n">
         <v>38.1</v>
       </c>
       <c r="R5" t="n">
-        <v>72.3</v>
+        <v>70.2</v>
       </c>
       <c r="S5" t="n">
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>241.51</v>
+        <v>238.55</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.15</v>
+        <v>-11.69</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.26</v>
+        <v>14.87</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.96</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.98</v>
+        <v>11.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.14</v>
+        <v>23.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.97</v>
+        <v>30.98</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="AF5" t="n">
-        <v>254.214</v>
+        <v>254.7736</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.4602</v>
+        <v>232.5094</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>77.7</v>
+        <v>75.5</v>
       </c>
       <c r="AK5" t="n">
         <v>38.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>72.3</v>
+        <v>70.2</v>
       </c>
       <c r="AM5" t="n">
         <v>753</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-5</v>
+        <v>-6.37</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.89</v>
+        <v>2.6</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>65.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1510,50 +1510,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>607418253312</v>
+        <v>2902586556416</v>
       </c>
       <c r="G6" t="n">
-        <v>60.8</v>
+        <v>23.29</v>
       </c>
       <c r="H6" t="n">
-        <v>37.99</v>
+        <v>20.2</v>
       </c>
       <c r="I6" t="n">
-        <v>29.71</v>
+        <v>39.34</v>
       </c>
       <c r="J6" t="n">
-        <v>52.24</v>
+        <v>34.01</v>
       </c>
       <c r="K6" t="n">
-        <v>13.2</v>
+        <v>18.3</v>
       </c>
       <c r="L6" t="n">
-        <v>12.99</v>
+        <v>30.27</v>
       </c>
       <c r="M6" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>33.6</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>72.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.5</v>
+        <v>44.1</v>
       </c>
       <c r="R6" t="n">
-        <v>34.5</v>
+        <v>67.8</v>
       </c>
       <c r="S6" t="n">
-        <v>62.6</v>
+        <v>62.4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,98 +1562,98 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1507.2</v>
+        <v>390.74</v>
       </c>
       <c r="X6" t="n">
-        <v>19.07</v>
+        <v>-3.36</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.88</v>
+        <v>-1</v>
       </c>
       <c r="Z6" t="n">
-        <v>57.03</v>
+        <v>-17.99</v>
       </c>
       <c r="AA6" t="n">
-        <v>128.6</v>
+        <v>-16.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>31.64</v>
+        <v>6.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>38.1</v>
+        <v>23.99</v>
       </c>
       <c r="AD6" t="n">
-        <v>-44.77</v>
+        <v>-33.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.83</v>
+        <v>0.26</v>
       </c>
       <c r="AF6" t="n">
-        <v>1298.5627</v>
+        <v>411.1971</v>
       </c>
       <c r="AG6" t="n">
-        <v>1056.5172</v>
+        <v>451.873</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>100</v>
+        <v>33.6</v>
       </c>
       <c r="AK6" t="n">
-        <v>18.5</v>
+        <v>44.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>34.5</v>
+        <v>67.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="AN6" t="n">
-        <v>1249</v>
+        <v>390.34</v>
       </c>
       <c r="AO6" t="n">
-        <v>1109.5466</v>
+        <v>355.9989</v>
       </c>
       <c r="AP6" t="n">
-        <v>1514.6</v>
+        <v>460.52</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1514.6</v>
+        <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.07</v>
+        <v>-4.98</v>
       </c>
       <c r="AS6" t="n">
-        <v>42.66</v>
+        <v>-13.53</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 16.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>26.2</v>
+        <v>56.7</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.1%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1514.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1709,50 +1709,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2899615154176</v>
+        <v>628076642304</v>
       </c>
       <c r="G7" t="n">
-        <v>23.22</v>
+        <v>63.04</v>
       </c>
       <c r="H7" t="n">
-        <v>20.18</v>
+        <v>39.28</v>
       </c>
       <c r="I7" t="n">
-        <v>39.34</v>
+        <v>29.71</v>
       </c>
       <c r="J7" t="n">
-        <v>34.01</v>
+        <v>52.24</v>
       </c>
       <c r="K7" t="n">
-        <v>18.3</v>
+        <v>13.2</v>
       </c>
       <c r="L7" t="n">
-        <v>30.27</v>
+        <v>12.99</v>
       </c>
       <c r="M7" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>72.40000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>44.1</v>
+        <v>18.4</v>
       </c>
       <c r="R7" t="n">
-        <v>67.8</v>
+        <v>16.8</v>
       </c>
       <c r="S7" t="n">
-        <v>61.6</v>
+        <v>60.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,98 +1761,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>390.34</v>
+        <v>1576</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.07</v>
+        <v>18.76</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.66</v>
+        <v>31.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>-20.31</v>
+        <v>65.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>-16.45</v>
+        <v>137.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.41</v>
+        <v>33.54</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.99</v>
+        <v>38.16</v>
       </c>
       <c r="AD7" t="n">
-        <v>-33.91</v>
+        <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.27</v>
+        <v>0.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>410.7537</v>
+        <v>1307.8918</v>
       </c>
       <c r="AG7" t="n">
-        <v>452.4137</v>
+        <v>1061.1137</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>44.1</v>
+        <v>18.4</v>
       </c>
       <c r="AL7" t="n">
-        <v>67.8</v>
+        <v>16.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="AN7" t="n">
-        <v>390.34</v>
+        <v>1249</v>
       </c>
       <c r="AO7" t="n">
-        <v>355.9989</v>
+        <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>460.52</v>
+        <v>1576</v>
       </c>
       <c r="AQ7" t="n">
-        <v>460.52</v>
+        <v>1576</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.97</v>
+        <v>20.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>-13.72</v>
+        <v>48.52</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 20.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>55.8</v>
+        <v>12.9</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.5%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1576.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1442915942400</v>
+        <v>1439235178496</v>
       </c>
       <c r="G8" t="n">
-        <v>20.66</v>
+        <v>20.61</v>
       </c>
       <c r="H8" t="n">
-        <v>15.72</v>
+        <v>15.68</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>22.1</v>
+        <v>27.3</v>
       </c>
       <c r="P8" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>29.2</v>
       </c>
       <c r="R8" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="S8" t="n">
-        <v>58.2</v>
+        <v>59.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>568.4299999999999</v>
+        <v>566.98</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.73</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>-10.85</v>
+        <v>-7.54</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.33</v>
+        <v>-12.64</v>
       </c>
       <c r="AA8" t="n">
-        <v>-18.82</v>
+        <v>-18.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>28.46</v>
+        <v>28.31</v>
       </c>
       <c r="AC8" t="n">
         <v>36.26</v>
@@ -1992,10 +1992,10 @@
         <v>0.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>622.0728</v>
+        <v>621.8278</v>
       </c>
       <c r="AG8" t="n">
-        <v>658.3557</v>
+        <v>657.4289</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,19 +2006,19 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22.1</v>
+        <v>27.3</v>
       </c>
       <c r="AK8" t="n">
         <v>29.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="AM8" t="n">
         <v>753</v>
       </c>
       <c r="AN8" t="n">
-        <v>568.4299999999999</v>
+        <v>566.98</v>
       </c>
       <c r="AO8" t="n">
         <v>525.72</v>
@@ -2030,10 +2030,10 @@
         <v>688.55</v>
       </c>
       <c r="AR8" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.82</v>
       </c>
       <c r="AS8" t="n">
-        <v>-13.66</v>
+        <v>-13.76</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 8.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>37.5</v>
+        <v>38.8</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 58.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1499097071616</v>
+        <v>1526438821888</v>
       </c>
       <c r="G9" t="n">
-        <v>359.59</v>
+        <v>376.32</v>
       </c>
       <c r="H9" t="n">
-        <v>159.54</v>
+        <v>162.45</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>50.9</v>
+        <v>55.6</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>78.2</v>
       </c>
       <c r="S9" t="n">
-        <v>39.4</v>
+        <v>40.6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>399.15</v>
+        <v>406.43</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.91</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>3.89</v>
       </c>
       <c r="Z9" t="n">
-        <v>-10.34</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.4</v>
+        <v>24.51</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.98</v>
+        <v>16.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>57.99</v>
+        <v>57.97</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>397.7966</v>
+        <v>398.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>415.4206</v>
+        <v>415.6944</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>50.9</v>
+        <v>55.6</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -2221,16 +2221,16 @@
         <v>343.25</v>
       </c>
       <c r="AP9" t="n">
-        <v>443.3</v>
+        <v>442.1</v>
       </c>
       <c r="AQ9" t="n">
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.34</v>
+        <v>2.04</v>
       </c>
       <c r="AS9" t="n">
-        <v>-3.92</v>
+        <v>-2.23</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>32.9</v>
+        <v>34.2</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 39.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
+          <t>TSLA: scenario base High Risk, score 40.6, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4386274148352</v>
+        <v>4504199102464</v>
       </c>
       <c r="G2" t="n">
-        <v>27.48</v>
+        <v>28.22</v>
       </c>
       <c r="H2" t="n">
-        <v>24.84</v>
+        <v>25.51</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -741,7 +741,7 @@
         <v>20.03</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>60.8</v>
+        <v>59</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="R2" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,57 +773,57 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>359.68</v>
+        <v>369.35</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.61</v>
+        <v>-7.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.06</v>
+        <v>20.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.47</v>
+        <v>18.37</v>
       </c>
       <c r="AA2" t="n">
-        <v>103.39</v>
+        <v>110.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.31</v>
+        <v>44.84</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.71</v>
+        <v>29.77</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AF2" t="n">
-        <v>362.0613</v>
+        <v>363.5364</v>
       </c>
       <c r="AG2" t="n">
-        <v>307.5641</v>
+        <v>308.3764</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN2" t="n">
         <v>356.38</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.66</v>
+        <v>1.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.94</v>
+        <v>19.77</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 79.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4275929874432</v>
+        <v>5145751453696</v>
       </c>
       <c r="G3" t="n">
-        <v>35.29</v>
+        <v>31.43</v>
       </c>
       <c r="H3" t="n">
-        <v>30.34</v>
+        <v>16.69</v>
       </c>
       <c r="I3" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="J3" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="K3" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L3" t="n">
-        <v>79.55</v>
+        <v>6.55</v>
       </c>
       <c r="M3" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>87.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="P3" t="n">
-        <v>43.9</v>
+        <v>67.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.1</v>
+        <v>14.1</v>
       </c>
       <c r="R3" t="n">
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>74.5</v>
+        <v>75.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,42 +967,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>291.13</v>
+        <v>212.45</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.59</v>
+        <v>-9.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>16.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.62</v>
+        <v>17.56</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.04</v>
+        <v>46.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.29</v>
+        <v>71.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>25.97</v>
+        <v>46.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.67</v>
+        <v>1.52</v>
       </c>
       <c r="AF3" t="n">
-        <v>285.3621</v>
+        <v>207.4098</v>
       </c>
       <c r="AG3" t="n">
-        <v>266.4564</v>
+        <v>189.1928</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,34 +1013,34 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>87.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>42.1</v>
+        <v>14.1</v>
       </c>
       <c r="AL3" t="n">
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN3" t="n">
-        <v>290.55</v>
+        <v>200.42</v>
       </c>
       <c r="AO3" t="n">
-        <v>246.403</v>
+        <v>164.9777</v>
       </c>
       <c r="AP3" t="n">
-        <v>315.2</v>
+        <v>224.0988</v>
       </c>
       <c r="AQ3" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.26</v>
+        <v>12.29</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>73.7</v>
+        <v>59.1</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.0%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4969906831360</v>
+        <v>4353626210304</v>
       </c>
       <c r="G4" t="n">
-        <v>31.37</v>
+        <v>35.84</v>
       </c>
       <c r="H4" t="n">
-        <v>16.12</v>
+        <v>30.89</v>
       </c>
       <c r="I4" t="n">
-        <v>62.97</v>
+        <v>27.15</v>
       </c>
       <c r="J4" t="n">
-        <v>114.29</v>
+        <v>141.47</v>
       </c>
       <c r="K4" t="n">
-        <v>85.2</v>
+        <v>16.6</v>
       </c>
       <c r="L4" t="n">
-        <v>6.55</v>
+        <v>79.55</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>87.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="P4" t="n">
-        <v>68.7</v>
+        <v>42.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.2</v>
+        <v>42.1</v>
       </c>
       <c r="R4" t="n">
-        <v>78.7</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>72.8</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,80 +1166,80 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>205.19</v>
+        <v>296.42</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.029999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.97</v>
+        <v>17.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.79</v>
+        <v>6.81</v>
       </c>
       <c r="AA4" t="n">
-        <v>43.85</v>
+        <v>49.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>71.5</v>
+        <v>17.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.93</v>
+        <v>26.02</v>
       </c>
       <c r="AD4" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.52</v>
+        <v>0.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>206.7045</v>
+        <v>286.1768</v>
       </c>
       <c r="AG4" t="n">
-        <v>189.0373</v>
+        <v>266.7893</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>87.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.2</v>
+        <v>42.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>78.7</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN4" t="n">
-        <v>200.42</v>
+        <v>290.55</v>
       </c>
       <c r="AO4" t="n">
-        <v>164.9777</v>
+        <v>246.403</v>
       </c>
       <c r="AP4" t="n">
-        <v>225.0577</v>
+        <v>315.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.73</v>
+        <v>3.58</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.539999999999999</v>
+        <v>11.11</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>55.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 72.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2566108479488</v>
+        <v>2646464266240</v>
       </c>
       <c r="G5" t="n">
-        <v>31.26</v>
+        <v>32.63</v>
       </c>
       <c r="H5" t="n">
-        <v>24.19</v>
+        <v>24.95</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>75.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>57.3</v>
+        <v>54.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="R5" t="n">
-        <v>70.2</v>
+        <v>74.2</v>
       </c>
       <c r="S5" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>238.55</v>
+        <v>246.02</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.69</v>
+        <v>-7.93</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.87</v>
+        <v>16.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>6.84</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.89</v>
+        <v>15.37</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.6</v>
+        <v>25.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.98</v>
+        <v>31.05</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>254.7736</v>
+        <v>255.4986</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.5094</v>
+        <v>232.5939</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,16 +1409,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>75.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>70.2</v>
+        <v>74.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN5" t="n">
         <v>238</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-6.37</v>
+        <v>-3.71</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.6</v>
+        <v>5.77</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 6.4% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>64.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.7%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2902586556416</v>
+        <v>2969591349248</v>
       </c>
       <c r="G6" t="n">
-        <v>23.29</v>
+        <v>23.8</v>
       </c>
       <c r="H6" t="n">
-        <v>20.2</v>
+        <v>20.66</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1541,19 +1541,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>33.6</v>
+        <v>36.1</v>
       </c>
       <c r="P6" t="n">
-        <v>72.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>44.1</v>
       </c>
       <c r="R6" t="n">
-        <v>67.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>62.4</v>
+        <v>63.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,25 +1567,25 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>390.74</v>
+        <v>399.76</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.36</v>
+        <v>-2.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1</v>
+        <v>0.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>-17.99</v>
+        <v>-16.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>-16.66</v>
+        <v>-15.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.99</v>
+        <v>23.96</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.91</v>
@@ -1594,10 +1594,10 @@
         <v>0.26</v>
       </c>
       <c r="AF6" t="n">
-        <v>411.1971</v>
+        <v>411.7392</v>
       </c>
       <c r="AG6" t="n">
-        <v>451.873</v>
+        <v>451.3541</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,16 +1608,16 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>33.6</v>
+        <v>36.1</v>
       </c>
       <c r="AK6" t="n">
         <v>44.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>67.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN6" t="n">
         <v>390.34</v>
@@ -1632,10 +1632,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.98</v>
+        <v>-2.91</v>
       </c>
       <c r="AS6" t="n">
-        <v>-13.53</v>
+        <v>-11.43</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1649,11 +1649,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>56.7</v>
+        <v>58.2</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.0%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.9%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1689,12 +1689,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1704,55 +1704,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>628076642304</v>
+        <v>1506503426048</v>
       </c>
       <c r="G7" t="n">
-        <v>63.04</v>
+        <v>21.58</v>
       </c>
       <c r="H7" t="n">
-        <v>39.28</v>
+        <v>16.37</v>
       </c>
       <c r="I7" t="n">
-        <v>29.71</v>
+        <v>32.84</v>
       </c>
       <c r="J7" t="n">
-        <v>52.24</v>
+        <v>32.93</v>
       </c>
       <c r="K7" t="n">
-        <v>13.2</v>
+        <v>33.1</v>
       </c>
       <c r="L7" t="n">
-        <v>12.99</v>
+        <v>35.61</v>
       </c>
       <c r="M7" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>33.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8.199999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.4</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>16.8</v>
+        <v>68.3</v>
       </c>
       <c r="S7" t="n">
-        <v>60.5</v>
+        <v>61.2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,79 +1766,79 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1576</v>
+        <v>593.48</v>
       </c>
       <c r="X7" t="n">
-        <v>18.76</v>
+        <v>-4.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>31.76</v>
+        <v>-5.41</v>
       </c>
       <c r="Z7" t="n">
-        <v>65.98</v>
+        <v>-8.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>137.07</v>
+        <v>-14.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>33.54</v>
+        <v>28.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.16</v>
+        <v>36.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>-44.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="AF7" t="n">
-        <v>1307.8918</v>
+        <v>622.2082</v>
       </c>
       <c r="AG7" t="n">
-        <v>1061.1137</v>
+        <v>656.6682</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>100</v>
+        <v>33.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.4</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>16.8</v>
+        <v>68.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>766</v>
+        <v>751</v>
       </c>
       <c r="AN7" t="n">
-        <v>1249</v>
+        <v>566.98</v>
       </c>
       <c r="AO7" t="n">
-        <v>1109.5466</v>
+        <v>525.72</v>
       </c>
       <c r="AP7" t="n">
-        <v>1576</v>
+        <v>635.29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1576</v>
+        <v>688.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>20.5</v>
+        <v>-4.62</v>
       </c>
       <c r="AS7" t="n">
-        <v>48.52</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 20.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>12.9</v>
+        <v>42</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 61.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1576.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1439235178496</v>
+        <v>625224515584</v>
       </c>
       <c r="G8" t="n">
-        <v>20.61</v>
+        <v>62.61</v>
       </c>
       <c r="H8" t="n">
-        <v>15.68</v>
+        <v>39.1</v>
       </c>
       <c r="I8" t="n">
-        <v>32.84</v>
+        <v>29.71</v>
       </c>
       <c r="J8" t="n">
-        <v>32.93</v>
+        <v>52.24</v>
       </c>
       <c r="K8" t="n">
-        <v>33.1</v>
+        <v>13.2</v>
       </c>
       <c r="L8" t="n">
-        <v>35.61</v>
+        <v>12.99</v>
       </c>
       <c r="M8" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>27.3</v>
+        <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>81.90000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.2</v>
+        <v>18.3</v>
       </c>
       <c r="R8" t="n">
-        <v>62</v>
+        <v>4.2</v>
       </c>
       <c r="S8" t="n">
-        <v>59.5</v>
+        <v>59.3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,79 +1965,79 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>566.98</v>
+        <v>1629.6</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.050000000000001</v>
+        <v>19.21</v>
       </c>
       <c r="Y8" t="n">
-        <v>-7.54</v>
+        <v>38.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>-12.64</v>
+        <v>72.87</v>
       </c>
       <c r="AA8" t="n">
-        <v>-18.06</v>
+        <v>146.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>28.31</v>
+        <v>34.97</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.26</v>
+        <v>38.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>-34.15</v>
+        <v>-44.77</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AF8" t="n">
-        <v>621.8278</v>
+        <v>1318.1492</v>
       </c>
       <c r="AG8" t="n">
-        <v>657.4289</v>
+        <v>1066.0075</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27.3</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>29.2</v>
+        <v>18.3</v>
       </c>
       <c r="AL8" t="n">
-        <v>62</v>
+        <v>4.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="AN8" t="n">
-        <v>566.98</v>
+        <v>1249</v>
       </c>
       <c r="AO8" t="n">
-        <v>525.72</v>
+        <v>1109.5466</v>
       </c>
       <c r="AP8" t="n">
-        <v>635.29</v>
+        <v>1629.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>688.55</v>
+        <v>1629.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>-8.82</v>
+        <v>23.63</v>
       </c>
       <c r="AS8" t="n">
-        <v>-13.76</v>
+        <v>52.87</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>38.8</v>
+        <v>3.5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 59.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1629.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1526438821888</v>
+        <v>1544165785600</v>
       </c>
       <c r="G9" t="n">
-        <v>376.32</v>
+        <v>373.77</v>
       </c>
       <c r="H9" t="n">
-        <v>162.45</v>
+        <v>164.46</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>55.6</v>
+        <v>57.9</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>78.2</v>
       </c>
       <c r="S9" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>406.43</v>
+        <v>411.15</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.720000000000001</v>
+        <v>-7.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.89</v>
+        <v>3.94</v>
       </c>
       <c r="Z9" t="n">
-        <v>-9.970000000000001</v>
+        <v>-8</v>
       </c>
       <c r="AA9" t="n">
-        <v>24.51</v>
+        <v>28.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.32</v>
+        <v>16.54</v>
       </c>
       <c r="AC9" t="n">
-        <v>57.97</v>
+        <v>58.04</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>398.3</v>
+        <v>399.3112</v>
       </c>
       <c r="AG9" t="n">
-        <v>415.6944</v>
+        <v>416.0022</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>55.6</v>
+        <v>57.9</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>78.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN9" t="n">
         <v>381.59</v>
@@ -2227,10 +2227,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.04</v>
+        <v>2.96</v>
       </c>
       <c r="AS9" t="n">
-        <v>-2.23</v>
+        <v>-1.17</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>34.2</v>
+        <v>34.7</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 40.6, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.0%.</t>
+          <t>TSLA: scenario base High Risk, score 41.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4504199102464</v>
+        <v>4554610442240</v>
       </c>
       <c r="G2" t="n">
-        <v>28.22</v>
+        <v>28.47</v>
       </c>
       <c r="H2" t="n">
-        <v>25.51</v>
+        <v>25.78</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,7 +750,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>59</v>
+        <v>58.3</v>
       </c>
       <c r="Q2" t="n">
         <v>40.4</v>
@@ -759,7 +759,7 @@
         <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>369.35</v>
+        <v>373.25</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.85</v>
+        <v>-5.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.95</v>
+        <v>20.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.37</v>
+        <v>20.84</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.82</v>
+        <v>114.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.84</v>
+        <v>45.52</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.77</v>
+        <v>29.78</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AF2" t="n">
-        <v>363.5364</v>
+        <v>365.0052</v>
       </c>
       <c r="AG2" t="n">
-        <v>308.3764</v>
+        <v>309.1874</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>273.3367</v>
       </c>
       <c r="AP2" t="n">
-        <v>396.7031</v>
+        <v>389.8971</v>
       </c>
       <c r="AQ2" t="n">
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.77</v>
+        <v>20.72</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5145751453696</v>
+        <v>4395044175872</v>
       </c>
       <c r="G3" t="n">
-        <v>31.43</v>
+        <v>36.18</v>
       </c>
       <c r="H3" t="n">
-        <v>16.69</v>
+        <v>31.19</v>
       </c>
       <c r="I3" t="n">
-        <v>62.97</v>
+        <v>27.15</v>
       </c>
       <c r="J3" t="n">
-        <v>114.29</v>
+        <v>141.47</v>
       </c>
       <c r="K3" t="n">
-        <v>85.2</v>
+        <v>16.6</v>
       </c>
       <c r="L3" t="n">
-        <v>6.55</v>
+        <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>94.7</v>
+        <v>92.8</v>
       </c>
       <c r="P3" t="n">
-        <v>67.8</v>
+        <v>41.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.1</v>
+        <v>42.1</v>
       </c>
       <c r="R3" t="n">
-        <v>82.8</v>
+        <v>81.7</v>
       </c>
       <c r="S3" t="n">
-        <v>75.8</v>
+        <v>75.3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,42 +967,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>212.45</v>
+        <v>299.24</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.77</v>
+        <v>-0.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.09</v>
+        <v>17.81</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.56</v>
+        <v>7.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.71</v>
+        <v>52.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>71.45</v>
+        <v>18.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>46.96</v>
+        <v>26.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>207.4098</v>
+        <v>286.9892</v>
       </c>
       <c r="AG3" t="n">
-        <v>189.1928</v>
+        <v>267.126</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,34 +1013,34 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94.7</v>
+        <v>92.8</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.1</v>
+        <v>42.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>82.8</v>
+        <v>81.7</v>
       </c>
       <c r="AM3" t="n">
         <v>751</v>
       </c>
       <c r="AN3" t="n">
-        <v>200.42</v>
+        <v>290.55</v>
       </c>
       <c r="AO3" t="n">
-        <v>164.9777</v>
+        <v>246.403</v>
       </c>
       <c r="AP3" t="n">
-        <v>224.0988</v>
+        <v>315.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.43</v>
+        <v>4.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.29</v>
+        <v>12.02</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>59.1</v>
+        <v>74.5</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4353626210304</v>
+        <v>5023677808640</v>
       </c>
       <c r="G4" t="n">
-        <v>35.84</v>
+        <v>31.81</v>
       </c>
       <c r="H4" t="n">
-        <v>30.89</v>
+        <v>16.3</v>
       </c>
       <c r="I4" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="J4" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="K4" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L4" t="n">
-        <v>79.55</v>
+        <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>90.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>42.4</v>
+        <v>68</v>
       </c>
       <c r="Q4" t="n">
-        <v>42.1</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,80 +1166,80 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>296.42</v>
+        <v>207.41</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6</v>
+        <v>-7.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.35</v>
+        <v>14.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.81</v>
+        <v>18.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>49.4</v>
+        <v>46.29</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.7</v>
+        <v>68.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.02</v>
+        <v>46.96</v>
       </c>
       <c r="AD4" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.68</v>
+        <v>1.46</v>
       </c>
       <c r="AF4" t="n">
-        <v>286.1768</v>
+        <v>208.0094</v>
       </c>
       <c r="AG4" t="n">
-        <v>266.7893</v>
+        <v>189.3302</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>90.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>42.1</v>
+        <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="AM4" t="n">
         <v>751</v>
       </c>
       <c r="AN4" t="n">
-        <v>290.55</v>
+        <v>200.42</v>
       </c>
       <c r="AO4" t="n">
-        <v>246.403</v>
+        <v>164.9777</v>
       </c>
       <c r="AP4" t="n">
-        <v>315.2</v>
+        <v>224.0988</v>
       </c>
       <c r="AQ4" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.58</v>
+        <v>-0.29</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.11</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>74.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 74.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2646464266240</v>
+        <v>2646249046016</v>
       </c>
       <c r="G5" t="n">
-        <v>32.63</v>
+        <v>31.66</v>
       </c>
       <c r="H5" t="n">
         <v>24.95</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>80.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="P5" t="n">
-        <v>54.7</v>
+        <v>55.8</v>
       </c>
       <c r="Q5" t="n">
         <v>38</v>
       </c>
       <c r="R5" t="n">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="S5" t="n">
-        <v>66.7</v>
+        <v>66.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,22 +1368,22 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>246.02</v>
+        <v>246</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.93</v>
+        <v>-6.87</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.19</v>
+        <v>14.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.84</v>
+        <v>8.76</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.37</v>
+        <v>15.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.34</v>
+        <v>25.24</v>
       </c>
       <c r="AC5" t="n">
         <v>31.05</v>
@@ -1392,13 +1392,13 @@
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AF5" t="n">
-        <v>255.4986</v>
+        <v>256.1628</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.5939</v>
+        <v>232.6659</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>80.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="AK5" t="n">
         <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="AM5" t="n">
         <v>751</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.71</v>
+        <v>-3.97</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.77</v>
+        <v>5.73</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>66.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.7%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.0%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2969591349248</v>
+        <v>2925540409344</v>
       </c>
       <c r="G6" t="n">
-        <v>23.8</v>
+        <v>23.46</v>
       </c>
       <c r="H6" t="n">
-        <v>20.66</v>
+        <v>20.36</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1535,25 +1535,25 @@
         <v>30.27</v>
       </c>
       <c r="M6" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>36.1</v>
+        <v>33.8</v>
       </c>
       <c r="P6" t="n">
-        <v>71.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>44.1</v>
       </c>
       <c r="R6" t="n">
-        <v>70.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>63.2</v>
+        <v>62.5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>399.76</v>
+        <v>393.83</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.15</v>
+        <v>-6.46</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.17</v>
+        <v>-1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>-16.95</v>
+        <v>-17.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>-15.85</v>
+        <v>-16.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.17</v>
+        <v>6.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.96</v>
+        <v>23.97</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>411.7392</v>
+        <v>412.1744</v>
       </c>
       <c r="AG6" t="n">
-        <v>451.3541</v>
+        <v>450.7911</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,13 +1608,13 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.1</v>
+        <v>33.8</v>
       </c>
       <c r="AK6" t="n">
         <v>44.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>70.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AM6" t="n">
         <v>751</v>
@@ -1632,10 +1632,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-2.91</v>
+        <v>-4.45</v>
       </c>
       <c r="AS6" t="n">
-        <v>-11.43</v>
+        <v>-12.64</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1649,11 +1649,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>58.2</v>
+        <v>57</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.9%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1506503426048</v>
+        <v>1523587088384</v>
       </c>
       <c r="G7" t="n">
-        <v>21.58</v>
+        <v>21.84</v>
       </c>
       <c r="H7" t="n">
-        <v>16.37</v>
+        <v>16.56</v>
       </c>
       <c r="I7" t="n">
         <v>32.84</v>
@@ -1734,25 +1734,25 @@
         <v>35.61</v>
       </c>
       <c r="M7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>33.5</v>
+        <v>38.2</v>
       </c>
       <c r="P7" t="n">
-        <v>79.8</v>
+        <v>79.2</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>68.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>61.2</v>
+        <v>62.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,22 +1766,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>593.48</v>
+        <v>600.21</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.03</v>
+        <v>-2.19</v>
       </c>
       <c r="Y7" t="n">
-        <v>-5.41</v>
+        <v>-3.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>-8.92</v>
+        <v>-6.59</v>
       </c>
       <c r="AA7" t="n">
-        <v>-14.14</v>
+        <v>-11.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>28.85</v>
+        <v>28.87</v>
       </c>
       <c r="AC7" t="n">
         <v>36.36</v>
@@ -1793,10 +1793,10 @@
         <v>0.79</v>
       </c>
       <c r="AF7" t="n">
-        <v>622.2082</v>
+        <v>622.1975</v>
       </c>
       <c r="AG7" t="n">
-        <v>656.6682</v>
+        <v>655.3206</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,34 +1807,34 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>33.5</v>
+        <v>38.2</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>68.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AM7" t="n">
         <v>751</v>
       </c>
       <c r="AN7" t="n">
-        <v>566.98</v>
+        <v>566.455</v>
       </c>
       <c r="AO7" t="n">
-        <v>525.72</v>
+        <v>525.2332</v>
       </c>
       <c r="AP7" t="n">
-        <v>635.29</v>
+        <v>634.7017</v>
       </c>
       <c r="AQ7" t="n">
-        <v>688.55</v>
+        <v>687.9124</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.62</v>
+        <v>-3.53</v>
       </c>
       <c r="AS7" t="n">
-        <v>-9.619999999999999</v>
+        <v>-8.41</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>42</v>
+        <v>43.7</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 61.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.5%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>625224515584</v>
+        <v>613276581888</v>
       </c>
       <c r="G8" t="n">
-        <v>62.61</v>
+        <v>61.7</v>
       </c>
       <c r="H8" t="n">
-        <v>39.1</v>
+        <v>38.36</v>
       </c>
       <c r="I8" t="n">
         <v>29.71</v>
@@ -1933,7 +1933,7 @@
         <v>12.99</v>
       </c>
       <c r="M8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1942,16 +1942,16 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q8" t="n">
         <v>18.3</v>
       </c>
       <c r="R8" t="n">
-        <v>4.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>1629.6</v>
+        <v>1622.2</v>
       </c>
       <c r="X8" t="n">
-        <v>19.21</v>
+        <v>24.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>38.36</v>
+        <v>37.83</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.87</v>
+        <v>73.02</v>
       </c>
       <c r="AA8" t="n">
-        <v>146.64</v>
+        <v>145.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>34.97</v>
+        <v>35.71</v>
       </c>
       <c r="AC8" t="n">
-        <v>38.24</v>
+        <v>38.22</v>
       </c>
       <c r="AD8" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="AF8" t="n">
-        <v>1318.1492</v>
+        <v>1326.8936</v>
       </c>
       <c r="AG8" t="n">
-        <v>1066.0075</v>
+        <v>1070.9524</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>18.3</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AM8" t="n">
         <v>764</v>
@@ -2030,10 +2030,10 @@
         <v>1629.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>23.63</v>
+        <v>22.26</v>
       </c>
       <c r="AS8" t="n">
-        <v>52.87</v>
+        <v>51.47</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 22.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 59.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 22.3%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1544165785600</v>
+        <v>1519791243264</v>
       </c>
       <c r="G9" t="n">
-        <v>373.77</v>
+        <v>364.56</v>
       </c>
       <c r="H9" t="n">
-        <v>164.46</v>
+        <v>161.87</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>57.9</v>
+        <v>50.9</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>78.2</v>
       </c>
       <c r="S9" t="n">
-        <v>41.1</v>
+        <v>39.4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>411.15</v>
+        <v>404.66</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.25</v>
+        <v>-4.16</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.94</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>-8</v>
+        <v>-11.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>28.84</v>
+        <v>24.39</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.54</v>
+        <v>13.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>58.04</v>
+        <v>57.97</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>399.3112</v>
+        <v>400.348</v>
       </c>
       <c r="AG9" t="n">
-        <v>416.0022</v>
+        <v>416.2956</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>57.9</v>
+        <v>50.9</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.96</v>
+        <v>1.08</v>
       </c>
       <c r="AS9" t="n">
-        <v>-1.17</v>
+        <v>-2.8</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>34.7</v>
+        <v>32.9</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 41.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.0%.</t>
+          <t>TSLA: scenario base High Risk, score 39.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4554610442240</v>
+        <v>4439174283264</v>
       </c>
       <c r="G2" t="n">
-        <v>28.47</v>
+        <v>27.77</v>
       </c>
       <c r="H2" t="n">
-        <v>25.78</v>
+        <v>25.12</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>58.3</v>
+        <v>60.1</v>
       </c>
       <c r="Q2" t="n">
         <v>40.4</v>
       </c>
       <c r="R2" t="n">
-        <v>82.8</v>
+        <v>78.8</v>
       </c>
       <c r="S2" t="n">
-        <v>79.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,45 +773,45 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>373.25</v>
+        <v>363.79</v>
       </c>
       <c r="X2" t="n">
-        <v>-5.87</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.12</v>
+        <v>18.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.84</v>
+        <v>18.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>114.3</v>
+        <v>106.39</v>
       </c>
       <c r="AB2" t="n">
-        <v>45.52</v>
+        <v>44.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.78</v>
+        <v>29.8</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>365.0052</v>
+        <v>366.1754</v>
       </c>
       <c r="AG2" t="n">
-        <v>309.1874</v>
+        <v>309.9449</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>100</v>
@@ -820,10 +820,10 @@
         <v>40.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>82.8</v>
+        <v>78.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
         <v>356.38</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.26</v>
+        <v>-0.65</v>
       </c>
       <c r="AS2" t="n">
-        <v>20.72</v>
+        <v>17.37</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>77.7</v>
+        <v>76.2</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4395044175872</v>
+        <v>4346723172352</v>
       </c>
       <c r="G3" t="n">
-        <v>36.18</v>
+        <v>35.83</v>
       </c>
       <c r="H3" t="n">
-        <v>31.19</v>
+        <v>30.84</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>92.8</v>
+        <v>93.3</v>
       </c>
       <c r="P3" t="n">
-        <v>41.6</v>
+        <v>42.5</v>
       </c>
       <c r="Q3" t="n">
         <v>42.1</v>
       </c>
       <c r="R3" t="n">
-        <v>81.7</v>
+        <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>299.24</v>
+        <v>295.95</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.33</v>
+        <v>-0.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.81</v>
+        <v>18.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.73</v>
+        <v>8.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>52.93</v>
+        <v>49.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.06</v>
+        <v>17.6</v>
       </c>
       <c r="AC3" t="n">
         <v>26.02</v>
@@ -996,13 +996,13 @@
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="AF3" t="n">
-        <v>286.9892</v>
+        <v>287.8428</v>
       </c>
       <c r="AG3" t="n">
-        <v>267.126</v>
+        <v>267.4483</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>92.8</v>
+        <v>93.3</v>
       </c>
       <c r="AK3" t="n">
         <v>42.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>81.7</v>
+        <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>290.55</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.27</v>
+        <v>2.82</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.02</v>
+        <v>10.66</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>74.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5023677808640</v>
+        <v>4956827418624</v>
       </c>
       <c r="G4" t="n">
-        <v>31.81</v>
+        <v>31.34</v>
       </c>
       <c r="H4" t="n">
-        <v>16.3</v>
+        <v>16.08</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1138,26 +1138,24 @@
       <c r="L4" t="n">
         <v>6.55</v>
       </c>
-      <c r="M4" t="n">
-        <v>47</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>92.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>68</v>
+        <v>68.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>79.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1169,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>207.41</v>
+        <v>204.65</v>
       </c>
       <c r="X4" t="n">
         <v>-7.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.14</v>
+        <v>13.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.65</v>
+        <v>16.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>46.29</v>
+        <v>41.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>68.61</v>
+        <v>67.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.96</v>
+        <v>46.94</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>208.0094</v>
+        <v>208.5445</v>
       </c>
       <c r="AG4" t="n">
-        <v>189.3302</v>
+        <v>189.4837</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,16 +1210,16 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>79.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
         <v>200.42</v>
@@ -1236,10 +1234,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.29</v>
+        <v>-1.87</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.550000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1255,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1264,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 74.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 73.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.9%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1315,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2646249046016</v>
+        <v>2554813480960</v>
       </c>
       <c r="G5" t="n">
-        <v>31.66</v>
+        <v>30.57</v>
       </c>
       <c r="H5" t="n">
-        <v>24.95</v>
+        <v>24.09</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1340,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>79.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>55.8</v>
+        <v>58.3</v>
       </c>
       <c r="Q5" t="n">
         <v>38</v>
       </c>
       <c r="R5" t="n">
-        <v>73.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>66.5</v>
+        <v>65.3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1366,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>246</v>
+        <v>237.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.87</v>
+        <v>-10.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.31</v>
+        <v>13.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.76</v>
+        <v>6.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.98</v>
+        <v>9.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.24</v>
+        <v>23.74</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.05</v>
+        <v>31.1</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AF5" t="n">
-        <v>256.1628</v>
+        <v>256.6374</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.6659</v>
+        <v>232.7084</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,19 +1407,19 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>79.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AK5" t="n">
         <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>73.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>238</v>
+        <v>237.5</v>
       </c>
       <c r="AO5" t="n">
         <v>199.34</v>
@@ -1433,10 +1431,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.97</v>
+        <v>-7.46</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.73</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1448,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 7.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>66</v>
+        <v>63.5</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1461,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.5%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1512,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2925540409344</v>
+        <v>2814708285440</v>
       </c>
       <c r="G6" t="n">
-        <v>23.46</v>
+        <v>22.58</v>
       </c>
       <c r="H6" t="n">
-        <v>20.36</v>
+        <v>19.59</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1535,25 +1533,25 @@
         <v>30.27</v>
       </c>
       <c r="M6" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>33.8</v>
+        <v>28.7</v>
       </c>
       <c r="P6" t="n">
-        <v>71.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="R6" t="n">
-        <v>68.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="S6" t="n">
-        <v>62.5</v>
+        <v>61</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,37 +1565,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>393.83</v>
+        <v>378.91</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.46</v>
+        <v>-10.34</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.18</v>
+        <v>-3.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>-17.33</v>
+        <v>-19.84</v>
       </c>
       <c r="AA6" t="n">
-        <v>-16.42</v>
+        <v>-20.29</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.09</v>
+        <v>4.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.97</v>
+        <v>24.05</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>412.1744</v>
+        <v>412.3229</v>
       </c>
       <c r="AG6" t="n">
-        <v>450.7911</v>
+        <v>450.1681</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,19 +1606,19 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>33.8</v>
+        <v>28.7</v>
       </c>
       <c r="AK6" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>68.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>390.34</v>
+        <v>378.91</v>
       </c>
       <c r="AO6" t="n">
         <v>355.9989</v>
@@ -1632,10 +1630,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.45</v>
+        <v>-8.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>-12.64</v>
+        <v>-15.83</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1649,11 +1647,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 4.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>57</v>
+        <v>54.1</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1660,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.5%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.1%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1689,12 +1687,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1704,55 +1702,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1523587088384</v>
+        <v>638405836800</v>
       </c>
       <c r="G7" t="n">
-        <v>21.84</v>
+        <v>63.86</v>
       </c>
       <c r="H7" t="n">
-        <v>16.56</v>
+        <v>39.93</v>
       </c>
       <c r="I7" t="n">
-        <v>32.84</v>
+        <v>29.71</v>
       </c>
       <c r="J7" t="n">
-        <v>32.93</v>
+        <v>52.24</v>
       </c>
       <c r="K7" t="n">
-        <v>33.1</v>
+        <v>13.2</v>
       </c>
       <c r="L7" t="n">
-        <v>35.61</v>
+        <v>12.99</v>
       </c>
       <c r="M7" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>38.2</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>79.2</v>
+        <v>7.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>18.3</v>
       </c>
       <c r="R7" t="n">
-        <v>69.90000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="S7" t="n">
-        <v>62.5</v>
+        <v>60.9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,79 +1764,79 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>600.21</v>
+        <v>1591.2</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.19</v>
+        <v>25.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>-3.52</v>
+        <v>33.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>-6.59</v>
+        <v>72.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>-11.75</v>
+        <v>145.59</v>
       </c>
       <c r="AB7" t="n">
-        <v>28.87</v>
+        <v>34.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>36.36</v>
+        <v>38.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>-34.15</v>
+        <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>622.1975</v>
+        <v>1335.5488</v>
       </c>
       <c r="AG7" t="n">
-        <v>655.3206</v>
+        <v>1075.7448</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38.2</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>18.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>69.90000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="AN7" t="n">
-        <v>566.455</v>
+        <v>1333</v>
       </c>
       <c r="AO7" t="n">
-        <v>525.2332</v>
+        <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>634.7017</v>
+        <v>1629.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>687.9124</v>
+        <v>1629.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>-3.53</v>
+        <v>19.14</v>
       </c>
       <c r="AS7" t="n">
-        <v>-8.41</v>
+        <v>47.92</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1848,11 +1846,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 19.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>43.7</v>
+        <v>16.8</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1859,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.5%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.1%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1629.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,19 +1879,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1903,55 +1901,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>613276581888</v>
+        <v>1440758366208</v>
       </c>
       <c r="G8" t="n">
-        <v>61.7</v>
+        <v>20.65</v>
       </c>
       <c r="H8" t="n">
-        <v>38.36</v>
+        <v>15.66</v>
       </c>
       <c r="I8" t="n">
-        <v>29.71</v>
+        <v>32.84</v>
       </c>
       <c r="J8" t="n">
-        <v>52.24</v>
+        <v>32.93</v>
       </c>
       <c r="K8" t="n">
-        <v>13.2</v>
+        <v>33.1</v>
       </c>
       <c r="L8" t="n">
-        <v>12.99</v>
+        <v>35.61</v>
       </c>
       <c r="M8" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>27.1</v>
       </c>
       <c r="P8" t="n">
-        <v>9.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="R8" t="n">
-        <v>9.699999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="S8" t="n">
-        <v>60</v>
+        <v>59.4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,79 +1963,79 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>1622.2</v>
+        <v>567.58</v>
       </c>
       <c r="X8" t="n">
-        <v>24.15</v>
+        <v>-7.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.83</v>
+        <v>-7.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.02</v>
+        <v>-12.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>145.89</v>
+        <v>-18.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>35.71</v>
+        <v>26.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>38.22</v>
+        <v>36.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>-44.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.93</v>
+        <v>0.72</v>
       </c>
       <c r="AF8" t="n">
-        <v>1326.8936</v>
+        <v>622.0587</v>
       </c>
       <c r="AG8" t="n">
-        <v>1070.9524</v>
+        <v>654.4771</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>27.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>9.699999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
-        <v>1249</v>
+        <v>566.455</v>
       </c>
       <c r="AO8" t="n">
-        <v>1109.5466</v>
+        <v>525.2332</v>
       </c>
       <c r="AP8" t="n">
-        <v>1629.6</v>
+        <v>634.7017</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1629.6</v>
+        <v>687.9124</v>
       </c>
       <c r="AR8" t="n">
-        <v>22.26</v>
+        <v>-8.76</v>
       </c>
       <c r="AS8" t="n">
-        <v>51.47</v>
+        <v>-13.28</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2047,11 +2045,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 22.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>7.7</v>
+        <v>38.7</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2058,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 22.3%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1629.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,19 +2078,19 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2100,174 +2098,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1519791243264</v>
-      </c>
-      <c r="G9" t="n">
-        <v>364.56</v>
-      </c>
-      <c r="H9" t="n">
-        <v>161.87</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>50.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>404.66</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-11.83</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>24.39</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>400.348</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>416.2956</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>50.9</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL9" t="n">
         <v>0</v>
       </c>
-      <c r="AL9" t="n">
-        <v>78.2</v>
-      </c>
       <c r="AM9" t="n">
-        <v>751</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>381.59</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>343.25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-2.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>32.9</v>
+        <v>32.3</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 39.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2277,19 +2225,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2297,124 +2245,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1488693755904</v>
+      </c>
+      <c r="G10" t="n">
+        <v>363.65</v>
+      </c>
+      <c r="H10" t="n">
+        <v>158.56</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>50</v>
-      </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>396.38</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-16.61</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>401.3426</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>416.6081</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>100</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+        <v>752</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>442.1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-4.86</v>
+      </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>32.3</v>
+        <v>29.9</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 36.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2424,7 +2422,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4439174283264</v>
+        <v>4490912595968</v>
       </c>
       <c r="G2" t="n">
-        <v>27.77</v>
+        <v>28.09</v>
       </c>
       <c r="H2" t="n">
-        <v>25.12</v>
+        <v>25.42</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>60.1</v>
+        <v>59.3</v>
       </c>
       <c r="Q2" t="n">
         <v>40.4</v>
       </c>
       <c r="R2" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>78.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,45 +773,45 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>363.79</v>
+        <v>368.03</v>
       </c>
       <c r="X2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.3</v>
+        <v>19.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.18</v>
+        <v>20.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>106.39</v>
+        <v>109.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.21</v>
+        <v>44.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.8</v>
+        <v>29.78</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>366.1754</v>
+        <v>367.1934</v>
       </c>
       <c r="AG2" t="n">
-        <v>309.9449</v>
+        <v>310.7313</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
         <v>100</v>
@@ -820,10 +820,10 @@
         <v>40.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
         <v>356.38</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.65</v>
+        <v>0.23</v>
       </c>
       <c r="AS2" t="n">
-        <v>17.37</v>
+        <v>18.44</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>76.2</v>
+        <v>77.8</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.2%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,48 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4346723172352</v>
+        <v>5103122644992</v>
       </c>
       <c r="G3" t="n">
-        <v>35.83</v>
+        <v>32.26</v>
       </c>
       <c r="H3" t="n">
-        <v>30.84</v>
+        <v>16.55</v>
       </c>
       <c r="I3" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="J3" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="K3" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L3" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="M3" t="n">
-        <v>36</v>
-      </c>
+        <v>6.55</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>93.3</v>
+        <v>98.2</v>
       </c>
       <c r="P3" t="n">
-        <v>42.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.1</v>
+        <v>14.2</v>
       </c>
       <c r="R3" t="n">
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>75.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,42 +965,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>295.95</v>
+        <v>210.69</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.63</v>
+        <v>-4.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.52</v>
+        <v>18.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.17</v>
+        <v>18.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>49.75</v>
+        <v>46.39</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.6</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.02</v>
+        <v>46.93</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.68</v>
+        <v>1.48</v>
       </c>
       <c r="AF3" t="n">
-        <v>287.8428</v>
+        <v>209.121</v>
       </c>
       <c r="AG3" t="n">
-        <v>267.4483</v>
+        <v>189.6844</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,34 +1011,34 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>93.3</v>
+        <v>98.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>42.1</v>
+        <v>14.2</v>
       </c>
       <c r="AL3" t="n">
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
-        <v>290.55</v>
+        <v>200.42</v>
       </c>
       <c r="AO3" t="n">
-        <v>246.403</v>
+        <v>164.9777</v>
       </c>
       <c r="AP3" t="n">
-        <v>315.2</v>
+        <v>224.0988</v>
       </c>
       <c r="AQ3" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.82</v>
+        <v>0.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.66</v>
+        <v>11.07</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,7 +1047,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1058,7 +1056,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>75.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1065,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.8%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1085,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,48 +1112,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4956827418624</v>
+        <v>4376979046400</v>
       </c>
       <c r="G4" t="n">
-        <v>31.34</v>
+        <v>36.08</v>
       </c>
       <c r="H4" t="n">
-        <v>16.08</v>
+        <v>31.06</v>
       </c>
       <c r="I4" t="n">
-        <v>62.97</v>
+        <v>27.15</v>
       </c>
       <c r="J4" t="n">
-        <v>114.29</v>
+        <v>141.47</v>
       </c>
       <c r="K4" t="n">
-        <v>85.2</v>
+        <v>16.6</v>
       </c>
       <c r="L4" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>79.55</v>
+      </c>
+      <c r="M4" t="n">
+        <v>36</v>
+      </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>89.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="P4" t="n">
-        <v>68.8</v>
+        <v>41.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.2</v>
+        <v>42.1</v>
       </c>
       <c r="R4" t="n">
-        <v>76.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>73</v>
+        <v>76.3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1164,80 +1164,80 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>204.65</v>
+        <v>298.01</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.84</v>
+        <v>-0.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.57</v>
+        <v>19.81</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.23</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>41.63</v>
+        <v>52.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>67.73</v>
+        <v>17.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.94</v>
+        <v>26</v>
       </c>
       <c r="AD4" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>208.5445</v>
+        <v>288.6298</v>
       </c>
       <c r="AG4" t="n">
-        <v>189.4837</v>
+        <v>267.793</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>89.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.2</v>
+        <v>42.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>76.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN4" t="n">
-        <v>200.42</v>
+        <v>290.55</v>
       </c>
       <c r="AO4" t="n">
-        <v>164.9777</v>
+        <v>246.403</v>
       </c>
       <c r="AP4" t="n">
-        <v>224.0988</v>
+        <v>315.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.87</v>
+        <v>3.25</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>11.28</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>55.6</v>
+        <v>75.8</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,17 +1264,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 73.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.2%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2554813480960</v>
+        <v>2628929978368</v>
       </c>
       <c r="G5" t="n">
-        <v>30.57</v>
+        <v>31.45</v>
       </c>
       <c r="H5" t="n">
-        <v>24.09</v>
+        <v>24.79</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1340,19 +1340,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>74.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="P5" t="n">
-        <v>58.3</v>
+        <v>56.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="R5" t="n">
-        <v>68.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="S5" t="n">
-        <v>65.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1366,37 +1366,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>237.5</v>
+        <v>244.39</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.33</v>
+        <v>-5.76</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.17</v>
+        <v>17.07</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.72</v>
+        <v>9.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.9</v>
+        <v>13.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.74</v>
+        <v>24.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.1</v>
+        <v>31.12</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>256.6374</v>
+        <v>257.1002</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.7084</v>
+        <v>232.8037</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1407,16 +1407,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>74.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>68.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
         <v>237.5</v>
@@ -1431,10 +1431,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-7.46</v>
+        <v>-4.94</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>4.98</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 7.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>63.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.5%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2814708285440</v>
+        <v>2818348154880</v>
       </c>
       <c r="G6" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="H6" t="n">
-        <v>19.59</v>
+        <v>19.61</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1539,19 +1539,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>28.7</v>
+        <v>29.8</v>
       </c>
       <c r="P6" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>44</v>
       </c>
       <c r="R6" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="S6" t="n">
-        <v>61</v>
+        <v>61.3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1565,25 +1565,25 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>378.91</v>
+        <v>379.4</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.34</v>
+        <v>-8.91</v>
       </c>
       <c r="Y6" t="n">
-        <v>-3.08</v>
+        <v>-2.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>-19.84</v>
+        <v>-20</v>
       </c>
       <c r="AA6" t="n">
-        <v>-20.29</v>
+        <v>-20</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.05</v>
+        <v>24.04</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.91</v>
@@ -1592,10 +1592,10 @@
         <v>0.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>412.3229</v>
+        <v>412.4404</v>
       </c>
       <c r="AG6" t="n">
-        <v>450.1681</v>
+        <v>449.5554</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1606,16 +1606,16 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28.7</v>
+        <v>29.8</v>
       </c>
       <c r="AK6" t="n">
         <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN6" t="n">
         <v>378.91</v>
@@ -1630,10 +1630,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-8.1</v>
+        <v>-8.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>-15.83</v>
+        <v>-15.61</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.1</v>
+        <v>54.5</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.1%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.0%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1702,55 +1702,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>638405836800</v>
+        <v>1465228591104</v>
       </c>
       <c r="G7" t="n">
-        <v>63.86</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>39.93</v>
+        <v>15.93</v>
       </c>
       <c r="I7" t="n">
-        <v>29.71</v>
+        <v>32.84</v>
       </c>
       <c r="J7" t="n">
-        <v>52.24</v>
+        <v>32.93</v>
       </c>
       <c r="K7" t="n">
-        <v>13.2</v>
+        <v>33.1</v>
       </c>
       <c r="L7" t="n">
-        <v>12.99</v>
+        <v>35.61</v>
       </c>
       <c r="M7" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>31.9</v>
       </c>
       <c r="P7" t="n">
-        <v>7.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="R7" t="n">
-        <v>22.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1764,79 +1764,79 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1591.2</v>
+        <v>577.22</v>
       </c>
       <c r="X7" t="n">
-        <v>25.85</v>
+        <v>-4.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.18</v>
+        <v>-4.77</v>
       </c>
       <c r="Z7" t="n">
-        <v>72.58</v>
+        <v>-12.01</v>
       </c>
       <c r="AA7" t="n">
-        <v>145.59</v>
+        <v>-16.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>34.75</v>
+        <v>27.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.24</v>
+        <v>36.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>-44.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
       <c r="AF7" t="n">
-        <v>1335.5488</v>
+        <v>621.3661</v>
       </c>
       <c r="AG7" t="n">
-        <v>1075.7448</v>
+        <v>653.6996</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>100</v>
+        <v>31.9</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>22.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AM7" t="n">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
-        <v>1333</v>
+        <v>566.455</v>
       </c>
       <c r="AO7" t="n">
-        <v>1109.5466</v>
+        <v>525.2332</v>
       </c>
       <c r="AP7" t="n">
-        <v>1629.6</v>
+        <v>634.7017</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1629.6</v>
+        <v>687.9124</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.14</v>
+        <v>-7.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>47.92</v>
+        <v>-11.7</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1846,11 +1846,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 19.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>16.8</v>
+        <v>40.6</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1859,17 +1859,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.1%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1629.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1879,19 +1879,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1901,55 +1901,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1440758366208</v>
+        <v>645959974912</v>
       </c>
       <c r="G8" t="n">
-        <v>20.65</v>
+        <v>64.61</v>
       </c>
       <c r="H8" t="n">
-        <v>15.66</v>
+        <v>40.4</v>
       </c>
       <c r="I8" t="n">
-        <v>32.84</v>
+        <v>29.71</v>
       </c>
       <c r="J8" t="n">
-        <v>32.93</v>
+        <v>52.24</v>
       </c>
       <c r="K8" t="n">
-        <v>33.1</v>
+        <v>13.2</v>
       </c>
       <c r="L8" t="n">
-        <v>35.61</v>
+        <v>12.99</v>
       </c>
       <c r="M8" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>27.1</v>
+        <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>81.90000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.9</v>
+        <v>18.2</v>
       </c>
       <c r="R8" t="n">
-        <v>62.1</v>
+        <v>6.7</v>
       </c>
       <c r="S8" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1963,79 +1963,79 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>567.58</v>
+        <v>1656.4</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.05</v>
+        <v>32.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>-7.73</v>
+        <v>39.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>-12.19</v>
+        <v>78.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>-18.9</v>
+        <v>156.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.44</v>
+        <v>36.49</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.48</v>
+        <v>38.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>-34.15</v>
+        <v>-44.77</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>622.0587</v>
+        <v>1346.4499</v>
       </c>
       <c r="AG8" t="n">
-        <v>654.4771</v>
+        <v>1080.9571</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27.1</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>28.9</v>
+        <v>18.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>62.1</v>
+        <v>6.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="AN8" t="n">
-        <v>566.455</v>
+        <v>1345.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>525.2332</v>
+        <v>1109.5466</v>
       </c>
       <c r="AP8" t="n">
-        <v>634.7017</v>
+        <v>1656.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>687.9124</v>
+        <v>1656.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>-8.76</v>
+        <v>23.02</v>
       </c>
       <c r="AS8" t="n">
-        <v>-13.28</v>
+        <v>53.23</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 23.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>38.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2058,17 +2058,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 59.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.0%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1656.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2078,19 +2078,19 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2098,124 +2098,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>1504129843200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="H9" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>50</v>
-      </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>400.49</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-18.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>402.4874</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>416.9638</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AK9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>100</v>
-      </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+        <v>753</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>442.1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-3.95</v>
+      </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 38.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.5%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2225,19 +2275,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2245,174 +2295,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1488693755904</v>
-      </c>
-      <c r="G10" t="n">
-        <v>363.65</v>
-      </c>
-      <c r="H10" t="n">
-        <v>158.56</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="S10" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>396.38</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-3.32</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-16.61</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>57.94</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>401.3426</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>416.6081</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>35</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL10" t="n">
         <v>0</v>
       </c>
-      <c r="AL10" t="n">
-        <v>73.40000000000001</v>
-      </c>
       <c r="AM10" t="n">
-        <v>752</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>381.59</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>343.25</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-4.86</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>29.9</v>
+        <v>32.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 36.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.2%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1794,7 +1794,7 @@
         <v>621.3661</v>
       </c>
       <c r="AG7" t="n">
-        <v>653.6996</v>
+        <v>653.6997</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>645959974912</v>
+        <v>638945394688</v>
       </c>
       <c r="G8" t="n">
-        <v>64.61</v>
+        <v>63.91</v>
       </c>
       <c r="H8" t="n">
-        <v>40.4</v>
+        <v>39.96</v>
       </c>
       <c r="I8" t="n">
         <v>29.71</v>
@@ -1940,16 +1940,16 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="R8" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="S8" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1963,37 +1963,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>1656.4</v>
+        <v>1676</v>
       </c>
       <c r="X8" t="n">
-        <v>32.62</v>
+        <v>25.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>39.06</v>
+        <v>41.03</v>
       </c>
       <c r="Z8" t="n">
-        <v>78.55</v>
+        <v>85.12</v>
       </c>
       <c r="AA8" t="n">
-        <v>156.71</v>
+        <v>152.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>36.49</v>
+        <v>36.97</v>
       </c>
       <c r="AC8" t="n">
-        <v>38.28</v>
+        <v>38.26</v>
       </c>
       <c r="AD8" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>1346.4499</v>
+        <v>1355.7714</v>
       </c>
       <c r="AG8" t="n">
-        <v>1080.9571</v>
+        <v>1086.2272</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2007,31 +2007,31 @@
         <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AN8" t="n">
-        <v>1345.2</v>
+        <v>1376.4</v>
       </c>
       <c r="AO8" t="n">
         <v>1109.5466</v>
       </c>
       <c r="AP8" t="n">
-        <v>1656.4</v>
+        <v>1676</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1656.4</v>
+        <v>1676</v>
       </c>
       <c r="AR8" t="n">
-        <v>23.02</v>
+        <v>23.62</v>
       </c>
       <c r="AS8" t="n">
-        <v>53.23</v>
+        <v>54.3</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2045,11 +2045,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 23.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 59.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 59.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1656.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4490912595968</v>
+        <v>4266995482624</v>
       </c>
       <c r="G2" t="n">
-        <v>28.09</v>
+        <v>26.69</v>
       </c>
       <c r="H2" t="n">
-        <v>25.42</v>
+        <v>24.12</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>59.3</v>
+        <v>62.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="R2" t="n">
-        <v>82.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>80.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,60 +773,60 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>368.03</v>
+        <v>349.68</v>
       </c>
       <c r="X2" t="n">
-        <v>-5.01</v>
+        <v>-10.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.9</v>
+        <v>16.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.2</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.76</v>
+        <v>102.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.7</v>
+        <v>42.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.78</v>
+        <v>29.92</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF2" t="n">
-        <v>367.1934</v>
+        <v>367.821</v>
       </c>
       <c r="AG2" t="n">
-        <v>310.7313</v>
+        <v>311.3296</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>82.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN2" t="n">
-        <v>356.38</v>
+        <v>349.68</v>
       </c>
       <c r="AO2" t="n">
         <v>273.3367</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.23</v>
+        <v>-4.93</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.44</v>
+        <v>12.32</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>77.8</v>
+        <v>74.5</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.2%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,48 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5103122644992</v>
+        <v>4362291642368</v>
       </c>
       <c r="G3" t="n">
-        <v>32.26</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
-        <v>16.55</v>
+        <v>30.94</v>
       </c>
       <c r="I3" t="n">
-        <v>62.97</v>
+        <v>27.15</v>
       </c>
       <c r="J3" t="n">
-        <v>114.29</v>
+        <v>141.47</v>
       </c>
       <c r="K3" t="n">
-        <v>85.2</v>
+        <v>16.6</v>
       </c>
       <c r="L3" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>79.55</v>
+      </c>
+      <c r="M3" t="n">
+        <v>36</v>
+      </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>98.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>67.09999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.2</v>
+        <v>42.1</v>
       </c>
       <c r="R3" t="n">
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>76.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -965,42 +967,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>210.69</v>
+        <v>297.01</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.39</v>
+        <v>-1.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.13</v>
+        <v>19.88</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.7</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.39</v>
+        <v>51.69</v>
       </c>
       <c r="AB3" t="n">
-        <v>69.26000000000001</v>
+        <v>17.41</v>
       </c>
       <c r="AC3" t="n">
-        <v>46.93</v>
+        <v>26.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.48</v>
+        <v>0.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>209.121</v>
+        <v>289.365</v>
       </c>
       <c r="AG3" t="n">
-        <v>189.6844</v>
+        <v>268.0891</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1011,34 +1013,34 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>98.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.2</v>
+        <v>42.1</v>
       </c>
       <c r="AL3" t="n">
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN3" t="n">
-        <v>200.42</v>
+        <v>290.55</v>
       </c>
       <c r="AO3" t="n">
-        <v>164.9777</v>
+        <v>246.403</v>
       </c>
       <c r="AP3" t="n">
-        <v>224.0988</v>
+        <v>315.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>235.4656</v>
+        <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.75</v>
+        <v>2.64</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.07</v>
+        <v>10.79</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1047,7 +1049,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1056,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>60</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1065,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1085,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1112,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4376979046400</v>
+        <v>5053711646720</v>
       </c>
       <c r="G4" t="n">
-        <v>36.08</v>
+        <v>31.95</v>
       </c>
       <c r="H4" t="n">
-        <v>31.06</v>
+        <v>16.39</v>
       </c>
       <c r="I4" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="J4" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="K4" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L4" t="n">
-        <v>79.55</v>
+        <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>41.9</v>
+        <v>67.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>42.1</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>76.3</v>
+        <v>75.7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1164,80 +1166,80 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>298.01</v>
+        <v>208.65</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.32</v>
+        <v>-6.52</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.81</v>
+        <v>20.96</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.720000000000001</v>
+        <v>22.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>52.93</v>
+        <v>43.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.84</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>26</v>
+        <v>46.97</v>
       </c>
       <c r="AD4" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="AF4" t="n">
-        <v>288.6298</v>
+        <v>209.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>267.793</v>
+        <v>189.8757</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>42.1</v>
+        <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN4" t="n">
-        <v>290.55</v>
+        <v>200.42</v>
       </c>
       <c r="AO4" t="n">
-        <v>246.403</v>
+        <v>164.9777</v>
       </c>
       <c r="AP4" t="n">
-        <v>315.2</v>
+        <v>224.0988</v>
       </c>
       <c r="AQ4" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.25</v>
+        <v>-0.46</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.28</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1246,7 +1248,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1255,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>75.8</v>
+        <v>59</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.2%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 75.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.5%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1284,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1315,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2628929978368</v>
+        <v>2504147599360</v>
       </c>
       <c r="G5" t="n">
-        <v>31.45</v>
+        <v>30.15</v>
       </c>
       <c r="H5" t="n">
-        <v>24.79</v>
+        <v>23.56</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1340,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>83.2</v>
+        <v>74.2</v>
       </c>
       <c r="P5" t="n">
-        <v>56.3</v>
+        <v>59.5</v>
       </c>
       <c r="Q5" t="n">
         <v>37.9</v>
       </c>
       <c r="R5" t="n">
-        <v>72.3</v>
+        <v>61.1</v>
       </c>
       <c r="S5" t="n">
-        <v>67.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1361,65 +1363,65 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>244.39</v>
+        <v>232.79</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.76</v>
+        <v>-12.16</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.07</v>
+        <v>13.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.81</v>
+        <v>5.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.77</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.89</v>
+        <v>21.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.12</v>
+        <v>31.19</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>257.1002</v>
+        <v>257.083</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.8037</v>
+        <v>232.8377</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AJ5" t="n">
-        <v>83.2</v>
+        <v>74.2</v>
       </c>
       <c r="AK5" t="n">
         <v>37.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>72.3</v>
+        <v>61.1</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN5" t="n">
-        <v>237.5</v>
+        <v>232.79</v>
       </c>
       <c r="AO5" t="n">
         <v>199.34</v>
@@ -1431,14 +1433,14 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.94</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.98</v>
+        <v>-0.02</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1448,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>66.59999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1461,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 63.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.4%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1512,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2818348154880</v>
+        <v>2728761229312</v>
       </c>
       <c r="G6" t="n">
-        <v>22.61</v>
+        <v>21.85</v>
       </c>
       <c r="H6" t="n">
-        <v>19.61</v>
+        <v>18.99</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1533,25 +1535,25 @@
         <v>30.27</v>
       </c>
       <c r="M6" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>29.8</v>
+        <v>25.7</v>
       </c>
       <c r="P6" t="n">
-        <v>73.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="Q6" t="n">
         <v>44</v>
       </c>
       <c r="R6" t="n">
-        <v>63.2</v>
+        <v>58.9</v>
       </c>
       <c r="S6" t="n">
-        <v>61.3</v>
+        <v>60.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1565,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>379.4</v>
+        <v>367.34</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.91</v>
+        <v>-12.57</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.26</v>
+        <v>-3.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>-20</v>
+        <v>-22.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>-20</v>
+        <v>-22.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.04</v>
+        <v>24.09</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>412.4404</v>
+        <v>412.342</v>
       </c>
       <c r="AG6" t="n">
-        <v>449.5554</v>
+        <v>448.8813</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1606,19 +1608,19 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>29.8</v>
+        <v>25.7</v>
       </c>
       <c r="AK6" t="n">
         <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.2</v>
+        <v>58.9</v>
       </c>
       <c r="AM6" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN6" t="n">
-        <v>378.91</v>
+        <v>367.34</v>
       </c>
       <c r="AO6" t="n">
         <v>355.9989</v>
@@ -1630,10 +1632,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-8.01</v>
+        <v>-10.91</v>
       </c>
       <c r="AS6" t="n">
-        <v>-15.61</v>
+        <v>-18.17</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1647,11 +1649,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 8.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 10.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.5</v>
+        <v>52.3</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1660,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.0%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.9%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1711,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1465228591104</v>
+        <v>1431289856000</v>
       </c>
       <c r="G7" t="n">
-        <v>21</v>
+        <v>20.52</v>
       </c>
       <c r="H7" t="n">
-        <v>15.93</v>
+        <v>15.56</v>
       </c>
       <c r="I7" t="n">
         <v>32.84</v>
@@ -1732,25 +1734,25 @@
         <v>35.61</v>
       </c>
       <c r="M7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>31.9</v>
+        <v>30.6</v>
       </c>
       <c r="P7" t="n">
-        <v>81.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="R7" t="n">
-        <v>64.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="S7" t="n">
-        <v>60.7</v>
+        <v>60.2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1764,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>577.22</v>
+        <v>563.85</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.12</v>
+        <v>-6.72</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.77</v>
+        <v>-4.93</v>
       </c>
       <c r="Z7" t="n">
-        <v>-12.01</v>
+        <v>-13.03</v>
       </c>
       <c r="AA7" t="n">
-        <v>-16.94</v>
+        <v>-18.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>27.11</v>
+        <v>25.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>36.47</v>
+        <v>36.53</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>621.3661</v>
+        <v>620.0869</v>
       </c>
       <c r="AG7" t="n">
-        <v>653.6997</v>
+        <v>652.8457</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1805,19 +1807,19 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>31.9</v>
+        <v>30.6</v>
       </c>
       <c r="AK7" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>64.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN7" t="n">
-        <v>566.455</v>
+        <v>563.85</v>
       </c>
       <c r="AO7" t="n">
         <v>525.2332</v>
@@ -1829,10 +1831,10 @@
         <v>687.9124</v>
       </c>
       <c r="AR7" t="n">
-        <v>-7.1</v>
+        <v>-9.07</v>
       </c>
       <c r="AS7" t="n">
-        <v>-11.7</v>
+        <v>-13.63</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1846,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>40.6</v>
+        <v>39.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1859,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.1%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1910,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>638945394688</v>
+        <v>638174560256</v>
       </c>
       <c r="G8" t="n">
-        <v>63.91</v>
+        <v>64.03</v>
       </c>
       <c r="H8" t="n">
-        <v>39.96</v>
+        <v>39.51</v>
       </c>
       <c r="I8" t="n">
         <v>29.71</v>
@@ -1931,7 +1933,7 @@
         <v>12.99</v>
       </c>
       <c r="M8" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1940,16 +1942,16 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3</v>
+        <v>12.7</v>
       </c>
       <c r="S8" t="n">
-        <v>59.1</v>
+        <v>60</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1963,25 +1965,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>1676</v>
+        <v>1657.8</v>
       </c>
       <c r="X8" t="n">
-        <v>25.73</v>
+        <v>23.24</v>
       </c>
       <c r="Y8" t="n">
-        <v>41.03</v>
+        <v>42.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>85.12</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>152.64</v>
+        <v>141.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>36.97</v>
+        <v>37.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>38.26</v>
+        <v>38.3</v>
       </c>
       <c r="AD8" t="n">
         <v>-44.77</v>
@@ -1990,10 +1992,10 @@
         <v>0.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>1355.7714</v>
+        <v>1364.2859</v>
       </c>
       <c r="AG8" t="n">
-        <v>1086.2272</v>
+        <v>1091.2953</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2007,13 +2009,13 @@
         <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.3</v>
+        <v>12.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AN8" t="n">
         <v>1376.4</v>
@@ -2028,10 +2030,10 @@
         <v>1676</v>
       </c>
       <c r="AR8" t="n">
-        <v>23.62</v>
+        <v>21.51</v>
       </c>
       <c r="AS8" t="n">
-        <v>54.3</v>
+        <v>51.91</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2045,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 21.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2058,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 59.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.5%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2109,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1504129843200</v>
+        <v>1521255841792</v>
       </c>
       <c r="G9" t="n">
-        <v>367.42</v>
+        <v>375.05</v>
       </c>
       <c r="H9" t="n">
-        <v>160.2</v>
+        <v>162.02</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2134,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>53.1</v>
+        <v>62.6</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2143,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>74.5</v>
+        <v>78.2</v>
       </c>
       <c r="S9" t="n">
-        <v>38.6</v>
+        <v>42.3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2160,57 +2162,57 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>400.49</v>
+        <v>405.05</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9</v>
+        <v>-2.93</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.31</v>
+        <v>10.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>-18.25</v>
+        <v>-13.31</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.6</v>
+        <v>25.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.48</v>
+        <v>16.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>57.91</v>
+        <v>57.86</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>402.4874</v>
+        <v>403.676</v>
       </c>
       <c r="AG9" t="n">
-        <v>416.9638</v>
+        <v>417.3186</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>53.1</v>
+        <v>62.6</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>74.5</v>
+        <v>78.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN9" t="n">
         <v>381.59</v>
@@ -2225,14 +2227,14 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.5</v>
+        <v>0.34</v>
       </c>
       <c r="AS9" t="n">
-        <v>-3.95</v>
+        <v>-2.94</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2246,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2255,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 38.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.5%.</t>
+          <t>TSLA: scenario base High Risk, score 42.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4266995482624</v>
+        <v>4223676710912</v>
       </c>
       <c r="G2" t="n">
-        <v>26.69</v>
+        <v>26.4</v>
       </c>
       <c r="H2" t="n">
-        <v>24.12</v>
+        <v>23.78</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -741,7 +741,7 @@
         <v>20.03</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>62.7</v>
+        <v>63.6</v>
       </c>
       <c r="Q2" t="n">
         <v>40.3</v>
       </c>
       <c r="R2" t="n">
-        <v>72.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>349.68</v>
+        <v>346.13</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.03</v>
+        <v>-10.66</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.24</v>
+        <v>14.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>14.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>102.33</v>
+        <v>108.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>42.67</v>
+        <v>43.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.92</v>
+        <v>29.86</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AF2" t="n">
-        <v>367.821</v>
+        <v>368.4026</v>
       </c>
       <c r="AG2" t="n">
-        <v>311.3296</v>
+        <v>311.9021</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
         <v>40.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>72.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="AM2" t="n">
         <v>751</v>
       </c>
       <c r="AN2" t="n">
-        <v>349.68</v>
+        <v>346.13</v>
       </c>
       <c r="AO2" t="n">
         <v>273.3367</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.93</v>
+        <v>-6.05</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.32</v>
+        <v>10.97</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>74.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.0%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4362291642368</v>
+        <v>4322488745984</v>
       </c>
       <c r="G3" t="n">
-        <v>36</v>
+        <v>35.63</v>
       </c>
       <c r="H3" t="n">
-        <v>30.94</v>
+        <v>30.65</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -946,10 +946,10 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>96.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="P3" t="n">
-        <v>42.2</v>
+        <v>43</v>
       </c>
       <c r="Q3" t="n">
         <v>42.1</v>
@@ -958,7 +958,7 @@
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>76.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>297.01</v>
+        <v>294.3</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.73</v>
+        <v>-3.51</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.88</v>
+        <v>17.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.460000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="AA3" t="n">
-        <v>51.69</v>
+        <v>47</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.41</v>
+        <v>17.35</v>
       </c>
       <c r="AC3" t="n">
         <v>26.02</v>
@@ -999,10 +999,10 @@
         <v>0.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>289.365</v>
+        <v>290.0462</v>
       </c>
       <c r="AG3" t="n">
-        <v>268.0891</v>
+        <v>268.365</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>96.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="AK3" t="n">
         <v>42.1</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.64</v>
+        <v>1.47</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.79</v>
+        <v>9.66</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>75.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.5%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5053711646720</v>
+        <v>4845168754688</v>
       </c>
       <c r="G4" t="n">
-        <v>31.95</v>
+        <v>30.63</v>
       </c>
       <c r="H4" t="n">
-        <v>16.39</v>
+        <v>15.72</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="P4" t="n">
-        <v>67.7</v>
+        <v>70.2</v>
       </c>
       <c r="Q4" t="n">
         <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>79.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="S4" t="n">
-        <v>75.7</v>
+        <v>72.7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,25 +1171,25 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>208.65</v>
+        <v>200.04</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.52</v>
+        <v>-8.76</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.96</v>
+        <v>14.02</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.21</v>
+        <v>15.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>43.61</v>
+        <v>39.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>71.06999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.97</v>
+        <v>46.98</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
@@ -1198,10 +1198,10 @@
         <v>1.51</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.62</v>
+        <v>209.8526</v>
       </c>
       <c r="AG4" t="n">
-        <v>189.8757</v>
+        <v>190.0187</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="AK4" t="n">
         <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>79.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="AM4" t="n">
         <v>751</v>
       </c>
       <c r="AN4" t="n">
-        <v>200.42</v>
+        <v>200.04</v>
       </c>
       <c r="AO4" t="n">
         <v>164.9777</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.46</v>
+        <v>-4.68</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.890000000000001</v>
+        <v>5.27</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.7% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>59</v>
+        <v>54.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 75.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.5%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 72.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.7%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2504147599360</v>
+        <v>2518346891264</v>
       </c>
       <c r="G5" t="n">
-        <v>30.15</v>
+        <v>31.81</v>
       </c>
       <c r="H5" t="n">
-        <v>23.56</v>
+        <v>23.69</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>74.2</v>
+        <v>70.8</v>
       </c>
       <c r="P5" t="n">
-        <v>59.5</v>
+        <v>57.4</v>
       </c>
       <c r="Q5" t="n">
         <v>37.9</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>63.1</v>
+        <v>63.9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1363,59 +1363,59 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>232.79</v>
+        <v>234.11</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.16</v>
+        <v>-12.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.35</v>
+        <v>11.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.21</v>
+        <v>3.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.539999999999999</v>
+        <v>11.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>21.8</v>
+        <v>22.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.19</v>
+        <v>31.18</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>257.083</v>
+        <v>256.9976</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.8377</v>
+        <v>232.8298</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>74.2</v>
+        <v>70.8</v>
       </c>
       <c r="AK5" t="n">
         <v>37.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>61.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AM5" t="n">
         <v>751</v>
@@ -1433,14 +1433,14 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-9.449999999999999</v>
+        <v>-8.91</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.02</v>
+        <v>0.55</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 63.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 63.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.9%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2728761229312</v>
+        <v>2777788973056</v>
       </c>
       <c r="G6" t="n">
-        <v>21.85</v>
+        <v>22.27</v>
       </c>
       <c r="H6" t="n">
-        <v>18.99</v>
+        <v>19.33</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1535,25 +1535,25 @@
         <v>30.27</v>
       </c>
       <c r="M6" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>25.7</v>
+        <v>28.3</v>
       </c>
       <c r="P6" t="n">
-        <v>75.7</v>
+        <v>74.7</v>
       </c>
       <c r="Q6" t="n">
         <v>44</v>
       </c>
       <c r="R6" t="n">
-        <v>58.9</v>
+        <v>61.3</v>
       </c>
       <c r="S6" t="n">
-        <v>60.2</v>
+        <v>60.9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,22 +1567,22 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>367.34</v>
+        <v>373.94</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.57</v>
+        <v>-10.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>-3.6</v>
+        <v>-2.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>-22.5</v>
+        <v>-22.39</v>
       </c>
       <c r="AA6" t="n">
-        <v>-22.9</v>
+        <v>-21.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.95</v>
+        <v>5.26</v>
       </c>
       <c r="AC6" t="n">
         <v>24.09</v>
@@ -1591,13 +1591,13 @@
         <v>-33.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>412.342</v>
+        <v>412.4194</v>
       </c>
       <c r="AG6" t="n">
-        <v>448.8813</v>
+        <v>448.2271</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,13 +1608,13 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25.7</v>
+        <v>28.3</v>
       </c>
       <c r="AK6" t="n">
         <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>58.9</v>
+        <v>61.3</v>
       </c>
       <c r="AM6" t="n">
         <v>751</v>
@@ -1632,10 +1632,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-10.91</v>
+        <v>-9.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>-18.17</v>
+        <v>-16.57</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1649,11 +1649,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 10.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>52.3</v>
+        <v>53.6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.9%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.3%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1689,12 +1689,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1704,55 +1704,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1431289856000</v>
+        <v>601559924736</v>
       </c>
       <c r="G7" t="n">
-        <v>20.52</v>
+        <v>60.43</v>
       </c>
       <c r="H7" t="n">
-        <v>15.56</v>
+        <v>37.25</v>
       </c>
       <c r="I7" t="n">
-        <v>32.84</v>
+        <v>29.71</v>
       </c>
       <c r="J7" t="n">
-        <v>32.93</v>
+        <v>52.24</v>
       </c>
       <c r="K7" t="n">
-        <v>33.1</v>
+        <v>13.2</v>
       </c>
       <c r="L7" t="n">
-        <v>35.61</v>
+        <v>12.99</v>
       </c>
       <c r="M7" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>30.6</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>82.2</v>
+        <v>11.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.8</v>
+        <v>18.2</v>
       </c>
       <c r="R7" t="n">
-        <v>61.6</v>
+        <v>16</v>
       </c>
       <c r="S7" t="n">
-        <v>60.2</v>
+        <v>60.9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,79 +1766,79 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>563.85</v>
+        <v>1655.8</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.72</v>
+        <v>17.52</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.93</v>
+        <v>47.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>-13.03</v>
+        <v>86.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>-18.69</v>
+        <v>140.32</v>
       </c>
       <c r="AB7" t="n">
-        <v>25.55</v>
+        <v>37.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>36.53</v>
+        <v>38.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>-34.15</v>
+        <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="AF7" t="n">
-        <v>620.0869</v>
+        <v>1372.058</v>
       </c>
       <c r="AG7" t="n">
-        <v>652.8457</v>
+        <v>1096.2908</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>30.6</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>28.8</v>
+        <v>18.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>61.6</v>
+        <v>16</v>
       </c>
       <c r="AM7" t="n">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="AN7" t="n">
-        <v>563.85</v>
+        <v>1376.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>525.2332</v>
+        <v>1109.5466</v>
       </c>
       <c r="AP7" t="n">
-        <v>634.7017</v>
+        <v>1676</v>
       </c>
       <c r="AQ7" t="n">
-        <v>687.9124</v>
+        <v>1676</v>
       </c>
       <c r="AR7" t="n">
-        <v>-9.07</v>
+        <v>20.68</v>
       </c>
       <c r="AS7" t="n">
-        <v>-13.63</v>
+        <v>51.04</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 20.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>39.4</v>
+        <v>12.5</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.7%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>638174560256</v>
+        <v>1427101581312</v>
       </c>
       <c r="G8" t="n">
-        <v>64.03</v>
+        <v>20.43</v>
       </c>
       <c r="H8" t="n">
-        <v>39.51</v>
+        <v>15.51</v>
       </c>
       <c r="I8" t="n">
-        <v>29.71</v>
+        <v>32.84</v>
       </c>
       <c r="J8" t="n">
-        <v>52.24</v>
+        <v>32.93</v>
       </c>
       <c r="K8" t="n">
-        <v>13.2</v>
+        <v>33.1</v>
       </c>
       <c r="L8" t="n">
-        <v>12.99</v>
+        <v>35.61</v>
       </c>
       <c r="M8" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8</v>
+        <v>82.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.2</v>
+        <v>28.9</v>
       </c>
       <c r="R8" t="n">
-        <v>12.7</v>
+        <v>61.5</v>
       </c>
       <c r="S8" t="n">
-        <v>60</v>
+        <v>59.4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,79 +1965,79 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>1657.8</v>
+        <v>562.2</v>
       </c>
       <c r="X8" t="n">
-        <v>23.24</v>
+        <v>-7.35</v>
       </c>
       <c r="Y8" t="n">
-        <v>42.18</v>
+        <v>-6.84</v>
       </c>
       <c r="Z8" t="n">
-        <v>90.34999999999999</v>
+        <v>-15.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>141.69</v>
+        <v>-17.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>37.23</v>
+        <v>26.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>38.3</v>
+        <v>36.47</v>
       </c>
       <c r="AD8" t="n">
-        <v>-44.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.97</v>
+        <v>0.74</v>
       </c>
       <c r="AF8" t="n">
-        <v>1364.2859</v>
+        <v>618.7454</v>
       </c>
       <c r="AG8" t="n">
-        <v>1091.2953</v>
+        <v>651.9257</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.2</v>
+        <v>28.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>12.7</v>
+        <v>61.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="AN8" t="n">
-        <v>1376.4</v>
+        <v>562.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>1109.5466</v>
+        <v>525.2332</v>
       </c>
       <c r="AP8" t="n">
-        <v>1676</v>
+        <v>634.7017</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1676</v>
+        <v>687.9124</v>
       </c>
       <c r="AR8" t="n">
-        <v>21.51</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>51.91</v>
+        <v>-13.76</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 21.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>9.800000000000001</v>
+        <v>38.5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2100,174 +2100,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1521255841792</v>
-      </c>
-      <c r="G9" t="n">
-        <v>375.05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>162.02</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>62.6</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>405.05</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-2.93</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-13.31</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>16.55</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>403.676</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>417.3186</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>62.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL9" t="n">
         <v>0</v>
       </c>
-      <c r="AL9" t="n">
-        <v>78.2</v>
-      </c>
       <c r="AM9" t="n">
-        <v>751</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>381.59</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>343.25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-2.94</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>36</v>
+        <v>32.3</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 42.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2277,19 +2227,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2297,124 +2247,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1433221726208</v>
+      </c>
+      <c r="G10" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>152.65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>50</v>
-      </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-21.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>404.3292</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>417.534</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>100</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>66.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+        <v>751</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>442.1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-8.6</v>
+      </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo 5.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>32.3</v>
+        <v>26.8</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 35.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4223676710912</v>
+        <v>4213426356224</v>
       </c>
       <c r="G2" t="n">
-        <v>26.4</v>
+        <v>26.32</v>
       </c>
       <c r="H2" t="n">
-        <v>23.78</v>
+        <v>23.73</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
       <c r="Q2" t="n">
         <v>40.3</v>
       </c>
       <c r="R2" t="n">
-        <v>70.7</v>
+        <v>70.2</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>346.13</v>
+        <v>345.29</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.66</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.66</v>
+        <v>18.96</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.59</v>
+        <v>12.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.3</v>
+        <v>109.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.78</v>
+        <v>43.59</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.86</v>
+        <v>29.84</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF2" t="n">
-        <v>368.4026</v>
+        <v>368.886</v>
       </c>
       <c r="AG2" t="n">
-        <v>311.9021</v>
+        <v>312.4569</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
         <v>40.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>70.7</v>
+        <v>70.2</v>
       </c>
       <c r="AM2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
-        <v>346.13</v>
+        <v>345.29</v>
       </c>
       <c r="AO2" t="n">
         <v>273.3367</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-6.05</v>
+        <v>-6.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.97</v>
+        <v>10.51</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 6.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.0%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4322488745984</v>
+        <v>4304570155008</v>
       </c>
       <c r="G3" t="n">
-        <v>35.63</v>
+        <v>35.44</v>
       </c>
       <c r="H3" t="n">
-        <v>30.65</v>
+        <v>30.5</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -940,16 +940,16 @@
         <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>90.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="Q3" t="n">
         <v>42.1</v>
@@ -958,7 +958,7 @@
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>75.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>294.3</v>
+        <v>293.08</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.51</v>
+        <v>-5.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.13</v>
+        <v>16.58</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.32</v>
+        <v>7.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>47</v>
+        <v>46.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.35</v>
+        <v>17.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.02</v>
+        <v>26</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="AF3" t="n">
-        <v>290.0462</v>
+        <v>290.7286</v>
       </c>
       <c r="AG3" t="n">
-        <v>268.365</v>
+        <v>268.6354</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>90.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AK3" t="n">
         <v>42.1</v>
@@ -1022,7 +1022,7 @@
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>290.55</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.47</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.66</v>
+        <v>9.1</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>74.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.5%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4845168754688</v>
+        <v>4819978813440</v>
       </c>
       <c r="G4" t="n">
-        <v>30.63</v>
+        <v>30.52</v>
       </c>
       <c r="H4" t="n">
-        <v>15.72</v>
+        <v>15.63</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>88.5</v>
+        <v>84.8</v>
       </c>
       <c r="P4" t="n">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>72.7</v>
+        <v>71.7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>200.04</v>
+        <v>199</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.76</v>
+        <v>-7.48</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.02</v>
+        <v>13.72</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.01</v>
+        <v>10.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>39.25</v>
+        <v>38.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>70.83</v>
+        <v>70.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.98</v>
+        <v>46.95</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.8526</v>
+        <v>210.0508</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.0187</v>
+        <v>190.1797</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>88.5</v>
+        <v>84.8</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>200.04</v>
+        <v>199</v>
       </c>
       <c r="AO4" t="n">
         <v>164.9777</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-4.68</v>
+        <v>-5.26</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.27</v>
+        <v>4.64</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 4.7% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>54.3</v>
+        <v>53.1</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 72.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.7%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2518346891264</v>
+        <v>2520068128768</v>
       </c>
       <c r="G5" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="H5" t="n">
-        <v>23.69</v>
+        <v>23.71</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>70.8</v>
+        <v>73.2</v>
       </c>
       <c r="P5" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
       <c r="Q5" t="n">
         <v>37.9</v>
       </c>
       <c r="R5" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="S5" t="n">
-        <v>63.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,25 +1368,25 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>234.11</v>
+        <v>234.27</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.8</v>
+        <v>-12.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.41</v>
+        <v>13.04</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.65</v>
+        <v>12.38</v>
       </c>
       <c r="AB5" t="n">
         <v>22.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.18</v>
+        <v>31.16</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
@@ -1395,10 +1395,10 @@
         <v>0.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>256.9976</v>
+        <v>256.8852</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.8298</v>
+        <v>232.8395</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,22 +1409,22 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>70.8</v>
+        <v>73.2</v>
       </c>
       <c r="AK5" t="n">
         <v>37.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
         <v>232.79</v>
       </c>
       <c r="AO5" t="n">
-        <v>199.34</v>
+        <v>200.95</v>
       </c>
       <c r="AP5" t="n">
         <v>274</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-8.91</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 8.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>61.7</v>
+        <v>62.4</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 63.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.9%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 64.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.8%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 199.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 200.95 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1510,50 +1510,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2777788973056</v>
+        <v>598862004224</v>
       </c>
       <c r="G6" t="n">
-        <v>22.27</v>
+        <v>59.97</v>
       </c>
       <c r="H6" t="n">
-        <v>19.33</v>
+        <v>37.08</v>
       </c>
       <c r="I6" t="n">
-        <v>39.34</v>
+        <v>29.71</v>
       </c>
       <c r="J6" t="n">
-        <v>34.01</v>
+        <v>52.24</v>
       </c>
       <c r="K6" t="n">
-        <v>18.3</v>
+        <v>13.2</v>
       </c>
       <c r="L6" t="n">
-        <v>30.27</v>
+        <v>12.99</v>
       </c>
       <c r="M6" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>28.3</v>
+        <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>74.7</v>
+        <v>11.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>18.1</v>
       </c>
       <c r="R6" t="n">
-        <v>61.3</v>
+        <v>45.7</v>
       </c>
       <c r="S6" t="n">
-        <v>60.9</v>
+        <v>63.9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,98 +1562,98 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>373.94</v>
+        <v>1560.8</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.77</v>
+        <v>9.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.15</v>
+        <v>33.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>-22.39</v>
+        <v>73.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>-21.05</v>
+        <v>132.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.26</v>
+        <v>34.84</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.09</v>
+        <v>38.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>-33.91</v>
+        <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.22</v>
+        <v>0.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>412.4194</v>
+        <v>1378.1336</v>
       </c>
       <c r="AG6" t="n">
-        <v>448.2271</v>
+        <v>1100.7298</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28.3</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>44</v>
+        <v>18.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>61.3</v>
+        <v>45.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="AN6" t="n">
-        <v>367.34</v>
+        <v>1376.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>355.9989</v>
+        <v>1109.5466</v>
       </c>
       <c r="AP6" t="n">
-        <v>460.52</v>
+        <v>1676</v>
       </c>
       <c r="AQ6" t="n">
-        <v>460.52</v>
+        <v>1676</v>
       </c>
       <c r="AR6" t="n">
-        <v>-9.33</v>
+        <v>13.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>-16.57</v>
+        <v>41.8</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 9.3% sotto MA50: attendere recupero</t>
+          <t>prezzo 13.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>53.6</v>
+        <v>34.6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.3%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 63.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.2%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1709,50 +1709,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>601559924736</v>
+        <v>2714795769856</v>
       </c>
       <c r="G7" t="n">
-        <v>60.43</v>
+        <v>21.77</v>
       </c>
       <c r="H7" t="n">
-        <v>37.25</v>
+        <v>18.89</v>
       </c>
       <c r="I7" t="n">
-        <v>29.71</v>
+        <v>39.34</v>
       </c>
       <c r="J7" t="n">
-        <v>52.24</v>
+        <v>34.01</v>
       </c>
       <c r="K7" t="n">
-        <v>13.2</v>
+        <v>18.3</v>
       </c>
       <c r="L7" t="n">
-        <v>12.99</v>
+        <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>26.8</v>
       </c>
       <c r="P7" t="n">
-        <v>11.1</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.2</v>
+        <v>43.9</v>
       </c>
       <c r="R7" t="n">
-        <v>16</v>
+        <v>58.3</v>
       </c>
       <c r="S7" t="n">
-        <v>60.9</v>
+        <v>60.4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,98 +1761,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1655.8</v>
+        <v>365.46</v>
       </c>
       <c r="X7" t="n">
-        <v>17.52</v>
+        <v>-12.69</v>
       </c>
       <c r="Y7" t="n">
-        <v>47.09</v>
+        <v>-1.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>86.14</v>
+        <v>-24.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>140.32</v>
+        <v>-24.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>37.95</v>
+        <v>4.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.29</v>
+        <v>24.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>-44.77</v>
+        <v>-33.91</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.99</v>
+        <v>0.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>1372.058</v>
+        <v>412.0578</v>
       </c>
       <c r="AG7" t="n">
-        <v>1096.2908</v>
+        <v>447.595</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>100</v>
+        <v>26.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.2</v>
+        <v>43.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>16</v>
+        <v>58.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
-        <v>1376.4</v>
+        <v>365.46</v>
       </c>
       <c r="AO7" t="n">
-        <v>1109.5466</v>
+        <v>358.1842</v>
       </c>
       <c r="AP7" t="n">
-        <v>1676</v>
+        <v>460.52</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1676</v>
+        <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>20.68</v>
+        <v>-11.31</v>
       </c>
       <c r="AS7" t="n">
-        <v>51.04</v>
+        <v>-18.35</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 20.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 11.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>12.5</v>
+        <v>52.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.7%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.3%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 358.18 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1427101581312</v>
+        <v>1415602503680</v>
       </c>
       <c r="G8" t="n">
-        <v>20.43</v>
+        <v>20.29</v>
       </c>
       <c r="H8" t="n">
-        <v>15.51</v>
+        <v>15.39</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
       <c r="P8" t="n">
-        <v>82.3</v>
+        <v>82.7</v>
       </c>
       <c r="Q8" t="n">
         <v>28.9</v>
       </c>
       <c r="R8" t="n">
-        <v>61.5</v>
+        <v>60.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>562.2</v>
+        <v>557.67</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.35</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.84</v>
+        <v>-5.86</v>
       </c>
       <c r="Z8" t="n">
-        <v>-15.24</v>
+        <v>-15.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>-17.34</v>
+        <v>-19.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.96</v>
+        <v>26.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.47</v>
+        <v>36.45</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="AF8" t="n">
-        <v>618.7454</v>
+        <v>617.2199000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>651.9257</v>
+        <v>650.9641</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,22 +2006,22 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
       <c r="AK8" t="n">
         <v>28.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>61.5</v>
+        <v>60.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
-        <v>562.2</v>
+        <v>557.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>525.2332</v>
+        <v>535.8834000000001</v>
       </c>
       <c r="AP8" t="n">
         <v>634.7017</v>
@@ -2030,10 +2030,10 @@
         <v>687.9124</v>
       </c>
       <c r="AR8" t="n">
-        <v>-9.140000000000001</v>
+        <v>-9.65</v>
       </c>
       <c r="AS8" t="n">
-        <v>-13.76</v>
+        <v>-14.33</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.7%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 535.88 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1433221726208</v>
+        <v>1410386886656</v>
       </c>
       <c r="G10" t="n">
-        <v>350.1</v>
+        <v>338.32</v>
       </c>
       <c r="H10" t="n">
-        <v>152.65</v>
+        <v>150.21</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>42.3</v>
+        <v>36</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>66.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>381.61</v>
+        <v>375.53</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.67</v>
+        <v>-11.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2</v>
+        <v>-1.96</v>
       </c>
       <c r="Z10" t="n">
-        <v>-21.05</v>
+        <v>-21.96</v>
       </c>
       <c r="AA10" t="n">
-        <v>18.45</v>
+        <v>7.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.67</v>
+        <v>16.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>57.85</v>
+        <v>57.82</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>404.3292</v>
+        <v>404.7914</v>
       </c>
       <c r="AG10" t="n">
-        <v>417.534</v>
+        <v>417.6574</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,19 +2350,19 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42.3</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>66.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AM10" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN10" t="n">
-        <v>381.59</v>
+        <v>375.53</v>
       </c>
       <c r="AO10" t="n">
         <v>343.25</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-5.62</v>
+        <v>-7.23</v>
       </c>
       <c r="AS10" t="n">
-        <v>-8.6</v>
+        <v>-10.09</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 5.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>26.8</v>
+        <v>24.5</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 35.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
+          <t>TSLA: scenario base High Risk, score 33.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4213426356224</v>
+        <v>4194146189312</v>
       </c>
       <c r="G2" t="n">
-        <v>26.32</v>
+        <v>26.2</v>
       </c>
       <c r="H2" t="n">
-        <v>23.73</v>
+        <v>23.62</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>63.7</v>
+        <v>64</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="R2" t="n">
-        <v>70.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>345.29</v>
+        <v>343.71</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.789999999999999</v>
+        <v>-11.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.96</v>
+        <v>18.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.56</v>
+        <v>11.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.62</v>
+        <v>106.69</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.59</v>
+        <v>43.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.84</v>
+        <v>29.82</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>368.886</v>
+        <v>369.106</v>
       </c>
       <c r="AG2" t="n">
-        <v>312.4569</v>
+        <v>313.0075</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -817,19 +817,19 @@
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>70.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
-        <v>345.29</v>
+        <v>343.71</v>
       </c>
       <c r="AO2" t="n">
-        <v>273.3367</v>
+        <v>287.3883</v>
       </c>
       <c r="AP2" t="n">
         <v>389.8971</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-6.4</v>
+        <v>-6.88</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.51</v>
+        <v>9.81</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 6.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>74</v>
+        <v>73.8</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.9%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 287.39 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4304570155008</v>
+        <v>4041225797632</v>
       </c>
       <c r="G3" t="n">
-        <v>35.44</v>
+        <v>33.31</v>
       </c>
       <c r="H3" t="n">
-        <v>30.5</v>
+        <v>28.63</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>89.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>43.5</v>
+        <v>48.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="R3" t="n">
-        <v>82.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>74.8</v>
+        <v>69.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,68 +967,68 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>293.08</v>
+        <v>275.15</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.1</v>
+        <v>-10.76</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.58</v>
+        <v>9.02</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.29</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.03</v>
+        <v>37.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.16</v>
+        <v>14.68</v>
       </c>
       <c r="AC3" t="n">
-        <v>26</v>
+        <v>26.23</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>290.7286</v>
+        <v>291.0597</v>
       </c>
       <c r="AG3" t="n">
-        <v>268.6354</v>
+        <v>268.8251</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>89.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>82.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
-        <v>290.55</v>
+        <v>275.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>246.403</v>
+        <v>253.2667</v>
       </c>
       <c r="AP3" t="n">
         <v>315.2</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.8100000000000001</v>
+        <v>-5.47</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.1</v>
+        <v>2.35</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>74</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 69.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.5%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 253.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4819978813440</v>
+        <v>4741018419200</v>
       </c>
       <c r="G4" t="n">
-        <v>30.52</v>
+        <v>29.98</v>
       </c>
       <c r="H4" t="n">
-        <v>15.63</v>
+        <v>15.38</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1145,19 +1145,19 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>84.8</v>
+        <v>75.7</v>
       </c>
       <c r="P4" t="n">
-        <v>70.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>71.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="S4" t="n">
-        <v>71.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>199</v>
+        <v>195.74</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.48</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.72</v>
+        <v>9.68</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.08</v>
+        <v>6.69</v>
       </c>
       <c r="AA4" t="n">
-        <v>38.22</v>
+        <v>32.52</v>
       </c>
       <c r="AB4" t="n">
-        <v>70.41</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.95</v>
+        <v>46.93</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF4" t="n">
-        <v>210.0508</v>
+        <v>210.04</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.1797</v>
+        <v>190.318</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,22 +1212,22 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>84.8</v>
+        <v>75.7</v>
       </c>
       <c r="AK4" t="n">
         <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>71.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN4" t="n">
-        <v>199</v>
+        <v>195.74</v>
       </c>
       <c r="AO4" t="n">
-        <v>164.9777</v>
+        <v>174.197</v>
       </c>
       <c r="AP4" t="n">
         <v>224.0988</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-5.26</v>
+        <v>-6.81</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.64</v>
+        <v>2.85</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>53.1</v>
+        <v>50.1</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 69.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 174.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,53 +1308,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2520068128768</v>
+        <v>614355763200</v>
       </c>
       <c r="G5" t="n">
-        <v>31.66</v>
+        <v>61.81</v>
       </c>
       <c r="H5" t="n">
-        <v>23.71</v>
+        <v>38.04</v>
       </c>
       <c r="I5" t="n">
-        <v>12.22</v>
+        <v>29.71</v>
       </c>
       <c r="J5" t="n">
-        <v>24.29</v>
+        <v>52.24</v>
       </c>
       <c r="K5" t="n">
-        <v>16.6</v>
+        <v>13.2</v>
       </c>
       <c r="L5" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>12.99</v>
+      </c>
+      <c r="M5" t="n">
+        <v>70</v>
+      </c>
       <c r="N5" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>73.2</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>57.6</v>
+        <v>9.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>37.9</v>
+        <v>18.1</v>
       </c>
       <c r="R5" t="n">
-        <v>66.5</v>
+        <v>40.3</v>
       </c>
       <c r="S5" t="n">
-        <v>64.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1363,98 +1365,98 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>234.27</v>
+        <v>1594</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.03</v>
+        <v>15.81</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.04</v>
+        <v>31.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.04</v>
+        <v>77.11</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.38</v>
+        <v>137.12</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.67</v>
+        <v>35.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.16</v>
+        <v>38.41</v>
       </c>
       <c r="AD5" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="AF5" t="n">
-        <v>256.8852</v>
+        <v>1390.9165</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.8395</v>
+        <v>1109.6879</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>73.2</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>37.9</v>
+        <v>18.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>66.5</v>
+        <v>40.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="AN5" t="n">
-        <v>232.79</v>
+        <v>1384.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>200.95</v>
+        <v>1111.3427</v>
       </c>
       <c r="AP5" t="n">
-        <v>274</v>
+        <v>1676</v>
       </c>
       <c r="AQ5" t="n">
-        <v>274.99</v>
+        <v>1676</v>
       </c>
       <c r="AR5" t="n">
-        <v>-8.800000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.61</v>
+        <v>43.64</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 14.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>62.4</v>
+        <v>30.5</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 64.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.8%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.6%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 200.95 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1505,55 +1507,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>598862004224</v>
+        <v>2441971499008</v>
       </c>
       <c r="G6" t="n">
-        <v>59.97</v>
+        <v>30.68</v>
       </c>
       <c r="H6" t="n">
-        <v>37.08</v>
+        <v>22.98</v>
       </c>
       <c r="I6" t="n">
-        <v>29.71</v>
+        <v>12.22</v>
       </c>
       <c r="J6" t="n">
-        <v>52.24</v>
+        <v>24.29</v>
       </c>
       <c r="K6" t="n">
-        <v>13.2</v>
+        <v>16.6</v>
       </c>
       <c r="L6" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="M6" t="n">
-        <v>69</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>61.4</v>
       </c>
       <c r="P6" t="n">
-        <v>11.3</v>
+        <v>59.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.1</v>
+        <v>37.9</v>
       </c>
       <c r="R6" t="n">
-        <v>45.7</v>
+        <v>58</v>
       </c>
       <c r="S6" t="n">
-        <v>63.9</v>
+        <v>59.7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,98 +1562,98 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1560.8</v>
+        <v>227.01</v>
       </c>
       <c r="X6" t="n">
-        <v>9.1</v>
+        <v>-14.43</v>
       </c>
       <c r="Y6" t="n">
-        <v>33.08</v>
+        <v>7.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>73.73</v>
+        <v>-0.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>132.25</v>
+        <v>6.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>34.84</v>
+        <v>21.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>38.43</v>
+        <v>31.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>-44.77</v>
+        <v>-30.88</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="AF6" t="n">
-        <v>1378.1336</v>
+        <v>256.445</v>
       </c>
       <c r="AG6" t="n">
-        <v>1100.7298</v>
+        <v>232.7954</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>100</v>
+        <v>61.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>18.1</v>
+        <v>37.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>45.7</v>
+        <v>58</v>
       </c>
       <c r="AM6" t="n">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="AN6" t="n">
-        <v>1376.4</v>
+        <v>227.01</v>
       </c>
       <c r="AO6" t="n">
-        <v>1109.5466</v>
+        <v>208.27</v>
       </c>
       <c r="AP6" t="n">
-        <v>1676</v>
+        <v>274</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1676</v>
+        <v>274.99</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.25</v>
+        <v>-11.48</v>
       </c>
       <c r="AS6" t="n">
-        <v>41.8</v>
+        <v>-2.49</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 13.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 11.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>34.6</v>
+        <v>56.3</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 63.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 59.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 208.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2714795769856</v>
+        <v>2620974694400</v>
       </c>
       <c r="G7" t="n">
-        <v>21.77</v>
+        <v>21.04</v>
       </c>
       <c r="H7" t="n">
-        <v>18.89</v>
+        <v>18.22</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1734,25 +1734,25 @@
         <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>26.8</v>
+        <v>20.4</v>
       </c>
       <c r="P7" t="n">
-        <v>75.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>43.9</v>
+        <v>43.4</v>
       </c>
       <c r="R7" t="n">
-        <v>58.3</v>
+        <v>53.9</v>
       </c>
       <c r="S7" t="n">
-        <v>60.4</v>
+        <v>58.6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>365.46</v>
+        <v>352.83</v>
       </c>
       <c r="X7" t="n">
-        <v>-12.69</v>
+        <v>-15.19</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.74</v>
+        <v>-4.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>-24.46</v>
+        <v>-26.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>-24.2</v>
+        <v>-27.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.44</v>
+        <v>3.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.11</v>
+        <v>24.18</v>
       </c>
       <c r="AD7" t="n">
-        <v>-33.91</v>
+        <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>412.0578</v>
+        <v>411.2692</v>
       </c>
       <c r="AG7" t="n">
-        <v>447.595</v>
+        <v>446.8838</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,22 +1807,22 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26.8</v>
+        <v>20.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>43.9</v>
+        <v>43.4</v>
       </c>
       <c r="AL7" t="n">
-        <v>58.3</v>
+        <v>53.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
-        <v>365.46</v>
+        <v>352.83</v>
       </c>
       <c r="AO7" t="n">
-        <v>358.1842</v>
+        <v>352.83</v>
       </c>
       <c r="AP7" t="n">
         <v>460.52</v>
@@ -1831,10 +1831,10 @@
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-11.31</v>
+        <v>-14.21</v>
       </c>
       <c r="AS7" t="n">
-        <v>-18.35</v>
+        <v>-21.05</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 11.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 14.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>52.4</v>
+        <v>49.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.3%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 58.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -14.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 358.18 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1415602503680</v>
+        <v>1378033860608</v>
       </c>
       <c r="G8" t="n">
-        <v>20.29</v>
+        <v>19.75</v>
       </c>
       <c r="H8" t="n">
-        <v>15.39</v>
+        <v>14.98</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1933,25 +1933,25 @@
         <v>35.61</v>
       </c>
       <c r="M8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>27.7</v>
+        <v>21.3</v>
       </c>
       <c r="P8" t="n">
-        <v>82.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>28.9</v>
       </c>
       <c r="R8" t="n">
-        <v>60.8</v>
+        <v>57.7</v>
       </c>
       <c r="S8" t="n">
-        <v>59.5</v>
+        <v>57.9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>557.67</v>
+        <v>542.87</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.529999999999999</v>
+        <v>-11.26</v>
       </c>
       <c r="Y8" t="n">
-        <v>-5.86</v>
+        <v>-8.66</v>
       </c>
       <c r="Z8" t="n">
-        <v>-15.2</v>
+        <v>-17.79</v>
       </c>
       <c r="AA8" t="n">
-        <v>-19.9</v>
+        <v>-23.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.57</v>
+        <v>25.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.45</v>
+        <v>36.46</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>617.2199000000001</v>
+        <v>614.8398</v>
       </c>
       <c r="AG8" t="n">
-        <v>650.9641</v>
+        <v>649.9292</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,22 +2006,22 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27.7</v>
+        <v>21.3</v>
       </c>
       <c r="AK8" t="n">
         <v>28.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>60.8</v>
+        <v>57.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
-        <v>557.67</v>
+        <v>542.87</v>
       </c>
       <c r="AO8" t="n">
-        <v>535.8834000000001</v>
+        <v>542.87</v>
       </c>
       <c r="AP8" t="n">
         <v>634.7017</v>
@@ -2030,10 +2030,10 @@
         <v>687.9124</v>
       </c>
       <c r="AR8" t="n">
-        <v>-9.65</v>
+        <v>-11.71</v>
       </c>
       <c r="AS8" t="n">
-        <v>-14.33</v>
+        <v>-16.47</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 9.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 11.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>38.5</v>
+        <v>36</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.7%.</t>
+          <t>META: scenario base Hold / Monitor, score 57.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.7%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 535.88 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1410386886656</v>
+        <v>1408847052800</v>
       </c>
       <c r="G10" t="n">
-        <v>338.32</v>
+        <v>344.15</v>
       </c>
       <c r="H10" t="n">
-        <v>150.21</v>
+        <v>150.04</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>36</v>
+        <v>34.7</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>64.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="S10" t="n">
-        <v>33.3</v>
+        <v>32.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,25 +2309,25 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>375.53</v>
+        <v>375.12</v>
       </c>
       <c r="X10" t="n">
-        <v>-11.85</v>
+        <v>-13.49</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.96</v>
+        <v>-2.81</v>
       </c>
       <c r="Z10" t="n">
-        <v>-21.96</v>
+        <v>-23.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.7</v>
+        <v>10.18</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.02</v>
+        <v>15.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>57.82</v>
+        <v>57.78</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
@@ -2336,10 +2336,10 @@
         <v>0.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>404.7914</v>
+        <v>405.0098</v>
       </c>
       <c r="AG10" t="n">
-        <v>417.6574</v>
+        <v>417.801</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,19 +2350,19 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>36</v>
+        <v>34.7</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>64.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="AM10" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN10" t="n">
-        <v>375.53</v>
+        <v>375.12</v>
       </c>
       <c r="AO10" t="n">
         <v>343.25</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-7.23</v>
+        <v>-7.38</v>
       </c>
       <c r="AS10" t="n">
-        <v>-10.09</v>
+        <v>-10.22</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 7.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 33.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
+          <t>TSLA: scenario base High Risk, score 32.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4194146189312</v>
+        <v>4117026308096</v>
       </c>
       <c r="G2" t="n">
-        <v>26.2</v>
+        <v>25.75</v>
       </c>
       <c r="H2" t="n">
-        <v>23.62</v>
+        <v>23.18</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -741,7 +741,7 @@
         <v>20.03</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>64</v>
+        <v>65.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="R2" t="n">
-        <v>69.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>343.71</v>
+        <v>337.39</v>
       </c>
       <c r="X2" t="n">
-        <v>-11.56</v>
+        <v>-13.18</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.21</v>
+        <v>20.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.1</v>
+        <v>7.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>106.69</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.3</v>
+        <v>42.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.82</v>
+        <v>29.84</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF2" t="n">
-        <v>369.106</v>
+        <v>369.1154</v>
       </c>
       <c r="AG2" t="n">
-        <v>313.0075</v>
+        <v>313.4987</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -817,31 +817,31 @@
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>69.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AM2" t="n">
         <v>753</v>
       </c>
       <c r="AN2" t="n">
-        <v>343.71</v>
+        <v>337.39</v>
       </c>
       <c r="AO2" t="n">
-        <v>287.3883</v>
+        <v>295.5934</v>
       </c>
       <c r="AP2" t="n">
-        <v>389.8971</v>
+        <v>380.1129</v>
       </c>
       <c r="AQ2" t="n">
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-6.88</v>
+        <v>-8.59</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.81</v>
+        <v>7.62</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 6.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>73.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.9%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.6%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 287.39 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 295.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4041225797632</v>
+        <v>4167977926656</v>
       </c>
       <c r="G3" t="n">
-        <v>33.31</v>
+        <v>34.4</v>
       </c>
       <c r="H3" t="n">
-        <v>28.63</v>
+        <v>29.53</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -940,25 +940,25 @@
         <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>73.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="P3" t="n">
-        <v>48.6</v>
+        <v>46.1</v>
       </c>
       <c r="Q3" t="n">
         <v>41.8</v>
       </c>
       <c r="R3" t="n">
-        <v>71.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="S3" t="n">
-        <v>69.5</v>
+        <v>71.3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>275.15</v>
+        <v>283.78</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.76</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.02</v>
+        <v>12.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>4.39</v>
       </c>
       <c r="AA3" t="n">
-        <v>37.91</v>
+        <v>41.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.68</v>
+        <v>15.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.23</v>
+        <v>26.28</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="AF3" t="n">
-        <v>291.0597</v>
+        <v>291.4116</v>
       </c>
       <c r="AG3" t="n">
-        <v>268.8251</v>
+        <v>269.0755</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>73.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AK3" t="n">
         <v>41.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>71.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="AM3" t="n">
         <v>753</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>-5.47</v>
+        <v>-2.62</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.35</v>
+        <v>5.46</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 5.5% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>66.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 69.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.5%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 71.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.6%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4741018419200</v>
+        <v>4663269130240</v>
       </c>
       <c r="G4" t="n">
-        <v>29.98</v>
+        <v>29.44</v>
       </c>
       <c r="H4" t="n">
-        <v>15.38</v>
+        <v>15.13</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>75.7</v>
+        <v>75</v>
       </c>
       <c r="P4" t="n">
-        <v>71.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>69.5</v>
+        <v>67.3</v>
       </c>
       <c r="S4" t="n">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195.74</v>
+        <v>192.53</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.68</v>
+        <v>12.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.69</v>
+        <v>1.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>32.52</v>
+        <v>24.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>69.34999999999999</v>
+        <v>66.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.93</v>
+        <v>46.92</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AF4" t="n">
-        <v>210.04</v>
+        <v>209.9179</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.318</v>
+        <v>190.428</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,22 +1212,22 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75.7</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="n">
         <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>69.5</v>
+        <v>67.3</v>
       </c>
       <c r="AM4" t="n">
         <v>753</v>
       </c>
       <c r="AN4" t="n">
-        <v>195.74</v>
+        <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>174.197</v>
+        <v>175.5454</v>
       </c>
       <c r="AP4" t="n">
         <v>224.0988</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-6.81</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.85</v>
+        <v>1.1</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>50.1</v>
+        <v>49.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 69.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 69.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 174.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 175.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>614355763200</v>
+        <v>608266158080</v>
       </c>
       <c r="G5" t="n">
-        <v>61.81</v>
+        <v>61.12</v>
       </c>
       <c r="H5" t="n">
-        <v>38.04</v>
+        <v>37.51</v>
       </c>
       <c r="I5" t="n">
         <v>29.71</v>
@@ -1338,7 +1338,7 @@
         <v>12.99</v>
       </c>
       <c r="M5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -1347,16 +1347,16 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>9.9</v>
+        <v>10.7</v>
       </c>
       <c r="Q5" t="n">
         <v>18.1</v>
       </c>
       <c r="R5" t="n">
-        <v>40.3</v>
+        <v>47.2</v>
       </c>
       <c r="S5" t="n">
-        <v>63.1</v>
+        <v>64</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1594</v>
+        <v>1578.2</v>
       </c>
       <c r="X5" t="n">
-        <v>15.81</v>
+        <v>13.46</v>
       </c>
       <c r="Y5" t="n">
-        <v>31.85</v>
+        <v>35.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>77.11</v>
+        <v>76.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>137.12</v>
+        <v>138.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>35.67</v>
+        <v>35.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>38.41</v>
+        <v>38.39</v>
       </c>
       <c r="AD5" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>1390.9165</v>
+        <v>1398.0824</v>
       </c>
       <c r="AG5" t="n">
-        <v>1109.6879</v>
+        <v>1114.1671</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         <v>18.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>40.3</v>
+        <v>47.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN5" t="n">
-        <v>1384.8</v>
+        <v>1394</v>
       </c>
       <c r="AO5" t="n">
         <v>1111.3427</v>
@@ -1435,10 +1435,10 @@
         <v>1676</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.6</v>
+        <v>12.88</v>
       </c>
       <c r="AS5" t="n">
-        <v>43.64</v>
+        <v>41.65</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 14.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 12.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>30.5</v>
+        <v>35.7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.9%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1492,12 +1492,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,53 +1507,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2441971499008</v>
+        <v>2770583420928</v>
       </c>
       <c r="G6" t="n">
-        <v>30.68</v>
+        <v>22.21</v>
       </c>
       <c r="H6" t="n">
-        <v>22.98</v>
+        <v>19.26</v>
       </c>
       <c r="I6" t="n">
-        <v>12.22</v>
+        <v>39.34</v>
       </c>
       <c r="J6" t="n">
-        <v>24.29</v>
+        <v>34.01</v>
       </c>
       <c r="K6" t="n">
-        <v>16.6</v>
+        <v>18.3</v>
       </c>
       <c r="L6" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>30.27</v>
+      </c>
+      <c r="M6" t="n">
+        <v>103</v>
+      </c>
       <c r="N6" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>61.4</v>
+        <v>33.2</v>
       </c>
       <c r="P6" t="n">
-        <v>59.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>37.9</v>
+        <v>43.1</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>61.5</v>
       </c>
       <c r="S6" t="n">
-        <v>59.7</v>
+        <v>62</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>227.01</v>
+        <v>372.97</v>
       </c>
       <c r="X6" t="n">
-        <v>-14.43</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.23</v>
+        <v>2.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.62</v>
+        <v>-23.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.69</v>
+        <v>-23.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>21.35</v>
+        <v>4.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>31.19</v>
+        <v>24.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>-30.88</v>
+        <v>-34.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.68</v>
+        <v>0.19</v>
       </c>
       <c r="AF6" t="n">
-        <v>256.445</v>
+        <v>410.522</v>
       </c>
       <c r="AG6" t="n">
-        <v>232.7954</v>
+        <v>446.2723</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,34 +1610,34 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>61.4</v>
+        <v>33.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>37.9</v>
+        <v>43.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>58</v>
+        <v>61.5</v>
       </c>
       <c r="AM6" t="n">
         <v>753</v>
       </c>
       <c r="AN6" t="n">
-        <v>227.01</v>
+        <v>352.83</v>
       </c>
       <c r="AO6" t="n">
-        <v>208.27</v>
+        <v>352.83</v>
       </c>
       <c r="AP6" t="n">
-        <v>274</v>
+        <v>460.52</v>
       </c>
       <c r="AQ6" t="n">
-        <v>274.99</v>
+        <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-11.48</v>
+        <v>-9.15</v>
       </c>
       <c r="AS6" t="n">
-        <v>-2.49</v>
+        <v>-16.43</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1649,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 11.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>56.3</v>
+        <v>54.7</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1664,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 59.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.5%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.2%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 208.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1684,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1704,55 +1706,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2620974694400</v>
+        <v>2503072022528</v>
       </c>
       <c r="G7" t="n">
-        <v>21.04</v>
+        <v>32.45</v>
       </c>
       <c r="H7" t="n">
-        <v>18.22</v>
+        <v>23.55</v>
       </c>
       <c r="I7" t="n">
-        <v>39.34</v>
+        <v>12.22</v>
       </c>
       <c r="J7" t="n">
-        <v>34.01</v>
+        <v>24.29</v>
       </c>
       <c r="K7" t="n">
-        <v>18.3</v>
+        <v>16.6</v>
       </c>
       <c r="L7" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="M7" t="n">
-        <v>100</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O7" t="n">
-        <v>20.4</v>
+        <v>69.5</v>
       </c>
       <c r="P7" t="n">
-        <v>77.8</v>
+        <v>56.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>43.4</v>
+        <v>37.8</v>
       </c>
       <c r="R7" t="n">
-        <v>53.9</v>
+        <v>61.5</v>
       </c>
       <c r="S7" t="n">
-        <v>58.6</v>
+        <v>61.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>352.83</v>
+        <v>232.69</v>
       </c>
       <c r="X7" t="n">
-        <v>-15.19</v>
+        <v>-14.41</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.7</v>
+        <v>12.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>-26.92</v>
+        <v>0.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>-27.44</v>
+        <v>9.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.21</v>
+        <v>21.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.18</v>
+        <v>31.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>-34.5</v>
+        <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>411.2692</v>
+        <v>256.1288</v>
       </c>
       <c r="AG7" t="n">
-        <v>446.8838</v>
+        <v>232.7676</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,34 +1807,34 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20.4</v>
+        <v>69.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>43.4</v>
+        <v>37.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>53.9</v>
+        <v>61.5</v>
       </c>
       <c r="AM7" t="n">
         <v>753</v>
       </c>
       <c r="AN7" t="n">
-        <v>352.83</v>
+        <v>227.01</v>
       </c>
       <c r="AO7" t="n">
-        <v>352.83</v>
+        <v>209.77</v>
       </c>
       <c r="AP7" t="n">
-        <v>460.52</v>
+        <v>270.64</v>
       </c>
       <c r="AQ7" t="n">
-        <v>460.52</v>
+        <v>274.99</v>
       </c>
       <c r="AR7" t="n">
-        <v>-14.21</v>
+        <v>-9.15</v>
       </c>
       <c r="AS7" t="n">
-        <v>-21.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 14.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>49.4</v>
+        <v>59.1</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 58.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -14.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 61.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 209.77 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1378033860608</v>
+        <v>1396767457280</v>
       </c>
       <c r="G8" t="n">
-        <v>19.75</v>
+        <v>19.99</v>
       </c>
       <c r="H8" t="n">
-        <v>14.98</v>
+        <v>15.18</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1933,25 +1933,25 @@
         <v>35.61</v>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>21.3</v>
+        <v>35</v>
       </c>
       <c r="P8" t="n">
-        <v>83.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="R8" t="n">
-        <v>57.7</v>
+        <v>60</v>
       </c>
       <c r="S8" t="n">
-        <v>57.9</v>
+        <v>61.4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>542.87</v>
+        <v>550.25</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.26</v>
+        <v>-13.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.66</v>
+        <v>0.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>-17.79</v>
+        <v>-17.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.53</v>
+        <v>-22.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>25.4</v>
+        <v>24.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.46</v>
+        <v>36.42</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="AF8" t="n">
-        <v>614.8398</v>
+        <v>612.4256</v>
       </c>
       <c r="AG8" t="n">
-        <v>649.9292</v>
+        <v>648.8645</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21.3</v>
+        <v>35</v>
       </c>
       <c r="AK8" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>57.7</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
         <v>753</v>
@@ -2024,16 +2024,16 @@
         <v>542.87</v>
       </c>
       <c r="AP8" t="n">
-        <v>634.7017</v>
+        <v>631.9243</v>
       </c>
       <c r="AQ8" t="n">
         <v>687.9124</v>
       </c>
       <c r="AR8" t="n">
-        <v>-11.71</v>
+        <v>-10.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>-16.47</v>
+        <v>-15.2</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>36</v>
+        <v>40.2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 57.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.7%.</t>
+          <t>META: scenario base Hold / Monitor, score 61.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.2%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1408847052800</v>
+        <v>1426085904384</v>
       </c>
       <c r="G10" t="n">
-        <v>344.15</v>
+        <v>348.36</v>
       </c>
       <c r="H10" t="n">
-        <v>150.04</v>
+        <v>151.76</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>34.7</v>
+        <v>43.8</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="S10" t="n">
-        <v>32.9</v>
+        <v>35.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>375.12</v>
+        <v>379.71</v>
       </c>
       <c r="X10" t="n">
-        <v>-13.49</v>
+        <v>-13.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.81</v>
+        <v>2.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>-23.25</v>
+        <v>-21.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.18</v>
+        <v>15.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.95</v>
+        <v>14.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>57.78</v>
+        <v>57.74</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>405.0098</v>
+        <v>404.765</v>
       </c>
       <c r="AG10" t="n">
-        <v>417.801</v>
+        <v>417.9647</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34.7</v>
+        <v>43.8</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="AM10" t="n">
         <v>753</v>
@@ -2368,16 +2368,16 @@
         <v>343.25</v>
       </c>
       <c r="AP10" t="n">
-        <v>442.1</v>
+        <v>435.79</v>
       </c>
       <c r="AQ10" t="n">
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-7.38</v>
+        <v>-6.19</v>
       </c>
       <c r="AS10" t="n">
-        <v>-10.22</v>
+        <v>-9.15</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 7.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>24.1</v>
+        <v>27</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 32.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
+          <t>TSLA: scenario base High Risk, score 35.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4117026308096</v>
+        <v>4315439693824</v>
       </c>
       <c r="G2" t="n">
-        <v>25.75</v>
+        <v>26.96</v>
       </c>
       <c r="H2" t="n">
-        <v>23.18</v>
+        <v>24.3</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>65.2</v>
+        <v>62.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>66.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="S2" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>337.39</v>
+        <v>353.65</v>
       </c>
       <c r="X2" t="n">
-        <v>-13.18</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.17</v>
+        <v>28.99</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.47</v>
+        <v>12.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>98.23999999999999</v>
+        <v>104.37</v>
       </c>
       <c r="AB2" t="n">
-        <v>42.42</v>
+        <v>44.26</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.84</v>
+        <v>29.99</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>369.1154</v>
+        <v>369.472</v>
       </c>
       <c r="AG2" t="n">
-        <v>313.4987</v>
+        <v>314.0734</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>66.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
@@ -832,16 +832,16 @@
         <v>295.5934</v>
       </c>
       <c r="AP2" t="n">
-        <v>380.1129</v>
+        <v>376.1453</v>
       </c>
       <c r="AQ2" t="n">
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-8.59</v>
+        <v>-4.28</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.62</v>
+        <v>12.6</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 8.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>73.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.6%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.3%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4167977926656</v>
+        <v>4138015391744</v>
       </c>
       <c r="G3" t="n">
-        <v>34.4</v>
+        <v>34.11</v>
       </c>
       <c r="H3" t="n">
-        <v>29.53</v>
+        <v>29.32</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -940,25 +940,25 @@
         <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>80.2</v>
+        <v>80.7</v>
       </c>
       <c r="P3" t="n">
-        <v>46.1</v>
+        <v>46.7</v>
       </c>
       <c r="Q3" t="n">
         <v>41.8</v>
       </c>
       <c r="R3" t="n">
-        <v>75.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>283.78</v>
+        <v>281.74</v>
       </c>
       <c r="X3" t="n">
-        <v>-8.710000000000001</v>
+        <v>-9.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.32</v>
+        <v>13.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.39</v>
+        <v>3.09</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.35</v>
+        <v>40.73</v>
       </c>
       <c r="AB3" t="n">
-        <v>15.3</v>
+        <v>13.87</v>
       </c>
       <c r="AC3" t="n">
         <v>26.28</v>
@@ -996,13 +996,13 @@
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="AF3" t="n">
-        <v>291.4116</v>
+        <v>291.7833</v>
       </c>
       <c r="AG3" t="n">
-        <v>269.0755</v>
+        <v>269.3535</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>80.2</v>
+        <v>80.7</v>
       </c>
       <c r="AK3" t="n">
         <v>41.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>75.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN3" t="n">
         <v>275.15</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2.62</v>
+        <v>-3.44</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.46</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 71.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 71.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4663269130240</v>
+        <v>4722368446464</v>
       </c>
       <c r="G4" t="n">
-        <v>29.44</v>
+        <v>29.86</v>
       </c>
       <c r="H4" t="n">
-        <v>15.13</v>
+        <v>15.27</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>75</v>
+        <v>81.7</v>
       </c>
       <c r="P4" t="n">
-        <v>72.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="Q4" t="n">
         <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>67.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>69.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>192.53</v>
+        <v>194.97</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.33</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.56</v>
+        <v>16.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.93</v>
+        <v>25.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>66.73</v>
+        <v>67.09</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.92</v>
+        <v>46.93</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.9179</v>
+        <v>209.8549</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.428</v>
+        <v>190.5174</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,22 +1212,22 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75</v>
+        <v>81.7</v>
       </c>
       <c r="AK4" t="n">
         <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>67.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN4" t="n">
         <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>175.5454</v>
+        <v>177.1835</v>
       </c>
       <c r="AP4" t="n">
         <v>224.0988</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-8.279999999999999</v>
+        <v>-7.09</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 8.3% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>49.3</v>
+        <v>51.6</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 69.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 70.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 175.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 177.18 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,55 +1308,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>608266158080</v>
+        <v>2583212326912</v>
       </c>
       <c r="G5" t="n">
-        <v>61.12</v>
+        <v>32.67</v>
       </c>
       <c r="H5" t="n">
-        <v>37.51</v>
+        <v>24.3</v>
       </c>
       <c r="I5" t="n">
-        <v>29.71</v>
+        <v>12.22</v>
       </c>
       <c r="J5" t="n">
-        <v>52.24</v>
+        <v>24.29</v>
       </c>
       <c r="K5" t="n">
-        <v>13.2</v>
+        <v>16.6</v>
       </c>
       <c r="L5" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="M5" t="n">
-        <v>68</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="P5" t="n">
-        <v>10.7</v>
+        <v>55.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.1</v>
+        <v>37.8</v>
       </c>
       <c r="R5" t="n">
-        <v>47.2</v>
+        <v>70.5</v>
       </c>
       <c r="S5" t="n">
-        <v>64</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,98 +1363,98 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1578.2</v>
+        <v>240.14</v>
       </c>
       <c r="X5" t="n">
-        <v>13.46</v>
+        <v>-12.36</v>
       </c>
       <c r="Y5" t="n">
-        <v>35.67</v>
+        <v>20.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.17</v>
+        <v>3.34</v>
       </c>
       <c r="AA5" t="n">
-        <v>138.07</v>
+        <v>10.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>35.17</v>
+        <v>22.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>38.39</v>
+        <v>31.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>-44.77</v>
+        <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>1398.0824</v>
+        <v>255.9376</v>
       </c>
       <c r="AG5" t="n">
-        <v>1114.1671</v>
+        <v>232.8167</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.1</v>
+        <v>37.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>47.2</v>
+        <v>70.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="AN5" t="n">
-        <v>1394</v>
+        <v>227.01</v>
       </c>
       <c r="AO5" t="n">
-        <v>1111.3427</v>
+        <v>209.77</v>
       </c>
       <c r="AP5" t="n">
-        <v>1676</v>
+        <v>261.26</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1676</v>
+        <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.88</v>
+        <v>-6.17</v>
       </c>
       <c r="AS5" t="n">
-        <v>41.65</v>
+        <v>3.15</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 12.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>35.7</v>
+        <v>66</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.9%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 67.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.2%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 209.77 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1483,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,55 +1505,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2770583420928</v>
+        <v>1428116865024</v>
       </c>
       <c r="G6" t="n">
-        <v>22.21</v>
+        <v>20.45</v>
       </c>
       <c r="H6" t="n">
-        <v>19.26</v>
+        <v>15.52</v>
       </c>
       <c r="I6" t="n">
-        <v>39.34</v>
+        <v>32.84</v>
       </c>
       <c r="J6" t="n">
-        <v>34.01</v>
+        <v>32.93</v>
       </c>
       <c r="K6" t="n">
-        <v>18.3</v>
+        <v>33.1</v>
       </c>
       <c r="L6" t="n">
-        <v>30.27</v>
+        <v>35.61</v>
       </c>
       <c r="M6" t="n">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>33.2</v>
+        <v>45.1</v>
       </c>
       <c r="P6" t="n">
-        <v>74.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.1</v>
+        <v>28.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.5</v>
+        <v>63.6</v>
       </c>
       <c r="S6" t="n">
-        <v>62</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1564,42 +1562,42 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>372.97</v>
+        <v>562.6</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.619999999999999</v>
+        <v>-11.36</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.13</v>
+        <v>7.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>-23.05</v>
+        <v>-15.57</v>
       </c>
       <c r="AA6" t="n">
-        <v>-23.63</v>
+        <v>-22.26</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.52</v>
+        <v>25.71</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.38</v>
+        <v>36.47</v>
       </c>
       <c r="AD6" t="n">
-        <v>-34.5</v>
+        <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.19</v>
+        <v>0.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>410.522</v>
+        <v>610.1527</v>
       </c>
       <c r="AG6" t="n">
-        <v>446.2723</v>
+        <v>647.9298</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,34 +1608,34 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>33.2</v>
+        <v>45.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>43.1</v>
+        <v>28.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>61.5</v>
+        <v>63.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN6" t="n">
-        <v>352.83</v>
+        <v>542.87</v>
       </c>
       <c r="AO6" t="n">
-        <v>352.83</v>
+        <v>542.87</v>
       </c>
       <c r="AP6" t="n">
-        <v>460.52</v>
+        <v>626.9888999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>460.52</v>
+        <v>687.9124</v>
       </c>
       <c r="AR6" t="n">
-        <v>-9.15</v>
+        <v>-7.79</v>
       </c>
       <c r="AS6" t="n">
-        <v>-16.43</v>
+        <v>-13.17</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1646,16 +1644,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.7</v>
+        <v>43.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 64.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.8%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1684,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1706,53 +1704,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2503072022528</v>
+        <v>621293273088</v>
       </c>
       <c r="G7" t="n">
-        <v>32.45</v>
+        <v>62.29</v>
       </c>
       <c r="H7" t="n">
-        <v>23.55</v>
+        <v>38</v>
       </c>
       <c r="I7" t="n">
-        <v>12.22</v>
+        <v>29.71</v>
       </c>
       <c r="J7" t="n">
-        <v>24.29</v>
+        <v>52.24</v>
       </c>
       <c r="K7" t="n">
-        <v>16.6</v>
+        <v>13.2</v>
       </c>
       <c r="L7" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>12.99</v>
+      </c>
+      <c r="M7" t="n">
+        <v>68</v>
+      </c>
       <c r="N7" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>69.5</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>56.9</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.8</v>
+        <v>18.1</v>
       </c>
       <c r="R7" t="n">
-        <v>61.5</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
-        <v>61.5</v>
+        <v>63.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,98 +1761,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>232.69</v>
+        <v>1612</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.41</v>
+        <v>16.41</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.12</v>
+        <v>40.93</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.24</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.76</v>
+        <v>139.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>21.77</v>
+        <v>34.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>31.21</v>
+        <v>38.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>256.1288</v>
+        <v>1405.4973</v>
       </c>
       <c r="AG7" t="n">
-        <v>232.7676</v>
+        <v>1118.7963</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>69.5</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>37.8</v>
+        <v>18.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>61.5</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="AN7" t="n">
-        <v>227.01</v>
+        <v>1461.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>209.77</v>
+        <v>1111.3427</v>
       </c>
       <c r="AP7" t="n">
-        <v>270.64</v>
+        <v>1676</v>
       </c>
       <c r="AQ7" t="n">
-        <v>274.99</v>
+        <v>1676</v>
       </c>
       <c r="AR7" t="n">
-        <v>-9.15</v>
+        <v>14.69</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.03</v>
+        <v>44.08</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 9.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 14.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>59.1</v>
+        <v>30.3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 61.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.7%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 209.77 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1396767457280</v>
+        <v>2737898258432</v>
       </c>
       <c r="G8" t="n">
-        <v>19.99</v>
+        <v>21.96</v>
       </c>
       <c r="H8" t="n">
-        <v>15.18</v>
+        <v>19.03</v>
       </c>
       <c r="I8" t="n">
-        <v>32.84</v>
+        <v>39.34</v>
       </c>
       <c r="J8" t="n">
-        <v>32.93</v>
+        <v>34.01</v>
       </c>
       <c r="K8" t="n">
-        <v>33.1</v>
+        <v>18.3</v>
       </c>
       <c r="L8" t="n">
-        <v>35.61</v>
+        <v>30.27</v>
       </c>
       <c r="M8" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="P8" t="n">
-        <v>83.3</v>
+        <v>75.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>43.1</v>
       </c>
       <c r="R8" t="n">
-        <v>60</v>
+        <v>60.3</v>
       </c>
       <c r="S8" t="n">
-        <v>61.4</v>
+        <v>62.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1960,42 +1960,42 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>550.25</v>
+        <v>368.57</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.3</v>
+        <v>-13.68</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.59</v>
+        <v>3.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>-17.1</v>
+        <v>-24.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>-22.1</v>
+        <v>-25.32</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.69</v>
+        <v>3.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.42</v>
+        <v>24.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>-34.15</v>
+        <v>-34.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.68</v>
+        <v>0.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>612.4256</v>
+        <v>409.5063</v>
       </c>
       <c r="AG8" t="n">
-        <v>648.8645</v>
+        <v>445.629</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,34 +2006,34 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>43.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>60.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN8" t="n">
-        <v>542.87</v>
+        <v>352.83</v>
       </c>
       <c r="AO8" t="n">
-        <v>542.87</v>
+        <v>352.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>631.9243</v>
+        <v>460.52</v>
       </c>
       <c r="AQ8" t="n">
-        <v>687.9124</v>
+        <v>460.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>-10.15</v>
+        <v>-10</v>
       </c>
       <c r="AS8" t="n">
-        <v>-15.2</v>
+        <v>-17.29</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2042,16 +2042,16 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 10.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>40.2</v>
+        <v>54.6</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 61.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.2%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.0%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2100,124 +2100,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>1546757210112</v>
+      </c>
+      <c r="G9" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>50</v>
-      </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>411.84</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-15.15</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>405.2238</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>418.285</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AK9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>100</v>
-      </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>78.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+        <v>751</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>423.74</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-1.54</v>
+      </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>32.3</v>
+        <v>37.1</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 43.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2227,19 +2277,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2247,174 +2297,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1426085904384</v>
-      </c>
-      <c r="G10" t="n">
-        <v>348.36</v>
-      </c>
-      <c r="H10" t="n">
-        <v>151.76</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>66</v>
-      </c>
-      <c r="S10" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>379.71</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-13.77</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-21.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>57.74</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>404.765</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>417.9647</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>35</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL10" t="n">
         <v>0</v>
       </c>
-      <c r="AL10" t="n">
-        <v>66</v>
-      </c>
       <c r="AM10" t="n">
-        <v>753</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>375.12</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>343.25</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>435.79</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-6.19</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-9.15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>27</v>
+        <v>32.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 35.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4315439693824</v>
+        <v>4360833335296</v>
       </c>
       <c r="G2" t="n">
-        <v>26.96</v>
+        <v>27.24</v>
       </c>
       <c r="H2" t="n">
-        <v>24.3</v>
+        <v>24.56</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -741,7 +741,7 @@
         <v>20.03</v>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>62.2</v>
+        <v>61.5</v>
       </c>
       <c r="Q2" t="n">
         <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>73.3</v>
+        <v>74.7</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>353.65</v>
+        <v>357.37</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-5.98</v>
       </c>
       <c r="Y2" t="n">
-        <v>28.99</v>
+        <v>30.74</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.74</v>
+        <v>14.14</v>
       </c>
       <c r="AA2" t="n">
-        <v>104.37</v>
+        <v>100.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.26</v>
+        <v>44.69</v>
       </c>
       <c r="AC2" t="n">
         <v>29.99</v>
@@ -797,13 +797,13 @@
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AF2" t="n">
-        <v>369.472</v>
+        <v>369.7899</v>
       </c>
       <c r="AG2" t="n">
-        <v>314.0734</v>
+        <v>314.6607</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>73.3</v>
+        <v>74.7</v>
       </c>
       <c r="AM2" t="n">
         <v>751</v>
@@ -829,19 +829,19 @@
         <v>337.39</v>
       </c>
       <c r="AO2" t="n">
-        <v>295.5934</v>
+        <v>299.8109</v>
       </c>
       <c r="AP2" t="n">
-        <v>376.1453</v>
+        <v>373.25</v>
       </c>
       <c r="AQ2" t="n">
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.28</v>
+        <v>-3.36</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.6</v>
+        <v>13.57</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 4.3% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>74.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.3%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 295.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 299.81 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4138015391744</v>
+        <v>4249933053952</v>
       </c>
       <c r="G3" t="n">
-        <v>34.11</v>
+        <v>35.07</v>
       </c>
       <c r="H3" t="n">
-        <v>29.32</v>
+        <v>30.11</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>80.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>46.7</v>
+        <v>44.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="R3" t="n">
-        <v>74.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="S3" t="n">
-        <v>71.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,42 +967,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>281.74</v>
+        <v>289.36</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.85</v>
+        <v>-7.27</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.34</v>
+        <v>17.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.09</v>
+        <v>6.03</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.73</v>
+        <v>44.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.87</v>
+        <v>15.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.28</v>
+        <v>26.32</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="AF3" t="n">
-        <v>291.7833</v>
+        <v>292.1709</v>
       </c>
       <c r="AG3" t="n">
-        <v>269.3535</v>
+        <v>269.6534</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>80.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>74.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="AM3" t="n">
         <v>751</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3.44</v>
+        <v>-0.96</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.6</v>
+        <v>7.31</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>69.2</v>
+        <v>72.2</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 71.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 73.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.0%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4722368446464</v>
+        <v>4846379859968</v>
       </c>
       <c r="G4" t="n">
-        <v>29.86</v>
+        <v>30.64</v>
       </c>
       <c r="H4" t="n">
-        <v>15.27</v>
+        <v>15.68</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1138,26 +1138,24 @@
       <c r="L4" t="n">
         <v>6.55</v>
       </c>
-      <c r="M4" t="n">
-        <v>52</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>81.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>71.7</v>
+        <v>70.2</v>
       </c>
       <c r="Q4" t="n">
         <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>69.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="S4" t="n">
-        <v>70.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1169,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>194.97</v>
+        <v>200.09</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.890000000000001</v>
+        <v>-5.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.52</v>
+        <v>21.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>5.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>25.94</v>
+        <v>27.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>67.09</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.93</v>
+        <v>46.95</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.8549</v>
+        <v>209.8278</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.5174</v>
+        <v>190.6331</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,13 +1210,13 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AK4" t="n">
         <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>69.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="AM4" t="n">
         <v>751</v>
@@ -1227,19 +1225,19 @@
         <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>177.1835</v>
+        <v>177.4332</v>
       </c>
       <c r="AP4" t="n">
-        <v>224.0988</v>
+        <v>222.5606</v>
       </c>
       <c r="AQ4" t="n">
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-7.09</v>
+        <v>-4.64</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.34</v>
+        <v>4.96</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1251,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>51.6</v>
+        <v>54.6</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1264,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 70.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 73.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.6%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1276,7 +1274,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 177.18 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 177.43 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1317,13 +1315,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2583212326912</v>
+        <v>2563849584640</v>
       </c>
       <c r="G5" t="n">
-        <v>32.67</v>
+        <v>31.4</v>
       </c>
       <c r="H5" t="n">
-        <v>24.3</v>
+        <v>24.12</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1340,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>83.3</v>
+        <v>79.2</v>
       </c>
       <c r="P5" t="n">
-        <v>55.5</v>
+        <v>57.3</v>
       </c>
       <c r="Q5" t="n">
         <v>37.8</v>
       </c>
       <c r="R5" t="n">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>67.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1366,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>240.14</v>
+        <v>238.34</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.36</v>
+        <v>-11.93</v>
       </c>
       <c r="Y5" t="n">
-        <v>20.47</v>
+        <v>18.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.6</v>
+        <v>6.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.75</v>
+        <v>22.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.28</v>
+        <v>31.29</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="AF5" t="n">
-        <v>255.9376</v>
+        <v>255.6932</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.8167</v>
+        <v>232.8586</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,13 +1407,13 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>83.3</v>
+        <v>79.2</v>
       </c>
       <c r="AK5" t="n">
         <v>37.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AM5" t="n">
         <v>751</v>
@@ -1424,19 +1422,19 @@
         <v>227.01</v>
       </c>
       <c r="AO5" t="n">
-        <v>209.77</v>
+        <v>212.79</v>
       </c>
       <c r="AP5" t="n">
-        <v>261.26</v>
+        <v>256.52</v>
       </c>
       <c r="AQ5" t="n">
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-6.17</v>
+        <v>-6.79</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1448,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>66</v>
+        <v>64.8</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1461,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 67.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1473,7 +1471,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 209.77 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 212.79 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1514,13 +1512,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1428116865024</v>
+        <v>1429868380160</v>
       </c>
       <c r="G6" t="n">
-        <v>20.45</v>
+        <v>20.48</v>
       </c>
       <c r="H6" t="n">
-        <v>15.52</v>
+        <v>15.54</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1535,25 +1533,25 @@
         <v>35.61</v>
       </c>
       <c r="M6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>45.1</v>
+        <v>42.5</v>
       </c>
       <c r="P6" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="Q6" t="n">
         <v>28.9</v>
       </c>
       <c r="R6" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="S6" t="n">
-        <v>64.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,22 +1565,22 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>562.6</v>
+        <v>563.29</v>
       </c>
       <c r="X6" t="n">
-        <v>-11.36</v>
+        <v>-10.86</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.11</v>
+        <v>5.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>-15.57</v>
+        <v>-14.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>-22.26</v>
+        <v>-22.97</v>
       </c>
       <c r="AB6" t="n">
-        <v>25.71</v>
+        <v>25.9</v>
       </c>
       <c r="AC6" t="n">
         <v>36.47</v>
@@ -1594,10 +1592,10 @@
         <v>0.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>610.1527</v>
+        <v>607.6603</v>
       </c>
       <c r="AG6" t="n">
-        <v>647.9298</v>
+        <v>647.0041</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,13 +1606,13 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>45.1</v>
+        <v>42.5</v>
       </c>
       <c r="AK6" t="n">
         <v>28.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="AM6" t="n">
         <v>751</v>
@@ -1632,10 +1630,10 @@
         <v>687.9124</v>
       </c>
       <c r="AR6" t="n">
-        <v>-7.79</v>
+        <v>-7.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>-13.17</v>
+        <v>-12.94</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1649,11 +1647,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 7.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>43.8</v>
+        <v>43.4</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1660,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 64.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 63.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.3%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1689,12 +1687,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1709,50 +1707,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>621293273088</v>
+        <v>2770954616832</v>
       </c>
       <c r="G7" t="n">
-        <v>62.29</v>
+        <v>22.19</v>
       </c>
       <c r="H7" t="n">
-        <v>38</v>
+        <v>19.26</v>
       </c>
       <c r="I7" t="n">
-        <v>29.71</v>
+        <v>39.34</v>
       </c>
       <c r="J7" t="n">
-        <v>52.24</v>
+        <v>34.01</v>
       </c>
       <c r="K7" t="n">
-        <v>13.2</v>
+        <v>18.3</v>
       </c>
       <c r="L7" t="n">
-        <v>12.99</v>
+        <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>35.8</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.1</v>
+        <v>43.1</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>62.2</v>
       </c>
       <c r="S7" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,98 +1759,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1612</v>
+        <v>373.02</v>
       </c>
       <c r="X7" t="n">
-        <v>16.41</v>
+        <v>-17.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>40.93</v>
+        <v>4.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>78.40000000000001</v>
+        <v>-23.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>139.8</v>
+        <v>-24.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>34.8</v>
+        <v>4.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.44</v>
+        <v>24.41</v>
       </c>
       <c r="AD7" t="n">
-        <v>-44.77</v>
+        <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.91</v>
+        <v>0.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1405.4973</v>
+        <v>408.5292</v>
       </c>
       <c r="AG7" t="n">
-        <v>1118.7963</v>
+        <v>445.0048</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>100</v>
+        <v>35.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.1</v>
+        <v>43.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>62.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="AN7" t="n">
-        <v>1461.8</v>
+        <v>352.83</v>
       </c>
       <c r="AO7" t="n">
-        <v>1111.3427</v>
+        <v>352.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>1676</v>
+        <v>441.31</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1676</v>
+        <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.69</v>
+        <v>-8.69</v>
       </c>
       <c r="AS7" t="n">
-        <v>44.08</v>
+        <v>-16.18</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 14.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.7% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>30.3</v>
+        <v>55.6</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1859,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.7%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.7%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,19 +1879,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1908,50 +1906,50 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2737898258432</v>
+        <v>663457955840</v>
       </c>
       <c r="G8" t="n">
-        <v>21.96</v>
+        <v>66.75</v>
       </c>
       <c r="H8" t="n">
-        <v>19.03</v>
+        <v>39.99</v>
       </c>
       <c r="I8" t="n">
-        <v>39.34</v>
+        <v>29.71</v>
       </c>
       <c r="J8" t="n">
-        <v>34.01</v>
+        <v>52.24</v>
       </c>
       <c r="K8" t="n">
-        <v>18.3</v>
+        <v>13.2</v>
       </c>
       <c r="L8" t="n">
-        <v>30.27</v>
+        <v>12.99</v>
       </c>
       <c r="M8" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>34.1</v>
+        <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>75.5</v>
+        <v>7.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>43.1</v>
+        <v>17.8</v>
       </c>
       <c r="R8" t="n">
-        <v>60.3</v>
+        <v>12.2</v>
       </c>
       <c r="S8" t="n">
-        <v>62.2</v>
+        <v>59.8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1960,98 +1958,98 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>368.57</v>
+        <v>1721.4</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.68</v>
+        <v>23.49</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.53</v>
+        <v>55.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>-24.14</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>-25.32</v>
+        <v>156.26</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.5</v>
+        <v>38.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>24.4</v>
+        <v>38.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>-34.5</v>
+        <v>-44.77</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.14</v>
+        <v>0.99</v>
       </c>
       <c r="AF8" t="n">
-        <v>409.5063</v>
+        <v>1415.0803</v>
       </c>
       <c r="AG8" t="n">
-        <v>445.629</v>
+        <v>1123.7757</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34.1</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>43.1</v>
+        <v>17.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>60.3</v>
+        <v>12.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="AN8" t="n">
-        <v>352.83</v>
+        <v>1462.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>352.83</v>
+        <v>1111.3427</v>
       </c>
       <c r="AP8" t="n">
-        <v>460.52</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>460.52</v>
+        <v>1721.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>-10</v>
+        <v>21.65</v>
       </c>
       <c r="AS8" t="n">
-        <v>-17.29</v>
+        <v>53.18</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 10.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 21.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>54.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2058,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 59.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,7 +2078,7 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2109,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1546757210112</v>
+        <v>1579657461760</v>
       </c>
       <c r="G9" t="n">
-        <v>374.4</v>
+        <v>393.08</v>
       </c>
       <c r="H9" t="n">
-        <v>164.6</v>
+        <v>168.1</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2134,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>66.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2145,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>78.2</v>
+        <v>82.8</v>
       </c>
       <c r="S9" t="n">
-        <v>43.4</v>
+        <v>47.7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,54 +2160,54 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>411.84</v>
+        <v>420.6</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.84</v>
+        <v>-3.49</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.82</v>
+        <v>18.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>-15.15</v>
+        <v>-11.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.42</v>
+        <v>29.96</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.42</v>
+        <v>14.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>58</v>
+        <v>57.88</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>405.2238</v>
+        <v>405.6234</v>
       </c>
       <c r="AG9" t="n">
-        <v>418.285</v>
+        <v>418.5439</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>66.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>78.2</v>
+        <v>82.8</v>
       </c>
       <c r="AM9" t="n">
         <v>751</v>
@@ -2227,10 +2225,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.63</v>
+        <v>3.69</v>
       </c>
       <c r="AS9" t="n">
-        <v>-1.54</v>
+        <v>0.49</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2244,11 +2242,11 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>37.1</v>
+        <v>41.6</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2255,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 43.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>TSLA: scenario base High Risk, score 47.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4360833335296</v>
+        <v>4407691313152</v>
       </c>
       <c r="G2" t="n">
-        <v>27.24</v>
+        <v>27.53</v>
       </c>
       <c r="H2" t="n">
-        <v>24.56</v>
+        <v>24.79</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>61.5</v>
+        <v>60.8</v>
       </c>
       <c r="Q2" t="n">
         <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>74.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>357.37</v>
+        <v>361.21</v>
       </c>
       <c r="X2" t="n">
-        <v>-5.98</v>
+        <v>-3.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>30.74</v>
+        <v>25.69</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.14</v>
+        <v>15.35</v>
       </c>
       <c r="AA2" t="n">
-        <v>100.74</v>
+        <v>105.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.69</v>
+        <v>45.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.99</v>
+        <v>29.98</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AF2" t="n">
-        <v>369.7899</v>
+        <v>370.2698</v>
       </c>
       <c r="AG2" t="n">
-        <v>314.6607</v>
+        <v>315.2651</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,16 +820,16 @@
         <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>74.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
       </c>
       <c r="AO2" t="n">
-        <v>299.8109</v>
+        <v>305.2776</v>
       </c>
       <c r="AP2" t="n">
         <v>373.25</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-3.36</v>
+        <v>-2.45</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.57</v>
+        <v>14.57</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 299.81 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 305.28 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4249933053952</v>
+        <v>4323663937536</v>
       </c>
       <c r="G3" t="n">
-        <v>35.07</v>
+        <v>35.68</v>
       </c>
       <c r="H3" t="n">
-        <v>30.11</v>
+        <v>30.64</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -940,25 +940,25 @@
         <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>89.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="P3" t="n">
-        <v>44.4</v>
+        <v>43</v>
       </c>
       <c r="Q3" t="n">
         <v>41.7</v>
       </c>
       <c r="R3" t="n">
-        <v>78.3</v>
+        <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>73.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>289.36</v>
+        <v>294.38</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.27</v>
+        <v>-3.89</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.43</v>
+        <v>16.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.03</v>
+        <v>7.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.47</v>
+        <v>44.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>15.2</v>
+        <v>15.84</v>
       </c>
       <c r="AC3" t="n">
         <v>26.32</v>
@@ -996,33 +996,33 @@
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>292.1709</v>
+        <v>292.6025</v>
       </c>
       <c r="AG3" t="n">
-        <v>269.6534</v>
+        <v>269.9582</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>89.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="AK3" t="n">
         <v>41.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>78.3</v>
+        <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>275.15</v>
@@ -1031,16 +1031,16 @@
         <v>253.2667</v>
       </c>
       <c r="AP3" t="n">
-        <v>315.2</v>
+        <v>311.23</v>
       </c>
       <c r="AQ3" t="n">
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.96</v>
+        <v>0.61</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.31</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>72.2</v>
+        <v>73.7</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.0%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4846379859968</v>
+        <v>4785584996352</v>
       </c>
       <c r="G4" t="n">
-        <v>30.64</v>
+        <v>30.3</v>
       </c>
       <c r="H4" t="n">
-        <v>15.68</v>
+        <v>15.48</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1138,24 +1138,26 @@
       <c r="L4" t="n">
         <v>6.55</v>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>50</v>
+      </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>89.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="P4" t="n">
-        <v>70.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>72.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>73</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1169,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>200.09</v>
+        <v>197.58</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.12</v>
+        <v>-11.83</v>
       </c>
       <c r="Y4" t="n">
-        <v>21.28</v>
+        <v>13.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>27.01</v>
+        <v>25.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>68.40000000000001</v>
+        <v>67.58</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.95</v>
+        <v>46.92</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.8278</v>
+        <v>209.7429</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.6331</v>
+        <v>190.733</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1210,34 +1212,34 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>89.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="AK4" t="n">
         <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>72.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
         <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>177.4332</v>
+        <v>177.8927</v>
       </c>
       <c r="AP4" t="n">
-        <v>222.5606</v>
+        <v>218.66</v>
       </c>
       <c r="AQ4" t="n">
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-4.64</v>
+        <v>-5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.96</v>
+        <v>3.59</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1251,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>54.6</v>
+        <v>51.2</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 73.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 70.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.8%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1274,7 +1276,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 177.43 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 177.89 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1291,12 +1293,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1306,53 +1308,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2563849584640</v>
+        <v>1555824902144</v>
       </c>
       <c r="G5" t="n">
-        <v>31.4</v>
+        <v>22.3</v>
       </c>
       <c r="H5" t="n">
-        <v>24.12</v>
+        <v>16.91</v>
       </c>
       <c r="I5" t="n">
-        <v>12.22</v>
+        <v>32.84</v>
       </c>
       <c r="J5" t="n">
-        <v>24.29</v>
+        <v>32.93</v>
       </c>
       <c r="K5" t="n">
-        <v>16.6</v>
+        <v>33.1</v>
       </c>
       <c r="L5" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>35.61</v>
+      </c>
+      <c r="M5" t="n">
+        <v>37</v>
+      </c>
       <c r="N5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O5" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="P5" t="n">
         <v>78.2</v>
       </c>
-      <c r="O5" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>57.3</v>
-      </c>
       <c r="Q5" t="n">
-        <v>37.8</v>
+        <v>28.5</v>
       </c>
       <c r="R5" t="n">
-        <v>69.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="S5" t="n">
-        <v>66.3</v>
+        <v>67.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1361,80 +1365,80 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>238.34</v>
+        <v>612.91</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.93</v>
+        <v>2.17</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.61</v>
+        <v>7.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.5</v>
+        <v>-6.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.74</v>
+        <v>-16.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.49</v>
+        <v>29.48</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.29</v>
+        <v>36.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>-30.88</v>
+        <v>-34.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>255.6932</v>
+        <v>606.5127</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.8586</v>
+        <v>646.303</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>79.2</v>
+        <v>51.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>37.8</v>
+        <v>28.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>69.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>227.01</v>
+        <v>542.87</v>
       </c>
       <c r="AO5" t="n">
-        <v>212.79</v>
+        <v>542.87</v>
       </c>
       <c r="AP5" t="n">
-        <v>256.52</v>
+        <v>626.9888999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>274.99</v>
+        <v>687.9124</v>
       </c>
       <c r="AR5" t="n">
-        <v>-6.79</v>
+        <v>1.05</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.35</v>
+        <v>-5.17</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1443,16 +1447,16 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>64.8</v>
+        <v>50</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1461,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 67.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 212.79 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1481,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1503,55 +1507,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1429868380160</v>
+        <v>2599993475072</v>
       </c>
       <c r="G6" t="n">
-        <v>20.48</v>
+        <v>32.1</v>
       </c>
       <c r="H6" t="n">
-        <v>15.54</v>
+        <v>24.46</v>
       </c>
       <c r="I6" t="n">
-        <v>32.84</v>
+        <v>12.22</v>
       </c>
       <c r="J6" t="n">
-        <v>32.93</v>
+        <v>24.29</v>
       </c>
       <c r="K6" t="n">
-        <v>33.1</v>
+        <v>16.6</v>
       </c>
       <c r="L6" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="M6" t="n">
-        <v>37</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O6" t="n">
-        <v>42.5</v>
+        <v>77.5</v>
       </c>
       <c r="P6" t="n">
-        <v>82.2</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="R6" t="n">
-        <v>64.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>63.5</v>
+        <v>65.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1560,98 +1562,98 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>563.29</v>
+        <v>241.7</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.86</v>
+        <v>-7.49</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.11</v>
+        <v>16.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>-14.92</v>
+        <v>4.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>-22.97</v>
+        <v>10.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>25.9</v>
+        <v>23.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>36.47</v>
+        <v>31.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>-34.15</v>
+        <v>-30.88</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="AF6" t="n">
-        <v>607.6603</v>
+        <v>255.5616</v>
       </c>
       <c r="AG6" t="n">
-        <v>647.0041</v>
+        <v>232.9264</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42.5</v>
+        <v>77.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>64.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>542.87</v>
+        <v>227.01</v>
       </c>
       <c r="AO6" t="n">
-        <v>542.87</v>
+        <v>213.77</v>
       </c>
       <c r="AP6" t="n">
-        <v>626.9888999999999</v>
+        <v>253.79</v>
       </c>
       <c r="AQ6" t="n">
-        <v>687.9124</v>
+        <v>274.99</v>
       </c>
       <c r="AR6" t="n">
-        <v>-7.3</v>
+        <v>-5.42</v>
       </c>
       <c r="AS6" t="n">
-        <v>-12.94</v>
+        <v>3.77</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 7.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>43.4</v>
+        <v>64.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1660,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 63.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.3%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.4%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 213.77 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1680,7 +1682,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -1711,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2770954616832</v>
+        <v>2854599000064</v>
       </c>
       <c r="G7" t="n">
-        <v>22.19</v>
+        <v>22.89</v>
       </c>
       <c r="H7" t="n">
-        <v>19.26</v>
+        <v>19.84</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1732,25 +1734,25 @@
         <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>35.8</v>
+        <v>37.7</v>
       </c>
       <c r="P7" t="n">
-        <v>74.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="Q7" t="n">
         <v>43.1</v>
       </c>
       <c r="R7" t="n">
-        <v>62.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>62.7</v>
+        <v>63.4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1764,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>373.02</v>
+        <v>384.28</v>
       </c>
       <c r="X7" t="n">
-        <v>-17.15</v>
+        <v>-16.56</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>-23.18</v>
+        <v>-20.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>-24.18</v>
+        <v>-22.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.18</v>
+        <v>5.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.41</v>
+        <v>24.45</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>408.5292</v>
+        <v>407.8715</v>
       </c>
       <c r="AG7" t="n">
-        <v>445.0048</v>
+        <v>444.3928</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1805,16 +1807,16 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>35.8</v>
+        <v>37.7</v>
       </c>
       <c r="AK7" t="n">
         <v>43.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>62.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AM7" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
         <v>352.83</v>
@@ -1823,16 +1825,16 @@
         <v>352.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>441.31</v>
+        <v>428.05</v>
       </c>
       <c r="AQ7" t="n">
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-8.69</v>
+        <v>-5.78</v>
       </c>
       <c r="AS7" t="n">
-        <v>-16.18</v>
+        <v>-13.53</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1846,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 8.7% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>55.6</v>
+        <v>57.3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1859,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.7%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.8%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1910,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>663457955840</v>
+        <v>632701648896</v>
       </c>
       <c r="G8" t="n">
-        <v>66.75</v>
+        <v>63.58</v>
       </c>
       <c r="H8" t="n">
-        <v>39.99</v>
+        <v>38.14</v>
       </c>
       <c r="I8" t="n">
         <v>29.71</v>
@@ -1931,7 +1933,7 @@
         <v>12.99</v>
       </c>
       <c r="M8" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1940,16 +1942,16 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="R8" t="n">
-        <v>12.2</v>
+        <v>37.4</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>62.8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1963,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>1721.4</v>
+        <v>1641.6</v>
       </c>
       <c r="X8" t="n">
-        <v>23.49</v>
+        <v>12.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>55.14</v>
+        <v>47</v>
       </c>
       <c r="Z8" t="n">
-        <v>88.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>156.26</v>
+        <v>150.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>38.11</v>
+        <v>35.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>38.62</v>
+        <v>38.72</v>
       </c>
       <c r="AD8" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="AF8" t="n">
-        <v>1415.0803</v>
+        <v>1423.2269</v>
       </c>
       <c r="AG8" t="n">
-        <v>1123.7757</v>
+        <v>1128.3386</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2007,10 +2009,10 @@
         <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>12.2</v>
+        <v>37.4</v>
       </c>
       <c r="AM8" t="n">
         <v>765</v>
@@ -2019,7 +2021,7 @@
         <v>1462.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>1111.3427</v>
+        <v>1171.8</v>
       </c>
       <c r="AP8" t="n">
         <v>1721.4</v>
@@ -2028,10 +2030,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>21.65</v>
+        <v>15.34</v>
       </c>
       <c r="AS8" t="n">
-        <v>53.18</v>
+        <v>45.49</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2045,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 21.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 15.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>9.300000000000001</v>
+        <v>28.3</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2058,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 59.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.3%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2068,7 +2070,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2109,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1579657461760</v>
+        <v>1597309321216</v>
       </c>
       <c r="G9" t="n">
-        <v>393.08</v>
+        <v>390.18</v>
       </c>
       <c r="H9" t="n">
-        <v>168.1</v>
+        <v>169.98</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2134,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>76.3</v>
+        <v>74.2</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2143,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>82.8</v>
+        <v>80</v>
       </c>
       <c r="S9" t="n">
-        <v>47.7</v>
+        <v>46.9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2160,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>420.6</v>
+        <v>425.3</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.49</v>
+        <v>2.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.39</v>
+        <v>14.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>-11.49</v>
+        <v>-7.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>29.96</v>
+        <v>33.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.65</v>
+        <v>15.06</v>
       </c>
       <c r="AC9" t="n">
-        <v>57.88</v>
+        <v>57.84</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>405.6234</v>
+        <v>406.2794</v>
       </c>
       <c r="AG9" t="n">
-        <v>418.5439</v>
+        <v>418.6907</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2201,16 +2203,16 @@
         <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>76.3</v>
+        <v>74.2</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>82.8</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN9" t="n">
         <v>375.12</v>
@@ -2219,16 +2221,16 @@
         <v>343.25</v>
       </c>
       <c r="AP9" t="n">
-        <v>423.74</v>
+        <v>425.3</v>
       </c>
       <c r="AQ9" t="n">
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.69</v>
+        <v>4.68</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.49</v>
+        <v>1.58</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2246,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>41.6</v>
+        <v>40.2</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2255,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 47.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.7%.</t>
+          <t>TSLA: scenario base High Risk, score 46.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4407691313152</v>
+        <v>4398234206208</v>
       </c>
       <c r="G2" t="n">
-        <v>27.53</v>
+        <v>27.49</v>
       </c>
       <c r="H2" t="n">
-        <v>24.79</v>
+        <v>24.76</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -741,7 +741,7 @@
         <v>20.03</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="Q2" t="n">
         <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>361.21</v>
+        <v>360.43</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.97</v>
+        <v>-0.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>25.69</v>
+        <v>21.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.35</v>
+        <v>14.99</v>
       </c>
       <c r="AA2" t="n">
-        <v>105.55</v>
+        <v>105.56</v>
       </c>
       <c r="AB2" t="n">
-        <v>45.14</v>
+        <v>44.96</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.98</v>
+        <v>29.96</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>370.2698</v>
+        <v>370.8365</v>
       </c>
       <c r="AG2" t="n">
-        <v>315.2651</v>
+        <v>315.8117</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,16 +820,16 @@
         <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
       </c>
       <c r="AO2" t="n">
-        <v>305.2776</v>
+        <v>317.0506</v>
       </c>
       <c r="AP2" t="n">
         <v>373.25</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-2.45</v>
+        <v>-2.81</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.57</v>
+        <v>14.13</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 305.28 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 317.05 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4323663937536</v>
+        <v>4536483708928</v>
       </c>
       <c r="G3" t="n">
-        <v>35.68</v>
+        <v>37.35</v>
       </c>
       <c r="H3" t="n">
-        <v>30.64</v>
+        <v>32.14</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>88.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>43</v>
+        <v>38.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="R3" t="n">
-        <v>82.8</v>
+        <v>77.8</v>
       </c>
       <c r="S3" t="n">
-        <v>74.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>294.38</v>
+        <v>308.8475</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.89</v>
+        <v>-2.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.1</v>
+        <v>20.93</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.73</v>
+        <v>13.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.05</v>
+        <v>49.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>15.84</v>
+        <v>17.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.32</v>
+        <v>26.45</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>292.6025</v>
+        <v>293.4609</v>
       </c>
       <c r="AG3" t="n">
-        <v>269.9582</v>
+        <v>270.3223</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,22 +1013,22 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>88.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>82.8</v>
+        <v>77.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
         <v>275.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>253.2667</v>
+        <v>258.5917</v>
       </c>
       <c r="AP3" t="n">
         <v>311.23</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.61</v>
+        <v>5.23</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.050000000000001</v>
+        <v>14.24</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>73.7</v>
+        <v>74.8</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 253.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 258.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4785584996352</v>
+        <v>4716555141120</v>
       </c>
       <c r="G4" t="n">
-        <v>30.3</v>
+        <v>29.87</v>
       </c>
       <c r="H4" t="n">
-        <v>15.48</v>
+        <v>15.26</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>78.2</v>
+        <v>74.5</v>
       </c>
       <c r="P4" t="n">
-        <v>70.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="Q4" t="n">
         <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>71.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>70.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>197.58</v>
+        <v>194.73</v>
       </c>
       <c r="X4" t="n">
-        <v>-11.83</v>
+        <v>-12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.42</v>
+        <v>10.93</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.1</v>
+        <v>3.96</v>
       </c>
       <c r="AA4" t="n">
-        <v>25.23</v>
+        <v>27.19</v>
       </c>
       <c r="AB4" t="n">
-        <v>67.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.92</v>
+        <v>46.9</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.7429</v>
+        <v>209.6445</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.733</v>
+        <v>190.8191</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,22 +1212,22 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>78.2</v>
+        <v>74.5</v>
       </c>
       <c r="AK4" t="n">
         <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>71.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN4" t="n">
         <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>177.8927</v>
+        <v>181.868</v>
       </c>
       <c r="AP4" t="n">
         <v>218.66</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-5.8</v>
+        <v>-7.12</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.59</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 5.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>51.2</v>
+        <v>49.7</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 70.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.8%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 69.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 177.89 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 181.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,55 +1308,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1555824902144</v>
+        <v>2614838165504</v>
       </c>
       <c r="G5" t="n">
-        <v>22.3</v>
+        <v>31.82</v>
       </c>
       <c r="H5" t="n">
-        <v>16.91</v>
+        <v>24.55</v>
       </c>
       <c r="I5" t="n">
-        <v>32.84</v>
+        <v>12.22</v>
       </c>
       <c r="J5" t="n">
-        <v>32.93</v>
+        <v>24.29</v>
       </c>
       <c r="K5" t="n">
-        <v>33.1</v>
+        <v>16.6</v>
       </c>
       <c r="L5" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="M5" t="n">
-        <v>37</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>51.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>78.2</v>
+        <v>56.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.5</v>
+        <v>37.8</v>
       </c>
       <c r="R5" t="n">
-        <v>78.2</v>
+        <v>72.5</v>
       </c>
       <c r="S5" t="n">
-        <v>67.5</v>
+        <v>65.8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,80 +1363,80 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>612.91</v>
+        <v>243.095</v>
       </c>
       <c r="X5" t="n">
-        <v>2.17</v>
+        <v>-5.23</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.23</v>
+        <v>15.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>-6.78</v>
+        <v>4.54</v>
       </c>
       <c r="AA5" t="n">
-        <v>-16.69</v>
+        <v>10.27</v>
       </c>
       <c r="AB5" t="n">
-        <v>29.48</v>
+        <v>23.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>36.79</v>
+        <v>31.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>-34.15</v>
+        <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="AF5" t="n">
-        <v>606.5127</v>
+        <v>255.4253</v>
       </c>
       <c r="AG5" t="n">
-        <v>646.303</v>
+        <v>232.9847</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>51.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>28.5</v>
+        <v>37.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>78.2</v>
+        <v>72.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
-        <v>542.87</v>
+        <v>227.01</v>
       </c>
       <c r="AO5" t="n">
-        <v>542.87</v>
+        <v>221.25</v>
       </c>
       <c r="AP5" t="n">
-        <v>626.9888999999999</v>
+        <v>253.79</v>
       </c>
       <c r="AQ5" t="n">
-        <v>687.9124</v>
+        <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.05</v>
+        <v>-4.83</v>
       </c>
       <c r="AS5" t="n">
-        <v>-5.17</v>
+        <v>4.34</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1447,16 +1445,16 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>50</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 67.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.8%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 221.25 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1483,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,53 +1505,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2599993475072</v>
+        <v>608112017408</v>
       </c>
       <c r="G6" t="n">
-        <v>32.1</v>
+        <v>60.82</v>
       </c>
       <c r="H6" t="n">
-        <v>24.46</v>
+        <v>36.54</v>
       </c>
       <c r="I6" t="n">
-        <v>12.22</v>
+        <v>29.71</v>
       </c>
       <c r="J6" t="n">
-        <v>24.29</v>
+        <v>52.24</v>
       </c>
       <c r="K6" t="n">
-        <v>16.6</v>
+        <v>13.2</v>
       </c>
       <c r="L6" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>12.99</v>
+      </c>
+      <c r="M6" t="n">
+        <v>66</v>
+      </c>
       <c r="N6" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>56</v>
+        <v>12.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>37.8</v>
+        <v>17.7</v>
       </c>
       <c r="R6" t="n">
-        <v>71.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="S6" t="n">
-        <v>65.8</v>
+        <v>65.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,80 +1562,80 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>241.7</v>
+        <v>1577.8</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.49</v>
+        <v>6.23</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.05</v>
+        <v>33.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.15</v>
+        <v>60.54</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.17</v>
+        <v>136.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>23.03</v>
+        <v>33.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>31.28</v>
+        <v>38.76</v>
       </c>
       <c r="AD6" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>255.5616</v>
+        <v>1429.842</v>
       </c>
       <c r="AG6" t="n">
-        <v>232.9264</v>
+        <v>1132.5621</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>37.8</v>
+        <v>17.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>71.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="AN6" t="n">
-        <v>227.01</v>
+        <v>1462.2</v>
       </c>
       <c r="AO6" t="n">
-        <v>213.77</v>
+        <v>1171.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>253.79</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>274.99</v>
+        <v>1721.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>-5.42</v>
+        <v>10.35</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.77</v>
+        <v>39.31</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1644,16 +1644,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 5.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 10.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>64.8</v>
+        <v>43.3</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.4%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 65.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.3%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 213.77 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2854599000064</v>
+        <v>2902809378816</v>
       </c>
       <c r="G7" t="n">
-        <v>22.89</v>
+        <v>23.27</v>
       </c>
       <c r="H7" t="n">
-        <v>19.84</v>
+        <v>20.18</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1733,26 +1733,24 @@
       <c r="L7" t="n">
         <v>30.27</v>
       </c>
-      <c r="M7" t="n">
-        <v>98</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>37.7</v>
+        <v>41.8</v>
       </c>
       <c r="P7" t="n">
-        <v>73.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>43.1</v>
       </c>
       <c r="R7" t="n">
-        <v>66.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="S7" t="n">
-        <v>63.4</v>
+        <v>64.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,22 +1764,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>384.28</v>
+        <v>390.785</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.56</v>
+        <v>-11.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.04</v>
+        <v>6.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>-20.76</v>
+        <v>-19.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>-22.13</v>
+        <v>-19.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.22</v>
+        <v>5.8</v>
       </c>
       <c r="AC7" t="n">
         <v>24.45</v>
@@ -1790,13 +1788,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="AF7" t="n">
-        <v>407.8715</v>
+        <v>407.2223</v>
       </c>
       <c r="AG7" t="n">
-        <v>444.3928</v>
+        <v>443.7861</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1805,16 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>37.7</v>
+        <v>41.8</v>
       </c>
       <c r="AK7" t="n">
         <v>43.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>66.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
         <v>352.83</v>
@@ -1831,10 +1829,10 @@
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-5.78</v>
+        <v>-4.04</v>
       </c>
       <c r="AS7" t="n">
-        <v>-13.53</v>
+        <v>-11.94</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1846,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 5.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1859,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.8%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 64.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1888,12 +1886,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1903,55 +1901,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>632701648896</v>
+        <v>1481563570176</v>
       </c>
       <c r="G8" t="n">
-        <v>63.58</v>
+        <v>21.21</v>
       </c>
       <c r="H8" t="n">
-        <v>38.14</v>
+        <v>15.97</v>
       </c>
       <c r="I8" t="n">
-        <v>29.71</v>
+        <v>32.84</v>
       </c>
       <c r="J8" t="n">
-        <v>52.24</v>
+        <v>32.93</v>
       </c>
       <c r="K8" t="n">
-        <v>13.2</v>
+        <v>33.1</v>
       </c>
       <c r="L8" t="n">
-        <v>12.99</v>
+        <v>35.61</v>
       </c>
       <c r="M8" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>39.2</v>
       </c>
       <c r="P8" t="n">
-        <v>9.800000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.7</v>
+        <v>28.4</v>
       </c>
       <c r="R8" t="n">
-        <v>37.4</v>
+        <v>70</v>
       </c>
       <c r="S8" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,79 +1963,79 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>1641.6</v>
+        <v>583.66</v>
       </c>
       <c r="X8" t="n">
-        <v>12.3</v>
+        <v>-2.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>47</v>
+        <v>0.86</v>
       </c>
       <c r="Z8" t="n">
-        <v>78.8</v>
+        <v>-12.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>150.94</v>
+        <v>-18.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>35.76</v>
+        <v>27.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>38.72</v>
+        <v>36.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>-44.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.92</v>
+        <v>0.74</v>
       </c>
       <c r="AF8" t="n">
-        <v>1423.2269</v>
+        <v>604.8215</v>
       </c>
       <c r="AG8" t="n">
-        <v>1128.3386</v>
+        <v>645.4103</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>39.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.7</v>
+        <v>28.4</v>
       </c>
       <c r="AL8" t="n">
-        <v>37.4</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
-        <v>1462.2</v>
+        <v>542.87</v>
       </c>
       <c r="AO8" t="n">
-        <v>1171.8</v>
+        <v>542.87</v>
       </c>
       <c r="AP8" t="n">
-        <v>1721.4</v>
+        <v>626.9888999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1721.4</v>
+        <v>687.9124</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.34</v>
+        <v>-3.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>45.49</v>
+        <v>-9.57</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2047,11 +2045,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 15.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>28.3</v>
+        <v>43.9</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2058,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.3%.</t>
+          <t>META: scenario base Hold / Monitor, score 62.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.5%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,19 +2078,19 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2100,174 +2098,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1597309321216</v>
-      </c>
-      <c r="G9" t="n">
-        <v>390.18</v>
-      </c>
-      <c r="H9" t="n">
-        <v>169.98</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>74.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>80</v>
-      </c>
-      <c r="S9" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>425.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-7.47</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>57.84</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>406.2794</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>418.6907</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>74.2</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL9" t="n">
         <v>0</v>
       </c>
-      <c r="AL9" t="n">
-        <v>80</v>
-      </c>
       <c r="AM9" t="n">
-        <v>752</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>375.12</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>343.25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>425.3</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>40.2</v>
+        <v>32.3</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 46.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2277,19 +2225,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2297,124 +2245,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1479867891712</v>
+      </c>
+      <c r="G10" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="H10" t="n">
+        <v>154.88</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>50</v>
-      </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>70.7</v>
       </c>
       <c r="S10" t="n">
         <v>38.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>394.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-13.28</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>406.4322</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>418.6108</v>
+      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>100</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>70.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+        <v>753</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>425.3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-5.86</v>
+      </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 38.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.0%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2424,7 +2422,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4398234206208</v>
+        <v>4391827931136</v>
       </c>
       <c r="G2" t="n">
-        <v>27.49</v>
+        <v>27.47</v>
       </c>
       <c r="H2" t="n">
-        <v>24.76</v>
+        <v>24.72</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="Q2" t="n">
         <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>75.5</v>
+        <v>75.3</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>360.43</v>
+        <v>359.91</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.33</v>
+        <v>-0.48</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.27</v>
+        <v>21.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.99</v>
+        <v>14.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>105.56</v>
+        <v>105.26</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.96</v>
+        <v>44.89</v>
       </c>
       <c r="AC2" t="n">
         <v>29.96</v>
@@ -800,10 +800,10 @@
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>370.8365</v>
+        <v>370.8261</v>
       </c>
       <c r="AG2" t="n">
-        <v>315.8117</v>
+        <v>315.8091</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>75.5</v>
+        <v>75.3</v>
       </c>
       <c r="AM2" t="n">
         <v>753</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-2.81</v>
+        <v>-2.94</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.13</v>
+        <v>13.96</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.9%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4536483708928</v>
+        <v>4532958920704</v>
       </c>
       <c r="G3" t="n">
-        <v>37.35</v>
+        <v>37.32</v>
       </c>
       <c r="H3" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -940,22 +940,22 @@
         <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="n">
         <v>41.6</v>
       </c>
       <c r="R3" t="n">
-        <v>77.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>76</v>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>308.8475</v>
+        <v>308.63</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.02</v>
+        <v>-2.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.93</v>
+        <v>20.84</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.31</v>
+        <v>13.23</v>
       </c>
       <c r="AA3" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.7</v>
+        <v>17.67</v>
       </c>
       <c r="AC3" t="n">
         <v>26.45</v>
@@ -999,10 +999,10 @@
         <v>0.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>293.4609</v>
+        <v>293.4566</v>
       </c>
       <c r="AG3" t="n">
-        <v>270.3223</v>
+        <v>270.3212</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>41.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>77.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AM3" t="n">
         <v>753</v>
@@ -1037,10 +1037,10 @@
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.23</v>
+        <v>5.17</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.24</v>
+        <v>14.17</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>74.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4716555141120</v>
+        <v>4718977351680</v>
       </c>
       <c r="G4" t="n">
-        <v>29.87</v>
+        <v>29.84</v>
       </c>
       <c r="H4" t="n">
         <v>15.26</v>
@@ -1145,7 +1145,7 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="P4" t="n">
         <v>71.7</v>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>194.73</v>
+        <v>194.83</v>
       </c>
       <c r="X4" t="n">
-        <v>-12.5</v>
+        <v>-12.46</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.93</v>
+        <v>10.99</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>27.19</v>
+        <v>27.26</v>
       </c>
       <c r="AB4" t="n">
-        <v>66.65000000000001</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>46.9</v>
@@ -1198,10 +1198,10 @@
         <v>1.42</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.6445</v>
+        <v>209.6465</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.8191</v>
+        <v>190.8196</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AK4" t="n">
         <v>14.2</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-7.12</v>
+        <v>-7.07</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2614838165504</v>
+        <v>2610427854848</v>
       </c>
       <c r="G5" t="n">
-        <v>31.82</v>
+        <v>31.64</v>
       </c>
       <c r="H5" t="n">
-        <v>24.55</v>
+        <v>24.51</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,16 +1342,16 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>76.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="P5" t="n">
-        <v>56.2</v>
+        <v>56.4</v>
       </c>
       <c r="Q5" t="n">
         <v>37.8</v>
       </c>
       <c r="R5" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="S5" t="n">
         <v>65.8</v>
@@ -1368,22 +1368,22 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>243.095</v>
+        <v>242.67</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.23</v>
+        <v>-5.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.45</v>
+        <v>15.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.27</v>
+        <v>10.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.23</v>
+        <v>23.16</v>
       </c>
       <c r="AC5" t="n">
         <v>31.26</v>
@@ -1395,10 +1395,10 @@
         <v>0.74</v>
       </c>
       <c r="AF5" t="n">
-        <v>255.4253</v>
+        <v>255.4168</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.9847</v>
+        <v>232.9826</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>76.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AK5" t="n">
         <v>37.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="AM5" t="n">
         <v>753</v>
@@ -1433,10 +1433,10 @@
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.83</v>
+        <v>-4.99</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.34</v>
+        <v>4.16</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 4.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.8%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1510,50 +1510,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>608112017408</v>
+        <v>2900729528320</v>
       </c>
       <c r="G6" t="n">
-        <v>60.82</v>
+        <v>23.26</v>
       </c>
       <c r="H6" t="n">
-        <v>36.54</v>
+        <v>20.16</v>
       </c>
       <c r="I6" t="n">
-        <v>29.71</v>
+        <v>39.34</v>
       </c>
       <c r="J6" t="n">
-        <v>52.24</v>
+        <v>34.01</v>
       </c>
       <c r="K6" t="n">
-        <v>13.2</v>
+        <v>18.3</v>
       </c>
       <c r="L6" t="n">
-        <v>12.99</v>
+        <v>30.27</v>
       </c>
       <c r="M6" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>41.6</v>
       </c>
       <c r="P6" t="n">
-        <v>12.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.7</v>
+        <v>43.1</v>
       </c>
       <c r="R6" t="n">
-        <v>57.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>65.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,98 +1562,98 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1577.8</v>
+        <v>390.49</v>
       </c>
       <c r="X6" t="n">
-        <v>6.23</v>
+        <v>-11.52</v>
       </c>
       <c r="Y6" t="n">
-        <v>33.15</v>
+        <v>5.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>60.54</v>
+        <v>-19.54</v>
       </c>
       <c r="AA6" t="n">
-        <v>136.81</v>
+        <v>-20.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>33.95</v>
+        <v>5.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>38.76</v>
+        <v>24.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>-44.77</v>
+        <v>-34.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.88</v>
+        <v>0.24</v>
       </c>
       <c r="AF6" t="n">
-        <v>1429.842</v>
+        <v>407.2164</v>
       </c>
       <c r="AG6" t="n">
-        <v>1132.5621</v>
+        <v>443.7846</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>100</v>
+        <v>41.6</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.7</v>
+        <v>43.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>57.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="AN6" t="n">
-        <v>1462.2</v>
+        <v>352.83</v>
       </c>
       <c r="AO6" t="n">
-        <v>1171.8</v>
+        <v>352.83</v>
       </c>
       <c r="AP6" t="n">
-        <v>1721.4</v>
+        <v>428.05</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1721.4</v>
+        <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.35</v>
+        <v>-4.11</v>
       </c>
       <c r="AS6" t="n">
-        <v>39.31</v>
+        <v>-12.01</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 10.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 4.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>43.3</v>
+        <v>59</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 65.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.3%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 64.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.1%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1709,48 +1709,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2902809378816</v>
+        <v>629926658048</v>
       </c>
       <c r="G7" t="n">
-        <v>23.27</v>
+        <v>63.15</v>
       </c>
       <c r="H7" t="n">
-        <v>20.18</v>
+        <v>37.85</v>
       </c>
       <c r="I7" t="n">
-        <v>39.34</v>
+        <v>29.71</v>
       </c>
       <c r="J7" t="n">
-        <v>34.01</v>
+        <v>52.24</v>
       </c>
       <c r="K7" t="n">
-        <v>18.3</v>
+        <v>13.2</v>
       </c>
       <c r="L7" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>12.99</v>
+      </c>
+      <c r="M7" t="n">
+        <v>68</v>
+      </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>41.8</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>72.40000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>43.1</v>
+        <v>17.6</v>
       </c>
       <c r="R7" t="n">
-        <v>69.2</v>
+        <v>44.2</v>
       </c>
       <c r="S7" t="n">
-        <v>64.5</v>
+        <v>63.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1759,98 +1761,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>390.785</v>
+        <v>1634.4</v>
       </c>
       <c r="X7" t="n">
-        <v>-11.45</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.03</v>
+        <v>41.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>-19.48</v>
+        <v>55.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>-19.95</v>
+        <v>142.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.8</v>
+        <v>35.46</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.45</v>
+        <v>38.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>-34.5</v>
+        <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.24</v>
+        <v>0.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>407.2223</v>
+        <v>1438.108</v>
       </c>
       <c r="AG7" t="n">
-        <v>443.7861</v>
+        <v>1136.7852</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>41.8</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>43.1</v>
+        <v>17.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>69.2</v>
+        <v>44.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="AN7" t="n">
-        <v>352.83</v>
+        <v>1507.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>352.83</v>
+        <v>1171.8</v>
       </c>
       <c r="AP7" t="n">
-        <v>428.05</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>460.52</v>
+        <v>1721.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.04</v>
+        <v>13.65</v>
       </c>
       <c r="AS7" t="n">
-        <v>-11.94</v>
+        <v>43.77</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 4.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 13.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>59.1</v>
+        <v>33.3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1859,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 64.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 63.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.7%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1879,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1910,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1481563570176</v>
+        <v>1479647035392</v>
       </c>
       <c r="G8" t="n">
-        <v>21.21</v>
+        <v>21.19</v>
       </c>
       <c r="H8" t="n">
-        <v>15.97</v>
+        <v>15.83</v>
       </c>
       <c r="I8" t="n">
         <v>32.84</v>
@@ -1931,22 +1933,22 @@
         <v>35.61</v>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>39.2</v>
+        <v>39</v>
       </c>
       <c r="P8" t="n">
-        <v>80.8</v>
+        <v>81</v>
       </c>
       <c r="Q8" t="n">
         <v>28.4</v>
       </c>
       <c r="R8" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="S8" t="n">
         <v>62.9</v>
@@ -1963,25 +1965,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>583.66</v>
+        <v>582.9</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.25</v>
+        <v>-2.37</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>-12.2</v>
+        <v>-12.31</v>
       </c>
       <c r="AA8" t="n">
-        <v>-18.58</v>
+        <v>-18.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.33</v>
+        <v>27.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.87</v>
+        <v>36.88</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
@@ -1990,10 +1992,10 @@
         <v>0.74</v>
       </c>
       <c r="AF8" t="n">
-        <v>604.8215</v>
+        <v>604.8063</v>
       </c>
       <c r="AG8" t="n">
-        <v>645.4103</v>
+        <v>645.4065000000001</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2004,13 +2006,13 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>39.2</v>
+        <v>39</v>
       </c>
       <c r="AK8" t="n">
         <v>28.4</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="AM8" t="n">
         <v>753</v>
@@ -2028,10 +2030,10 @@
         <v>687.9124</v>
       </c>
       <c r="AR8" t="n">
-        <v>-3.5</v>
+        <v>-3.62</v>
       </c>
       <c r="AS8" t="n">
-        <v>-9.57</v>
+        <v>-9.68</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2058,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 62.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 62.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2256,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1479867891712</v>
+        <v>1477689606144</v>
       </c>
       <c r="G10" t="n">
-        <v>354.98</v>
+        <v>357.68</v>
       </c>
       <c r="H10" t="n">
-        <v>154.88</v>
+        <v>154.47</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2281,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>54.5</v>
+        <v>54.1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2290,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>70.7</v>
+        <v>70.5</v>
       </c>
       <c r="S10" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2307,22 +2309,22 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>394.06</v>
+        <v>393.45</v>
       </c>
       <c r="X10" t="n">
-        <v>-7</v>
+        <v>-7.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>-13.28</v>
+        <v>-13.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>31.04</v>
+        <v>30.84</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.14</v>
+        <v>12.08</v>
       </c>
       <c r="AC10" t="n">
         <v>57.97</v>
@@ -2334,10 +2336,10 @@
         <v>0.21</v>
       </c>
       <c r="AF10" t="n">
-        <v>406.4322</v>
+        <v>406.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>418.6108</v>
+        <v>418.6078</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2348,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>54.5</v>
+        <v>54.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>70.7</v>
+        <v>70.5</v>
       </c>
       <c r="AM10" t="n">
         <v>753</v>
@@ -2372,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-3.04</v>
+        <v>-3.19</v>
       </c>
       <c r="AS10" t="n">
-        <v>-5.86</v>
+        <v>-6.01</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2393,7 +2395,7 @@
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2402,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 38.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.0%.</t>
+          <t>TSLA: scenario base High Risk, score 38.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4391827931136</v>
+        <v>4471754588160</v>
       </c>
       <c r="G2" t="n">
-        <v>27.47</v>
+        <v>27.97</v>
       </c>
       <c r="H2" t="n">
-        <v>24.72</v>
+        <v>25.17</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>61</v>
+        <v>59.7</v>
       </c>
       <c r="Q2" t="n">
         <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>75.3</v>
+        <v>77.8</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>359.91</v>
+        <v>366.46</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.48</v>
+        <v>2.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.1</v>
+        <v>23.97</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.83</v>
+        <v>17.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>105.26</v>
+        <v>105.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.89</v>
+        <v>46.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.96</v>
+        <v>29.99</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF2" t="n">
-        <v>370.8261</v>
+        <v>371.373</v>
       </c>
       <c r="AG2" t="n">
-        <v>315.8091</v>
+        <v>316.3881</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>75.3</v>
+        <v>77.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-2.94</v>
+        <v>-1.32</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.96</v>
+        <v>15.83</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>75.2</v>
+        <v>75.8</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.9%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.3%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4532958920704</v>
+        <v>4592148938752</v>
       </c>
       <c r="G3" t="n">
-        <v>37.32</v>
+        <v>37.81</v>
       </c>
       <c r="H3" t="n">
-        <v>32.12</v>
+        <v>32.54</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>39</v>
+        <v>37.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="R3" t="n">
-        <v>78.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="S3" t="n">
-        <v>76</v>
+        <v>75.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>308.63</v>
+        <v>312.66</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.08</v>
+        <v>0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.84</v>
+        <v>22.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.23</v>
+        <v>15.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>49.1</v>
+        <v>47.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.67</v>
+        <v>18.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.45</v>
+        <v>26.49</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>293.4566</v>
+        <v>294.2514</v>
       </c>
       <c r="AG3" t="n">
-        <v>270.3212</v>
+        <v>270.6971</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>78.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN3" t="n">
         <v>275.15</v>
@@ -1031,16 +1031,16 @@
         <v>258.5917</v>
       </c>
       <c r="AP3" t="n">
-        <v>311.23</v>
+        <v>312.66</v>
       </c>
       <c r="AQ3" t="n">
         <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.17</v>
+        <v>6.26</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.17</v>
+        <v>15.5</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>74.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.3%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4718977351680</v>
+        <v>4736416743424</v>
       </c>
       <c r="G4" t="n">
-        <v>29.84</v>
+        <v>29.95</v>
       </c>
       <c r="H4" t="n">
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1145,19 +1145,19 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>74.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>71.7</v>
+        <v>71.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>69.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="S4" t="n">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>194.83</v>
+        <v>195.55</v>
       </c>
       <c r="X4" t="n">
-        <v>-12.46</v>
+        <v>-8.83</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.99</v>
+        <v>10.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.01</v>
+        <v>4.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>27.26</v>
+        <v>24.52</v>
       </c>
       <c r="AB4" t="n">
-        <v>66.68000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.9</v>
+        <v>46.96</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.6465</v>
+        <v>209.5122</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.8196</v>
+        <v>190.924</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,34 +1212,34 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>74.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>69.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN4" t="n">
         <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>181.868</v>
+        <v>183.6959</v>
       </c>
       <c r="AP4" t="n">
-        <v>218.66</v>
+        <v>212.45</v>
       </c>
       <c r="AQ4" t="n">
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-7.07</v>
+        <v>-6.66</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.7% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 69.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 68.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.7%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 181.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 183.70 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2610427854848</v>
+        <v>2626455863296</v>
       </c>
       <c r="G5" t="n">
-        <v>31.64</v>
+        <v>31.83</v>
       </c>
       <c r="H5" t="n">
-        <v>24.51</v>
+        <v>24.66</v>
       </c>
       <c r="I5" t="n">
         <v>12.22</v>
@@ -1342,19 +1342,19 @@
         <v>78.2</v>
       </c>
       <c r="O5" t="n">
-        <v>76.5</v>
+        <v>79.2</v>
       </c>
       <c r="P5" t="n">
-        <v>56.4</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="n">
         <v>37.8</v>
       </c>
       <c r="R5" t="n">
-        <v>72.3</v>
+        <v>73.3</v>
       </c>
       <c r="S5" t="n">
-        <v>65.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>242.67</v>
+        <v>244.16</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.4</v>
+        <v>-2.34</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.24</v>
+        <v>16.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.36</v>
+        <v>5.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.07</v>
+        <v>11.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.16</v>
+        <v>23.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.26</v>
+        <v>31.28</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="AF5" t="n">
-        <v>255.4168</v>
+        <v>255.1928</v>
       </c>
       <c r="AG5" t="n">
-        <v>232.9826</v>
+        <v>233.0331</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,34 +1409,34 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>76.5</v>
+        <v>79.2</v>
       </c>
       <c r="AK5" t="n">
         <v>37.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>72.3</v>
+        <v>73.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN5" t="n">
         <v>227.01</v>
       </c>
       <c r="AO5" t="n">
-        <v>221.25</v>
+        <v>227.01</v>
       </c>
       <c r="AP5" t="n">
-        <v>253.79</v>
+        <v>246.03</v>
       </c>
       <c r="AQ5" t="n">
         <v>274.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.99</v>
+        <v>-4.32</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.16</v>
+        <v>4.77</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.3% sotto MA50: attendere recupero; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>64.8</v>
+        <v>65.8</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.3%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 221.25 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1505,55 +1505,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2900729528320</v>
+        <v>1523790118912</v>
       </c>
       <c r="G6" t="n">
-        <v>23.26</v>
+        <v>21.82</v>
       </c>
       <c r="H6" t="n">
-        <v>20.16</v>
+        <v>16.3</v>
       </c>
       <c r="I6" t="n">
-        <v>39.34</v>
+        <v>32.84</v>
       </c>
       <c r="J6" t="n">
-        <v>34.01</v>
+        <v>32.93</v>
       </c>
       <c r="K6" t="n">
-        <v>18.3</v>
+        <v>33.1</v>
       </c>
       <c r="L6" t="n">
-        <v>30.27</v>
+        <v>35.61</v>
       </c>
       <c r="M6" t="n">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>41.6</v>
+        <v>47.2</v>
       </c>
       <c r="P6" t="n">
-        <v>72.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.1</v>
+        <v>28.4</v>
       </c>
       <c r="R6" t="n">
-        <v>69.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="S6" t="n">
-        <v>64.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,42 +1562,42 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>390.49</v>
+        <v>600.29</v>
       </c>
       <c r="X6" t="n">
-        <v>-11.52</v>
+        <v>-3.55</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.95</v>
+        <v>4.59</v>
       </c>
       <c r="Z6" t="n">
-        <v>-19.54</v>
+        <v>-8.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>-20.01</v>
+        <v>-15.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.78</v>
+        <v>27.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.45</v>
+        <v>36.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>-34.5</v>
+        <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.24</v>
+        <v>0.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>407.2164</v>
+        <v>603.3302</v>
       </c>
       <c r="AG6" t="n">
-        <v>443.7846</v>
+        <v>644.5257</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,34 +1608,34 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>41.6</v>
+        <v>47.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>43.1</v>
+        <v>28.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>69.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN6" t="n">
-        <v>352.83</v>
+        <v>542.87</v>
       </c>
       <c r="AO6" t="n">
-        <v>352.83</v>
+        <v>542.87</v>
       </c>
       <c r="AP6" t="n">
-        <v>428.05</v>
+        <v>612.91</v>
       </c>
       <c r="AQ6" t="n">
-        <v>460.52</v>
+        <v>687.9124</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.11</v>
+        <v>-0.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>-12.01</v>
+        <v>-6.86</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1644,16 +1644,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 4.1% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>59</v>
+        <v>47.3</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 64.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.1%.</t>
+          <t>META: scenario base Hold / Monitor, score 65.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>629926658048</v>
+        <v>627614154752</v>
       </c>
       <c r="G7" t="n">
-        <v>63.15</v>
+        <v>63.07</v>
       </c>
       <c r="H7" t="n">
-        <v>37.85</v>
+        <v>37.66</v>
       </c>
       <c r="I7" t="n">
         <v>29.71</v>
@@ -1734,7 +1734,7 @@
         <v>12.99</v>
       </c>
       <c r="M7" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1743,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="Q7" t="n">
         <v>17.6</v>
       </c>
       <c r="R7" t="n">
-        <v>44.2</v>
+        <v>48.2</v>
       </c>
       <c r="S7" t="n">
-        <v>63.5</v>
+        <v>63.9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,22 +1766,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1634.4</v>
+        <v>1628.4</v>
       </c>
       <c r="X7" t="n">
-        <v>9.109999999999999</v>
+        <v>11.37</v>
       </c>
       <c r="Y7" t="n">
-        <v>41.09</v>
+        <v>46.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>55.74</v>
+        <v>54.02</v>
       </c>
       <c r="AA7" t="n">
-        <v>142.67</v>
+        <v>141.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>35.46</v>
+        <v>37.21</v>
       </c>
       <c r="AC7" t="n">
         <v>38.79</v>
@@ -1790,13 +1790,13 @@
         <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1438.108</v>
+        <v>1445.684</v>
       </c>
       <c r="AG7" t="n">
-        <v>1136.7852</v>
+        <v>1140.9797</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         <v>17.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>44.2</v>
+        <v>48.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AN7" t="n">
         <v>1507.2</v>
@@ -1831,10 +1831,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.65</v>
+        <v>12.64</v>
       </c>
       <c r="AS7" t="n">
-        <v>43.77</v>
+        <v>42.72</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 13.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 12.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>33.3</v>
+        <v>36.3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 63.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.7%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 63.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.6%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1888,12 +1888,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1479647035392</v>
+        <v>2872872796160</v>
       </c>
       <c r="G8" t="n">
-        <v>21.19</v>
+        <v>23.03</v>
       </c>
       <c r="H8" t="n">
-        <v>15.83</v>
+        <v>19.97</v>
       </c>
       <c r="I8" t="n">
-        <v>32.84</v>
+        <v>39.34</v>
       </c>
       <c r="J8" t="n">
-        <v>32.93</v>
+        <v>34.01</v>
       </c>
       <c r="K8" t="n">
-        <v>33.1</v>
+        <v>18.3</v>
       </c>
       <c r="L8" t="n">
-        <v>35.61</v>
+        <v>30.27</v>
       </c>
       <c r="M8" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>39</v>
+        <v>38.3</v>
       </c>
       <c r="P8" t="n">
-        <v>81</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.4</v>
+        <v>43</v>
       </c>
       <c r="R8" t="n">
-        <v>69.8</v>
+        <v>68</v>
       </c>
       <c r="S8" t="n">
-        <v>62.9</v>
+        <v>63.6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1960,42 +1960,42 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>582.9</v>
+        <v>386.74</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.37</v>
+        <v>-9.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.73</v>
+        <v>3.78</v>
       </c>
       <c r="Z8" t="n">
-        <v>-12.31</v>
+        <v>-19.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>-18.69</v>
+        <v>-20.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.28</v>
+        <v>5.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>36.88</v>
+        <v>24.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>-34.15</v>
+        <v>-34.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.74</v>
+        <v>0.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>604.8063</v>
+        <v>406.3115</v>
       </c>
       <c r="AG8" t="n">
-        <v>645.4065000000001</v>
+        <v>443.1892</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,34 +2006,34 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>39</v>
+        <v>38.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>28.4</v>
+        <v>43</v>
       </c>
       <c r="AL8" t="n">
-        <v>69.8</v>
+        <v>68</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN8" t="n">
-        <v>542.87</v>
+        <v>352.83</v>
       </c>
       <c r="AO8" t="n">
-        <v>542.87</v>
+        <v>352.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>626.9888999999999</v>
+        <v>416.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>687.9124</v>
+        <v>460.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>-3.62</v>
+        <v>-4.82</v>
       </c>
       <c r="AS8" t="n">
-        <v>-9.68</v>
+        <v>-12.74</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2042,16 +2042,16 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>43.9</v>
+        <v>57.8</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 62.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.6%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.8%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2100,124 +2100,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>1576540176384</v>
+      </c>
+      <c r="G9" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="H9" t="n">
+        <v>164.81</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>50</v>
-      </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>419.77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>407.0652</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>418.5985</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AK9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>100</v>
-      </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+        <v>751</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>345.62</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>425.3</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.28</v>
+      </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>32.3</v>
+        <v>41.8</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 47.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 345.62 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2227,19 +2277,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2247,174 +2297,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1477689606144</v>
-      </c>
-      <c r="G10" t="n">
-        <v>357.68</v>
-      </c>
-      <c r="H10" t="n">
-        <v>154.47</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
-        <v>54.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>393.45</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-7.15</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-13.42</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>30.84</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>406.42</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>418.6078</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>35</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>54.1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL10" t="n">
         <v>0</v>
       </c>
-      <c r="AL10" t="n">
-        <v>70.5</v>
-      </c>
       <c r="AM10" t="n">
-        <v>753</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>375.12</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>343.25</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>425.3</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-3.19</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-6.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>31</v>
+        <v>32.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 38.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.2%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4471754588160</v>
+        <v>4478710317056</v>
       </c>
       <c r="G2" t="n">
         <v>27.97</v>
       </c>
       <c r="H2" t="n">
-        <v>25.17</v>
+        <v>25.21</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>366.46</v>
+        <v>367.03</v>
       </c>
       <c r="X2" t="n">
-        <v>2.14</v>
+        <v>-1.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.97</v>
+        <v>22.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.23</v>
+        <v>16.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>105.72</v>
+        <v>105.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>46.09</v>
+        <v>47.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.99</v>
+        <v>29.95</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AF2" t="n">
-        <v>371.373</v>
+        <v>371.9398</v>
       </c>
       <c r="AG2" t="n">
-        <v>316.3881</v>
+        <v>316.978</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>-1.32</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.83</v>
+        <v>15.79</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4592148938752</v>
+        <v>4769841152000</v>
       </c>
       <c r="G3" t="n">
-        <v>37.81</v>
+        <v>30.16</v>
       </c>
       <c r="H3" t="n">
-        <v>32.54</v>
+        <v>15.43</v>
       </c>
       <c r="I3" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="J3" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="K3" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L3" t="n">
-        <v>79.55</v>
+        <v>6.55</v>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>73.7</v>
       </c>
       <c r="P3" t="n">
-        <v>37.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.5</v>
+        <v>14.1</v>
       </c>
       <c r="R3" t="n">
-        <v>73.7</v>
+        <v>70.7</v>
       </c>
       <c r="S3" t="n">
-        <v>75.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,80 +967,80 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>312.66</v>
+        <v>196.93</v>
       </c>
       <c r="X3" t="n">
-        <v>0.77</v>
+        <v>-9.94</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.28</v>
+        <v>10.86</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.22</v>
+        <v>4.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.76</v>
+        <v>23.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.6</v>
+        <v>67.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.49</v>
+        <v>46.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.7</v>
+        <v>1.44</v>
       </c>
       <c r="AF3" t="n">
-        <v>294.2514</v>
+        <v>209.6028</v>
       </c>
       <c r="AG3" t="n">
-        <v>270.6971</v>
+        <v>191.255</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>73.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.5</v>
+        <v>14.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>73.7</v>
+        <v>70.7</v>
       </c>
       <c r="AM3" t="n">
         <v>751</v>
       </c>
       <c r="AN3" t="n">
-        <v>275.15</v>
+        <v>192.53</v>
       </c>
       <c r="AO3" t="n">
-        <v>258.5917</v>
+        <v>188.63</v>
       </c>
       <c r="AP3" t="n">
-        <v>312.66</v>
+        <v>212.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>315.2</v>
+        <v>235.74</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.26</v>
+        <v>-6.05</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.5</v>
+        <v>2.97</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 6.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>73.59999999999999</v>
+        <v>49.9</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 68.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.0%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.74 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 258.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 188.63 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4736416743424</v>
+        <v>581903581184</v>
       </c>
       <c r="G4" t="n">
-        <v>29.95</v>
+        <v>58.32</v>
       </c>
       <c r="H4" t="n">
-        <v>15.32</v>
+        <v>34.92</v>
       </c>
       <c r="I4" t="n">
-        <v>62.97</v>
+        <v>29.71</v>
       </c>
       <c r="J4" t="n">
-        <v>114.29</v>
+        <v>52.24</v>
       </c>
       <c r="K4" t="n">
-        <v>85.2</v>
+        <v>13.2</v>
       </c>
       <c r="L4" t="n">
-        <v>6.55</v>
+        <v>12.99</v>
       </c>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>73.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>71.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>17.4</v>
       </c>
       <c r="R4" t="n">
-        <v>69.8</v>
+        <v>82.7</v>
       </c>
       <c r="S4" t="n">
-        <v>68.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,75 +1171,75 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195.55</v>
+        <v>1509.8</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.83</v>
+        <v>-0.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.37</v>
+        <v>24.78</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.98</v>
+        <v>44.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.52</v>
+        <v>120.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>66.98999999999999</v>
+        <v>33.79</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.96</v>
+        <v>39.02</v>
       </c>
       <c r="AD4" t="n">
-        <v>-36.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.43</v>
+        <v>0.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.5122</v>
+        <v>1451.628</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.924</v>
+        <v>1144.4962</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>73.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.1</v>
+        <v>17.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>69.8</v>
+        <v>82.7</v>
       </c>
       <c r="AM4" t="n">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="AN4" t="n">
-        <v>192.53</v>
+        <v>1507.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>183.6959</v>
+        <v>1171.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>212.45</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>235.4656</v>
+        <v>1721.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>-6.66</v>
+        <v>4.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.42</v>
+        <v>31.92</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 6.7% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>49.6</v>
+        <v>56.9</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 68.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.7%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 68.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 183.70 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,53 +1308,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2626455863296</v>
+        <v>1562602635264</v>
       </c>
       <c r="G5" t="n">
-        <v>31.83</v>
+        <v>22.39</v>
       </c>
       <c r="H5" t="n">
-        <v>24.66</v>
+        <v>16.72</v>
       </c>
       <c r="I5" t="n">
-        <v>12.22</v>
+        <v>32.84</v>
       </c>
       <c r="J5" t="n">
-        <v>24.29</v>
+        <v>32.93</v>
       </c>
       <c r="K5" t="n">
-        <v>16.6</v>
+        <v>33.1</v>
       </c>
       <c r="L5" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>35.61</v>
+      </c>
+      <c r="M5" t="n">
+        <v>35</v>
+      </c>
       <c r="N5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O5" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="P5" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="R5" t="n">
         <v>78.2</v>
       </c>
-      <c r="O5" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>73.3</v>
-      </c>
       <c r="S5" t="n">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1363,80 +1365,80 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>244.16</v>
+        <v>615.58</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.34</v>
+        <v>-1.82</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.39</v>
+        <v>7.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.78</v>
+        <v>-5.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.02</v>
+        <v>-14.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.62</v>
+        <v>28.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.28</v>
+        <v>36.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>-30.88</v>
+        <v>-34.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AF5" t="n">
-        <v>255.1928</v>
+        <v>602.471</v>
       </c>
       <c r="AG5" t="n">
-        <v>233.0331</v>
+        <v>643.7376</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>79.2</v>
+        <v>53.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>37.8</v>
+        <v>28.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>73.3</v>
+        <v>78.2</v>
       </c>
       <c r="AM5" t="n">
         <v>751</v>
       </c>
       <c r="AN5" t="n">
-        <v>227.01</v>
+        <v>542.87</v>
       </c>
       <c r="AO5" t="n">
-        <v>227.01</v>
+        <v>542.87</v>
       </c>
       <c r="AP5" t="n">
-        <v>246.03</v>
+        <v>615.58</v>
       </c>
       <c r="AQ5" t="n">
-        <v>274.99</v>
+        <v>687.9124</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.32</v>
+        <v>2.18</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.77</v>
+        <v>-4.37</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1445,16 +1447,16 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 4.3% sotto MA50: attendere recupero; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>65.8</v>
+        <v>50.5</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.3%.</t>
+          <t>META: scenario base Hold / Monitor, score 68.0, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1505,55 +1507,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1523790118912</v>
+        <v>2646033825792</v>
       </c>
       <c r="G6" t="n">
-        <v>21.82</v>
+        <v>31.86</v>
       </c>
       <c r="H6" t="n">
-        <v>16.3</v>
+        <v>24.84</v>
       </c>
       <c r="I6" t="n">
-        <v>32.84</v>
+        <v>12.22</v>
       </c>
       <c r="J6" t="n">
-        <v>32.93</v>
+        <v>24.29</v>
       </c>
       <c r="K6" t="n">
-        <v>33.1</v>
+        <v>16.6</v>
       </c>
       <c r="L6" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="M6" t="n">
-        <v>36</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O6" t="n">
-        <v>47.2</v>
+        <v>79.5</v>
       </c>
       <c r="P6" t="n">
-        <v>79.59999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.4</v>
+        <v>37.8</v>
       </c>
       <c r="R6" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>65.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,98 +1562,98 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>600.29</v>
+        <v>245.98</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.55</v>
+        <v>-3.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.59</v>
+        <v>15.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>-8.9</v>
+        <v>8.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>-15.6</v>
+        <v>10.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>27.95</v>
+        <v>24.79</v>
       </c>
       <c r="AC6" t="n">
-        <v>36.92</v>
+        <v>31.26</v>
       </c>
       <c r="AD6" t="n">
-        <v>-34.15</v>
+        <v>-30.88</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>603.3302</v>
+        <v>255.0108</v>
       </c>
       <c r="AG6" t="n">
-        <v>644.5257</v>
+        <v>233.1049</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>47.2</v>
+        <v>79.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>28.4</v>
+        <v>37.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AM6" t="n">
         <v>751</v>
       </c>
       <c r="AN6" t="n">
-        <v>542.87</v>
+        <v>227.01</v>
       </c>
       <c r="AO6" t="n">
-        <v>542.87</v>
+        <v>227.01</v>
       </c>
       <c r="AP6" t="n">
-        <v>612.91</v>
+        <v>246.02</v>
       </c>
       <c r="AQ6" t="n">
-        <v>687.9124</v>
+        <v>274.99</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.5</v>
+        <v>-3.54</v>
       </c>
       <c r="AS6" t="n">
-        <v>-6.86</v>
+        <v>5.52</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>47.3</v>
+        <v>66.2</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 65.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.5%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1702,57 +1702,35 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>627614154752</v>
-      </c>
-      <c r="G7" t="n">
-        <v>63.07</v>
-      </c>
-      <c r="H7" t="n">
-        <v>37.66</v>
-      </c>
-      <c r="I7" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="J7" t="n">
-        <v>52.24</v>
-      </c>
-      <c r="K7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="M7" t="n">
-        <v>66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.6</v>
+        <v>41.5</v>
       </c>
       <c r="R7" t="n">
-        <v>48.2</v>
+        <v>77.5</v>
       </c>
       <c r="S7" t="n">
-        <v>63.9</v>
+        <v>65.2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,42 +1739,42 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1628.4</v>
+        <v>310.66</v>
       </c>
       <c r="X7" t="n">
-        <v>11.37</v>
+        <v>-0.18</v>
       </c>
       <c r="Y7" t="n">
-        <v>46.53</v>
+        <v>20.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>54.02</v>
+        <v>14.84</v>
       </c>
       <c r="AA7" t="n">
-        <v>141.46</v>
+        <v>46.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>37.21</v>
+        <v>18.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.79</v>
+        <v>26.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>-44.77</v>
+        <v>-33.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.96</v>
+        <v>0.71</v>
       </c>
       <c r="AF7" t="n">
-        <v>1445.684</v>
+        <v>295.0011</v>
       </c>
       <c r="AG7" t="n">
-        <v>1140.9797</v>
+        <v>271.0589</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,52 +1785,52 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.6</v>
+        <v>41.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>48.2</v>
+        <v>77.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="AN7" t="n">
-        <v>1507.2</v>
+        <v>275.15</v>
       </c>
       <c r="AO7" t="n">
-        <v>1171.8</v>
+        <v>258.5917</v>
       </c>
       <c r="AP7" t="n">
-        <v>1721.4</v>
+        <v>312.66</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1721.4</v>
+        <v>315.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.64</v>
+        <v>5.31</v>
       </c>
       <c r="AS7" t="n">
-        <v>42.72</v>
+        <v>14.61</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 12.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>36.3</v>
+        <v>69.7</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1839,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 63.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.6%.</t>
+          <t>AAPL: scenario base Hold / Monitor, score 65.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.3%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 258.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1859,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1890,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2872872796160</v>
+        <v>2888472723456</v>
       </c>
       <c r="G8" t="n">
-        <v>23.03</v>
+        <v>23.17</v>
       </c>
       <c r="H8" t="n">
-        <v>19.97</v>
+        <v>20.08</v>
       </c>
       <c r="I8" t="n">
         <v>39.34</v>
@@ -1933,25 +1911,25 @@
         <v>30.27</v>
       </c>
       <c r="M8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>38.3</v>
+        <v>40.5</v>
       </c>
       <c r="P8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="R8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="S8" t="n">
-        <v>63.6</v>
+        <v>64.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1943,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>386.74</v>
+        <v>388.84</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.5</v>
+        <v>-9.16</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.78</v>
+        <v>4.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>-19.68</v>
+        <v>-17.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>-20.62</v>
+        <v>-21.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.53</v>
+        <v>6.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>24.48</v>
+        <v>24.46</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>406.3115</v>
+        <v>405.7913</v>
       </c>
       <c r="AG8" t="n">
-        <v>443.1892</v>
+        <v>442.5993</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,13 +1984,13 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38.3</v>
+        <v>40.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AM8" t="n">
         <v>751</v>
@@ -2024,16 +2002,16 @@
         <v>352.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>416.67</v>
+        <v>411.74</v>
       </c>
       <c r="AQ8" t="n">
         <v>460.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>-4.82</v>
+        <v>-4.18</v>
       </c>
       <c r="AS8" t="n">
-        <v>-12.74</v>
+        <v>-12.15</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2025,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 4.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>57.8</v>
+        <v>58.7</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2038,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.8%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 64.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.2%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2111,13 +2089,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1576540176384</v>
+        <v>1513181151232</v>
       </c>
       <c r="G9" t="n">
-        <v>381.61</v>
+        <v>369.63</v>
       </c>
       <c r="H9" t="n">
-        <v>164.81</v>
+        <v>158.19</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2114,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>77.2</v>
+        <v>72</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2145,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>82.8</v>
+        <v>73.5</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,54 +2140,54 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>419.77</v>
+        <v>402.9</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.93</v>
+        <v>-3.72</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.41</v>
+        <v>14.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>-6.66</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>32.99</v>
+        <v>27.76</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.33</v>
+        <v>14.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>58.16</v>
+        <v>58.2</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>407.0652</v>
+        <v>407.6488</v>
       </c>
       <c r="AG9" t="n">
-        <v>418.5985</v>
+        <v>418.4837</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>77.2</v>
+        <v>72</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>82.8</v>
+        <v>73.5</v>
       </c>
       <c r="AM9" t="n">
         <v>751</v>
@@ -2218,7 +2196,7 @@
         <v>375.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>345.62</v>
+        <v>348.95</v>
       </c>
       <c r="AP9" t="n">
         <v>425.3</v>
@@ -2227,14 +2205,14 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.12</v>
+        <v>-1.16</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.28</v>
+        <v>-3.72</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2248,7 +2226,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>41.8</v>
+        <v>36.6</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2235,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 47.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.1%.</t>
+          <t>TSLA: scenario base High Risk, score 43.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.2%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -2267,7 +2245,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 345.62 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 348.95 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4478710317056</v>
+        <v>4416355172352</v>
       </c>
       <c r="G2" t="n">
-        <v>27.97</v>
+        <v>27.63</v>
       </c>
       <c r="H2" t="n">
-        <v>25.21</v>
+        <v>24.86</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,13 +750,13 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>59.7</v>
+        <v>60.6</v>
       </c>
       <c r="Q2" t="n">
         <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>77.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>78.59999999999999</v>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>367.03</v>
+        <v>361.89</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.42</v>
+        <v>18.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.61</v>
+        <v>14.48</v>
       </c>
       <c r="AA2" t="n">
-        <v>105.02</v>
+        <v>105.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>47.43</v>
+        <v>46.66</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.95</v>
+        <v>29.94</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AF2" t="n">
-        <v>371.9398</v>
+        <v>372.2937</v>
       </c>
       <c r="AG2" t="n">
-        <v>316.978</v>
+        <v>317.5297</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,16 +820,16 @@
         <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>77.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
       </c>
       <c r="AO2" t="n">
-        <v>317.0506</v>
+        <v>321.1182</v>
       </c>
       <c r="AP2" t="n">
         <v>373.25</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.32</v>
+        <v>-2.78</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.79</v>
+        <v>13.99</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>75.8</v>
+        <v>75.3</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.3%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 317.05 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 321.12 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4769841152000</v>
+        <v>4602870628352</v>
       </c>
       <c r="G3" t="n">
-        <v>30.16</v>
+        <v>37.94</v>
       </c>
       <c r="H3" t="n">
-        <v>15.43</v>
+        <v>32.61</v>
       </c>
       <c r="I3" t="n">
-        <v>62.97</v>
+        <v>27.15</v>
       </c>
       <c r="J3" t="n">
-        <v>114.29</v>
+        <v>141.47</v>
       </c>
       <c r="K3" t="n">
-        <v>85.2</v>
+        <v>16.6</v>
       </c>
       <c r="L3" t="n">
-        <v>6.55</v>
+        <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>73.7</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>71.09999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.1</v>
+        <v>41.5</v>
       </c>
       <c r="R3" t="n">
-        <v>70.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>68.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,80 +967,80 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>196.93</v>
+        <v>313.32</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.94</v>
+        <v>1.95</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.86</v>
+        <v>23.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.28</v>
+        <v>17.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.61</v>
+        <v>49.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>67.75</v>
+        <v>19.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>46.96</v>
+        <v>26.47</v>
       </c>
       <c r="AD3" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>209.6028</v>
+        <v>295.8513</v>
       </c>
       <c r="AG3" t="n">
-        <v>191.255</v>
+        <v>271.4394</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>73.7</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.1</v>
+        <v>41.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>70.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
-        <v>192.53</v>
+        <v>275.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>188.63</v>
+        <v>258.5917</v>
       </c>
       <c r="AP3" t="n">
-        <v>212.45</v>
+        <v>313.32</v>
       </c>
       <c r="AQ3" t="n">
-        <v>235.74</v>
+        <v>315.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>-6.05</v>
+        <v>5.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.97</v>
+        <v>15.43</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 6.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>49.9</v>
+        <v>74</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 68.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.0%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.9%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.74 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 188.63 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 258.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>581903581184</v>
+        <v>4943990226944</v>
       </c>
       <c r="G4" t="n">
-        <v>58.32</v>
+        <v>31.21</v>
       </c>
       <c r="H4" t="n">
-        <v>34.92</v>
+        <v>15.99</v>
       </c>
       <c r="I4" t="n">
-        <v>29.71</v>
+        <v>62.97</v>
       </c>
       <c r="J4" t="n">
-        <v>52.24</v>
+        <v>114.29</v>
       </c>
       <c r="K4" t="n">
-        <v>13.2</v>
+        <v>85.2</v>
       </c>
       <c r="L4" t="n">
-        <v>12.99</v>
+        <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>14.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.4</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>82.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>68.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,75 +1171,75 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1509.8</v>
+        <v>204.16</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.32</v>
+        <v>-0.46</v>
       </c>
       <c r="Y4" t="n">
-        <v>24.78</v>
+        <v>14.63</v>
       </c>
       <c r="Z4" t="n">
-        <v>44.05</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>120.56</v>
+        <v>29.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>33.79</v>
+        <v>69.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.02</v>
+        <v>46.97</v>
       </c>
       <c r="AD4" t="n">
-        <v>-44.77</v>
+        <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.87</v>
+        <v>1.48</v>
       </c>
       <c r="AF4" t="n">
-        <v>1451.628</v>
+        <v>209.5206</v>
       </c>
       <c r="AG4" t="n">
-        <v>1144.4962</v>
+        <v>191.3947</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.4</v>
+        <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>1507.2</v>
+        <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>1171.8</v>
+        <v>189.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1721.4</v>
+        <v>212.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1721.4</v>
+        <v>235.74</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.01</v>
+        <v>-2.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>31.92</v>
+        <v>6.68</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>56.9</v>
+        <v>53.7</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 68.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.0%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.74 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 189.31 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,55 +1308,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1562602635264</v>
+        <v>589303578624</v>
       </c>
       <c r="G5" t="n">
-        <v>22.39</v>
+        <v>59.22</v>
       </c>
       <c r="H5" t="n">
-        <v>16.72</v>
+        <v>35.32</v>
       </c>
       <c r="I5" t="n">
-        <v>32.84</v>
+        <v>29.71</v>
       </c>
       <c r="J5" t="n">
-        <v>32.93</v>
+        <v>52.24</v>
       </c>
       <c r="K5" t="n">
-        <v>33.1</v>
+        <v>13.2</v>
       </c>
       <c r="L5" t="n">
-        <v>35.61</v>
+        <v>12.99</v>
       </c>
       <c r="M5" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>53.9</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>78.3</v>
+        <v>13.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.3</v>
+        <v>17.4</v>
       </c>
       <c r="R5" t="n">
-        <v>78.2</v>
+        <v>79.5</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,75 +1370,75 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>615.58</v>
+        <v>1529</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.82</v>
+        <v>1.37</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.53</v>
+        <v>24.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>-5.19</v>
+        <v>51.47</v>
       </c>
       <c r="AA5" t="n">
-        <v>-14.1</v>
+        <v>125.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>28.5</v>
+        <v>34.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>36.94</v>
+        <v>39.02</v>
       </c>
       <c r="AD5" t="n">
-        <v>-34.15</v>
+        <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="AF5" t="n">
-        <v>602.471</v>
+        <v>1458.772</v>
       </c>
       <c r="AG5" t="n">
-        <v>643.7376</v>
+        <v>1148.0639</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>53.9</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>28.3</v>
+        <v>17.4</v>
       </c>
       <c r="AL5" t="n">
-        <v>78.2</v>
+        <v>79.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="AN5" t="n">
-        <v>542.87</v>
+        <v>1509.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>542.87</v>
+        <v>1171.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>615.58</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>687.9124</v>
+        <v>1721.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.18</v>
+        <v>4.81</v>
       </c>
       <c r="AS5" t="n">
-        <v>-4.37</v>
+        <v>33.18</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>50.5</v>
+        <v>55.9</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 68.0, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.8%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,53 +1507,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2646033825792</v>
+        <v>1530973782016</v>
       </c>
       <c r="G6" t="n">
-        <v>31.86</v>
+        <v>21.92</v>
       </c>
       <c r="H6" t="n">
-        <v>24.84</v>
+        <v>16.37</v>
       </c>
       <c r="I6" t="n">
-        <v>12.22</v>
+        <v>32.84</v>
       </c>
       <c r="J6" t="n">
-        <v>24.29</v>
+        <v>32.93</v>
       </c>
       <c r="K6" t="n">
-        <v>16.6</v>
+        <v>33.1</v>
       </c>
       <c r="L6" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>35.61</v>
+      </c>
+      <c r="M6" t="n">
+        <v>34</v>
+      </c>
       <c r="N6" t="n">
+        <v>100</v>
+      </c>
+      <c r="O6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="R6" t="n">
         <v>78.2</v>
       </c>
-      <c r="O6" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>74.40000000000001</v>
-      </c>
       <c r="S6" t="n">
-        <v>66.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,80 +1564,80 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>245.98</v>
+        <v>603.175</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.08</v>
+        <v>1.81</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.6</v>
+        <v>4.99</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.1</v>
+        <v>-15.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>24.79</v>
+        <v>27.59</v>
       </c>
       <c r="AC6" t="n">
-        <v>31.26</v>
+        <v>36.94</v>
       </c>
       <c r="AD6" t="n">
-        <v>-30.88</v>
+        <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>255.0108</v>
+        <v>601.0463999999999</v>
       </c>
       <c r="AG6" t="n">
-        <v>233.1049</v>
+        <v>642.865</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>79.5</v>
+        <v>48.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>37.8</v>
+        <v>28.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>74.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>227.01</v>
+        <v>542.87</v>
       </c>
       <c r="AO6" t="n">
-        <v>227.01</v>
+        <v>542.87</v>
       </c>
       <c r="AP6" t="n">
-        <v>246.02</v>
+        <v>615.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>274.99</v>
+        <v>687.9124</v>
       </c>
       <c r="AR6" t="n">
-        <v>-3.54</v>
+        <v>0.37</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.52</v>
+        <v>-6.16</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1644,16 +1646,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>66.2</v>
+        <v>49</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1664,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 66.7, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1684,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1702,35 +1704,55 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Internet Retail</t>
+        </is>
+      </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>2620647014400</v>
+      </c>
+      <c r="G7" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="H7" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>53.3</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>78.2</v>
       </c>
       <c r="O7" t="n">
-        <v>98.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="P7" t="n">
-        <v>50</v>
+        <v>56.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.5</v>
+        <v>37.8</v>
       </c>
       <c r="R7" t="n">
-        <v>77.5</v>
+        <v>73.3</v>
       </c>
       <c r="S7" t="n">
-        <v>65.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1744,75 +1766,75 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>310.66</v>
+        <v>243.6</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.18</v>
+        <v>-0.99</v>
       </c>
       <c r="Y7" t="n">
-        <v>20.12</v>
+        <v>13.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.84</v>
+        <v>4.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>46.05</v>
+        <v>9.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>18.78</v>
+        <v>24.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>26.48</v>
+        <v>31.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>-33.36</v>
+        <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>295.0011</v>
+        <v>254.603</v>
       </c>
       <c r="AG7" t="n">
-        <v>271.0589</v>
+        <v>233.1668</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>98.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>41.5</v>
+        <v>37.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>77.5</v>
+        <v>73.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
-        <v>275.15</v>
+        <v>227.01</v>
       </c>
       <c r="AO7" t="n">
-        <v>258.5917</v>
+        <v>227.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>312.66</v>
+        <v>246.02</v>
       </c>
       <c r="AQ7" t="n">
-        <v>315.2</v>
+        <v>274.99</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.31</v>
+        <v>-4.31</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.61</v>
+        <v>4.49</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1826,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 4.3% sotto MA50: attendere recupero; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>69.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1839,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Hold / Monitor, score 65.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.3%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.3%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 258.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1859,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -1890,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2888472723456</v>
+        <v>2845528817664</v>
       </c>
       <c r="G8" t="n">
-        <v>23.17</v>
+        <v>22.8</v>
       </c>
       <c r="H8" t="n">
-        <v>20.08</v>
+        <v>19.79</v>
       </c>
       <c r="I8" t="n">
         <v>39.34</v>
@@ -1917,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>40.5</v>
+        <v>37.7</v>
       </c>
       <c r="P8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="Q8" t="n">
         <v>43.1</v>
       </c>
       <c r="R8" t="n">
-        <v>69</v>
+        <v>67.2</v>
       </c>
       <c r="S8" t="n">
-        <v>64.2</v>
+        <v>63.4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1943,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>388.84</v>
+        <v>383.19</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.16</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.51</v>
+        <v>3.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>-17.42</v>
+        <v>-18.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>-21.43</v>
+        <v>-22.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.29</v>
+        <v>5.77</v>
       </c>
       <c r="AC8" t="n">
         <v>24.46</v>
@@ -1967,13 +1989,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AF8" t="n">
-        <v>405.7913</v>
+        <v>404.981</v>
       </c>
       <c r="AG8" t="n">
-        <v>442.5993</v>
+        <v>441.989</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1984,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40.5</v>
+        <v>37.7</v>
       </c>
       <c r="AK8" t="n">
         <v>43.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>69</v>
+        <v>67.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
         <v>352.83</v>
@@ -2002,16 +2024,16 @@
         <v>352.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>411.74</v>
+        <v>403.41</v>
       </c>
       <c r="AQ8" t="n">
         <v>460.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>-4.18</v>
+        <v>-5.39</v>
       </c>
       <c r="AS8" t="n">
-        <v>-12.15</v>
+        <v>-13.31</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2025,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 4.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>58.7</v>
+        <v>57.5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2038,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 64.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.2%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.4%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2089,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1513181151232</v>
+        <v>1479492239360</v>
       </c>
       <c r="G9" t="n">
-        <v>369.63</v>
+        <v>361.4</v>
       </c>
       <c r="H9" t="n">
-        <v>158.19</v>
+        <v>154.16</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2114,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>72</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2123,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>73.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>43.2</v>
+        <v>42.3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2140,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>402.9</v>
+        <v>393.9</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.72</v>
+        <v>0.74</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.19</v>
+        <v>13.63</v>
       </c>
       <c r="Z9" t="n">
-        <v>-8.029999999999999</v>
+        <v>-12.79</v>
       </c>
       <c r="AA9" t="n">
-        <v>27.76</v>
+        <v>34.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.43</v>
+        <v>13.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>58.2</v>
+        <v>58.17</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>407.6488</v>
+        <v>408.0008</v>
       </c>
       <c r="AG9" t="n">
-        <v>418.4837</v>
+        <v>418.369</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2181,22 +2203,22 @@
         <v>35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>72</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>73.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AM9" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN9" t="n">
         <v>375.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>348.95</v>
+        <v>352.42</v>
       </c>
       <c r="AP9" t="n">
         <v>425.3</v>
@@ -2205,10 +2227,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.16</v>
+        <v>-3.43</v>
       </c>
       <c r="AS9" t="n">
-        <v>-3.72</v>
+        <v>-5.83</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2226,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>36.6</v>
+        <v>35</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2235,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 43.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.2%.</t>
+          <t>TSLA: scenario base High Risk, score 42.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -2245,7 +2267,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 348.95 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.42 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4416355172352</v>
+        <v>4379381596160</v>
       </c>
       <c r="G2" t="n">
-        <v>27.63</v>
+        <v>27.4</v>
       </c>
       <c r="H2" t="n">
-        <v>24.86</v>
+        <v>24.65</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>60.6</v>
+        <v>61.2</v>
       </c>
       <c r="Q2" t="n">
         <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>75.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="S2" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>361.89</v>
+        <v>358.89</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.74</v>
+        <v>-1.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.54</v>
+        <v>13.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.48</v>
+        <v>14.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>105.28</v>
+        <v>106.42</v>
       </c>
       <c r="AB2" t="n">
-        <v>46.66</v>
+        <v>46.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.94</v>
+        <v>29.93</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AF2" t="n">
-        <v>372.2937</v>
+        <v>372.4695</v>
       </c>
       <c r="AG2" t="n">
-        <v>317.5297</v>
+        <v>318.0532</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,16 +820,16 @@
         <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>75.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
       </c>
       <c r="AO2" t="n">
-        <v>321.1182</v>
+        <v>332.0916</v>
       </c>
       <c r="AP2" t="n">
         <v>373.25</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-2.78</v>
+        <v>-3.65</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.99</v>
+        <v>12.84</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.6%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 321.12 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 332.09 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4602870628352</v>
+        <v>4644435656704</v>
       </c>
       <c r="G3" t="n">
-        <v>37.94</v>
+        <v>38.24</v>
       </c>
       <c r="H3" t="n">
-        <v>32.61</v>
+        <v>32.91</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -940,7 +940,7 @@
         <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
@@ -949,16 +949,16 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>37.5</v>
+        <v>36.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="R3" t="n">
-        <v>75.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>313.32</v>
+        <v>316.22</v>
       </c>
       <c r="X3" t="n">
-        <v>1.95</v>
+        <v>4.87</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.71</v>
+        <v>22.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.45</v>
+        <v>20.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>49.83</v>
+        <v>51.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.09</v>
+        <v>19.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.47</v>
+        <v>26.46</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>295.8513</v>
+        <v>296.8298</v>
       </c>
       <c r="AG3" t="n">
-        <v>271.4394</v>
+        <v>271.7968</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1016,13 +1016,13 @@
         <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>75.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
         <v>275.15</v>
@@ -1031,16 +1031,16 @@
         <v>258.5917</v>
       </c>
       <c r="AP3" t="n">
-        <v>313.32</v>
+        <v>316.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>315.2</v>
+        <v>316.22</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.9</v>
+        <v>6.53</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.43</v>
+        <v>16.34</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>74</v>
+        <v>73.2</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.5%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 316.22 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4943990226944</v>
+        <v>4911534178304</v>
       </c>
       <c r="G4" t="n">
-        <v>31.21</v>
+        <v>31.05</v>
       </c>
       <c r="H4" t="n">
-        <v>15.99</v>
+        <v>15.89</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1138,26 +1138,24 @@
       <c r="L4" t="n">
         <v>6.55</v>
       </c>
-      <c r="M4" t="n">
-        <v>51</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>82.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>69.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>71.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1169,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>204.16</v>
+        <v>202.78</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.46</v>
+        <v>-2.81</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.63</v>
+        <v>11.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.529999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.04</v>
+        <v>26.76</v>
       </c>
       <c r="AB4" t="n">
-        <v>69.67</v>
+        <v>69.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.97</v>
+        <v>46.94</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.5206</v>
+        <v>209.2432</v>
       </c>
       <c r="AG4" t="n">
-        <v>191.3947</v>
+        <v>191.5251</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,22 +1210,22 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>82.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN4" t="n">
         <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>189.31</v>
+        <v>192.53</v>
       </c>
       <c r="AP4" t="n">
         <v>212.45</v>
@@ -1236,10 +1234,10 @@
         <v>235.74</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2.55</v>
+        <v>-3.09</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.68</v>
+        <v>5.88</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1255,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>53.7</v>
+        <v>52.1</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1264,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 70.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1276,7 +1274,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 189.31 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 192.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1293,12 +1291,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,55 +1306,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>589303578624</v>
+        <v>1602963505152</v>
       </c>
       <c r="G5" t="n">
-        <v>59.22</v>
+        <v>22.96</v>
       </c>
       <c r="H5" t="n">
-        <v>35.32</v>
+        <v>17.14</v>
       </c>
       <c r="I5" t="n">
-        <v>29.71</v>
+        <v>32.84</v>
       </c>
       <c r="J5" t="n">
-        <v>52.24</v>
+        <v>32.93</v>
       </c>
       <c r="K5" t="n">
-        <v>13.2</v>
+        <v>33.1</v>
       </c>
       <c r="L5" t="n">
-        <v>12.99</v>
+        <v>35.61</v>
       </c>
       <c r="M5" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>48.9</v>
       </c>
       <c r="P5" t="n">
-        <v>13.8</v>
+        <v>77</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.4</v>
+        <v>28.3</v>
       </c>
       <c r="R5" t="n">
-        <v>79.5</v>
+        <v>73.3</v>
       </c>
       <c r="S5" t="n">
-        <v>67.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,75 +1368,75 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1529</v>
+        <v>631.48</v>
       </c>
       <c r="X5" t="n">
-        <v>1.37</v>
+        <v>7.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>24.1</v>
+        <v>3.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>51.47</v>
+        <v>-4.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>125.36</v>
+        <v>-12.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>34.02</v>
+        <v>29.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.02</v>
+        <v>37.01</v>
       </c>
       <c r="AD5" t="n">
-        <v>-44.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1458.772</v>
+        <v>600.1151</v>
       </c>
       <c r="AG5" t="n">
-        <v>1148.0639</v>
+        <v>642.1429000000001</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>48.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.4</v>
+        <v>28.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>79.5</v>
+        <v>73.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
-        <v>1509.8</v>
+        <v>542.87</v>
       </c>
       <c r="AO5" t="n">
-        <v>1171.8</v>
+        <v>542.87</v>
       </c>
       <c r="AP5" t="n">
-        <v>1721.4</v>
+        <v>631.48</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1721.4</v>
+        <v>687.9124</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.81</v>
+        <v>5.23</v>
       </c>
       <c r="AS5" t="n">
-        <v>33.18</v>
+        <v>-1.66</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1452,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>55.9</v>
+        <v>47.6</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 66.0, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1483,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,55 +1505,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1530973782016</v>
+        <v>617747447808</v>
       </c>
       <c r="G6" t="n">
-        <v>21.92</v>
+        <v>62.03</v>
       </c>
       <c r="H6" t="n">
-        <v>16.37</v>
+        <v>37.02</v>
       </c>
       <c r="I6" t="n">
-        <v>32.84</v>
+        <v>29.71</v>
       </c>
       <c r="J6" t="n">
-        <v>32.93</v>
+        <v>52.24</v>
       </c>
       <c r="K6" t="n">
-        <v>33.1</v>
+        <v>13.2</v>
       </c>
       <c r="L6" t="n">
-        <v>35.61</v>
+        <v>12.99</v>
       </c>
       <c r="M6" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>48.1</v>
+        <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>79.40000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.4</v>
+        <v>17.3</v>
       </c>
       <c r="R6" t="n">
-        <v>78.2</v>
+        <v>61.7</v>
       </c>
       <c r="S6" t="n">
-        <v>66.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,75 +1567,75 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>603.175</v>
+        <v>1602.8</v>
       </c>
       <c r="X6" t="n">
-        <v>1.81</v>
+        <v>6.34</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.99</v>
+        <v>26.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>-8.279999999999999</v>
+        <v>48.71</v>
       </c>
       <c r="AA6" t="n">
-        <v>-15.76</v>
+        <v>135.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>27.59</v>
+        <v>36.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>36.94</v>
+        <v>39.09</v>
       </c>
       <c r="AD6" t="n">
-        <v>-34.15</v>
+        <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>601.0463999999999</v>
+        <v>1466.976</v>
       </c>
       <c r="AG6" t="n">
-        <v>642.865</v>
+        <v>1152.0593</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>48.1</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>28.4</v>
+        <v>17.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>78.2</v>
+        <v>61.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="AN6" t="n">
-        <v>542.87</v>
+        <v>1509.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>542.87</v>
+        <v>1171.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>615.58</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>687.9124</v>
+        <v>1721.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.37</v>
+        <v>9.26</v>
       </c>
       <c r="AS6" t="n">
-        <v>-6.16</v>
+        <v>39.12</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1651,11 +1649,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 9.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>49</v>
+        <v>46.4</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 66.7, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 65.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.3%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1684,7 +1682,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1715,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2620647014400</v>
+        <v>2657436303360</v>
       </c>
       <c r="G7" t="n">
-        <v>31.35</v>
+        <v>32.08</v>
       </c>
       <c r="H7" t="n">
-        <v>24.63</v>
+        <v>24.97</v>
       </c>
       <c r="I7" t="n">
         <v>12.22</v>
@@ -1740,19 +1738,19 @@
         <v>78.2</v>
       </c>
       <c r="O7" t="n">
-        <v>74.5</v>
+        <v>71</v>
       </c>
       <c r="P7" t="n">
-        <v>56.6</v>
+        <v>55.3</v>
       </c>
       <c r="Q7" t="n">
         <v>37.8</v>
       </c>
       <c r="R7" t="n">
-        <v>73.3</v>
+        <v>75.5</v>
       </c>
       <c r="S7" t="n">
-        <v>65.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1764,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>243.6</v>
+        <v>247.04</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.99</v>
+        <v>0.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.95</v>
+        <v>11.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.52</v>
+        <v>2.54</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.01</v>
+        <v>12.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.35</v>
+        <v>24.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>31.24</v>
+        <v>31.23</v>
       </c>
       <c r="AD7" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>254.603</v>
+        <v>254.3218</v>
       </c>
       <c r="AG7" t="n">
-        <v>233.1668</v>
+        <v>233.2447</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1805,16 @@
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>74.5</v>
+        <v>71</v>
       </c>
       <c r="AK7" t="n">
         <v>37.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>73.3</v>
+        <v>75.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
         <v>227.01</v>
@@ -1825,16 +1823,16 @@
         <v>227.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>246.02</v>
+        <v>247.04</v>
       </c>
       <c r="AQ7" t="n">
         <v>274.99</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.31</v>
+        <v>-2.86</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.49</v>
+        <v>5.91</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1846,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 4.3% sotto MA50: attendere recupero; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>64.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1859,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.3%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 64.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.9%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1910,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2845528817664</v>
+        <v>2855193018368</v>
       </c>
       <c r="G8" t="n">
-        <v>22.8</v>
+        <v>22.89</v>
       </c>
       <c r="H8" t="n">
-        <v>19.79</v>
+        <v>19.86</v>
       </c>
       <c r="I8" t="n">
         <v>39.34</v>
@@ -1933,25 +1931,25 @@
         <v>30.27</v>
       </c>
       <c r="M8" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>37.7</v>
+        <v>37</v>
       </c>
       <c r="P8" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="Q8" t="n">
         <v>43.1</v>
       </c>
       <c r="R8" t="n">
-        <v>67.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>63.4</v>
+        <v>63.3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,25 +1963,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>383.19</v>
+        <v>384.36</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.039999999999999</v>
+        <v>-6.65</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>-18.6</v>
+        <v>-19.32</v>
       </c>
       <c r="AA8" t="n">
-        <v>-22.4</v>
+        <v>-21.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.77</v>
+        <v>5.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>24.46</v>
+        <v>24.44</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.5</v>
@@ -1992,10 +1990,10 @@
         <v>0.24</v>
       </c>
       <c r="AF8" t="n">
-        <v>404.981</v>
+        <v>404.1932</v>
       </c>
       <c r="AG8" t="n">
-        <v>441.989</v>
+        <v>441.3382</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2004,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>37.7</v>
+        <v>37</v>
       </c>
       <c r="AK8" t="n">
         <v>43.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>67.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
         <v>352.83</v>
@@ -2024,16 +2022,16 @@
         <v>352.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>403.41</v>
+        <v>399.76</v>
       </c>
       <c r="AQ8" t="n">
         <v>460.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>-5.39</v>
+        <v>-4.91</v>
       </c>
       <c r="AS8" t="n">
-        <v>-13.31</v>
+        <v>-12.91</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,7 +2045,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 5.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
@@ -2060,7 +2058,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.4%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2111,13 +2109,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1479492239360</v>
+        <v>1526889447424</v>
       </c>
       <c r="G9" t="n">
-        <v>361.4</v>
+        <v>369.59</v>
       </c>
       <c r="H9" t="n">
-        <v>154.16</v>
+        <v>158.75</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2134,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>69.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2145,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>70.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="S9" t="n">
-        <v>42.3</v>
+        <v>45.6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,37 +2160,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>393.9</v>
+        <v>406.55</v>
       </c>
       <c r="X9" t="n">
-        <v>0.74</v>
+        <v>-0.59</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.63</v>
+        <v>18.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>-12.79</v>
+        <v>-6.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>34.01</v>
+        <v>36.51</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.55</v>
+        <v>14.74</v>
       </c>
       <c r="AC9" t="n">
-        <v>58.17</v>
+        <v>58.16</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>408.0008</v>
+        <v>408.5616</v>
       </c>
       <c r="AG9" t="n">
-        <v>418.369</v>
+        <v>418.2721</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2203,22 +2201,22 @@
         <v>35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>69.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>70.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN9" t="n">
         <v>375.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>352.42</v>
+        <v>364.2</v>
       </c>
       <c r="AP9" t="n">
         <v>425.3</v>
@@ -2227,10 +2225,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-3.43</v>
+        <v>-0.49</v>
       </c>
       <c r="AS9" t="n">
-        <v>-5.83</v>
+        <v>-2.8</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2248,7 +2246,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>35</v>
+        <v>39.3</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2255,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 42.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.4%.</t>
+          <t>TSLA: scenario base High Risk, score 45.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.5%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -2267,7 +2265,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.42 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 364.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4379381596160</v>
+        <v>4359796293632</v>
       </c>
       <c r="G2" t="n">
-        <v>27.4</v>
+        <v>27.27</v>
       </c>
       <c r="H2" t="n">
-        <v>24.65</v>
+        <v>24.52</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -741,25 +741,25 @@
         <v>20.03</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="P2" t="n">
-        <v>61.2</v>
+        <v>61.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="R2" t="n">
-        <v>74.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>358.89</v>
+        <v>357.285</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.22</v>
+        <v>-1.91</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.17</v>
+        <v>12.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.32</v>
+        <v>11.11</v>
       </c>
       <c r="AA2" t="n">
-        <v>106.42</v>
+        <v>102.87</v>
       </c>
       <c r="AB2" t="n">
-        <v>46.17</v>
+        <v>45.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.93</v>
+        <v>29.91</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AF2" t="n">
-        <v>372.4695</v>
+        <v>372.6238</v>
       </c>
       <c r="AG2" t="n">
-        <v>318.0532</v>
+        <v>318.5795</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>74.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-3.65</v>
+        <v>-4.12</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.84</v>
+        <v>12.15</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.6%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.1%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4644435656704</v>
+        <v>4626076663808</v>
       </c>
       <c r="G3" t="n">
-        <v>38.24</v>
+        <v>38.18</v>
       </c>
       <c r="H3" t="n">
-        <v>32.91</v>
+        <v>32.78</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -949,16 +949,16 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="n">
         <v>41.6</v>
       </c>
       <c r="R3" t="n">
-        <v>72.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,25 +972,25 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>316.22</v>
+        <v>314.96</v>
       </c>
       <c r="X3" t="n">
-        <v>4.87</v>
+        <v>8.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.25</v>
+        <v>21.02</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.75</v>
+        <v>21.21</v>
       </c>
       <c r="AA3" t="n">
-        <v>51.17</v>
+        <v>49.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.43</v>
+        <v>19.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.46</v>
+        <v>26.44</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
@@ -999,10 +999,10 @@
         <v>0.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>296.8298</v>
+        <v>297.7198</v>
       </c>
       <c r="AG3" t="n">
-        <v>271.7968</v>
+        <v>272.0948</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1019,16 +1019,16 @@
         <v>41.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>72.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN3" t="n">
         <v>275.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>258.5917</v>
+        <v>263.1575</v>
       </c>
       <c r="AP3" t="n">
         <v>316.22</v>
@@ -1037,10 +1037,10 @@
         <v>316.22</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.53</v>
+        <v>5.79</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.34</v>
+        <v>15.76</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>73.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.5%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 258.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 263.16 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4911534178304</v>
+        <v>5101356843008</v>
       </c>
       <c r="G4" t="n">
-        <v>31.05</v>
+        <v>32.25</v>
       </c>
       <c r="H4" t="n">
-        <v>15.89</v>
+        <v>16.5</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1138,24 +1138,26 @@
       <c r="L4" t="n">
         <v>6.55</v>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>49</v>
+      </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>77.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="P4" t="n">
-        <v>69.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="Q4" t="n">
         <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>75.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>70.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1169,57 +1171,57 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>202.78</v>
+        <v>210.6171</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.81</v>
+        <v>1.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.37</v>
+        <v>14.66</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.31</v>
+        <v>11.51</v>
       </c>
       <c r="AA4" t="n">
-        <v>26.76</v>
+        <v>29.48</v>
       </c>
       <c r="AB4" t="n">
-        <v>69.17</v>
+        <v>71.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.94</v>
+        <v>46.95</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.2432</v>
+        <v>209.0669</v>
       </c>
       <c r="AG4" t="n">
-        <v>191.5251</v>
+        <v>191.4667</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>77.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="AK4" t="n">
         <v>14.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>75.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN4" t="n">
         <v>192.53</v>
@@ -1231,13 +1233,13 @@
         <v>212.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>235.74</v>
+        <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-3.09</v>
+        <v>0.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.88</v>
+        <v>10.01</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1251,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>52.1</v>
+        <v>56.5</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,12 +1266,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 70.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.74 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1315,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1602963505152</v>
+        <v>1701382062080</v>
       </c>
       <c r="G5" t="n">
-        <v>22.96</v>
+        <v>24.4</v>
       </c>
       <c r="H5" t="n">
-        <v>17.14</v>
+        <v>18.14</v>
       </c>
       <c r="I5" t="n">
         <v>32.84</v>
@@ -1336,25 +1338,25 @@
         <v>35.61</v>
       </c>
       <c r="M5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>48.9</v>
+        <v>59.5</v>
       </c>
       <c r="P5" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="R5" t="n">
-        <v>73.3</v>
+        <v>52</v>
       </c>
       <c r="S5" t="n">
-        <v>66</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,57 +1370,57 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>631.48</v>
+        <v>670.29</v>
       </c>
       <c r="X5" t="n">
-        <v>7.97</v>
+        <v>14.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.21</v>
+        <v>6.77</v>
       </c>
       <c r="Z5" t="n">
-        <v>-4.24</v>
+        <v>3.51</v>
       </c>
       <c r="AA5" t="n">
-        <v>-12.09</v>
+        <v>-8.23</v>
       </c>
       <c r="AB5" t="n">
-        <v>29.52</v>
+        <v>32.08</v>
       </c>
       <c r="AC5" t="n">
-        <v>37.01</v>
+        <v>37.15</v>
       </c>
       <c r="AD5" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AF5" t="n">
-        <v>600.1151</v>
+        <v>600.1065</v>
       </c>
       <c r="AG5" t="n">
-        <v>642.1429000000001</v>
+        <v>641.6785</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>48.9</v>
+        <v>59.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>73.3</v>
+        <v>52</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN5" t="n">
         <v>542.87</v>
@@ -1427,20 +1429,20 @@
         <v>542.87</v>
       </c>
       <c r="AP5" t="n">
-        <v>631.48</v>
+        <v>670.29</v>
       </c>
       <c r="AQ5" t="n">
         <v>687.9124</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.23</v>
+        <v>11.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1.66</v>
+        <v>4.46</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1450,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>47.6</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 66.0, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 67.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>617747447808</v>
+        <v>604720332800</v>
       </c>
       <c r="G6" t="n">
-        <v>62.03</v>
+        <v>60.79</v>
       </c>
       <c r="H6" t="n">
-        <v>37.02</v>
+        <v>35.97</v>
       </c>
       <c r="I6" t="n">
         <v>29.71</v>
@@ -1535,7 +1537,7 @@
         <v>12.99</v>
       </c>
       <c r="M6" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1544,16 +1546,16 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q6" t="n">
         <v>17.3</v>
       </c>
       <c r="R6" t="n">
-        <v>61.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>65.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,22 +1569,22 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1602.8</v>
+        <v>1569</v>
       </c>
       <c r="X6" t="n">
-        <v>6.34</v>
+        <v>-0.44</v>
       </c>
       <c r="Y6" t="n">
-        <v>26.48</v>
+        <v>24.82</v>
       </c>
       <c r="Z6" t="n">
-        <v>48.71</v>
+        <v>44.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>135.07</v>
+        <v>123.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>36.06</v>
+        <v>35.06</v>
       </c>
       <c r="AC6" t="n">
         <v>39.09</v>
@@ -1591,13 +1593,13 @@
         <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AF6" t="n">
-        <v>1466.976</v>
+        <v>1473.908</v>
       </c>
       <c r="AG6" t="n">
-        <v>1152.0593</v>
+        <v>1155.8673</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1614,10 +1616,10 @@
         <v>17.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>61.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN6" t="n">
         <v>1509.8</v>
@@ -1632,10 +1634,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.26</v>
+        <v>6.45</v>
       </c>
       <c r="AS6" t="n">
-        <v>39.12</v>
+        <v>35.74</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1649,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 9.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>46.4</v>
+        <v>53.9</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 65.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.3%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1689,12 +1691,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1704,53 +1706,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2657436303360</v>
+        <v>2865072963584</v>
       </c>
       <c r="G7" t="n">
-        <v>32.08</v>
+        <v>22.96</v>
       </c>
       <c r="H7" t="n">
-        <v>24.97</v>
+        <v>19.92</v>
       </c>
       <c r="I7" t="n">
-        <v>12.22</v>
+        <v>39.34</v>
       </c>
       <c r="J7" t="n">
-        <v>24.29</v>
+        <v>34.01</v>
       </c>
       <c r="K7" t="n">
-        <v>16.6</v>
+        <v>18.3</v>
       </c>
       <c r="L7" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>30.27</v>
+      </c>
+      <c r="M7" t="n">
+        <v>95</v>
+      </c>
       <c r="N7" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>71</v>
+        <v>37.4</v>
       </c>
       <c r="P7" t="n">
-        <v>55.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.8</v>
+        <v>43.1</v>
       </c>
       <c r="R7" t="n">
-        <v>75.5</v>
+        <v>68.7</v>
       </c>
       <c r="S7" t="n">
-        <v>64.5</v>
+        <v>63.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1759,84 +1763,84 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>247.04</v>
+        <v>385.6722</v>
       </c>
       <c r="X7" t="n">
-        <v>0.74</v>
+        <v>-4.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.66</v>
+        <v>3.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.54</v>
+        <v>-19.87</v>
       </c>
       <c r="AA7" t="n">
-        <v>12.62</v>
+        <v>-22.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.9</v>
+        <v>5.98</v>
       </c>
       <c r="AC7" t="n">
-        <v>31.23</v>
+        <v>24.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>-30.88</v>
+        <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="AF7" t="n">
-        <v>254.3218</v>
+        <v>403.3402</v>
       </c>
       <c r="AG7" t="n">
-        <v>233.2447</v>
+        <v>440.7105</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>71</v>
+        <v>37.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>37.8</v>
+        <v>43.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>75.5</v>
+        <v>68.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN7" t="n">
-        <v>227.01</v>
+        <v>352.83</v>
       </c>
       <c r="AO7" t="n">
-        <v>227.01</v>
+        <v>352.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>247.04</v>
+        <v>399.76</v>
       </c>
       <c r="AQ7" t="n">
-        <v>274.99</v>
+        <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-2.86</v>
+        <v>-4.38</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.91</v>
+        <v>-12.48</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1846,11 +1850,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 4.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>64.2</v>
+        <v>57.8</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1859,17 +1863,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 64.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.9%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.4%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1879,19 +1883,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1901,55 +1905,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2855193018368</v>
+        <v>2640547676160</v>
       </c>
       <c r="G8" t="n">
-        <v>22.89</v>
+        <v>31.43</v>
       </c>
       <c r="H8" t="n">
-        <v>19.86</v>
+        <v>24.82</v>
       </c>
       <c r="I8" t="n">
-        <v>39.34</v>
+        <v>12.22</v>
       </c>
       <c r="J8" t="n">
-        <v>34.01</v>
+        <v>24.29</v>
       </c>
       <c r="K8" t="n">
-        <v>18.3</v>
+        <v>16.6</v>
       </c>
       <c r="L8" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="M8" t="n">
-        <v>95</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>37</v>
+        <v>60.6</v>
       </c>
       <c r="P8" t="n">
-        <v>73.3</v>
+        <v>56.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>43.1</v>
+        <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>67.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="S8" t="n">
-        <v>63.3</v>
+        <v>62</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1958,84 +1960,84 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>384.36</v>
+        <v>245.47</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.65</v>
+        <v>0.52</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.9</v>
+        <v>5.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>-19.32</v>
+        <v>1.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>-21.99</v>
+        <v>10.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.87</v>
+        <v>24.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>24.44</v>
+        <v>31.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>-34.5</v>
+        <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.24</v>
+        <v>0.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>404.1932</v>
+        <v>254.0372</v>
       </c>
       <c r="AG8" t="n">
-        <v>441.3382</v>
+        <v>233.3339</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>37</v>
+        <v>60.6</v>
       </c>
       <c r="AK8" t="n">
-        <v>43.1</v>
+        <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>67.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN8" t="n">
-        <v>352.83</v>
+        <v>227.01</v>
       </c>
       <c r="AO8" t="n">
-        <v>352.83</v>
+        <v>227.01</v>
       </c>
       <c r="AP8" t="n">
-        <v>399.76</v>
+        <v>247.04</v>
       </c>
       <c r="AQ8" t="n">
-        <v>460.52</v>
+        <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-4.91</v>
+        <v>-3.37</v>
       </c>
       <c r="AS8" t="n">
-        <v>-12.91</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2045,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>57.5</v>
+        <v>61.3</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2058,17 +2060,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.9%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 62.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2078,7 +2080,7 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -2109,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1526889447424</v>
+        <v>1531621670912</v>
       </c>
       <c r="G9" t="n">
-        <v>369.59</v>
+        <v>370.74</v>
       </c>
       <c r="H9" t="n">
-        <v>158.75</v>
+        <v>158.21</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2134,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2143,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>74.5</v>
+        <v>74.7</v>
       </c>
       <c r="S9" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2160,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>406.55</v>
+        <v>407.81</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.59</v>
+        <v>2.81</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.44</v>
+        <v>17.99</v>
       </c>
       <c r="Z9" t="n">
-        <v>-6.1</v>
+        <v>-5.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>36.51</v>
+        <v>37.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.74</v>
+        <v>14.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>58.16</v>
+        <v>58.12</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>408.5616</v>
+        <v>409.1974</v>
       </c>
       <c r="AG9" t="n">
-        <v>418.2721</v>
+        <v>418.1401</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2201,22 +2203,22 @@
         <v>35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>74.5</v>
+        <v>74.7</v>
       </c>
       <c r="AM9" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN9" t="n">
         <v>375.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>364.2</v>
+        <v>372.8</v>
       </c>
       <c r="AP9" t="n">
         <v>425.3</v>
@@ -2225,10 +2227,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.49</v>
+        <v>-0.36</v>
       </c>
       <c r="AS9" t="n">
-        <v>-2.8</v>
+        <v>-2.49</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2246,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2255,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 45.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.5%.</t>
+          <t>TSLA: scenario base High Risk, score 45.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.4%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -2265,7 +2267,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 364.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 372.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4359796293632</v>
+        <v>4302993358848</v>
       </c>
       <c r="G2" t="n">
-        <v>27.27</v>
+        <v>26.9</v>
       </c>
       <c r="H2" t="n">
-        <v>24.52</v>
+        <v>24.1</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -747,63 +747,63 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>99.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="R2" t="n">
-        <v>73.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="S2" t="n">
-        <v>78.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>357.285</v>
+        <v>352.6352</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.91</v>
+        <v>-1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.25</v>
+        <v>11.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.11</v>
+        <v>8.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>102.87</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>45.88</v>
+        <v>42.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.91</v>
+        <v>29.83</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AF2" t="n">
-        <v>372.6238</v>
+        <v>372.6798</v>
       </c>
       <c r="AG2" t="n">
-        <v>318.5795</v>
+        <v>319.0863</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>99.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>73.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AM2" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.12</v>
+        <v>-5.39</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.15</v>
+        <v>10.51</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 4.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>74.7</v>
+        <v>73.2</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.1%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 77.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.4%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4626076663808</v>
+        <v>4665291833344</v>
       </c>
       <c r="G3" t="n">
-        <v>38.18</v>
+        <v>38.46</v>
       </c>
       <c r="H3" t="n">
-        <v>32.78</v>
+        <v>33.04</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -949,16 +949,16 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>37</v>
+        <v>36.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="R3" t="n">
-        <v>75.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="S3" t="n">
-        <v>75.5</v>
+        <v>75.2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,25 +972,25 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>314.96</v>
+        <v>317.66</v>
       </c>
       <c r="X3" t="n">
-        <v>8.4</v>
+        <v>8.94</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.02</v>
+        <v>22.06</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.21</v>
+        <v>22.86</v>
       </c>
       <c r="AA3" t="n">
-        <v>49.76</v>
+        <v>50.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.25</v>
+        <v>19.24</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.44</v>
+        <v>26.47</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
@@ -999,10 +999,10 @@
         <v>0.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>297.7198</v>
+        <v>298.6817</v>
       </c>
       <c r="AG3" t="n">
-        <v>272.0948</v>
+        <v>272.4164</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1016,13 +1016,13 @@
         <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>75.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="AM3" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>275.15</v>
@@ -1031,16 +1031,16 @@
         <v>263.1575</v>
       </c>
       <c r="AP3" t="n">
-        <v>316.22</v>
+        <v>317.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>316.22</v>
+        <v>317.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.79</v>
+        <v>6.35</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.76</v>
+        <v>16.6</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>74.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.8%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.3%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 316.22 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 317.65 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5101356843008</v>
+        <v>4942295203840</v>
       </c>
       <c r="G4" t="n">
-        <v>32.25</v>
+        <v>31.2</v>
       </c>
       <c r="H4" t="n">
-        <v>16.5</v>
+        <v>15.95</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>84.8</v>
+        <v>74</v>
       </c>
       <c r="P4" t="n">
-        <v>67.2</v>
+        <v>69.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>76.2</v>
       </c>
       <c r="S4" t="n">
-        <v>73.2</v>
+        <v>69.2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>210.6171</v>
+        <v>204.075</v>
       </c>
       <c r="X4" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.66</v>
+        <v>8.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.51</v>
+        <v>10.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.48</v>
+        <v>24.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>71.28</v>
+        <v>64.88</v>
       </c>
       <c r="AC4" t="n">
         <v>46.95</v>
@@ -1195,33 +1195,33 @@
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.0669</v>
+        <v>208.9751</v>
       </c>
       <c r="AG4" t="n">
-        <v>191.4667</v>
+        <v>191.5978</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>84.8</v>
+        <v>74</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>76.2</v>
       </c>
       <c r="AM4" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
         <v>192.53</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.75</v>
+        <v>-2.36</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.01</v>
+        <v>6.5</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>56.5</v>
+        <v>51.4</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 69.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.4%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,59 +1308,59 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1701382062080</v>
+        <v>593851580416</v>
       </c>
       <c r="G5" t="n">
-        <v>24.4</v>
+        <v>59.51</v>
       </c>
       <c r="H5" t="n">
-        <v>18.14</v>
+        <v>35</v>
       </c>
       <c r="I5" t="n">
-        <v>32.84</v>
+        <v>29.71</v>
       </c>
       <c r="J5" t="n">
-        <v>32.93</v>
+        <v>52.24</v>
       </c>
       <c r="K5" t="n">
-        <v>33.1</v>
+        <v>13.2</v>
       </c>
       <c r="L5" t="n">
-        <v>35.61</v>
+        <v>12.99</v>
       </c>
       <c r="M5" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>74</v>
+        <v>14.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.1</v>
+        <v>17.3</v>
       </c>
       <c r="R5" t="n">
-        <v>52</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>67.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>670.29</v>
+        <v>1540.8</v>
       </c>
       <c r="X5" t="n">
-        <v>14.77</v>
+        <v>-5.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.77</v>
+        <v>20.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.51</v>
+        <v>40.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>-8.23</v>
+        <v>148.18</v>
       </c>
       <c r="AB5" t="n">
-        <v>32.08</v>
+        <v>33.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>37.15</v>
+        <v>39.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>-34.15</v>
+        <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>600.1065</v>
+        <v>1480.976</v>
       </c>
       <c r="AG5" t="n">
-        <v>641.6785</v>
+        <v>1159.5288</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,38 +1411,38 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>28.1</v>
+        <v>17.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>52</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="AN5" t="n">
-        <v>542.87</v>
+        <v>1509.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>542.87</v>
+        <v>1171.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>670.29</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>687.9124</v>
+        <v>1721.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.7</v>
+        <v>4.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.46</v>
+        <v>32.88</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>56.8</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 67.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 68.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,55 +1507,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>604720332800</v>
+        <v>1663187681280</v>
       </c>
       <c r="G6" t="n">
-        <v>60.79</v>
+        <v>23.83</v>
       </c>
       <c r="H6" t="n">
-        <v>35.97</v>
+        <v>18.04</v>
       </c>
       <c r="I6" t="n">
-        <v>29.71</v>
+        <v>32.84</v>
       </c>
       <c r="J6" t="n">
-        <v>52.24</v>
+        <v>32.93</v>
       </c>
       <c r="K6" t="n">
-        <v>13.2</v>
+        <v>33.1</v>
       </c>
       <c r="L6" t="n">
-        <v>12.99</v>
+        <v>35.61</v>
       </c>
       <c r="M6" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>54.3</v>
       </c>
       <c r="P6" t="n">
-        <v>12.9</v>
+        <v>74.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.3</v>
+        <v>28.1</v>
       </c>
       <c r="R6" t="n">
-        <v>72.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="S6" t="n">
-        <v>66.8</v>
+        <v>67.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1569</v>
+        <v>655.24</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.44</v>
+        <v>14.86</v>
       </c>
       <c r="Y6" t="n">
-        <v>24.82</v>
+        <v>4.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>44.94</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>123.98</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>35.06</v>
+        <v>28.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.09</v>
+        <v>37.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>-44.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>1473.908</v>
+        <v>599.8197</v>
       </c>
       <c r="AG6" t="n">
-        <v>1155.8673</v>
+        <v>641.1821</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,34 +1610,34 @@
         <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>100</v>
+        <v>54.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.3</v>
+        <v>28.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>72.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>1509.8</v>
+        <v>542.87</v>
       </c>
       <c r="AO6" t="n">
-        <v>1171.8</v>
+        <v>542.87</v>
       </c>
       <c r="AP6" t="n">
-        <v>1721.4</v>
+        <v>669.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1721.4</v>
+        <v>687.9124</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.45</v>
+        <v>9.23</v>
       </c>
       <c r="AS6" t="n">
-        <v>35.74</v>
+        <v>2.19</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 9.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>53.9</v>
+        <v>42</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 67.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.2%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2865072963584</v>
+        <v>2904073175040</v>
       </c>
       <c r="G7" t="n">
-        <v>22.96</v>
+        <v>23.28</v>
       </c>
       <c r="H7" t="n">
-        <v>19.92</v>
+        <v>20.19</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1742,19 +1742,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>37.4</v>
+        <v>41.8</v>
       </c>
       <c r="P7" t="n">
-        <v>73.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="Q7" t="n">
         <v>43.1</v>
       </c>
       <c r="R7" t="n">
-        <v>68.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>63.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1768,37 +1768,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>385.6722</v>
+        <v>390.9401</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.4</v>
+        <v>-1.62</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.6</v>
+        <v>5.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>-19.87</v>
+        <v>-17.87</v>
       </c>
       <c r="AA7" t="n">
-        <v>-22.79</v>
+        <v>-21.42</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.98</v>
+        <v>5.34</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.43</v>
+        <v>24.44</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>403.3402</v>
+        <v>402.6767</v>
       </c>
       <c r="AG7" t="n">
-        <v>440.7105</v>
+        <v>440.1322</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,16 +1809,16 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>37.4</v>
+        <v>41.8</v>
       </c>
       <c r="AK7" t="n">
         <v>43.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>68.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
         <v>352.83</v>
@@ -1833,10 +1833,10 @@
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.38</v>
+        <v>-2.91</v>
       </c>
       <c r="AS7" t="n">
-        <v>-12.48</v>
+        <v>-11.18</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1850,11 +1850,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 4.4% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>57.8</v>
+        <v>59.5</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.4%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 64.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.9%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2640547676160</v>
+        <v>2656252985344</v>
       </c>
       <c r="G8" t="n">
-        <v>31.43</v>
+        <v>29.5</v>
       </c>
       <c r="H8" t="n">
-        <v>24.82</v>
+        <v>24.98</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>60.6</v>
+        <v>58</v>
       </c>
       <c r="P8" t="n">
-        <v>56.2</v>
+        <v>58.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="R8" t="n">
-        <v>74.7</v>
+        <v>75.7</v>
       </c>
       <c r="S8" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>245.47</v>
+        <v>246.93</v>
       </c>
       <c r="X8" t="n">
-        <v>0.52</v>
+        <v>3.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.06</v>
+        <v>3.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.62</v>
+        <v>0.26</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.6</v>
+        <v>22.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.21</v>
+        <v>31.2</v>
       </c>
       <c r="AD8" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AF8" t="n">
-        <v>254.0372</v>
+        <v>253.7124</v>
       </c>
       <c r="AG8" t="n">
-        <v>233.3339</v>
+        <v>233.4643</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60.6</v>
+        <v>58</v>
       </c>
       <c r="AK8" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>74.7</v>
+        <v>75.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
         <v>227.01</v>
@@ -2030,10 +2030,10 @@
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-3.37</v>
+        <v>-2.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>5.77</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 62.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 61.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1531621670912</v>
+        <v>1480956968960</v>
       </c>
       <c r="G9" t="n">
-        <v>370.74</v>
+        <v>358.47</v>
       </c>
       <c r="H9" t="n">
-        <v>158.21</v>
+        <v>152.98</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>81.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>74.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>45.7</v>
+        <v>42.1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>407.81</v>
+        <v>394.235</v>
       </c>
       <c r="X9" t="n">
-        <v>2.81</v>
+        <v>3.31</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.99</v>
+        <v>12.98</v>
       </c>
       <c r="Z9" t="n">
-        <v>-5.47</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>37.83</v>
+        <v>27.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.83</v>
+        <v>12.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>58.12</v>
+        <v>58.22</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="AF9" t="n">
-        <v>409.1974</v>
+        <v>409.6251</v>
       </c>
       <c r="AG9" t="n">
-        <v>418.1401</v>
+        <v>417.9818</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2203,16 +2203,16 @@
         <v>35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>81.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>74.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AM9" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN9" t="n">
         <v>375.12</v>
@@ -2227,10 +2227,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.36</v>
+        <v>-3.76</v>
       </c>
       <c r="AS9" t="n">
-        <v>-2.49</v>
+        <v>-5.68</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>39.5</v>
+        <v>34.7</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 45.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.4%.</t>
+          <t>TSLA: scenario base High Risk, score 42.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.8%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4302993358848</v>
+        <v>4389631688704</v>
       </c>
       <c r="G2" t="n">
-        <v>26.9</v>
+        <v>27.44</v>
       </c>
       <c r="H2" t="n">
-        <v>24.1</v>
+        <v>24.65</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -747,19 +747,19 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>95.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="P2" t="n">
-        <v>62.5</v>
+        <v>61.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="R2" t="n">
-        <v>71.7</v>
+        <v>74.7</v>
       </c>
       <c r="S2" t="n">
-        <v>77.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>352.6352</v>
+        <v>359.73</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.05</v>
+        <v>0.55</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.22</v>
+        <v>12.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.5</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>99.09999999999999</v>
+        <v>100.21</v>
       </c>
       <c r="AB2" t="n">
-        <v>42.15</v>
+        <v>42.77</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.83</v>
+        <v>29.85</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF2" t="n">
-        <v>372.6798</v>
+        <v>372.1805</v>
       </c>
       <c r="AG2" t="n">
-        <v>319.0863</v>
+        <v>319.651</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,13 +814,13 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>95.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>71.7</v>
+        <v>74.7</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-5.39</v>
+        <v>-3.35</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.51</v>
+        <v>12.54</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 5.4% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>73.2</v>
+        <v>74.5</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 77.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.4%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 78.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4665291833344</v>
+        <v>4629160525824</v>
       </c>
       <c r="G3" t="n">
-        <v>38.46</v>
+        <v>38.2</v>
       </c>
       <c r="H3" t="n">
-        <v>33.04</v>
+        <v>32.76</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -949,16 +949,16 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>36.3</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="n">
         <v>41.5</v>
       </c>
       <c r="R3" t="n">
-        <v>73.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>75.2</v>
+        <v>75.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>317.66</v>
+        <v>315.185</v>
       </c>
       <c r="X3" t="n">
-        <v>8.94</v>
+        <v>6.61</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.06</v>
+        <v>21.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.86</v>
+        <v>21.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>50.14</v>
+        <v>49.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.24</v>
+        <v>18.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.47</v>
+        <v>26.48</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="AF3" t="n">
-        <v>298.6817</v>
+        <v>299.5564</v>
       </c>
       <c r="AG3" t="n">
-        <v>272.4164</v>
+        <v>272.7326</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>41.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>73.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
@@ -1028,19 +1028,19 @@
         <v>275.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>263.1575</v>
+        <v>265.925</v>
       </c>
       <c r="AP3" t="n">
-        <v>317.65</v>
+        <v>317.31</v>
       </c>
       <c r="AQ3" t="n">
-        <v>317.65</v>
+        <v>317.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.35</v>
+        <v>5.22</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.6</v>
+        <v>15.57</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>73.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.3%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 317.65 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 317.31 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 263.16 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 265.93 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4942295203840</v>
+        <v>5132429819904</v>
       </c>
       <c r="G4" t="n">
-        <v>31.2</v>
+        <v>32.45</v>
       </c>
       <c r="H4" t="n">
-        <v>15.95</v>
+        <v>16.57</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,25 +1139,25 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>74</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>69.2</v>
+        <v>66.8</v>
       </c>
       <c r="Q4" t="n">
         <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>76.2</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>69.2</v>
+        <v>72.7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,54 +1171,54 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>204.075</v>
+        <v>211.9</v>
       </c>
       <c r="X4" t="n">
-        <v>1.82</v>
+        <v>3.43</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.31</v>
+        <v>12.06</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.42</v>
+        <v>14.77</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.53</v>
+        <v>28.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>64.88</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.95</v>
+        <v>47.01</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>208.9751</v>
+        <v>209.2155</v>
       </c>
       <c r="AG4" t="n">
-        <v>191.5978</v>
+        <v>191.7708</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>74</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AK4" t="n">
         <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>76.2</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
         <v>752</v>
@@ -1236,10 +1236,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2.36</v>
+        <v>1.28</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>51.4</v>
+        <v>56</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 69.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.4%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>593851580416</v>
+        <v>599632838656</v>
       </c>
       <c r="G5" t="n">
-        <v>59.51</v>
+        <v>60.09</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>35.34</v>
       </c>
       <c r="I5" t="n">
         <v>29.71</v>
@@ -1347,20 +1347,20 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="Q5" t="n">
         <v>17.3</v>
       </c>
       <c r="R5" t="n">
-        <v>82.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>67.7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1540.8</v>
+        <v>1555.8</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.45</v>
+        <v>-4.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>20.25</v>
+        <v>26.77</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.24</v>
+        <v>44.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>148.18</v>
+        <v>141.19</v>
       </c>
       <c r="AB5" t="n">
-        <v>33.16</v>
+        <v>32.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.1</v>
+        <v>39.06</v>
       </c>
       <c r="AD5" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>1480.976</v>
+        <v>1487.512</v>
       </c>
       <c r="AG5" t="n">
-        <v>1159.5288</v>
+        <v>1163.2022</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>17.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>82.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AM5" t="n">
         <v>765</v>
@@ -1435,10 +1435,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.04</v>
+        <v>4.59</v>
       </c>
       <c r="AS5" t="n">
-        <v>32.88</v>
+        <v>33.75</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>56.8</v>
+        <v>56.2</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 68.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.6%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1663187681280</v>
+        <v>1672338604032</v>
       </c>
       <c r="G6" t="n">
-        <v>23.83</v>
+        <v>23.94</v>
       </c>
       <c r="H6" t="n">
-        <v>18.04</v>
+        <v>18.13</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1543,19 +1543,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="P6" t="n">
-        <v>74.8</v>
+        <v>74.5</v>
       </c>
       <c r="Q6" t="n">
         <v>28.1</v>
       </c>
       <c r="R6" t="n">
-        <v>61.8</v>
+        <v>60.1</v>
       </c>
       <c r="S6" t="n">
-        <v>67.2</v>
+        <v>67</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>655.24</v>
+        <v>658.87</v>
       </c>
       <c r="X6" t="n">
-        <v>14.86</v>
+        <v>16.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.13</v>
+        <v>3.93</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.6</v>
+        <v>1.07</v>
       </c>
       <c r="AA6" t="n">
-        <v>-9.609999999999999</v>
+        <v>-7.87</v>
       </c>
       <c r="AB6" t="n">
-        <v>28.41</v>
+        <v>29.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.14</v>
+        <v>37.13</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>599.8197</v>
+        <v>600.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>641.1821</v>
+        <v>640.6905</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,13 +1610,13 @@
         <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="AK6" t="n">
         <v>28.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>61.8</v>
+        <v>60.1</v>
       </c>
       <c r="AM6" t="n">
         <v>752</v>
@@ -1634,10 +1634,10 @@
         <v>687.9124</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.23</v>
+        <v>9.66</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 9.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>42</v>
+        <v>40.7</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 67.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 67.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.7%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2904073175040</v>
+        <v>2864330309632</v>
       </c>
       <c r="G7" t="n">
-        <v>23.28</v>
+        <v>22.99</v>
       </c>
       <c r="H7" t="n">
-        <v>20.19</v>
+        <v>19.92</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1742,19 +1742,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>41.8</v>
+        <v>33.5</v>
       </c>
       <c r="P7" t="n">
-        <v>72.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>43.1</v>
       </c>
       <c r="R7" t="n">
-        <v>70.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="S7" t="n">
-        <v>64.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1768,37 +1768,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>390.9401</v>
+        <v>385.59</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.62</v>
+        <v>-1.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.64</v>
+        <v>0.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>-17.87</v>
+        <v>-19.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>-21.42</v>
+        <v>-22.78</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.34</v>
+        <v>4.59</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.44</v>
+        <v>24.45</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="AF7" t="n">
-        <v>402.6767</v>
+        <v>402.2515</v>
       </c>
       <c r="AG7" t="n">
-        <v>440.1322</v>
+        <v>439.5257</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>41.8</v>
+        <v>33.5</v>
       </c>
       <c r="AK7" t="n">
         <v>43.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>70.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="AM7" t="n">
         <v>752</v>
@@ -1833,10 +1833,10 @@
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-2.91</v>
+        <v>-4.14</v>
       </c>
       <c r="AS7" t="n">
-        <v>-11.18</v>
+        <v>-12.27</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1850,11 +1850,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>59.5</v>
+        <v>56.9</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 64.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.9%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.1%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2656252985344</v>
+        <v>2670775238656</v>
       </c>
       <c r="G8" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="H8" t="n">
-        <v>24.98</v>
+        <v>25.11</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,16 +1939,16 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>58</v>
+        <v>57.7</v>
       </c>
       <c r="P8" t="n">
-        <v>58.3</v>
+        <v>57.8</v>
       </c>
       <c r="Q8" t="n">
         <v>37.9</v>
       </c>
       <c r="R8" t="n">
-        <v>75.7</v>
+        <v>76.7</v>
       </c>
       <c r="S8" t="n">
         <v>61.8</v>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>246.93</v>
+        <v>248.28</v>
       </c>
       <c r="X8" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.1</v>
+        <v>10.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.64</v>
+        <v>22.75</v>
       </c>
       <c r="AC8" t="n">
         <v>31.2</v>
@@ -1992,10 +1992,10 @@
         <v>0.73</v>
       </c>
       <c r="AF8" t="n">
-        <v>253.7124</v>
+        <v>253.3844</v>
       </c>
       <c r="AG8" t="n">
-        <v>233.4643</v>
+        <v>233.6065</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>58</v>
+        <v>57.7</v>
       </c>
       <c r="AK8" t="n">
         <v>37.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>75.7</v>
+        <v>76.7</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
@@ -2024,16 +2024,16 @@
         <v>227.01</v>
       </c>
       <c r="AP8" t="n">
-        <v>247.04</v>
+        <v>248.28</v>
       </c>
       <c r="AQ8" t="n">
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.67</v>
+        <v>-2.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.77</v>
+        <v>6.28</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 61.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 61.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.0%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1480956968960</v>
+        <v>1490036457472</v>
       </c>
       <c r="G9" t="n">
-        <v>358.47</v>
+        <v>357.42</v>
       </c>
       <c r="H9" t="n">
-        <v>152.98</v>
+        <v>153.04</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>69.3</v>
+        <v>67.7</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>69.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,25 +2162,25 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>394.235</v>
+        <v>396.715</v>
       </c>
       <c r="X9" t="n">
-        <v>3.31</v>
+        <v>-0.61</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.98</v>
+        <v>12.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>-9.539999999999999</v>
+        <v>-10.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>27.23</v>
+        <v>26.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.43</v>
+        <v>12.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>58.22</v>
+        <v>58.21</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
@@ -2189,10 +2189,10 @@
         <v>0.21</v>
       </c>
       <c r="AF9" t="n">
-        <v>409.6251</v>
+        <v>409.9373</v>
       </c>
       <c r="AG9" t="n">
-        <v>417.9818</v>
+        <v>417.7541</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2203,13 +2203,13 @@
         <v>35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>69.3</v>
+        <v>67.7</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>69.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AM9" t="n">
         <v>752</v>
@@ -2227,10 +2227,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-3.76</v>
+        <v>-3.23</v>
       </c>
       <c r="AS9" t="n">
-        <v>-5.68</v>
+        <v>-5.04</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 42.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.8%.</t>
+          <t>TSLA: scenario base High Risk, score 41.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.2%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4389631688704</v>
+        <v>4524958285824</v>
       </c>
       <c r="G2" t="n">
-        <v>27.44</v>
+        <v>28.26</v>
       </c>
       <c r="H2" t="n">
-        <v>24.65</v>
+        <v>25.41</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -741,69 +741,69 @@
         <v>20.03</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>97.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>61.1</v>
+        <v>59.1</v>
       </c>
       <c r="Q2" t="n">
         <v>40.3</v>
       </c>
       <c r="R2" t="n">
-        <v>74.7</v>
+        <v>79.3</v>
       </c>
       <c r="S2" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>359.73</v>
+        <v>370.82</v>
       </c>
       <c r="X2" t="n">
-        <v>0.55</v>
+        <v>3.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.02</v>
+        <v>11.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.630000000000001</v>
+        <v>11.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>100.21</v>
+        <v>104.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>42.77</v>
+        <v>44.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.85</v>
+        <v>29.9</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AF2" t="n">
-        <v>372.1805</v>
+        <v>371.8833</v>
       </c>
       <c r="AG2" t="n">
-        <v>319.651</v>
+        <v>320.2775</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,13 +814,13 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>97.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>40.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>74.7</v>
+        <v>79.3</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-3.35</v>
+        <v>-0.29</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.54</v>
+        <v>15.78</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>74.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 78.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.3%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4629160525824</v>
+        <v>4789326315520</v>
       </c>
       <c r="G3" t="n">
-        <v>38.2</v>
+        <v>39.53</v>
       </c>
       <c r="H3" t="n">
-        <v>32.76</v>
+        <v>33.89</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -949,16 +949,16 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>37</v>
+        <v>33.9</v>
       </c>
       <c r="Q3" t="n">
         <v>41.5</v>
       </c>
       <c r="R3" t="n">
-        <v>77.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="S3" t="n">
-        <v>75.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>315.185</v>
+        <v>326.07</v>
       </c>
       <c r="X3" t="n">
-        <v>6.61</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.71</v>
+        <v>26.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.75</v>
+        <v>25.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>49.86</v>
+        <v>56.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.89</v>
+        <v>19.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.48</v>
+        <v>26.54</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="AF3" t="n">
-        <v>299.5564</v>
+        <v>300.4737</v>
       </c>
       <c r="AG3" t="n">
-        <v>272.7326</v>
+        <v>273.0806</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>41.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>77.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
@@ -1031,16 +1031,16 @@
         <v>265.925</v>
       </c>
       <c r="AP3" t="n">
-        <v>317.31</v>
+        <v>326.085</v>
       </c>
       <c r="AQ3" t="n">
-        <v>317.31</v>
+        <v>326.085</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.22</v>
+        <v>8.52</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.57</v>
+        <v>19.41</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>74.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.5%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 317.31 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 326.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5132429819904</v>
+        <v>5129523167232</v>
       </c>
       <c r="G4" t="n">
-        <v>32.45</v>
+        <v>32.48</v>
       </c>
       <c r="H4" t="n">
-        <v>16.57</v>
+        <v>16.54</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,13 +1139,13 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>82.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="P4" t="n">
         <v>66.8</v>
@@ -1157,7 +1157,7 @@
         <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>72.7</v>
+        <v>71.3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>211.9</v>
+        <v>211.78</v>
       </c>
       <c r="X4" t="n">
-        <v>3.43</v>
+        <v>3.21</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.06</v>
+        <v>7.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.77</v>
+        <v>14.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.66</v>
+        <v>29.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>67.59999999999999</v>
+        <v>66.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>47.01</v>
+        <v>46.99</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.2155</v>
+        <v>209.4847</v>
       </c>
       <c r="AG4" t="n">
-        <v>191.7708</v>
+        <v>191.9419</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>82.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="AK4" t="n">
         <v>14.1</v>
@@ -1230,16 +1230,16 @@
         <v>192.53</v>
       </c>
       <c r="AP4" t="n">
-        <v>212.45</v>
+        <v>211.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.5</v>
+        <v>10.34</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>56</v>
+        <v>54.5</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>599632838656</v>
+        <v>597166129152</v>
       </c>
       <c r="G5" t="n">
-        <v>60.09</v>
+        <v>59.98</v>
       </c>
       <c r="H5" t="n">
-        <v>35.34</v>
+        <v>35.15</v>
       </c>
       <c r="I5" t="n">
         <v>29.71</v>
@@ -1347,20 +1347,20 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="R5" t="n">
-        <v>80.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="S5" t="n">
-        <v>67.7</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1555.8</v>
+        <v>1549.4</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.09</v>
+        <v>-2.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>26.77</v>
+        <v>27.01</v>
       </c>
       <c r="Z5" t="n">
-        <v>44.01</v>
+        <v>35.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>141.19</v>
+        <v>146.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>32.16</v>
+        <v>33.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.06</v>
+        <v>39.02</v>
       </c>
       <c r="AD5" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1487.512</v>
+        <v>1492.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1163.2022</v>
+        <v>1166.8307</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AL5" t="n">
-        <v>80.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AM5" t="n">
         <v>765</v>
@@ -1435,10 +1435,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.59</v>
+        <v>3.82</v>
       </c>
       <c r="AS5" t="n">
-        <v>33.75</v>
+        <v>32.79</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>56.2</v>
+        <v>56.9</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.6%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 68.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1672338604032</v>
+        <v>1724135243776</v>
       </c>
       <c r="G6" t="n">
-        <v>23.94</v>
+        <v>24.7</v>
       </c>
       <c r="H6" t="n">
-        <v>18.13</v>
+        <v>18.7</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1537,25 +1537,25 @@
         <v>35.61</v>
       </c>
       <c r="M6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>54.2</v>
+        <v>55.9</v>
       </c>
       <c r="P6" t="n">
-        <v>74.5</v>
+        <v>72.8</v>
       </c>
       <c r="Q6" t="n">
         <v>28.1</v>
       </c>
       <c r="R6" t="n">
-        <v>60.1</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
-        <v>67</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>658.87</v>
+        <v>679.215</v>
       </c>
       <c r="X6" t="n">
-        <v>16.02</v>
+        <v>19.91</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.93</v>
+        <v>2.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.07</v>
+        <v>5.99</v>
       </c>
       <c r="AA6" t="n">
-        <v>-7.87</v>
+        <v>-5.48</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.28</v>
+        <v>30.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.13</v>
+        <v>37.16</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>600.8</v>
+        <v>602.264</v>
       </c>
       <c r="AG6" t="n">
-        <v>640.6905</v>
+        <v>640.3626</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,13 +1610,13 @@
         <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>54.2</v>
+        <v>55.9</v>
       </c>
       <c r="AK6" t="n">
         <v>28.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>60.1</v>
+        <v>47.6</v>
       </c>
       <c r="AM6" t="n">
         <v>752</v>
@@ -1628,20 +1628,20 @@
         <v>542.87</v>
       </c>
       <c r="AP6" t="n">
-        <v>669.21</v>
+        <v>679.215</v>
       </c>
       <c r="AQ6" t="n">
-        <v>687.9124</v>
+        <v>679.215</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.66</v>
+        <v>12.78</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.83</v>
+        <v>6.07</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 9.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 12.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>40.7</v>
+        <v>31.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 67.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.7%.</t>
+          <t>META: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.8%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 679.22 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2864330309632</v>
+        <v>2935234756608</v>
       </c>
       <c r="G7" t="n">
-        <v>22.99</v>
+        <v>23.55</v>
       </c>
       <c r="H7" t="n">
-        <v>19.92</v>
+        <v>20.4</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1742,19 +1742,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="P7" t="n">
-        <v>73.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="R7" t="n">
-        <v>69</v>
+        <v>72.7</v>
       </c>
       <c r="S7" t="n">
-        <v>62.5</v>
+        <v>63.2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1768,37 +1768,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>385.59</v>
+        <v>395.135</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.22</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.53</v>
+        <v>0.73</v>
       </c>
       <c r="Z7" t="n">
-        <v>-19.19</v>
+        <v>-16.82</v>
       </c>
       <c r="AA7" t="n">
-        <v>-22.78</v>
+        <v>-20.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.59</v>
+        <v>5.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.45</v>
+        <v>24.5</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>402.2515</v>
+        <v>401.8702</v>
       </c>
       <c r="AG7" t="n">
-        <v>439.5257</v>
+        <v>438.9789</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="AK7" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="AL7" t="n">
-        <v>69</v>
+        <v>72.7</v>
       </c>
       <c r="AM7" t="n">
         <v>752</v>
@@ -1827,16 +1827,16 @@
         <v>352.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>399.76</v>
+        <v>395.135</v>
       </c>
       <c r="AQ7" t="n">
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.14</v>
+        <v>-1.68</v>
       </c>
       <c r="AS7" t="n">
-        <v>-12.27</v>
+        <v>-9.99</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1850,11 +1850,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 4.1% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>56.9</v>
+        <v>58.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.1%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.7%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2670775238656</v>
+        <v>2733059080192</v>
       </c>
       <c r="G8" t="n">
-        <v>29.7</v>
+        <v>30.35</v>
       </c>
       <c r="H8" t="n">
-        <v>25.11</v>
+        <v>25.7</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="P8" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>76.7</v>
+        <v>82.8</v>
       </c>
       <c r="S8" t="n">
-        <v>61.8</v>
+        <v>63.1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,54 +1965,54 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>248.28</v>
+        <v>254.07</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>6.51</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.36</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.34</v>
+        <v>12.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.75</v>
+        <v>24.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.2</v>
+        <v>31.23</v>
       </c>
       <c r="AD8" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AF8" t="n">
-        <v>253.3844</v>
+        <v>253.0848</v>
       </c>
       <c r="AG8" t="n">
-        <v>233.6065</v>
+        <v>233.7822</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="AK8" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>76.7</v>
+        <v>82.8</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
@@ -2024,16 +2024,16 @@
         <v>227.01</v>
       </c>
       <c r="AP8" t="n">
-        <v>248.28</v>
+        <v>254.04</v>
       </c>
       <c r="AQ8" t="n">
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.01</v>
+        <v>0.38</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.28</v>
+        <v>8.67</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>61.3</v>
+        <v>63.4</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 61.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1490036457472</v>
+        <v>1482722246656</v>
       </c>
       <c r="G9" t="n">
-        <v>357.42</v>
+        <v>355.67</v>
       </c>
       <c r="H9" t="n">
-        <v>153.04</v>
+        <v>154.57</v>
       </c>
       <c r="I9" t="n">
         <v>3.95</v>
@@ -2136,7 +2136,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>67.7</v>
+        <v>60.6</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>70.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="S9" t="n">
-        <v>41.8</v>
+        <v>40</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2162,37 +2162,37 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>396.715</v>
+        <v>394.71</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.61</v>
+        <v>-2.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>-10.85</v>
+        <v>-12.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.54</v>
+        <v>24.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.2</v>
+        <v>10.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>58.21</v>
+        <v>58.19</v>
       </c>
       <c r="AD9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>409.9373</v>
+        <v>410.0044</v>
       </c>
       <c r="AG9" t="n">
-        <v>417.7541</v>
+        <v>417.608</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2203,13 +2203,13 @@
         <v>35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>67.7</v>
+        <v>60.6</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>70.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="AM9" t="n">
         <v>752</v>
@@ -2227,10 +2227,10 @@
         <v>445.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-3.23</v>
+        <v>-3.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>-5.04</v>
+        <v>-5.46</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>34.6</v>
+        <v>32.5</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 41.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.2%.</t>
+          <t>TSLA: scenario base High Risk, score 40.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.7%.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4524958285824</v>
+        <v>4329899819008</v>
       </c>
       <c r="G2" t="n">
-        <v>28.26</v>
+        <v>27.11</v>
       </c>
       <c r="H2" t="n">
-        <v>25.41</v>
+        <v>24.26</v>
       </c>
       <c r="I2" t="n">
         <v>37.92</v>
@@ -747,63 +747,63 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>99.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="P2" t="n">
-        <v>59.1</v>
+        <v>62.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="R2" t="n">
-        <v>79.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>78.5</v>
+        <v>74.8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>370.82</v>
+        <v>354.835</v>
       </c>
       <c r="X2" t="n">
-        <v>3.1</v>
+        <v>-3.93</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.45</v>
+        <v>5.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.89</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>104.82</v>
+        <v>95.52</v>
       </c>
       <c r="AB2" t="n">
-        <v>44.53</v>
+        <v>42.34</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.9</v>
+        <v>29.99</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AF2" t="n">
-        <v>371.8833</v>
+        <v>371.3215</v>
       </c>
       <c r="AG2" t="n">
-        <v>320.2775</v>
+        <v>320.8219</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>99.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>79.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
         <v>337.39</v>
@@ -832,16 +832,16 @@
         <v>332.0916</v>
       </c>
       <c r="AP2" t="n">
-        <v>373.25</v>
+        <v>370.92</v>
       </c>
       <c r="AQ2" t="n">
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.29</v>
+        <v>-4.44</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.78</v>
+        <v>10.6</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 4.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>76.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.3%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 74.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.4%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4789326315520</v>
+        <v>4888686755840</v>
       </c>
       <c r="G3" t="n">
-        <v>39.53</v>
+        <v>40.35</v>
       </c>
       <c r="H3" t="n">
-        <v>33.89</v>
+        <v>34.6</v>
       </c>
       <c r="I3" t="n">
         <v>27.15</v>
@@ -940,7 +940,7 @@
         <v>79.55</v>
       </c>
       <c r="M3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
@@ -949,16 +949,16 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="R3" t="n">
-        <v>64.7</v>
+        <v>57.3</v>
       </c>
       <c r="S3" t="n">
-        <v>73.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>326.07</v>
+        <v>332.85</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>12.29</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.09</v>
+        <v>25.04</v>
       </c>
       <c r="Z3" t="n">
-        <v>25.52</v>
+        <v>27.74</v>
       </c>
       <c r="AA3" t="n">
-        <v>56.92</v>
+        <v>59.81</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.56</v>
+        <v>20.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.54</v>
+        <v>26.55</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>300.4737</v>
+        <v>301.6278</v>
       </c>
       <c r="AG3" t="n">
-        <v>273.0806</v>
+        <v>273.4783</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1016,13 +1016,13 @@
         <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>64.7</v>
+        <v>57.3</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
         <v>275.15</v>
@@ -1031,16 +1031,16 @@
         <v>265.925</v>
       </c>
       <c r="AP3" t="n">
-        <v>326.085</v>
+        <v>332.85</v>
       </c>
       <c r="AQ3" t="n">
-        <v>326.085</v>
+        <v>332.85</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.52</v>
+        <v>10.35</v>
       </c>
       <c r="AS3" t="n">
-        <v>19.41</v>
+        <v>21.71</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 8.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>67.90000000000001</v>
+        <v>62.3</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.5%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.3%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 326.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 332.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,54 +1114,54 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5129523167232</v>
+        <v>613945442304</v>
       </c>
       <c r="G4" t="n">
-        <v>32.48</v>
+        <v>57.96</v>
       </c>
       <c r="H4" t="n">
-        <v>16.54</v>
+        <v>32.43</v>
       </c>
       <c r="I4" t="n">
-        <v>62.97</v>
+        <v>30.11</v>
       </c>
       <c r="J4" t="n">
-        <v>114.29</v>
+        <v>53.94</v>
       </c>
       <c r="K4" t="n">
-        <v>85.2</v>
+        <v>21.3</v>
       </c>
       <c r="L4" t="n">
-        <v>6.55</v>
+        <v>9.09</v>
       </c>
       <c r="M4" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>77.2</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>66.8</v>
+        <v>18</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>17.3</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>72</v>
       </c>
       <c r="S4" t="n">
-        <v>71.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>211.78</v>
+        <v>1598.4</v>
       </c>
       <c r="X4" t="n">
-        <v>3.21</v>
+        <v>-3.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.9</v>
+        <v>28.77</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.65</v>
+        <v>37.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.25</v>
+        <v>158.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>66.36</v>
+        <v>34.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.99</v>
+        <v>39.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>-36.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.41</v>
+        <v>0.89</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.4847</v>
+        <v>1498.368</v>
       </c>
       <c r="AG4" t="n">
-        <v>191.9419</v>
+        <v>1170.6379</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,34 +1212,34 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>77.2</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.1</v>
+        <v>17.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>72</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="AN4" t="n">
-        <v>192.53</v>
+        <v>1509.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>192.53</v>
+        <v>1171.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>211.8</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>235.4656</v>
+        <v>1721.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.1</v>
+        <v>6.68</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.34</v>
+        <v>36.54</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>54.5</v>
+        <v>54</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.7%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 192.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1313,54 +1313,54 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>597166129152</v>
+        <v>4995338993664</v>
       </c>
       <c r="G5" t="n">
-        <v>59.98</v>
+        <v>31.63</v>
       </c>
       <c r="H5" t="n">
-        <v>35.15</v>
+        <v>16.11</v>
       </c>
       <c r="I5" t="n">
-        <v>29.71</v>
+        <v>62.97</v>
       </c>
       <c r="J5" t="n">
-        <v>52.24</v>
+        <v>114.29</v>
       </c>
       <c r="K5" t="n">
-        <v>13.2</v>
+        <v>85.2</v>
       </c>
       <c r="L5" t="n">
-        <v>12.99</v>
+        <v>6.55</v>
       </c>
       <c r="M5" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>67.2</v>
       </c>
       <c r="P5" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="Q5" t="n">
         <v>14.1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>17.4</v>
-      </c>
       <c r="R5" t="n">
-        <v>82.8</v>
+        <v>77.3</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1370,75 +1370,75 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1549.4</v>
+        <v>206.21</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.63</v>
+        <v>-2.94</v>
       </c>
       <c r="Y5" t="n">
-        <v>27.01</v>
+        <v>3.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.28</v>
+        <v>11.11</v>
       </c>
       <c r="AA5" t="n">
-        <v>146.53</v>
+        <v>20.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>33.29</v>
+        <v>64.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.02</v>
+        <v>47</v>
       </c>
       <c r="AD5" t="n">
-        <v>-44.77</v>
+        <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.85</v>
+        <v>1.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>1492.4</v>
+        <v>209.6583</v>
       </c>
       <c r="AG5" t="n">
-        <v>1166.8307</v>
+        <v>192.0868</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>67.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.4</v>
+        <v>14.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>82.8</v>
+        <v>77.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
-        <v>1509.8</v>
+        <v>192.53</v>
       </c>
       <c r="AO5" t="n">
-        <v>1171.8</v>
+        <v>192.53</v>
       </c>
       <c r="AP5" t="n">
-        <v>1721.4</v>
+        <v>212.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1721.4</v>
+        <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.82</v>
+        <v>-1.64</v>
       </c>
       <c r="AS5" t="n">
-        <v>32.79</v>
+        <v>7.35</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>56.9</v>
+        <v>49.9</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 68.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.6%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 192.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1724135243776</v>
+        <v>1683825098752</v>
       </c>
       <c r="G6" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="H6" t="n">
-        <v>18.7</v>
+        <v>18.26</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1537,25 +1537,25 @@
         <v>35.61</v>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>55.9</v>
+        <v>50</v>
       </c>
       <c r="P6" t="n">
-        <v>72.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>28.1</v>
       </c>
       <c r="R6" t="n">
-        <v>47.6</v>
+        <v>59</v>
       </c>
       <c r="S6" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>679.215</v>
+        <v>663.335</v>
       </c>
       <c r="X6" t="n">
-        <v>19.91</v>
+        <v>11.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.62</v>
+        <v>-1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.99</v>
+        <v>5.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.48</v>
+        <v>-6.32</v>
       </c>
       <c r="AB6" t="n">
-        <v>30.36</v>
+        <v>29.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.16</v>
+        <v>37.17</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>602.264</v>
+        <v>603.3757000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>640.3626</v>
+        <v>639.9806</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,16 +1610,16 @@
         <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55.9</v>
+        <v>50</v>
       </c>
       <c r="AK6" t="n">
         <v>28.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>47.6</v>
+        <v>59</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN6" t="n">
         <v>542.87</v>
@@ -1628,20 +1628,20 @@
         <v>542.87</v>
       </c>
       <c r="AP6" t="n">
-        <v>679.215</v>
+        <v>681.3099999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>679.215</v>
+        <v>681.3099999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.78</v>
+        <v>9.94</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.07</v>
+        <v>3.65</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 12.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>31.8</v>
+        <v>38.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 65.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 679.22 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 681.31 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2935234756608</v>
+        <v>2971299741696</v>
       </c>
       <c r="G7" t="n">
-        <v>23.55</v>
+        <v>23.85</v>
       </c>
       <c r="H7" t="n">
-        <v>20.4</v>
+        <v>20.64</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1736,25 +1736,25 @@
         <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>35.7</v>
+        <v>32.6</v>
       </c>
       <c r="P7" t="n">
-        <v>71.7</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="n">
         <v>43</v>
       </c>
       <c r="R7" t="n">
-        <v>72.7</v>
+        <v>74.7</v>
       </c>
       <c r="S7" t="n">
-        <v>63.2</v>
+        <v>62.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1768,22 +1768,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>395.135</v>
+        <v>400.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.73</v>
+        <v>-2.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>-16.82</v>
+        <v>-14.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>-20.82</v>
+        <v>-20.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.4</v>
+        <v>5.83</v>
       </c>
       <c r="AC7" t="n">
         <v>24.5</v>
@@ -1792,13 +1792,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AF7" t="n">
-        <v>401.8702</v>
+        <v>401.6259</v>
       </c>
       <c r="AG7" t="n">
-        <v>438.9789</v>
+        <v>438.4403</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,16 +1809,16 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>35.7</v>
+        <v>32.6</v>
       </c>
       <c r="AK7" t="n">
         <v>43</v>
       </c>
       <c r="AL7" t="n">
-        <v>72.7</v>
+        <v>74.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
         <v>352.83</v>
@@ -1827,16 +1827,16 @@
         <v>352.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>395.135</v>
+        <v>399.99</v>
       </c>
       <c r="AQ7" t="n">
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.68</v>
+        <v>-0.41</v>
       </c>
       <c r="AS7" t="n">
-        <v>-9.99</v>
+        <v>-8.77</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>58.4</v>
+        <v>58.1</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.7%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.4%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2733059080192</v>
+        <v>2708532625408</v>
       </c>
       <c r="G8" t="n">
-        <v>30.35</v>
+        <v>30.12</v>
       </c>
       <c r="H8" t="n">
-        <v>25.7</v>
+        <v>25.42</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>57.8</v>
+        <v>56.9</v>
       </c>
       <c r="P8" t="n">
-        <v>56.2</v>
+        <v>56.9</v>
       </c>
       <c r="Q8" t="n">
         <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>82.8</v>
+        <v>79.2</v>
       </c>
       <c r="S8" t="n">
-        <v>63.1</v>
+        <v>61.6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>254.07</v>
+        <v>251.765</v>
       </c>
       <c r="X8" t="n">
-        <v>6.51</v>
+        <v>2.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.03</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>3.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.57</v>
+        <v>11.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.05</v>
+        <v>23.63</v>
       </c>
       <c r="AC8" t="n">
         <v>31.23</v>
@@ -1989,33 +1989,33 @@
         <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AF8" t="n">
-        <v>253.0848</v>
+        <v>252.6969</v>
       </c>
       <c r="AG8" t="n">
-        <v>233.7822</v>
+        <v>233.9466</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>57.8</v>
+        <v>56.9</v>
       </c>
       <c r="AK8" t="n">
         <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>82.8</v>
+        <v>79.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
         <v>227.01</v>
@@ -2024,16 +2024,16 @@
         <v>227.01</v>
       </c>
       <c r="AP8" t="n">
-        <v>254.04</v>
+        <v>254.96</v>
       </c>
       <c r="AQ8" t="n">
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.67</v>
+        <v>7.63</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>63.4</v>
+        <v>61.7</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 61.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.4%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>STM.MI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2100,174 +2100,124 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1482722246656</v>
-      </c>
-      <c r="G9" t="n">
-        <v>355.67</v>
-      </c>
-      <c r="H9" t="n">
-        <v>154.57</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>18.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>64.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>60.6</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Nessun dato prezzo disponibile</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>40</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>High Risk</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>394.71</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-12.08</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>24.55</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>410.0044</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>417.608</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
-        <v>35</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>60.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL9" t="n">
         <v>0</v>
       </c>
-      <c r="AL9" t="n">
-        <v>69.7</v>
-      </c>
       <c r="AM9" t="n">
-        <v>752</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>375.12</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>372.8</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>425.3</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-5.46</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No Data</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>Dati prezzo insufficienti.</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 40.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.7%.</t>
+          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 372.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2277,19 +2227,19 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Italy / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STM.MI</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2297,124 +2247,174 @@
           <t>Stock</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1467812020224</v>
+      </c>
+      <c r="G10" t="n">
+        <v>355.29</v>
+      </c>
+      <c r="H10" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.74</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>50</v>
-      </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>390.82</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-4.94</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-12.61</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>409.9656</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>417.3588</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Nessun dato prezzo disponibile</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>100</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+        <v>753</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>425.3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-6.38</v>
+      </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No Data</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>Dati prezzo insufficienti.</t>
+          <t>prezzo 4.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>32.3</v>
+        <v>28.9</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>STM.MI: scenario base Avoid for Now, score 38.5, trend No Data. Entry zone: No Data. Distanza da MA50: n/d.</t>
+          <t>TSLA: scenario base High Risk, score 36.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.7%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area n/d con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area n/d o peggioramento trend; rischio attuale: No Data.</t>
+          <t>Scenario negativo: perdita area 372.80 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Italy / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -696,12 +696,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -711,55 +711,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4329899819008</v>
+        <v>4894113660928</v>
       </c>
       <c r="G2" t="n">
-        <v>27.11</v>
+        <v>40.34</v>
       </c>
       <c r="H2" t="n">
-        <v>24.26</v>
+        <v>34.57</v>
       </c>
       <c r="I2" t="n">
-        <v>37.92</v>
+        <v>27.15</v>
       </c>
       <c r="J2" t="n">
-        <v>38.88</v>
+        <v>141.47</v>
       </c>
       <c r="K2" t="n">
-        <v>21.8</v>
+        <v>16.6</v>
       </c>
       <c r="L2" t="n">
-        <v>20.03</v>
+        <v>79.55</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>84.8</v>
+        <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>62.1</v>
+        <v>31.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.2</v>
+        <v>41.5</v>
       </c>
       <c r="R2" t="n">
-        <v>73.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="S2" t="n">
-        <v>74.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,80 +768,80 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>354.835</v>
+        <v>333.2</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.93</v>
+        <v>11.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.32</v>
+        <v>26.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.75</v>
+        <v>28.41</v>
       </c>
       <c r="AA2" t="n">
-        <v>95.52</v>
+        <v>59.17</v>
       </c>
       <c r="AB2" t="n">
-        <v>42.34</v>
+        <v>20.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.99</v>
+        <v>26.54</v>
       </c>
       <c r="AD2" t="n">
-        <v>-29.81</v>
+        <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.41</v>
+        <v>0.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>371.3215</v>
+        <v>302.6216</v>
       </c>
       <c r="AG2" t="n">
-        <v>320.8219</v>
+        <v>273.8777</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>84.8</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.2</v>
+        <v>41.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>73.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN2" t="n">
-        <v>337.39</v>
+        <v>275.15</v>
       </c>
       <c r="AO2" t="n">
-        <v>332.0916</v>
+        <v>267.3636</v>
       </c>
       <c r="AP2" t="n">
-        <v>370.92</v>
+        <v>333.26</v>
       </c>
       <c r="AQ2" t="n">
-        <v>402.3797</v>
+        <v>333.26</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.44</v>
+        <v>10.11</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.6</v>
+        <v>21.67</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 4.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>70.7</v>
+        <v>63</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,17 +868,17 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 74.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.4%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 333.26 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 332.09 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 267.36 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -888,19 +888,19 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -910,55 +910,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4888686755840</v>
+        <v>4200369750016</v>
       </c>
       <c r="G3" t="n">
-        <v>40.35</v>
+        <v>27.52</v>
       </c>
       <c r="H3" t="n">
-        <v>34.6</v>
+        <v>23.52</v>
       </c>
       <c r="I3" t="n">
-        <v>27.15</v>
+        <v>37.92</v>
       </c>
       <c r="J3" t="n">
-        <v>141.47</v>
+        <v>38.88</v>
       </c>
       <c r="K3" t="n">
-        <v>16.6</v>
+        <v>21.8</v>
       </c>
       <c r="L3" t="n">
-        <v>79.55</v>
+        <v>20.03</v>
       </c>
       <c r="M3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>77.2</v>
       </c>
       <c r="P3" t="n">
-        <v>31.9</v>
+        <v>62.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.4</v>
+        <v>40.1</v>
       </c>
       <c r="R3" t="n">
-        <v>57.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>72.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,80 +967,80 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>332.85</v>
+        <v>344.22</v>
       </c>
       <c r="X3" t="n">
-        <v>12.29</v>
+        <v>-7.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.04</v>
+        <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.74</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>59.81</v>
+        <v>88.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.36</v>
+        <v>40.84</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.55</v>
+        <v>30.03</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33.36</v>
+        <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.77</v>
+        <v>1.36</v>
       </c>
       <c r="AF3" t="n">
-        <v>301.6278</v>
+        <v>370.4345</v>
       </c>
       <c r="AG3" t="n">
-        <v>273.4783</v>
+        <v>321.3232</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>77.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.4</v>
+        <v>40.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>57.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN3" t="n">
-        <v>275.15</v>
+        <v>337.39</v>
       </c>
       <c r="AO3" t="n">
-        <v>265.925</v>
+        <v>337.39</v>
       </c>
       <c r="AP3" t="n">
-        <v>332.85</v>
+        <v>370.92</v>
       </c>
       <c r="AQ3" t="n">
-        <v>332.85</v>
+        <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.35</v>
+        <v>-7.07</v>
       </c>
       <c r="AS3" t="n">
-        <v>21.71</v>
+        <v>7.14</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 10.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>62.3</v>
+        <v>67.5</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.3%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 72.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 332.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 265.93 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 337.39 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>613945442304</v>
+        <v>590361722880</v>
       </c>
       <c r="G4" t="n">
-        <v>57.96</v>
+        <v>55.91</v>
       </c>
       <c r="H4" t="n">
-        <v>32.43</v>
+        <v>30.51</v>
       </c>
       <c r="I4" t="n">
-        <v>30.11</v>
+        <v>29.71</v>
       </c>
       <c r="J4" t="n">
-        <v>53.94</v>
+        <v>52.24</v>
       </c>
       <c r="K4" t="n">
-        <v>21.3</v>
+        <v>13.2</v>
       </c>
       <c r="L4" t="n">
-        <v>9.09</v>
+        <v>12.99</v>
       </c>
       <c r="M4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -1148,20 +1148,20 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>18</v>
+        <v>20.7</v>
       </c>
       <c r="Q4" t="n">
         <v>17.3</v>
       </c>
       <c r="R4" t="n">
-        <v>72</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>67.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1598.4</v>
+        <v>1537</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.5</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>28.77</v>
+        <v>23.73</v>
       </c>
       <c r="Z4" t="n">
-        <v>37.43</v>
+        <v>37.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>158.16</v>
+        <v>157.19</v>
       </c>
       <c r="AB4" t="n">
-        <v>34.61</v>
+        <v>32.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.04</v>
+        <v>39.08</v>
       </c>
       <c r="AD4" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="AF4" t="n">
-        <v>1498.368</v>
+        <v>1502.72</v>
       </c>
       <c r="AG4" t="n">
-        <v>1170.6379</v>
+        <v>1173.9582</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1218,10 +1218,10 @@
         <v>17.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>72</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN4" t="n">
         <v>1509.8</v>
@@ -1236,10 +1236,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.68</v>
+        <v>2.28</v>
       </c>
       <c r="AS4" t="n">
-        <v>36.54</v>
+        <v>30.92</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>54</v>
+        <v>57.4</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.7%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 69.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4995338993664</v>
+        <v>4922070269952</v>
       </c>
       <c r="G5" t="n">
-        <v>31.63</v>
+        <v>31.12</v>
       </c>
       <c r="H5" t="n">
-        <v>16.11</v>
+        <v>15.84</v>
       </c>
       <c r="I5" t="n">
         <v>62.97</v>
@@ -1338,25 +1338,25 @@
         <v>6.55</v>
       </c>
       <c r="M5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>67.2</v>
+        <v>65</v>
       </c>
       <c r="P5" t="n">
-        <v>68.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>14.1</v>
       </c>
       <c r="R5" t="n">
-        <v>77.3</v>
+        <v>75</v>
       </c>
       <c r="S5" t="n">
-        <v>67.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>206.21</v>
+        <v>203.2399</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.94</v>
+        <v>-2.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.81</v>
+        <v>2.58</v>
       </c>
       <c r="Z5" t="n">
         <v>11.11</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.96</v>
+        <v>18.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>64.77</v>
+        <v>63.87</v>
       </c>
       <c r="AC5" t="n">
-        <v>47</v>
+        <v>46.97</v>
       </c>
       <c r="AD5" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>209.6583</v>
+        <v>209.8215</v>
       </c>
       <c r="AG5" t="n">
-        <v>192.0868</v>
+        <v>192.2008</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,16 +1411,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>67.2</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
         <v>14.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>77.3</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN5" t="n">
         <v>192.53</v>
@@ -1435,10 +1435,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.64</v>
+        <v>-3.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.35</v>
+        <v>5.73</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>49.9</v>
+        <v>48.7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.6%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 66.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1683825098752</v>
+        <v>1631190777856</v>
       </c>
       <c r="G6" t="n">
-        <v>24.1</v>
+        <v>23.36</v>
       </c>
       <c r="H6" t="n">
-        <v>18.26</v>
+        <v>17.69</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1537,25 +1537,25 @@
         <v>35.61</v>
       </c>
       <c r="M6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>50</v>
+        <v>43.7</v>
       </c>
       <c r="P6" t="n">
-        <v>74.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>59</v>
+        <v>73.3</v>
       </c>
       <c r="S6" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>663.335</v>
+        <v>642.6</v>
       </c>
       <c r="X6" t="n">
-        <v>11.77</v>
+        <v>7.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.14</v>
+        <v>-4.98</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.3</v>
+        <v>4.59</v>
       </c>
       <c r="AA6" t="n">
-        <v>-6.32</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.28</v>
+        <v>27.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.17</v>
+        <v>37.2</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>603.3757000000001</v>
+        <v>604.1638</v>
       </c>
       <c r="AG6" t="n">
-        <v>639.9806</v>
+        <v>639.4923</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,16 +1610,16 @@
         <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>50</v>
+        <v>43.7</v>
       </c>
       <c r="AK6" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>59</v>
+        <v>73.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN6" t="n">
         <v>542.87</v>
@@ -1634,10 +1634,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.94</v>
+        <v>6.36</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.65</v>
+        <v>0.49</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 9.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>38.8</v>
+        <v>46.7</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 65.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
+          <t>META: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2971299741696</v>
+        <v>2936014635008</v>
       </c>
       <c r="G7" t="n">
-        <v>23.85</v>
+        <v>23.51</v>
       </c>
       <c r="H7" t="n">
-        <v>20.64</v>
+        <v>20.4</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1736,25 +1736,25 @@
         <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>32.6</v>
+        <v>28.5</v>
       </c>
       <c r="P7" t="n">
-        <v>71</v>
+        <v>71.8</v>
       </c>
       <c r="Q7" t="n">
         <v>43</v>
       </c>
       <c r="R7" t="n">
-        <v>74.7</v>
+        <v>73</v>
       </c>
       <c r="S7" t="n">
-        <v>62.5</v>
+        <v>61.4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1768,22 +1768,22 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>400.02</v>
+        <v>395.28</v>
       </c>
       <c r="X7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.51</v>
+        <v>-5.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>-14.63</v>
+        <v>-13.57</v>
       </c>
       <c r="AA7" t="n">
-        <v>-20.28</v>
+        <v>-21.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.83</v>
+        <v>5.4</v>
       </c>
       <c r="AC7" t="n">
         <v>24.5</v>
@@ -1792,13 +1792,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>401.6259</v>
+        <v>401.3433</v>
       </c>
       <c r="AG7" t="n">
-        <v>438.4403</v>
+        <v>437.8653</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,16 +1809,16 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32.6</v>
+        <v>28.5</v>
       </c>
       <c r="AK7" t="n">
         <v>43</v>
       </c>
       <c r="AL7" t="n">
-        <v>74.7</v>
+        <v>73</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN7" t="n">
         <v>352.83</v>
@@ -1827,16 +1827,16 @@
         <v>352.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>399.99</v>
+        <v>401.1</v>
       </c>
       <c r="AQ7" t="n">
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.41</v>
+        <v>-1.52</v>
       </c>
       <c r="AS7" t="n">
-        <v>-8.77</v>
+        <v>-9.73</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1850,11 +1850,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>58.1</v>
+        <v>56.6</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.4%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2708532625408</v>
+        <v>2653133471744</v>
       </c>
       <c r="G8" t="n">
-        <v>30.12</v>
+        <v>29.47</v>
       </c>
       <c r="H8" t="n">
-        <v>25.42</v>
+        <v>24.89</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>56.9</v>
+        <v>53.4</v>
       </c>
       <c r="P8" t="n">
-        <v>56.9</v>
+        <v>58.4</v>
       </c>
       <c r="Q8" t="n">
         <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>79.2</v>
+        <v>76.5</v>
       </c>
       <c r="S8" t="n">
-        <v>61.6</v>
+        <v>60.8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>251.765</v>
+        <v>246.64</v>
       </c>
       <c r="X8" t="n">
-        <v>2.34</v>
+        <v>0.26</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>-1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.78</v>
+        <v>4.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.23</v>
+        <v>10.51</v>
       </c>
       <c r="AB8" t="n">
-        <v>23.63</v>
+        <v>22.75</v>
       </c>
       <c r="AC8" t="n">
         <v>31.23</v>
@@ -1989,13 +1989,13 @@
         <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="AF8" t="n">
-        <v>252.6969</v>
+        <v>252.1212</v>
       </c>
       <c r="AG8" t="n">
-        <v>233.9466</v>
+        <v>234.0596</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>56.9</v>
+        <v>53.4</v>
       </c>
       <c r="AK8" t="n">
         <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>79.2</v>
+        <v>76.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN8" t="n">
         <v>227.01</v>
@@ -2030,10 +2030,10 @@
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.36</v>
+        <v>-2.17</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.63</v>
+        <v>5.38</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>61.7</v>
+        <v>60.2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 61.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 60.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.2%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1467812020224</v>
+        <v>1434705330176</v>
       </c>
       <c r="G10" t="n">
-        <v>355.29</v>
+        <v>350.46</v>
       </c>
       <c r="H10" t="n">
-        <v>153.02</v>
+        <v>149.57</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>48.5</v>
+        <v>44.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>68.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>36.8</v>
+        <v>35.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>390.82</v>
+        <v>382.03</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.94</v>
+        <v>-5.59</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.29</v>
+        <v>-1.77</v>
       </c>
       <c r="Z10" t="n">
-        <v>-12.61</v>
+        <v>-13.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>25.75</v>
+        <v>18.76</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.45</v>
+        <v>9.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.15</v>
+        <v>58.13</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>409.9656</v>
+        <v>409.8236</v>
       </c>
       <c r="AG10" t="n">
-        <v>417.3588</v>
+        <v>417.0541</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48.5</v>
+        <v>44.4</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>68.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AM10" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN10" t="n">
         <v>375.12</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-4.69</v>
+        <v>-6.79</v>
       </c>
       <c r="AS10" t="n">
-        <v>-6.38</v>
+        <v>-8.41</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 4.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>28.9</v>
+        <v>26.9</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 36.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.7%.</t>
+          <t>TSLA: scenario base High Risk, score 35.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.8%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4894113660928</v>
+        <v>4796743417856</v>
       </c>
       <c r="G2" t="n">
-        <v>40.34</v>
+        <v>39.63</v>
       </c>
       <c r="H2" t="n">
-        <v>34.57</v>
+        <v>33.88</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>31.9</v>
+        <v>33.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="R2" t="n">
-        <v>58.3</v>
+        <v>68.2</v>
       </c>
       <c r="S2" t="n">
-        <v>72.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>333.2</v>
+        <v>326.59</v>
       </c>
       <c r="X2" t="n">
-        <v>11.35</v>
+        <v>10.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>26.62</v>
+        <v>20.97</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.41</v>
+        <v>26.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>59.17</v>
+        <v>56.12</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.38</v>
+        <v>20.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.54</v>
+        <v>26.61</v>
       </c>
       <c r="AD2" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>302.6216</v>
+        <v>303.4193</v>
       </c>
       <c r="AG2" t="n">
-        <v>273.8777</v>
+        <v>274.2438</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>58.3</v>
+        <v>68.2</v>
       </c>
       <c r="AM2" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN2" t="n">
         <v>275.15</v>
@@ -832,16 +832,16 @@
         <v>267.3636</v>
       </c>
       <c r="AP2" t="n">
-        <v>333.26</v>
+        <v>333.74</v>
       </c>
       <c r="AQ2" t="n">
-        <v>333.26</v>
+        <v>333.74</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.11</v>
+        <v>7.64</v>
       </c>
       <c r="AS2" t="n">
-        <v>21.67</v>
+        <v>19.09</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>63</v>
+        <v>70.5</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,12 +868,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.6%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 333.26 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 333.74 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4200369750016</v>
+        <v>4295183564800</v>
       </c>
       <c r="G3" t="n">
-        <v>27.52</v>
+        <v>26.85</v>
       </c>
       <c r="H3" t="n">
-        <v>23.52</v>
+        <v>24.03</v>
       </c>
       <c r="I3" t="n">
         <v>37.92</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>77.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
       <c r="Q3" t="n">
         <v>40.1</v>
       </c>
       <c r="R3" t="n">
-        <v>69.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>72.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>344.22</v>
+        <v>351.99</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.78</v>
+        <v>-3.24</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.63</v>
+        <v>5.91</v>
       </c>
       <c r="AA3" t="n">
-        <v>88.67</v>
+        <v>92.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>40.84</v>
+        <v>43.91</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.03</v>
+        <v>30.02</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AF3" t="n">
-        <v>370.4345</v>
+        <v>369.5692</v>
       </c>
       <c r="AG3" t="n">
-        <v>321.3232</v>
+        <v>321.8828</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>77.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>40.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>69.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN3" t="n">
         <v>337.39</v>
@@ -1037,10 +1037,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>-7.07</v>
+        <v>-4.76</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.14</v>
+        <v>9.35</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 7.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 4.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>67.5</v>
+        <v>69.5</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 72.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 73.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>590361722880</v>
+        <v>584139276288</v>
       </c>
       <c r="G4" t="n">
-        <v>55.91</v>
+        <v>59.97</v>
       </c>
       <c r="H4" t="n">
-        <v>30.51</v>
+        <v>30.18</v>
       </c>
       <c r="I4" t="n">
-        <v>29.71</v>
+        <v>30.11</v>
       </c>
       <c r="J4" t="n">
-        <v>52.24</v>
+        <v>53.94</v>
       </c>
       <c r="K4" t="n">
-        <v>13.2</v>
+        <v>21.3</v>
       </c>
       <c r="L4" t="n">
-        <v>12.99</v>
+        <v>9.09</v>
       </c>
       <c r="M4" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -1148,16 +1148,16 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="R4" t="n">
         <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>69.2</v>
+        <v>69.3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1537</v>
+        <v>1520.8</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.289999999999999</v>
+        <v>-8.26</v>
       </c>
       <c r="Y4" t="n">
-        <v>23.73</v>
+        <v>23.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>37.67</v>
+        <v>33.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>157.19</v>
+        <v>152.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>32.84</v>
+        <v>35.54</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.08</v>
+        <v>39.01</v>
       </c>
       <c r="AD4" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>1502.72</v>
+        <v>1507.024</v>
       </c>
       <c r="AG4" t="n">
-        <v>1173.9582</v>
+        <v>1177.185</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1215,13 +1215,13 @@
         <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AL4" t="n">
         <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AN4" t="n">
         <v>1509.8</v>
@@ -1236,10 +1236,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.28</v>
+        <v>0.91</v>
       </c>
       <c r="AS4" t="n">
-        <v>30.92</v>
+        <v>29.19</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 69.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 69.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.9%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4922070269952</v>
+        <v>4923644706816</v>
       </c>
       <c r="G5" t="n">
-        <v>31.12</v>
+        <v>31.13</v>
       </c>
       <c r="H5" t="n">
-        <v>15.84</v>
+        <v>15.83</v>
       </c>
       <c r="I5" t="n">
         <v>62.97</v>
@@ -1338,13 +1338,13 @@
         <v>6.55</v>
       </c>
       <c r="M5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P5" t="n">
         <v>69.40000000000001</v>
@@ -1353,10 +1353,10 @@
         <v>14.1</v>
       </c>
       <c r="R5" t="n">
-        <v>75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>66.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>203.2399</v>
+        <v>203.28</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.01</v>
+        <v>-0.67</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.58</v>
+        <v>0.91</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.11</v>
+        <v>8.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.76</v>
+        <v>17.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>63.87</v>
+        <v>66.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>46.97</v>
+        <v>46.98</v>
       </c>
       <c r="AD5" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF5" t="n">
-        <v>209.8215</v>
+        <v>209.7267</v>
       </c>
       <c r="AG5" t="n">
-        <v>192.2008</v>
+        <v>192.2833</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,16 +1411,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AK5" t="n">
         <v>14.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN5" t="n">
         <v>192.53</v>
@@ -1435,10 +1435,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.15</v>
+        <v>-3.07</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.73</v>
+        <v>5.72</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>48.7</v>
+        <v>47.7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 66.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 65.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1631190777856</v>
+        <v>1639440580608</v>
       </c>
       <c r="G6" t="n">
-        <v>23.36</v>
+        <v>23.47</v>
       </c>
       <c r="H6" t="n">
-        <v>17.69</v>
+        <v>17.78</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1537,25 +1537,25 @@
         <v>35.61</v>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>43.7</v>
+        <v>42.1</v>
       </c>
       <c r="P6" t="n">
-        <v>75.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="R6" t="n">
-        <v>73.3</v>
+        <v>71.7</v>
       </c>
       <c r="S6" t="n">
-        <v>65.90000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>642.6</v>
+        <v>645.85</v>
       </c>
       <c r="X6" t="n">
-        <v>7.06</v>
+        <v>13.79</v>
       </c>
       <c r="Y6" t="n">
-        <v>-4.98</v>
+        <v>-6.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.59</v>
+        <v>4.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>-8.279999999999999</v>
+        <v>-7.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>27.87</v>
+        <v>30.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.2</v>
+        <v>37.13</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>604.1638</v>
+        <v>604.9028</v>
       </c>
       <c r="AG6" t="n">
-        <v>639.4923</v>
+        <v>639.0762</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,16 +1610,16 @@
         <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>43.7</v>
+        <v>42.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>73.3</v>
+        <v>71.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN6" t="n">
         <v>542.87</v>
@@ -1634,10 +1634,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.36</v>
+        <v>6.77</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.49</v>
+        <v>1.06</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>46.7</v>
+        <v>45.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
+          <t>META: scenario base Hold / Monitor, score 65.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.8%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2936014635008</v>
+        <v>2988385239040</v>
       </c>
       <c r="G7" t="n">
-        <v>23.51</v>
+        <v>23.97</v>
       </c>
       <c r="H7" t="n">
-        <v>20.4</v>
+        <v>20.76</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1736,25 +1736,25 @@
         <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>28.5</v>
+        <v>31.4</v>
       </c>
       <c r="P7" t="n">
-        <v>71.8</v>
+        <v>70.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="R7" t="n">
-        <v>73</v>
+        <v>78.2</v>
       </c>
       <c r="S7" t="n">
-        <v>61.4</v>
+        <v>63.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1763,62 +1763,62 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>395.28</v>
+        <v>402.29</v>
       </c>
       <c r="X7" t="n">
-        <v>0.37</v>
+        <v>6.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>-5.74</v>
+        <v>-4.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>-13.57</v>
+        <v>-11.51</v>
       </c>
       <c r="AA7" t="n">
-        <v>-21.2</v>
+        <v>-20.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.4</v>
+        <v>6.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.5</v>
+        <v>24.43</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="AF7" t="n">
-        <v>401.3433</v>
+        <v>401.0986</v>
       </c>
       <c r="AG7" t="n">
-        <v>437.8653</v>
+        <v>437.296</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28.5</v>
+        <v>31.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>73</v>
+        <v>78.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN7" t="n">
         <v>352.83</v>
@@ -1827,20 +1827,20 @@
         <v>352.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>401.1</v>
+        <v>402.29</v>
       </c>
       <c r="AQ7" t="n">
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.52</v>
+        <v>0.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>-9.73</v>
+        <v>-8.01</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1850,11 +1850,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>56.6</v>
+        <v>59.3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2653133471744</v>
+        <v>2689169883136</v>
       </c>
       <c r="G8" t="n">
-        <v>29.47</v>
+        <v>29.9</v>
       </c>
       <c r="H8" t="n">
-        <v>24.89</v>
+        <v>25.19</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>53.4</v>
+        <v>55.6</v>
       </c>
       <c r="P8" t="n">
-        <v>58.4</v>
+        <v>57.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="R8" t="n">
-        <v>76.5</v>
+        <v>78.8</v>
       </c>
       <c r="S8" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>246.64</v>
+        <v>249.99</v>
       </c>
       <c r="X8" t="n">
-        <v>0.26</v>
+        <v>5.26</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.23</v>
+        <v>-0.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.22</v>
+        <v>4.96</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.51</v>
+        <v>11.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.75</v>
+        <v>24.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.23</v>
+        <v>31.19</v>
       </c>
       <c r="AD8" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>252.1212</v>
+        <v>251.633</v>
       </c>
       <c r="AG8" t="n">
-        <v>234.0596</v>
+        <v>234.2146</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>53.4</v>
+        <v>55.6</v>
       </c>
       <c r="AK8" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>76.5</v>
+        <v>78.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN8" t="n">
         <v>227.01</v>
@@ -2030,10 +2030,10 @@
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.17</v>
+        <v>-0.65</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.38</v>
+        <v>6.74</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>60.2</v>
+        <v>61.4</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 60.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 61.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1434705330176</v>
+        <v>1388002803712</v>
       </c>
       <c r="G10" t="n">
-        <v>350.46</v>
+        <v>335.97</v>
       </c>
       <c r="H10" t="n">
-        <v>149.57</v>
+        <v>144.7</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>44.4</v>
+        <v>33.6</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>65.09999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="S10" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>382.03</v>
+        <v>369.57</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.59</v>
+        <v>-6.76</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.77</v>
+        <v>-7.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>-13.02</v>
+        <v>-15.73</v>
       </c>
       <c r="AA10" t="n">
-        <v>18.76</v>
+        <v>15.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.6</v>
+        <v>12.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.13</v>
+        <v>57.99</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>409.8236</v>
+        <v>409.2166</v>
       </c>
       <c r="AG10" t="n">
-        <v>417.0541</v>
+        <v>416.6724</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,22 +2350,22 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44.4</v>
+        <v>33.6</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>65.09999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN10" t="n">
-        <v>375.12</v>
+        <v>369.57</v>
       </c>
       <c r="AO10" t="n">
-        <v>372.8</v>
+        <v>369.57</v>
       </c>
       <c r="AP10" t="n">
         <v>425.3</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-6.79</v>
+        <v>-9.69</v>
       </c>
       <c r="AS10" t="n">
-        <v>-8.41</v>
+        <v>-11.3</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 6.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>26.9</v>
+        <v>22.8</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 35.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.8%.</t>
+          <t>TSLA: scenario base High Risk, score 32.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.7%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 372.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 369.57 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4796743417856</v>
+        <v>4814221606912</v>
       </c>
       <c r="G2" t="n">
-        <v>39.63</v>
+        <v>39.68</v>
       </c>
       <c r="H2" t="n">
-        <v>33.88</v>
+        <v>34.01</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -741,7 +741,7 @@
         <v>79.55</v>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>33.8</v>
+        <v>33.5</v>
       </c>
       <c r="Q2" t="n">
         <v>41.4</v>
       </c>
       <c r="R2" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="S2" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>326.59</v>
+        <v>327.795</v>
       </c>
       <c r="X2" t="n">
-        <v>10.35</v>
+        <v>9.99</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.97</v>
+        <v>20.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.72</v>
+        <v>28.52</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.12</v>
+        <v>55.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.08</v>
+        <v>20.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.61</v>
+        <v>26.59</v>
       </c>
       <c r="AD2" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AF2" t="n">
-        <v>303.4193</v>
+        <v>304.2317</v>
       </c>
       <c r="AG2" t="n">
-        <v>274.2438</v>
+        <v>274.6092</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         <v>41.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
         <v>275.15</v>
@@ -838,10 +838,10 @@
         <v>333.74</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.64</v>
+        <v>7.74</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.09</v>
+        <v>19.36</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>70.5</v>
+        <v>70.2</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.7%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4295183564800</v>
+        <v>4235634933760</v>
       </c>
       <c r="G3" t="n">
-        <v>26.85</v>
+        <v>26.52</v>
       </c>
       <c r="H3" t="n">
-        <v>24.03</v>
+        <v>23.7</v>
       </c>
       <c r="I3" t="n">
         <v>37.92</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>80.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="P3" t="n">
-        <v>62.7</v>
+        <v>63.6</v>
       </c>
       <c r="Q3" t="n">
         <v>40.1</v>
       </c>
       <c r="R3" t="n">
-        <v>72.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="S3" t="n">
-        <v>73.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>351.99</v>
+        <v>347.085</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.24</v>
+        <v>-5.69</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.91</v>
+        <v>5.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>92.28</v>
+        <v>88.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.91</v>
+        <v>43.16</v>
       </c>
       <c r="AC3" t="n">
         <v>30.02</v>
@@ -996,13 +996,13 @@
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AF3" t="n">
-        <v>369.5692</v>
+        <v>368.5559</v>
       </c>
       <c r="AG3" t="n">
-        <v>321.8828</v>
+        <v>322.3961</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>80.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="AK3" t="n">
         <v>40.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>72.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="AM3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>337.39</v>
@@ -1037,10 +1037,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>-4.76</v>
+        <v>-5.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.35</v>
+        <v>7.66</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 4.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>69.5</v>
+        <v>68.7</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 73.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.8%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 73.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>584139276288</v>
+        <v>612024975360</v>
       </c>
       <c r="G4" t="n">
-        <v>59.97</v>
+        <v>62.73</v>
       </c>
       <c r="H4" t="n">
-        <v>30.18</v>
+        <v>31.62</v>
       </c>
       <c r="I4" t="n">
         <v>30.11</v>
@@ -1148,16 +1148,16 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>21.2</v>
+        <v>19.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>77.7</v>
       </c>
       <c r="S4" t="n">
-        <v>69.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1520.8</v>
+        <v>1593.4</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.26</v>
+        <v>-3.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>23.21</v>
+        <v>27.77</v>
       </c>
       <c r="Z4" t="n">
-        <v>33.88</v>
+        <v>38.47</v>
       </c>
       <c r="AA4" t="n">
-        <v>152.71</v>
+        <v>160.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>35.54</v>
+        <v>37.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.01</v>
+        <v>39.1</v>
       </c>
       <c r="AD4" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>1507.024</v>
+        <v>1513.576</v>
       </c>
       <c r="AG4" t="n">
-        <v>1177.185</v>
+        <v>1180.6893</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>77.7</v>
       </c>
       <c r="AM4" t="n">
         <v>765</v>
@@ -1236,10 +1236,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.91</v>
+        <v>5.27</v>
       </c>
       <c r="AS4" t="n">
-        <v>29.19</v>
+        <v>34.96</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>57.5</v>
+        <v>55.8</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 69.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.9%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 68.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4923644706816</v>
+        <v>5029490589696</v>
       </c>
       <c r="G5" t="n">
-        <v>31.13</v>
+        <v>31.8</v>
       </c>
       <c r="H5" t="n">
-        <v>15.83</v>
+        <v>16.17</v>
       </c>
       <c r="I5" t="n">
         <v>62.97</v>
@@ -1344,19 +1344,19 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>61</v>
+        <v>66.2</v>
       </c>
       <c r="P5" t="n">
-        <v>69.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="Q5" t="n">
         <v>14.1</v>
       </c>
       <c r="R5" t="n">
-        <v>75.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="S5" t="n">
-        <v>65.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>203.28</v>
+        <v>207.67</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.67</v>
+        <v>-1.43</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.91</v>
+        <v>2.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.81</v>
+        <v>11.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.66</v>
+        <v>20.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>66.83</v>
+        <v>67.92</v>
       </c>
       <c r="AC5" t="n">
-        <v>46.98</v>
+        <v>46.96</v>
       </c>
       <c r="AD5" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>209.7267</v>
+        <v>209.655</v>
       </c>
       <c r="AG5" t="n">
-        <v>192.2833</v>
+        <v>192.3867</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,16 +1411,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>61</v>
+        <v>66.2</v>
       </c>
       <c r="AK5" t="n">
         <v>14.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>75.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
         <v>192.53</v>
@@ -1435,10 +1435,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.07</v>
+        <v>-0.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.72</v>
+        <v>7.93</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>47.7</v>
+        <v>49.9</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 65.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 67.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.0%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1639440580608</v>
+        <v>1634846113792</v>
       </c>
       <c r="G6" t="n">
-        <v>23.47</v>
+        <v>23.41</v>
       </c>
       <c r="H6" t="n">
-        <v>17.78</v>
+        <v>17.73</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1543,19 +1543,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>42.1</v>
+        <v>44.9</v>
       </c>
       <c r="P6" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="R6" t="n">
-        <v>71.7</v>
+        <v>73.3</v>
       </c>
       <c r="S6" t="n">
-        <v>65.3</v>
+        <v>66.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,25 +1569,25 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>645.85</v>
+        <v>644.01</v>
       </c>
       <c r="X6" t="n">
-        <v>13.79</v>
+        <v>11.57</v>
       </c>
       <c r="Y6" t="n">
-        <v>-6.11</v>
+        <v>-3.92</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.22</v>
+        <v>4.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>-7.62</v>
+        <v>-8.26</v>
       </c>
       <c r="AB6" t="n">
-        <v>30.57</v>
+        <v>30.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.13</v>
+        <v>37.1</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.15</v>
@@ -1596,10 +1596,10 @@
         <v>0.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>604.9028</v>
+        <v>605.4582</v>
       </c>
       <c r="AG6" t="n">
-        <v>639.0762</v>
+        <v>638.7189</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,16 +1610,16 @@
         <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42.1</v>
+        <v>44.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>71.7</v>
+        <v>73.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
         <v>542.87</v>
@@ -1634,10 +1634,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.77</v>
+        <v>6.37</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.06</v>
+        <v>0.83</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>45.8</v>
+        <v>47.1</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 65.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 66.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2988385239040</v>
+        <v>2955625627648</v>
       </c>
       <c r="G7" t="n">
-        <v>23.97</v>
+        <v>23.71</v>
       </c>
       <c r="H7" t="n">
-        <v>20.76</v>
+        <v>20.53</v>
       </c>
       <c r="I7" t="n">
         <v>39.34</v>
@@ -1736,25 +1736,25 @@
         <v>30.27</v>
       </c>
       <c r="M7" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>31.4</v>
+        <v>30.3</v>
       </c>
       <c r="P7" t="n">
-        <v>70.7</v>
+        <v>71.3</v>
       </c>
       <c r="Q7" t="n">
         <v>43.1</v>
       </c>
       <c r="R7" t="n">
-        <v>78.2</v>
+        <v>74.2</v>
       </c>
       <c r="S7" t="n">
-        <v>63.5</v>
+        <v>61.9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1763,62 +1763,62 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>402.29</v>
+        <v>397.91</v>
       </c>
       <c r="X7" t="n">
-        <v>6.17</v>
+        <v>4.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.64</v>
+        <v>-4.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>-11.51</v>
+        <v>-13.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>-20.75</v>
+        <v>-21.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.43</v>
+        <v>24.42</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AF7" t="n">
-        <v>401.0986</v>
+        <v>400.6596</v>
       </c>
       <c r="AG7" t="n">
-        <v>437.296</v>
+        <v>436.7033</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>31.4</v>
+        <v>30.3</v>
       </c>
       <c r="AK7" t="n">
         <v>43.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>78.2</v>
+        <v>74.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
         <v>352.83</v>
@@ -1833,14 +1833,14 @@
         <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.3</v>
+        <v>-0.68</v>
       </c>
       <c r="AS7" t="n">
-        <v>-8.01</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1850,11 +1850,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>59.3</v>
+        <v>57.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2689169883136</v>
+        <v>2663514112000</v>
       </c>
       <c r="G8" t="n">
-        <v>29.9</v>
+        <v>29.65</v>
       </c>
       <c r="H8" t="n">
-        <v>25.19</v>
+        <v>24.97</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>55.6</v>
+        <v>54.1</v>
       </c>
       <c r="P8" t="n">
-        <v>57.5</v>
+        <v>58.1</v>
       </c>
       <c r="Q8" t="n">
         <v>37.9</v>
       </c>
       <c r="R8" t="n">
-        <v>78.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>61.4</v>
+        <v>61</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>249.99</v>
+        <v>247.61</v>
       </c>
       <c r="X8" t="n">
-        <v>5.26</v>
+        <v>1.32</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.96</v>
+        <v>3.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.66</v>
+        <v>9.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.53</v>
+        <v>24.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.19</v>
+        <v>31.17</v>
       </c>
       <c r="AD8" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AF8" t="n">
-        <v>251.633</v>
+        <v>251.1618</v>
       </c>
       <c r="AG8" t="n">
-        <v>234.2146</v>
+        <v>234.3495</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55.6</v>
+        <v>54.1</v>
       </c>
       <c r="AK8" t="n">
         <v>37.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>78.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
         <v>227.01</v>
@@ -2030,10 +2030,10 @@
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.65</v>
+        <v>-1.42</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.74</v>
+        <v>5.66</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>61.4</v>
+        <v>60.6</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 61.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 61.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.4%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1388002803712</v>
+        <v>1423701049344</v>
       </c>
       <c r="G10" t="n">
-        <v>335.97</v>
+        <v>354.28</v>
       </c>
       <c r="H10" t="n">
-        <v>144.7</v>
+        <v>147.73</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>33.6</v>
+        <v>41</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>60.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>32.3</v>
+        <v>34.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>369.57</v>
+        <v>379.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.76</v>
+        <v>-5.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>-7.75</v>
+        <v>-3.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>-15.73</v>
+        <v>-13.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.7</v>
+        <v>15.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.52</v>
+        <v>13.47</v>
       </c>
       <c r="AC10" t="n">
-        <v>57.99</v>
+        <v>57.97</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="AF10" t="n">
-        <v>409.2166</v>
+        <v>408.5634</v>
       </c>
       <c r="AG10" t="n">
-        <v>416.6724</v>
+        <v>416.2708</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>33.6</v>
+        <v>41</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>60.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AM10" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN10" t="n">
         <v>369.57</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-9.69</v>
+        <v>-7.21</v>
       </c>
       <c r="AS10" t="n">
-        <v>-11.3</v>
+        <v>-8.93</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 9.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>22.8</v>
+        <v>25.8</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 32.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.7%.</t>
+          <t>TSLA: scenario base High Risk, score 34.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4814221606912</v>
+        <v>4786241929216</v>
       </c>
       <c r="G2" t="n">
-        <v>39.68</v>
+        <v>39.45</v>
       </c>
       <c r="H2" t="n">
-        <v>34.01</v>
+        <v>33.81</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>33.5</v>
+        <v>34.1</v>
       </c>
       <c r="Q2" t="n">
         <v>41.4</v>
       </c>
       <c r="R2" t="n">
-        <v>67.8</v>
+        <v>71.2</v>
       </c>
       <c r="S2" t="n">
-        <v>74.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>327.795</v>
+        <v>325.88</v>
       </c>
       <c r="X2" t="n">
-        <v>9.99</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.16</v>
+        <v>22.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.52</v>
+        <v>32.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>55.84</v>
+        <v>53.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.59</v>
+        <v>26.6</v>
       </c>
       <c r="AD2" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="AF2" t="n">
-        <v>304.2317</v>
+        <v>304.8872</v>
       </c>
       <c r="AG2" t="n">
-        <v>274.6092</v>
+        <v>274.9563</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>41.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>67.8</v>
+        <v>71.2</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
@@ -838,10 +838,10 @@
         <v>333.74</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.74</v>
+        <v>6.89</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.36</v>
+        <v>18.52</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>70.2</v>
+        <v>72.5</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.7%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.9%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4235634933760</v>
+        <v>4196769726464</v>
       </c>
       <c r="G3" t="n">
-        <v>26.52</v>
+        <v>26.21</v>
       </c>
       <c r="H3" t="n">
-        <v>23.7</v>
+        <v>23.44</v>
       </c>
       <c r="I3" t="n">
         <v>37.92</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="P3" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="Q3" t="n">
         <v>40.1</v>
       </c>
       <c r="R3" t="n">
-        <v>71</v>
+        <v>70.2</v>
       </c>
       <c r="S3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>347.085</v>
+        <v>343.96</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.69</v>
+        <v>-1.64</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.93</v>
+        <v>3.57</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.31</v>
+        <v>6.96</v>
       </c>
       <c r="AA3" t="n">
-        <v>88.09</v>
+        <v>81.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.16</v>
+        <v>42.13</v>
       </c>
       <c r="AC3" t="n">
         <v>30.02</v>
@@ -996,13 +996,13 @@
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>368.5559</v>
+        <v>367.4252</v>
       </c>
       <c r="AG3" t="n">
-        <v>322.3961</v>
+        <v>322.8902</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="AK3" t="n">
         <v>40.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>71</v>
+        <v>70.2</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
@@ -1037,10 +1037,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>-5.83</v>
+        <v>-6.39</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.66</v>
+        <v>6.53</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 5.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 73.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.8%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 73.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>612024975360</v>
+        <v>5148900327424</v>
       </c>
       <c r="G4" t="n">
-        <v>62.73</v>
+        <v>32.55</v>
       </c>
       <c r="H4" t="n">
-        <v>31.62</v>
+        <v>16.52</v>
       </c>
       <c r="I4" t="n">
-        <v>30.11</v>
+        <v>62.97</v>
       </c>
       <c r="J4" t="n">
-        <v>53.94</v>
+        <v>114.29</v>
       </c>
       <c r="K4" t="n">
-        <v>21.3</v>
+        <v>85.2</v>
       </c>
       <c r="L4" t="n">
-        <v>9.09</v>
+        <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>76.8</v>
       </c>
       <c r="P4" t="n">
-        <v>19.1</v>
+        <v>66.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.3</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>77.7</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1593.4</v>
+        <v>212.54</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.77</v>
+        <v>1.86</v>
       </c>
       <c r="Y4" t="n">
-        <v>27.77</v>
+        <v>6.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>38.47</v>
+        <v>19.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>160.78</v>
+        <v>24.18</v>
       </c>
       <c r="AB4" t="n">
-        <v>37.25</v>
+        <v>68.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.1</v>
+        <v>46.97</v>
       </c>
       <c r="AD4" t="n">
-        <v>-44.77</v>
+        <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.95</v>
+        <v>1.47</v>
       </c>
       <c r="AF4" t="n">
-        <v>1513.576</v>
+        <v>209.5993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1180.6893</v>
+        <v>192.5042</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,34 +1212,34 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>76.8</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.3</v>
+        <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>77.7</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>1509.8</v>
+        <v>192.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>1171.8</v>
+        <v>192.53</v>
       </c>
       <c r="AP4" t="n">
-        <v>1721.4</v>
+        <v>212.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1721.4</v>
+        <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.27</v>
+        <v>1.43</v>
       </c>
       <c r="AS4" t="n">
-        <v>34.96</v>
+        <v>10.44</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>55.8</v>
+        <v>54.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 68.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1171.80 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 192.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1313,29 +1313,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5029490589696</v>
+        <v>610565357568</v>
       </c>
       <c r="G5" t="n">
-        <v>31.8</v>
+        <v>62.73</v>
       </c>
       <c r="H5" t="n">
-        <v>16.17</v>
+        <v>31.31</v>
       </c>
       <c r="I5" t="n">
-        <v>62.97</v>
+        <v>30.11</v>
       </c>
       <c r="J5" t="n">
-        <v>114.29</v>
+        <v>53.94</v>
       </c>
       <c r="K5" t="n">
-        <v>85.2</v>
+        <v>21.3</v>
       </c>
       <c r="L5" t="n">
-        <v>6.55</v>
+        <v>9.09</v>
       </c>
       <c r="M5" t="n">
         <v>49</v>
@@ -1344,23 +1344,23 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>66.2</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>68.2</v>
+        <v>19.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.1</v>
+        <v>17.3</v>
       </c>
       <c r="R5" t="n">
-        <v>78.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>67.3</v>
+        <v>68.7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1370,75 +1370,75 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>207.67</v>
+        <v>1589.6</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.43</v>
+        <v>1.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.9</v>
+        <v>30.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.65</v>
+        <v>35.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.61</v>
+        <v>164.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>67.92</v>
+        <v>37.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>46.96</v>
+        <v>39.09</v>
       </c>
       <c r="AD5" t="n">
-        <v>-36.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.45</v>
+        <v>0.97</v>
       </c>
       <c r="AF5" t="n">
-        <v>209.655</v>
+        <v>1518.828</v>
       </c>
       <c r="AG5" t="n">
-        <v>192.3867</v>
+        <v>1184.2865</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>66.2</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>14.1</v>
+        <v>17.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>78.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="AN5" t="n">
-        <v>192.53</v>
+        <v>1509.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>192.53</v>
+        <v>1187.4</v>
       </c>
       <c r="AP5" t="n">
-        <v>212.5</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>235.4656</v>
+        <v>1721.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.96</v>
+        <v>4.66</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.93</v>
+        <v>34.22</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>49.9</v>
+        <v>56.5</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 67.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.0%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 68.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 192.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1187.40 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1634846113792</v>
+        <v>1585638146048</v>
       </c>
       <c r="G6" t="n">
-        <v>23.41</v>
+        <v>22.72</v>
       </c>
       <c r="H6" t="n">
-        <v>17.73</v>
+        <v>16.88</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1543,19 +1543,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>44.9</v>
+        <v>40</v>
       </c>
       <c r="P6" t="n">
-        <v>75.7</v>
+        <v>77.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="R6" t="n">
-        <v>73.3</v>
+        <v>78.2</v>
       </c>
       <c r="S6" t="n">
-        <v>66.2</v>
+        <v>64.3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,54 +1569,54 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>644.01</v>
+        <v>624.6547</v>
       </c>
       <c r="X6" t="n">
-        <v>11.57</v>
+        <v>10.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>-3.92</v>
+        <v>-6.52</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.02</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>-8.26</v>
+        <v>-12.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>30.4</v>
+        <v>29.46</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.1</v>
+        <v>37.14</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>605.4582</v>
+        <v>605.766</v>
       </c>
       <c r="AG6" t="n">
-        <v>638.7189</v>
+        <v>638.2153</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44.9</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>73.3</v>
+        <v>78.2</v>
       </c>
       <c r="AM6" t="n">
         <v>752</v>
@@ -1634,10 +1634,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.37</v>
+        <v>3.12</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.83</v>
+        <v>-2.12</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 66.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
+          <t>META: scenario base Hold / Monitor, score 64.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1691,12 +1691,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1706,55 +1706,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2955625627648</v>
+        <v>2633125330944</v>
       </c>
       <c r="G7" t="n">
-        <v>23.71</v>
+        <v>29.24</v>
       </c>
       <c r="H7" t="n">
-        <v>20.53</v>
+        <v>24.68</v>
       </c>
       <c r="I7" t="n">
-        <v>39.34</v>
+        <v>12.22</v>
       </c>
       <c r="J7" t="n">
-        <v>34.01</v>
+        <v>24.29</v>
       </c>
       <c r="K7" t="n">
-        <v>18.3</v>
+        <v>16.6</v>
       </c>
       <c r="L7" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="M7" t="n">
-        <v>90</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O7" t="n">
-        <v>30.3</v>
+        <v>52.4</v>
       </c>
       <c r="P7" t="n">
-        <v>71.3</v>
+        <v>59</v>
       </c>
       <c r="Q7" t="n">
-        <v>43.1</v>
+        <v>37.9</v>
       </c>
       <c r="R7" t="n">
-        <v>74.2</v>
+        <v>76.3</v>
       </c>
       <c r="S7" t="n">
-        <v>61.9</v>
+        <v>60.6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1763,84 +1761,84 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>397.91</v>
+        <v>244.78</v>
       </c>
       <c r="X7" t="n">
-        <v>4.88</v>
+        <v>5.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.62</v>
+        <v>-2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>-13.09</v>
+        <v>5.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>-21.36</v>
+        <v>6.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.85</v>
+        <v>24.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.42</v>
+        <v>31.18</v>
       </c>
       <c r="AD7" t="n">
-        <v>-34.5</v>
+        <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.24</v>
+        <v>0.77</v>
       </c>
       <c r="AF7" t="n">
-        <v>400.6596</v>
+        <v>250.6026</v>
       </c>
       <c r="AG7" t="n">
-        <v>436.7033</v>
+        <v>234.4611</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>30.3</v>
+        <v>52.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>43.1</v>
+        <v>37.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>74.2</v>
+        <v>76.3</v>
       </c>
       <c r="AM7" t="n">
         <v>752</v>
       </c>
       <c r="AN7" t="n">
-        <v>352.83</v>
+        <v>227.01</v>
       </c>
       <c r="AO7" t="n">
-        <v>352.83</v>
+        <v>227.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>402.29</v>
+        <v>254.96</v>
       </c>
       <c r="AQ7" t="n">
-        <v>460.52</v>
+        <v>274.99</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.68</v>
+        <v>-2.32</v>
       </c>
       <c r="AS7" t="n">
-        <v>-8.880000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>57.4</v>
+        <v>59.9</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.7%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 60.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.3%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1883,19 +1881,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1905,53 +1903,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2663514112000</v>
+        <v>2891369938944</v>
       </c>
       <c r="G8" t="n">
-        <v>29.65</v>
+        <v>23.18</v>
       </c>
       <c r="H8" t="n">
-        <v>24.97</v>
+        <v>20.09</v>
       </c>
       <c r="I8" t="n">
-        <v>12.22</v>
+        <v>39.34</v>
       </c>
       <c r="J8" t="n">
-        <v>24.29</v>
+        <v>34.01</v>
       </c>
       <c r="K8" t="n">
-        <v>16.6</v>
+        <v>18.3</v>
       </c>
       <c r="L8" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>30.27</v>
+      </c>
+      <c r="M8" t="n">
+        <v>92</v>
+      </c>
       <c r="N8" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>54.1</v>
+        <v>24.6</v>
       </c>
       <c r="P8" t="n">
-        <v>58.1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.9</v>
+        <v>43.1</v>
       </c>
       <c r="R8" t="n">
-        <v>77.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="S8" t="n">
-        <v>61</v>
+        <v>60.4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1960,84 +1960,84 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>247.61</v>
+        <v>389.2736</v>
       </c>
       <c r="X8" t="n">
-        <v>1.32</v>
+        <v>5.97</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.27</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.55</v>
+        <v>-13.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.5</v>
+        <v>-23.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.1</v>
+        <v>4.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.17</v>
+        <v>24.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>-30.88</v>
+        <v>-34.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.77</v>
+        <v>0.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>251.1618</v>
+        <v>400.1574</v>
       </c>
       <c r="AG8" t="n">
-        <v>234.3495</v>
+        <v>436.0864</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>54.1</v>
+        <v>24.6</v>
       </c>
       <c r="AK8" t="n">
-        <v>37.9</v>
+        <v>43.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>77.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
       </c>
       <c r="AN8" t="n">
-        <v>227.01</v>
+        <v>352.83</v>
       </c>
       <c r="AO8" t="n">
-        <v>227.01</v>
+        <v>352.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>254.96</v>
+        <v>402.29</v>
       </c>
       <c r="AQ8" t="n">
-        <v>274.99</v>
+        <v>460.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.42</v>
+        <v>-2.73</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.66</v>
+        <v>-10.74</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>60.6</v>
+        <v>55.1</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 61.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.4%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.7%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1423701049344</v>
+        <v>1405767385088</v>
       </c>
       <c r="G10" t="n">
-        <v>354.28</v>
+        <v>340.27</v>
       </c>
       <c r="H10" t="n">
-        <v>147.73</v>
+        <v>145.87</v>
       </c>
       <c r="I10" t="n">
         <v>3.95</v>
@@ -2283,7 +2283,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>41</v>
+        <v>42.7</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>64.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="S10" t="n">
-        <v>34.5</v>
+        <v>34.8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>379.13</v>
+        <v>374.2851</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.33</v>
+        <v>-7.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.41</v>
+        <v>-3.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>-13.34</v>
+        <v>-10.73</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.01</v>
+        <v>13.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>13.47</v>
+        <v>11.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>57.97</v>
+        <v>57.94</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>408.5634</v>
+        <v>407.4781</v>
       </c>
       <c r="AG10" t="n">
-        <v>416.2708</v>
+        <v>415.9612</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>41</v>
+        <v>42.7</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>64.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="AM10" t="n">
         <v>752</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-7.21</v>
+        <v>-8.15</v>
       </c>
       <c r="AS10" t="n">
-        <v>-8.93</v>
+        <v>-10.02</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 34.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
+          <t>TSLA: scenario base High Risk, score 34.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4786241929216</v>
+        <v>4716770623488</v>
       </c>
       <c r="G2" t="n">
-        <v>39.45</v>
+        <v>38.93</v>
       </c>
       <c r="H2" t="n">
-        <v>33.81</v>
+        <v>33.31</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>34.1</v>
+        <v>35.4</v>
       </c>
       <c r="Q2" t="n">
         <v>41.4</v>
       </c>
       <c r="R2" t="n">
-        <v>71.2</v>
+        <v>78.2</v>
       </c>
       <c r="S2" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>325.88</v>
+        <v>321.13</v>
       </c>
       <c r="X2" t="n">
-        <v>9.720000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.55</v>
+        <v>17.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>32.34</v>
+        <v>29.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>53.98</v>
+        <v>50.38</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.8</v>
+        <v>19.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.6</v>
+        <v>26.59</v>
       </c>
       <c r="AD2" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="AF2" t="n">
-        <v>304.8872</v>
+        <v>305.4564</v>
       </c>
       <c r="AG2" t="n">
-        <v>274.9563</v>
+        <v>275.2755</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,16 +820,16 @@
         <v>41.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>71.2</v>
+        <v>78.2</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
         <v>275.15</v>
       </c>
       <c r="AO2" t="n">
-        <v>267.3636</v>
+        <v>269.9213</v>
       </c>
       <c r="AP2" t="n">
         <v>333.74</v>
@@ -838,10 +838,10 @@
         <v>333.74</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.89</v>
+        <v>5.14</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.52</v>
+        <v>16.66</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>72.5</v>
+        <v>74.7</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.1%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 267.36 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 269.92 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -910,55 +910,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4196769726464</v>
+        <v>606570676224</v>
       </c>
       <c r="G3" t="n">
-        <v>26.21</v>
+        <v>62.1</v>
       </c>
       <c r="H3" t="n">
-        <v>23.44</v>
+        <v>31.01</v>
       </c>
       <c r="I3" t="n">
-        <v>37.92</v>
+        <v>30.11</v>
       </c>
       <c r="J3" t="n">
-        <v>38.88</v>
+        <v>53.94</v>
       </c>
       <c r="K3" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="L3" t="n">
-        <v>20.03</v>
+        <v>9.09</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>64.3</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.1</v>
+        <v>17.3</v>
       </c>
       <c r="R3" t="n">
-        <v>70.2</v>
+        <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>73.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,80 +967,80 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>343.96</v>
+        <v>1579.2</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.57</v>
+        <v>26.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.96</v>
+        <v>34.51</v>
       </c>
       <c r="AA3" t="n">
-        <v>81.45</v>
+        <v>152.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.13</v>
+        <v>37.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.02</v>
+        <v>39.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>-29.81</v>
+        <v>-44.77</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="AF3" t="n">
-        <v>367.4252</v>
+        <v>1523.072</v>
       </c>
       <c r="AG3" t="n">
-        <v>322.8902</v>
+        <v>1187.946</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>40.1</v>
+        <v>17.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>70.2</v>
+        <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="AN3" t="n">
-        <v>337.39</v>
+        <v>1509.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>337.39</v>
+        <v>1187.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>370.92</v>
+        <v>1721.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>402.3797</v>
+        <v>1721.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>-6.39</v>
+        <v>3.69</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.53</v>
+        <v>32.94</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 6.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>68.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 73.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 337.39 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1187.40 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5148900327424</v>
+        <v>5026341715968</v>
       </c>
       <c r="G4" t="n">
-        <v>32.55</v>
+        <v>31.78</v>
       </c>
       <c r="H4" t="n">
-        <v>16.52</v>
+        <v>16.13</v>
       </c>
       <c r="I4" t="n">
         <v>62.97</v>
@@ -1139,29 +1139,29 @@
         <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>76.8</v>
+        <v>67.7</v>
       </c>
       <c r="P4" t="n">
-        <v>66.8</v>
+        <v>68.2</v>
       </c>
       <c r="Q4" t="n">
         <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>71.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1171,57 +1171,57 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>212.54</v>
+        <v>207.5</v>
       </c>
       <c r="X4" t="n">
-        <v>1.86</v>
+        <v>3.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.46</v>
+        <v>2.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.5</v>
+        <v>13.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.18</v>
+        <v>24.39</v>
       </c>
       <c r="AB4" t="n">
-        <v>68.84</v>
+        <v>67.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.97</v>
+        <v>46.96</v>
       </c>
       <c r="AD4" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.5993</v>
+        <v>209.356</v>
       </c>
       <c r="AG4" t="n">
-        <v>192.5042</v>
+        <v>192.6024</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>76.8</v>
+        <v>67.7</v>
       </c>
       <c r="AK4" t="n">
         <v>14.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN4" t="n">
         <v>192.53</v>
@@ -1230,16 +1230,16 @@
         <v>192.53</v>
       </c>
       <c r="AP4" t="n">
-        <v>212.6</v>
+        <v>212.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.43</v>
+        <v>-0.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.44</v>
+        <v>7.75</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>54.3</v>
+        <v>50.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.9%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,155 +1308,155 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>610565357568</v>
+        <v>3887129427968</v>
       </c>
       <c r="G5" t="n">
-        <v>62.73</v>
+        <v>15.98</v>
       </c>
       <c r="H5" t="n">
-        <v>31.31</v>
+        <v>21.59</v>
       </c>
       <c r="I5" t="n">
-        <v>30.11</v>
+        <v>54.77</v>
       </c>
       <c r="J5" t="n">
-        <v>53.94</v>
+        <v>48.68</v>
       </c>
       <c r="K5" t="n">
-        <v>21.3</v>
+        <v>24.2</v>
       </c>
       <c r="L5" t="n">
-        <v>9.09</v>
+        <v>17.61</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="P5" t="n">
-        <v>19.6</v>
+        <v>78.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.3</v>
+        <v>39.8</v>
       </c>
       <c r="R5" t="n">
-        <v>80.09999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="S5" t="n">
-        <v>68.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1589.6</v>
+        <v>318.55</v>
       </c>
       <c r="X5" t="n">
-        <v>1.85</v>
+        <v>-7.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>30.18</v>
+        <v>-6.07</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.6</v>
+        <v>-2.87</v>
       </c>
       <c r="AA5" t="n">
-        <v>164.89</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>37.86</v>
+        <v>38.46</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.09</v>
+        <v>30.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>-44.77</v>
+        <v>-29.81</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.97</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1518.828</v>
+        <v>365.9906</v>
       </c>
       <c r="AG5" t="n">
-        <v>1184.2865</v>
+        <v>323.2492</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.3</v>
+        <v>39.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>80.09999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="AM5" t="n">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
-        <v>1509.8</v>
+        <v>318.55</v>
       </c>
       <c r="AO5" t="n">
-        <v>1187.4</v>
+        <v>318.55</v>
       </c>
       <c r="AP5" t="n">
-        <v>1721.4</v>
+        <v>370.92</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1721.4</v>
+        <v>402.3797</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.66</v>
+        <v>-12.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>34.22</v>
+        <v>-1.45</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 13.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>56.5</v>
+        <v>58.7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 68.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
+          <t>GOOGL: scenario base Hold / Monitor, score 67.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -13.0%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1187.40 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 318.55 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1585638146048</v>
+        <v>1537421344768</v>
       </c>
       <c r="G6" t="n">
-        <v>22.72</v>
+        <v>22.05</v>
       </c>
       <c r="H6" t="n">
-        <v>16.88</v>
+        <v>16.36</v>
       </c>
       <c r="I6" t="n">
         <v>32.84</v>
@@ -1543,19 +1543,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>40</v>
+        <v>31.7</v>
       </c>
       <c r="P6" t="n">
-        <v>77.7</v>
+        <v>79.2</v>
       </c>
       <c r="Q6" t="n">
         <v>28.1</v>
       </c>
       <c r="R6" t="n">
-        <v>78.2</v>
+        <v>75.2</v>
       </c>
       <c r="S6" t="n">
-        <v>64.3</v>
+        <v>61.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,57 +1569,57 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>624.6547</v>
+        <v>605.6</v>
       </c>
       <c r="X6" t="n">
-        <v>10.78</v>
+        <v>7.72</v>
       </c>
       <c r="Y6" t="n">
-        <v>-6.52</v>
+        <v>-10.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>-1.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>-12.1</v>
+        <v>-13.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.46</v>
+        <v>28.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.14</v>
+        <v>37.17</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>605.766</v>
+        <v>605.9622000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>638.2153</v>
+        <v>637.7123</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40</v>
+        <v>31.7</v>
       </c>
       <c r="AK6" t="n">
         <v>28.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>78.2</v>
+        <v>75.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN6" t="n">
         <v>542.87</v>
@@ -1634,14 +1634,14 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.12</v>
+        <v>-0.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>-2.12</v>
+        <v>-5.03</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>46.7</v>
+        <v>43.3</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 64.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.1%.</t>
+          <t>META: scenario base Hold / Monitor, score 61.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.1%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1691,12 +1691,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1706,53 +1706,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2633125330944</v>
+        <v>2825219735552</v>
       </c>
       <c r="G7" t="n">
-        <v>29.24</v>
+        <v>22.67</v>
       </c>
       <c r="H7" t="n">
-        <v>24.68</v>
+        <v>19.63</v>
       </c>
       <c r="I7" t="n">
-        <v>12.22</v>
+        <v>39.34</v>
       </c>
       <c r="J7" t="n">
-        <v>24.29</v>
+        <v>34.01</v>
       </c>
       <c r="K7" t="n">
-        <v>16.6</v>
+        <v>18.3</v>
       </c>
       <c r="L7" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>30.27</v>
+      </c>
+      <c r="M7" t="n">
+        <v>93</v>
+      </c>
       <c r="N7" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>52.4</v>
+        <v>18.8</v>
       </c>
       <c r="P7" t="n">
-        <v>59</v>
+        <v>73.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.9</v>
+        <v>43</v>
       </c>
       <c r="R7" t="n">
-        <v>76.3</v>
+        <v>68</v>
       </c>
       <c r="S7" t="n">
-        <v>60.6</v>
+        <v>58.9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,84 +1763,84 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>244.78</v>
+        <v>380.33</v>
       </c>
       <c r="X7" t="n">
-        <v>5.15</v>
+        <v>1.71</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.05</v>
+        <v>-11.96</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.97</v>
+        <v>-13.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.75</v>
+        <v>-24.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.01</v>
+        <v>4.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>31.18</v>
+        <v>24.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>-30.88</v>
+        <v>-34.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.77</v>
+        <v>0.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>250.6026</v>
+        <v>399.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>234.4611</v>
+        <v>435.4229</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>52.4</v>
+        <v>18.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>37.9</v>
+        <v>43</v>
       </c>
       <c r="AL7" t="n">
-        <v>76.3</v>
+        <v>68</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
-        <v>227.01</v>
+        <v>352.83</v>
       </c>
       <c r="AO7" t="n">
-        <v>227.01</v>
+        <v>352.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>254.96</v>
+        <v>402.29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>274.99</v>
+        <v>460.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-2.32</v>
+        <v>-4.81</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>-12.65</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1848,11 +1850,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>59.9</v>
+        <v>52.8</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1863,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 60.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.3%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 58.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.8%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,19 +1883,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1903,55 +1905,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2891369938944</v>
+        <v>2511623684096</v>
       </c>
       <c r="G8" t="n">
-        <v>23.18</v>
+        <v>27.96</v>
       </c>
       <c r="H8" t="n">
-        <v>20.09</v>
+        <v>23.54</v>
       </c>
       <c r="I8" t="n">
-        <v>39.34</v>
+        <v>12.22</v>
       </c>
       <c r="J8" t="n">
-        <v>34.01</v>
+        <v>24.29</v>
       </c>
       <c r="K8" t="n">
-        <v>18.3</v>
+        <v>16.6</v>
       </c>
       <c r="L8" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="M8" t="n">
-        <v>92</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>24.6</v>
+        <v>39.2</v>
       </c>
       <c r="P8" t="n">
-        <v>72.59999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>43.1</v>
+        <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>71.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>60.4</v>
+        <v>55.3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>389.2736</v>
+        <v>233.485</v>
       </c>
       <c r="X8" t="n">
-        <v>5.97</v>
+        <v>-0.27</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.029999999999999</v>
+        <v>-8.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.07</v>
+        <v>2.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.94</v>
+        <v>22.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>24.45</v>
+        <v>31.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>-34.5</v>
+        <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>400.1574</v>
+        <v>249.8939</v>
       </c>
       <c r="AG8" t="n">
-        <v>436.0864</v>
+        <v>234.5313</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,34 +2006,34 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24.6</v>
+        <v>39.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>43.1</v>
+        <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>71.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
-        <v>352.83</v>
+        <v>227.01</v>
       </c>
       <c r="AO8" t="n">
-        <v>352.83</v>
+        <v>227.01</v>
       </c>
       <c r="AP8" t="n">
-        <v>402.29</v>
+        <v>254.96</v>
       </c>
       <c r="AQ8" t="n">
-        <v>460.52</v>
+        <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.73</v>
+        <v>-6.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>-10.74</v>
+        <v>-0.45</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 6.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>55.1</v>
+        <v>52.8</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.7%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 55.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -2258,32 +2258,32 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1405767385088</v>
+        <v>1201643847680</v>
       </c>
       <c r="G10" t="n">
-        <v>340.27</v>
+        <v>296.25</v>
       </c>
       <c r="H10" t="n">
-        <v>145.87</v>
+        <v>142.59</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>3.67</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9</v>
+        <v>4.67</v>
       </c>
       <c r="K10" t="n">
-        <v>15.8</v>
+        <v>25.5</v>
       </c>
       <c r="L10" t="n">
-        <v>18.74</v>
+        <v>10.67</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>64.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>42.7</v>
+        <v>9.1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>63</v>
+        <v>43.7</v>
       </c>
       <c r="S10" t="n">
-        <v>34.8</v>
+        <v>25.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>374.2851</v>
+        <v>319.83</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.6</v>
+        <v>-16.19</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.14</v>
+        <v>-17.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>-10.73</v>
+        <v>-25.87</v>
       </c>
       <c r="AA10" t="n">
-        <v>13.94</v>
+        <v>-3.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.7</v>
+        <v>5.96</v>
       </c>
       <c r="AC10" t="n">
-        <v>57.94</v>
+        <v>58.51</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>407.4781</v>
+        <v>404.9692</v>
       </c>
       <c r="AG10" t="n">
-        <v>415.9612</v>
+        <v>415.4099</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,22 +2350,22 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42.7</v>
+        <v>9.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>63</v>
+        <v>43.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN10" t="n">
-        <v>369.57</v>
+        <v>319.83</v>
       </c>
       <c r="AO10" t="n">
-        <v>369.57</v>
+        <v>319.83</v>
       </c>
       <c r="AP10" t="n">
         <v>425.3</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-8.15</v>
+        <v>-21.02</v>
       </c>
       <c r="AS10" t="n">
-        <v>-10.02</v>
+        <v>-23.01</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 21.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>25.8</v>
+        <v>11.9</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 34.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.2%.</t>
+          <t>TSLA: scenario base High Risk, score 25.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -21.0%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 369.57 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 319.83 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4716770623488</v>
+        <v>4888539430912</v>
       </c>
       <c r="G2" t="n">
-        <v>38.93</v>
+        <v>40.25</v>
       </c>
       <c r="H2" t="n">
-        <v>33.31</v>
+        <v>34.52</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -741,7 +741,7 @@
         <v>79.55</v>
       </c>
       <c r="M2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>35.4</v>
+        <v>32.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="R2" t="n">
-        <v>78.2</v>
+        <v>64</v>
       </c>
       <c r="S2" t="n">
-        <v>75.5</v>
+        <v>73.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>321.13</v>
+        <v>332.8301</v>
       </c>
       <c r="X2" t="n">
-        <v>9.119999999999999</v>
+        <v>13.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.67</v>
+        <v>21.84</v>
       </c>
       <c r="Z2" t="n">
-        <v>29.91</v>
+        <v>34.27</v>
       </c>
       <c r="AA2" t="n">
-        <v>50.38</v>
+        <v>56.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.18</v>
+        <v>20.59</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.59</v>
+        <v>26.64</v>
       </c>
       <c r="AD2" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>305.4564</v>
+        <v>306.2276</v>
       </c>
       <c r="AG2" t="n">
-        <v>275.2755</v>
+        <v>275.6625</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>78.2</v>
+        <v>64</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN2" t="n">
-        <v>275.15</v>
+        <v>281.74</v>
       </c>
       <c r="AO2" t="n">
         <v>269.9213</v>
@@ -838,10 +838,10 @@
         <v>333.74</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.14</v>
+        <v>8.69</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.66</v>
+        <v>20.74</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>74.7</v>
+        <v>67.2</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.1%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.7%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>606570676224</v>
+        <v>600348295168</v>
       </c>
       <c r="G3" t="n">
-        <v>62.1</v>
+        <v>61.46</v>
       </c>
       <c r="H3" t="n">
-        <v>31.01</v>
+        <v>30.7</v>
       </c>
       <c r="I3" t="n">
         <v>30.11</v>
@@ -949,7 +949,7 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="Q3" t="n">
         <v>17.3</v>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>1579.2</v>
+        <v>1563</v>
       </c>
       <c r="X3" t="n">
-        <v>1.63</v>
+        <v>-1.94</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.38</v>
+        <v>28.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.51</v>
+        <v>33.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>152.68</v>
+        <v>152.22</v>
       </c>
       <c r="AB3" t="n">
-        <v>37.5</v>
+        <v>36.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>39.07</v>
+        <v>39.05</v>
       </c>
       <c r="AD3" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1523.072</v>
+        <v>1528.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1187.946</v>
+        <v>1191.5346</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN3" t="n">
         <v>1509.8</v>
@@ -1037,10 +1037,10 @@
         <v>1721.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.69</v>
+        <v>2.28</v>
       </c>
       <c r="AS3" t="n">
-        <v>32.94</v>
+        <v>31.18</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.7%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,52 +1109,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5026341715968</v>
+        <v>3911499907072</v>
       </c>
       <c r="G4" t="n">
-        <v>31.78</v>
+        <v>16.06</v>
       </c>
       <c r="H4" t="n">
-        <v>16.13</v>
+        <v>21.64</v>
       </c>
       <c r="I4" t="n">
-        <v>62.97</v>
+        <v>54.77</v>
       </c>
       <c r="J4" t="n">
-        <v>114.29</v>
+        <v>48.68</v>
       </c>
       <c r="K4" t="n">
-        <v>85.2</v>
+        <v>24.2</v>
       </c>
       <c r="L4" t="n">
-        <v>6.55</v>
+        <v>17.61</v>
       </c>
       <c r="M4" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>67.7</v>
+        <v>57.5</v>
       </c>
       <c r="P4" t="n">
-        <v>68.2</v>
+        <v>78.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>39.8</v>
       </c>
       <c r="R4" t="n">
-        <v>78.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="S4" t="n">
         <v>67.7</v>
@@ -1166,98 +1166,98 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>207.5</v>
+        <v>319.83</v>
       </c>
       <c r="X4" t="n">
-        <v>3.73</v>
+        <v>-7.37</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.59</v>
+        <v>-5.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.33</v>
+        <v>-3.11</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.39</v>
+        <v>68.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>67.38</v>
+        <v>38.59</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.96</v>
+        <v>30.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>-36.88</v>
+        <v>-29.81</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.356</v>
+        <v>364.6276</v>
       </c>
       <c r="AG4" t="n">
-        <v>192.6024</v>
+        <v>323.5944</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AJ4" t="n">
-        <v>67.7</v>
+        <v>57.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.1</v>
+        <v>39.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>78.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN4" t="n">
-        <v>192.53</v>
+        <v>317.69</v>
       </c>
       <c r="AO4" t="n">
-        <v>192.53</v>
+        <v>317.69</v>
       </c>
       <c r="AP4" t="n">
-        <v>212.5</v>
+        <v>370.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>235.4656</v>
+        <v>402.3797</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.88</v>
+        <v>-12.29</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.75</v>
+        <v>-1.16</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 12.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>50.3</v>
+        <v>59.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.9%.</t>
+          <t>GOOGL: scenario base Hold / Monitor, score 67.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -12.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 192.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,55 +1308,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3887129427968</v>
+        <v>4978965479424</v>
       </c>
       <c r="G5" t="n">
-        <v>15.98</v>
+        <v>31.48</v>
       </c>
       <c r="H5" t="n">
-        <v>21.59</v>
+        <v>15.97</v>
       </c>
       <c r="I5" t="n">
-        <v>54.77</v>
+        <v>62.97</v>
       </c>
       <c r="J5" t="n">
-        <v>48.68</v>
+        <v>114.29</v>
       </c>
       <c r="K5" t="n">
-        <v>24.2</v>
+        <v>85.2</v>
       </c>
       <c r="L5" t="n">
-        <v>17.61</v>
+        <v>6.55</v>
       </c>
       <c r="M5" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>56.5</v>
+        <v>66.3</v>
       </c>
       <c r="P5" t="n">
-        <v>78.8</v>
+        <v>68.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.8</v>
+        <v>14.2</v>
       </c>
       <c r="R5" t="n">
-        <v>55.8</v>
+        <v>77.2</v>
       </c>
       <c r="S5" t="n">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,98 +1365,98 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>318.55</v>
+        <v>205.564</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.97</v>
+        <v>3.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>-6.07</v>
+        <v>3.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2.87</v>
+        <v>11.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>66.95999999999999</v>
+        <v>20.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>38.46</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.28</v>
+        <v>46.93</v>
       </c>
       <c r="AD5" t="n">
-        <v>-29.81</v>
+        <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AF5" t="n">
-        <v>365.9906</v>
+        <v>209.082</v>
       </c>
       <c r="AG5" t="n">
-        <v>323.2492</v>
+        <v>192.71</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>56.5</v>
+        <v>66.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>39.8</v>
+        <v>14.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>55.8</v>
+        <v>77.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN5" t="n">
-        <v>318.55</v>
+        <v>192.53</v>
       </c>
       <c r="AO5" t="n">
-        <v>318.55</v>
+        <v>192.53</v>
       </c>
       <c r="AP5" t="n">
-        <v>370.92</v>
+        <v>212.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>402.3797</v>
+        <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>-12.96</v>
+        <v>-1.68</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1.45</v>
+        <v>6.67</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 13.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>58.7</v>
+        <v>49.7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Hold / Monitor, score 67.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -13.0%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 67.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.7%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 318.55 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 192.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,55 +1507,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1537421344768</v>
+        <v>2844644868096</v>
       </c>
       <c r="G6" t="n">
-        <v>22.05</v>
+        <v>22.81</v>
       </c>
       <c r="H6" t="n">
-        <v>16.36</v>
+        <v>19.76</v>
       </c>
       <c r="I6" t="n">
-        <v>32.84</v>
+        <v>39.34</v>
       </c>
       <c r="J6" t="n">
-        <v>32.93</v>
+        <v>34.01</v>
       </c>
       <c r="K6" t="n">
-        <v>33.1</v>
+        <v>18.3</v>
       </c>
       <c r="L6" t="n">
-        <v>35.61</v>
+        <v>30.27</v>
       </c>
       <c r="M6" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>31.7</v>
+        <v>24.5</v>
       </c>
       <c r="P6" t="n">
-        <v>79.2</v>
+        <v>73.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.1</v>
+        <v>43.1</v>
       </c>
       <c r="R6" t="n">
-        <v>75.2</v>
+        <v>69.2</v>
       </c>
       <c r="S6" t="n">
-        <v>61.2</v>
+        <v>60.4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1564,42 +1564,42 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>605.6</v>
+        <v>382.94</v>
       </c>
       <c r="X6" t="n">
-        <v>7.72</v>
+        <v>4.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>-10.16</v>
+        <v>-7.69</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.02</v>
+        <v>-14.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>-13.79</v>
+        <v>-23.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>28.08</v>
+        <v>4.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.17</v>
+        <v>24.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>-34.15</v>
+        <v>-34.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.76</v>
+        <v>0.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>605.9622000000001</v>
+        <v>399.096</v>
       </c>
       <c r="AG6" t="n">
-        <v>637.7123</v>
+        <v>434.7177</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,34 +1610,34 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>31.7</v>
+        <v>24.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>28.1</v>
+        <v>43.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>75.2</v>
+        <v>69.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN6" t="n">
-        <v>542.87</v>
+        <v>368.57</v>
       </c>
       <c r="AO6" t="n">
-        <v>542.87</v>
+        <v>352.83</v>
       </c>
       <c r="AP6" t="n">
-        <v>681.3099999999999</v>
+        <v>402.29</v>
       </c>
       <c r="AQ6" t="n">
-        <v>681.3099999999999</v>
+        <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.05</v>
+        <v>-4.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>-5.03</v>
+        <v>-11.91</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1646,16 +1646,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>43.3</v>
+        <v>54.6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 61.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.1%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.0%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 681.31 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1684,19 +1684,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1706,55 +1706,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2825219735552</v>
+        <v>1514626351104</v>
       </c>
       <c r="G7" t="n">
-        <v>22.67</v>
+        <v>21.68</v>
       </c>
       <c r="H7" t="n">
-        <v>19.63</v>
+        <v>16.12</v>
       </c>
       <c r="I7" t="n">
-        <v>39.34</v>
+        <v>32.84</v>
       </c>
       <c r="J7" t="n">
-        <v>34.01</v>
+        <v>32.93</v>
       </c>
       <c r="K7" t="n">
-        <v>18.3</v>
+        <v>33.1</v>
       </c>
       <c r="L7" t="n">
-        <v>30.27</v>
+        <v>35.61</v>
       </c>
       <c r="M7" t="n">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>18.8</v>
+        <v>28.2</v>
       </c>
       <c r="P7" t="n">
-        <v>73.8</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>28.1</v>
       </c>
       <c r="R7" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="S7" t="n">
-        <v>58.9</v>
+        <v>60.3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1763,42 +1763,42 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>380.33</v>
+        <v>596.58</v>
       </c>
       <c r="X7" t="n">
-        <v>1.71</v>
+        <v>6.98</v>
       </c>
       <c r="Y7" t="n">
-        <v>-11.96</v>
+        <v>-9.41</v>
       </c>
       <c r="Z7" t="n">
-        <v>-13.98</v>
+        <v>-7.72</v>
       </c>
       <c r="AA7" t="n">
-        <v>-24.13</v>
+        <v>-16.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.12</v>
+        <v>27.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.48</v>
+        <v>37.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>-34.5</v>
+        <v>-34.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.17</v>
+        <v>0.74</v>
       </c>
       <c r="AF7" t="n">
-        <v>399.55</v>
+        <v>605.8549</v>
       </c>
       <c r="AG7" t="n">
-        <v>435.4229</v>
+        <v>637.1287</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,34 +1809,34 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18.8</v>
+        <v>28.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>43</v>
+        <v>28.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN7" t="n">
-        <v>352.83</v>
+        <v>550.25</v>
       </c>
       <c r="AO7" t="n">
-        <v>352.83</v>
+        <v>542.87</v>
       </c>
       <c r="AP7" t="n">
-        <v>402.29</v>
+        <v>681.3099999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>460.52</v>
+        <v>681.3099999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.81</v>
+        <v>-1.53</v>
       </c>
       <c r="AS7" t="n">
-        <v>-12.65</v>
+        <v>-6.36</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1845,16 +1845,16 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 4.8% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>52.8</v>
+        <v>41.8</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 58.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 681.31 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2511623684096</v>
+        <v>2495810895872</v>
       </c>
       <c r="G8" t="n">
-        <v>27.96</v>
+        <v>27.72</v>
       </c>
       <c r="H8" t="n">
-        <v>23.54</v>
+        <v>23.42</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,23 +1939,23 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>39.2</v>
+        <v>37.1</v>
       </c>
       <c r="P8" t="n">
-        <v>62.1</v>
+        <v>62.6</v>
       </c>
       <c r="Q8" t="n">
         <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>65.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>55.3</v>
+        <v>54.8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1965,25 +1965,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>233.485</v>
+        <v>232.0001</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.27</v>
+        <v>-0.97</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.57</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.03</v>
+        <v>21.74</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.28</v>
+        <v>31.26</v>
       </c>
       <c r="AD8" t="n">
         <v>-30.88</v>
@@ -1992,10 +1992,10 @@
         <v>0.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>249.8939</v>
+        <v>249.221</v>
       </c>
       <c r="AG8" t="n">
-        <v>234.5313</v>
+        <v>234.5877</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,19 +2006,19 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>39.2</v>
+        <v>37.1</v>
       </c>
       <c r="AK8" t="n">
         <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>65.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN8" t="n">
-        <v>227.01</v>
+        <v>232.015</v>
       </c>
       <c r="AO8" t="n">
         <v>227.01</v>
@@ -2030,10 +2030,10 @@
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-6.57</v>
+        <v>-6.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.45</v>
+        <v>-1.1</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 6.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>52.8</v>
+        <v>52.1</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 55.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.6%.</t>
+          <t>AMZN: scenario base Avoid for Now, score 54.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.9%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1201643847680</v>
+        <v>1226097557504</v>
       </c>
       <c r="G10" t="n">
-        <v>296.25</v>
+        <v>333.81</v>
       </c>
       <c r="H10" t="n">
-        <v>142.59</v>
+        <v>138.59</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>43.7</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
-        <v>25.9</v>
+        <v>24.8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>319.83</v>
+        <v>310.473</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.19</v>
+        <v>-17.32</v>
       </c>
       <c r="Y10" t="n">
-        <v>-17.47</v>
+        <v>-16.92</v>
       </c>
       <c r="Z10" t="n">
-        <v>-25.87</v>
+        <v>-30.91</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.7</v>
+        <v>-6.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.96</v>
+        <v>4.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.51</v>
+        <v>58.5</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>404.9692</v>
+        <v>402.5069</v>
       </c>
       <c r="AG10" t="n">
-        <v>415.4099</v>
+        <v>414.6953</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,22 +2350,22 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>43.7</v>
+        <v>41</v>
       </c>
       <c r="AM10" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN10" t="n">
-        <v>319.83</v>
+        <v>310.44</v>
       </c>
       <c r="AO10" t="n">
-        <v>319.83</v>
+        <v>310.44</v>
       </c>
       <c r="AP10" t="n">
         <v>425.3</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-21.02</v>
+        <v>-22.87</v>
       </c>
       <c r="AS10" t="n">
-        <v>-23.01</v>
+        <v>-25.14</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 21.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 22.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>11.9</v>
+        <v>10.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 25.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -21.0%.</t>
+          <t>TSLA: scenario base High Risk, score 24.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -22.9%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 319.83 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 310.44 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4888539430912</v>
+        <v>4948317175808</v>
       </c>
       <c r="G2" t="n">
-        <v>40.25</v>
+        <v>40.79</v>
       </c>
       <c r="H2" t="n">
-        <v>34.52</v>
+        <v>34.93</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -741,7 +741,7 @@
         <v>79.55</v>
       </c>
       <c r="M2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>32.1</v>
+        <v>30.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>64</v>
+        <v>58.8</v>
       </c>
       <c r="S2" t="n">
-        <v>73.5</v>
+        <v>72.7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,25 +773,25 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>332.8301</v>
+        <v>336.91</v>
       </c>
       <c r="X2" t="n">
-        <v>13.56</v>
+        <v>14.95</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.84</v>
+        <v>23.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>34.27</v>
+        <v>35.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>56.04</v>
+        <v>57.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.59</v>
+        <v>20.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.64</v>
+        <v>26.76</v>
       </c>
       <c r="AD2" t="n">
         <v>-33.36</v>
@@ -800,10 +800,10 @@
         <v>0.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>306.2276</v>
+        <v>306.3092</v>
       </c>
       <c r="AG2" t="n">
-        <v>275.6625</v>
+        <v>275.6829</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>64</v>
+        <v>58.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="AN2" t="n">
         <v>281.74</v>
@@ -832,16 +832,16 @@
         <v>269.9213</v>
       </c>
       <c r="AP2" t="n">
-        <v>333.74</v>
+        <v>336.91</v>
       </c>
       <c r="AQ2" t="n">
-        <v>333.74</v>
+        <v>336.91</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.69</v>
+        <v>9.99</v>
       </c>
       <c r="AS2" t="n">
-        <v>20.74</v>
+        <v>22.21</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 8.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>67.2</v>
+        <v>63.2</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,12 +868,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.7%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.0%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 333.74 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 336.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -910,55 +910,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>600348295168</v>
+        <v>3993807618048</v>
       </c>
       <c r="G3" t="n">
-        <v>61.46</v>
+        <v>16.39</v>
       </c>
       <c r="H3" t="n">
-        <v>30.7</v>
+        <v>22.16</v>
       </c>
       <c r="I3" t="n">
-        <v>30.11</v>
+        <v>54.77</v>
       </c>
       <c r="J3" t="n">
-        <v>53.94</v>
+        <v>48.68</v>
       </c>
       <c r="K3" t="n">
-        <v>21.3</v>
+        <v>24.2</v>
       </c>
       <c r="L3" t="n">
-        <v>9.09</v>
+        <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>62.4</v>
       </c>
       <c r="P3" t="n">
-        <v>20.4</v>
+        <v>77.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.3</v>
+        <v>39.9</v>
       </c>
       <c r="R3" t="n">
-        <v>82.8</v>
+        <v>64</v>
       </c>
       <c r="S3" t="n">
-        <v>69.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,80 +967,80 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>1563</v>
+        <v>326.56</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.94</v>
+        <v>-5.42</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.9</v>
+        <v>-3.58</v>
       </c>
       <c r="Z3" t="n">
-        <v>33.15</v>
+        <v>-1.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>152.22</v>
+        <v>72.16</v>
       </c>
       <c r="AB3" t="n">
-        <v>36.98</v>
+        <v>35.78</v>
       </c>
       <c r="AC3" t="n">
-        <v>39.05</v>
+        <v>30.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>-44.77</v>
+        <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>1528.2</v>
+        <v>364.7622</v>
       </c>
       <c r="AG3" t="n">
-        <v>1191.5346</v>
+        <v>323.628</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>62.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.3</v>
+        <v>39.9</v>
       </c>
       <c r="AL3" t="n">
-        <v>82.8</v>
+        <v>64</v>
       </c>
       <c r="AM3" t="n">
-        <v>767</v>
+        <v>750</v>
       </c>
       <c r="AN3" t="n">
-        <v>1509.8</v>
+        <v>317.69</v>
       </c>
       <c r="AO3" t="n">
-        <v>1187.4</v>
+        <v>317.69</v>
       </c>
       <c r="AP3" t="n">
-        <v>1721.4</v>
+        <v>370.92</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1721.4</v>
+        <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.28</v>
+        <v>-10.47</v>
       </c>
       <c r="AS3" t="n">
-        <v>31.18</v>
+        <v>0.91</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 10.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>57.4</v>
+        <v>63.3</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 71.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -10.5%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1187.40 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,55 +1109,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3911499907072</v>
+        <v>549186207744</v>
       </c>
       <c r="G4" t="n">
-        <v>16.06</v>
+        <v>56.11</v>
       </c>
       <c r="H4" t="n">
-        <v>21.64</v>
+        <v>28.08</v>
       </c>
       <c r="I4" t="n">
-        <v>54.77</v>
+        <v>30.11</v>
       </c>
       <c r="J4" t="n">
-        <v>48.68</v>
+        <v>53.94</v>
       </c>
       <c r="K4" t="n">
-        <v>24.2</v>
+        <v>21.3</v>
       </c>
       <c r="L4" t="n">
-        <v>17.61</v>
+        <v>9.09</v>
       </c>
       <c r="M4" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>57.5</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>78.7</v>
+        <v>24.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.8</v>
+        <v>17.1</v>
       </c>
       <c r="R4" t="n">
-        <v>56.8</v>
+        <v>70</v>
       </c>
       <c r="S4" t="n">
-        <v>67.7</v>
+        <v>67.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,98 +1166,98 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>319.83</v>
+        <v>1429.8</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.37</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>-5.57</v>
+        <v>22.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3.11</v>
+        <v>17.99</v>
       </c>
       <c r="AA4" t="n">
-        <v>68.61</v>
+        <v>129.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>38.59</v>
+        <v>30.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>30.28</v>
+        <v>39.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>-29.81</v>
+        <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.27</v>
+        <v>0.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>364.6276</v>
+        <v>1529.7003</v>
       </c>
       <c r="AG4" t="n">
-        <v>323.5944</v>
+        <v>1193.2073</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>57.5</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>39.8</v>
+        <v>17.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>56.8</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="AN4" t="n">
-        <v>317.69</v>
+        <v>1429.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>317.69</v>
+        <v>1227.5217</v>
       </c>
       <c r="AP4" t="n">
-        <v>370.92</v>
+        <v>1719.3295</v>
       </c>
       <c r="AQ4" t="n">
-        <v>402.3797</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR4" t="n">
-        <v>-12.29</v>
+        <v>-6.53</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1.16</v>
+        <v>19.83</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 12.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>59.3</v>
+        <v>53.4</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Hold / Monitor, score 67.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -12.3%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.5%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1227.52 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4978965479424</v>
+        <v>4759668391936</v>
       </c>
       <c r="G5" t="n">
-        <v>31.48</v>
+        <v>30.05</v>
       </c>
       <c r="H5" t="n">
-        <v>15.97</v>
+        <v>15.27</v>
       </c>
       <c r="I5" t="n">
         <v>62.97</v>
@@ -1344,19 +1344,19 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>66.3</v>
+        <v>55.6</v>
       </c>
       <c r="P5" t="n">
-        <v>68.8</v>
+        <v>71.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="R5" t="n">
-        <v>77.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>67.3</v>
+        <v>64.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>205.564</v>
+        <v>196.51</v>
       </c>
       <c r="X5" t="n">
-        <v>3.3</v>
+        <v>-1.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.09</v>
+        <v>-1.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.35</v>
+        <v>6.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.53</v>
+        <v>15.22</v>
       </c>
       <c r="AB5" t="n">
-        <v>66.73999999999999</v>
+        <v>62.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>46.93</v>
+        <v>47.15</v>
       </c>
       <c r="AD5" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>209.082</v>
+        <v>208.9009</v>
       </c>
       <c r="AG5" t="n">
-        <v>192.71</v>
+        <v>192.6648</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,16 +1411,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>66.3</v>
+        <v>55.6</v>
       </c>
       <c r="AK5" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>77.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="AN5" t="n">
         <v>192.53</v>
@@ -1435,10 +1435,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.68</v>
+        <v>-5.93</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.67</v>
+        <v>2</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>49.7</v>
+        <v>45.2</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 67.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.7%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 64.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.9%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2844644868096</v>
+        <v>2890404200448</v>
       </c>
       <c r="G6" t="n">
-        <v>22.81</v>
+        <v>23.17</v>
       </c>
       <c r="H6" t="n">
-        <v>19.76</v>
+        <v>20.08</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1543,19 +1543,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>24.5</v>
+        <v>27.7</v>
       </c>
       <c r="P6" t="n">
-        <v>73.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="R6" t="n">
-        <v>69.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>60.4</v>
+        <v>61.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>382.94</v>
+        <v>389.1</v>
       </c>
       <c r="X6" t="n">
-        <v>4.78</v>
+        <v>6.47</v>
       </c>
       <c r="Y6" t="n">
-        <v>-7.69</v>
+        <v>-6.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>-14.74</v>
+        <v>-13.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>-23.7</v>
+        <v>-22.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.35</v>
+        <v>5.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.45</v>
+        <v>24.35</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>399.096</v>
+        <v>399.2192</v>
       </c>
       <c r="AG6" t="n">
-        <v>434.7177</v>
+        <v>434.7485</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,16 +1610,16 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24.5</v>
+        <v>27.7</v>
       </c>
       <c r="AK6" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>69.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="AN6" t="n">
         <v>368.57</v>
@@ -1634,10 +1634,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.05</v>
+        <v>-2.53</v>
       </c>
       <c r="AS6" t="n">
-        <v>-11.91</v>
+        <v>-10.5</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 4.0% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.6</v>
+        <v>56</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.0%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1514626351104</v>
+        <v>1507493412864</v>
       </c>
       <c r="G7" t="n">
-        <v>21.68</v>
+        <v>21.6</v>
       </c>
       <c r="H7" t="n">
-        <v>16.12</v>
+        <v>16.05</v>
       </c>
       <c r="I7" t="n">
         <v>32.84</v>
@@ -1736,25 +1736,25 @@
         <v>35.61</v>
       </c>
       <c r="M7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>28.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>28.1</v>
-      </c>
       <c r="R7" t="n">
-        <v>73</v>
+        <v>72.3</v>
       </c>
       <c r="S7" t="n">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1768,37 +1768,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>596.58</v>
+        <v>593.87</v>
       </c>
       <c r="X7" t="n">
-        <v>6.98</v>
+        <v>6.49</v>
       </c>
       <c r="Y7" t="n">
-        <v>-9.41</v>
+        <v>-9.82</v>
       </c>
       <c r="Z7" t="n">
-        <v>-7.72</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>-16.12</v>
+        <v>-16.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>27.4</v>
+        <v>22.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>37.15</v>
+        <v>37.08</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.74</v>
+        <v>0.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>605.8549</v>
+        <v>605.8007</v>
       </c>
       <c r="AG7" t="n">
-        <v>637.1287</v>
+        <v>637.1151</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,16 +1809,16 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AK7" t="n">
         <v>28.2</v>
       </c>
-      <c r="AK7" t="n">
-        <v>28.1</v>
-      </c>
       <c r="AL7" t="n">
-        <v>73</v>
+        <v>72.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="AN7" t="n">
         <v>550.25</v>
@@ -1833,10 +1833,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.53</v>
+        <v>-1.97</v>
       </c>
       <c r="AS7" t="n">
-        <v>-6.36</v>
+        <v>-6.79</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2495810895872</v>
+        <v>2489087688704</v>
       </c>
       <c r="G8" t="n">
-        <v>27.72</v>
+        <v>27.68</v>
       </c>
       <c r="H8" t="n">
-        <v>23.42</v>
+        <v>23.33</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="P8" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
       <c r="Q8" t="n">
         <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>64.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="S8" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>232.0001</v>
+        <v>231.39</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.97</v>
+        <v>-1.23</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>21.74</v>
+        <v>20.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.26</v>
+        <v>31.29</v>
       </c>
       <c r="AD8" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>249.221</v>
+        <v>249.2088</v>
       </c>
       <c r="AG8" t="n">
-        <v>234.5877</v>
+        <v>234.5846</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,19 +2006,19 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="AK8" t="n">
         <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>64.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="AN8" t="n">
-        <v>232.015</v>
+        <v>231.39</v>
       </c>
       <c r="AO8" t="n">
         <v>227.01</v>
@@ -2030,10 +2030,10 @@
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-6.9</v>
+        <v>-7.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>-1.1</v>
+        <v>-1.36</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 6.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Avoid for Now, score 54.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.9%.</t>
+          <t>AMZN: scenario base Avoid for Now, score 54.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1226097557504</v>
+        <v>1221279088640</v>
       </c>
       <c r="G10" t="n">
-        <v>333.81</v>
+        <v>281.11</v>
       </c>
       <c r="H10" t="n">
-        <v>138.59</v>
+        <v>139.31</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2276,14 +2276,14 @@
         <v>25.5</v>
       </c>
       <c r="L10" t="n">
-        <v>10.67</v>
+        <v>18.37</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="S10" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>310.473</v>
+        <v>309.22</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.32</v>
+        <v>-17.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>-16.92</v>
+        <v>-17.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>-30.91</v>
+        <v>-31.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>-6.64</v>
+        <v>-7.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.9</v>
+        <v>5.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.5</v>
+        <v>58.58</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>402.5069</v>
+        <v>402.4818</v>
       </c>
       <c r="AG10" t="n">
-        <v>414.6953</v>
+        <v>414.689</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,22 +2350,22 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="AN10" t="n">
-        <v>310.44</v>
+        <v>309.22</v>
       </c>
       <c r="AO10" t="n">
-        <v>310.44</v>
+        <v>309.22</v>
       </c>
       <c r="AP10" t="n">
         <v>425.3</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-22.87</v>
+        <v>-23.17</v>
       </c>
       <c r="AS10" t="n">
-        <v>-25.14</v>
+        <v>-25.43</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 22.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 23.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 24.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -22.9%.</t>
+          <t>TSLA: scenario base High Risk, score 24.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -23.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 310.44 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 309.22 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4948317175808</v>
+        <v>5000016691200</v>
       </c>
       <c r="G2" t="n">
-        <v>40.79</v>
+        <v>41.26</v>
       </c>
       <c r="H2" t="n">
-        <v>34.93</v>
+        <v>35.29</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>30.9</v>
+        <v>29.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="R2" t="n">
-        <v>58.8</v>
+        <v>56.4</v>
       </c>
       <c r="S2" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>336.91</v>
+        <v>340.4325</v>
       </c>
       <c r="X2" t="n">
-        <v>14.95</v>
+        <v>19.96</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.33</v>
+        <v>27.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>35.91</v>
+        <v>33.54</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.95</v>
+        <v>59.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.56</v>
+        <v>20.92</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.76</v>
+        <v>26.68</v>
       </c>
       <c r="AD2" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>306.3092</v>
+        <v>307.8367</v>
       </c>
       <c r="AG2" t="n">
-        <v>275.6829</v>
+        <v>276.4847</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -817,31 +817,31 @@
         <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>58.8</v>
+        <v>56.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
-        <v>281.74</v>
+        <v>289.36</v>
       </c>
       <c r="AO2" t="n">
-        <v>269.9213</v>
+        <v>275.15</v>
       </c>
       <c r="AP2" t="n">
-        <v>336.91</v>
+        <v>340.43</v>
       </c>
       <c r="AQ2" t="n">
-        <v>336.91</v>
+        <v>340.43</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.99</v>
+        <v>10.59</v>
       </c>
       <c r="AS2" t="n">
-        <v>22.21</v>
+        <v>23.13</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 10.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>63.2</v>
+        <v>61.4</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,17 +868,17 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.0%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.6%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 336.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 340.43 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 269.92 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 275.15 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3993807618048</v>
+        <v>4081251516416</v>
       </c>
       <c r="G3" t="n">
-        <v>16.39</v>
+        <v>16.75</v>
       </c>
       <c r="H3" t="n">
-        <v>22.16</v>
+        <v>22.67</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -940,25 +940,25 @@
         <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="P3" t="n">
-        <v>77.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="R3" t="n">
-        <v>64</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>326.56</v>
+        <v>333.71</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.42</v>
+        <v>-1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3.58</v>
+        <v>-4.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.08</v>
+        <v>0.27</v>
       </c>
       <c r="AA3" t="n">
-        <v>72.16</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>35.78</v>
+        <v>36.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.19</v>
+        <v>30.16</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>364.7622</v>
+        <v>361.767</v>
       </c>
       <c r="AG3" t="n">
-        <v>323.628</v>
+        <v>324.4482</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>64</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>317.69</v>
@@ -1037,10 +1037,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>-10.47</v>
+        <v>-7.76</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.91</v>
+        <v>2.85</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 10.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>63.3</v>
+        <v>64.3</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 71.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -10.5%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 71.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>549186207744</v>
+        <v>533284454400</v>
       </c>
       <c r="G4" t="n">
-        <v>56.11</v>
+        <v>54.55</v>
       </c>
       <c r="H4" t="n">
-        <v>28.08</v>
+        <v>27.27</v>
       </c>
       <c r="I4" t="n">
         <v>30.11</v>
@@ -1139,7 +1139,7 @@
         <v>9.09</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -1148,16 +1148,16 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>24.2</v>
+        <v>25.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="R4" t="n">
-        <v>70</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1429.8</v>
+        <v>1388.4</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.289999999999999</v>
+        <v>-13.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>22.16</v>
+        <v>16.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.99</v>
+        <v>16.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>129.35</v>
+        <v>127.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>30.64</v>
+        <v>29.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.24</v>
+        <v>39.28</v>
       </c>
       <c r="AD4" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1529.7003</v>
+        <v>1532.5183</v>
       </c>
       <c r="AG4" t="n">
-        <v>1193.2073</v>
+        <v>1195.9567</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1215,31 +1215,31 @@
         <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AM4" t="n">
         <v>765</v>
       </c>
       <c r="AN4" t="n">
-        <v>1429.8</v>
+        <v>1388.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>1227.5217</v>
+        <v>1247.4977</v>
       </c>
       <c r="AP4" t="n">
-        <v>1719.3295</v>
+        <v>1639.6254</v>
       </c>
       <c r="AQ4" t="n">
         <v>1719.3295</v>
       </c>
       <c r="AR4" t="n">
-        <v>-6.53</v>
+        <v>-9.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>19.83</v>
+        <v>16.09</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 6.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>53.4</v>
+        <v>52.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.5%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -9.4%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1227.52 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1247.50 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4759668391936</v>
+        <v>4778318888960</v>
       </c>
       <c r="G5" t="n">
-        <v>30.05</v>
+        <v>30.26</v>
       </c>
       <c r="H5" t="n">
-        <v>15.27</v>
+        <v>15.33</v>
       </c>
       <c r="I5" t="n">
         <v>62.97</v>
@@ -1338,25 +1338,25 @@
         <v>6.55</v>
       </c>
       <c r="M5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>55.6</v>
+        <v>44.7</v>
       </c>
       <c r="P5" t="n">
-        <v>71.5</v>
+        <v>71.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>70.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="S5" t="n">
-        <v>64.5</v>
+        <v>61.8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,25 +1370,25 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>196.51</v>
+        <v>197.3</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.45</v>
+        <v>-8.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.44</v>
+        <v>5.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.22</v>
+        <v>13.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>62.11</v>
+        <v>62.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>47.15</v>
+        <v>47.06</v>
       </c>
       <c r="AD5" t="n">
         <v>-36.88</v>
@@ -1397,10 +1397,10 @@
         <v>1.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>208.9009</v>
+        <v>207.763</v>
       </c>
       <c r="AG5" t="n">
-        <v>192.6648</v>
+        <v>192.8171</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>55.6</v>
+        <v>44.7</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="AL5" t="n">
-        <v>70.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>192.53</v>
+        <v>194.83</v>
       </c>
       <c r="AO5" t="n">
         <v>192.53</v>
@@ -1435,10 +1435,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>-5.93</v>
+        <v>-5.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 5.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>45.2</v>
+        <v>42.7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 64.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.9%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 61.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2890404200448</v>
+        <v>2923609194496</v>
       </c>
       <c r="G6" t="n">
-        <v>23.17</v>
+        <v>23.41</v>
       </c>
       <c r="H6" t="n">
-        <v>20.08</v>
+        <v>20.3</v>
       </c>
       <c r="I6" t="n">
         <v>39.34</v>
@@ -1537,25 +1537,25 @@
         <v>30.27</v>
       </c>
       <c r="M6" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>27.7</v>
+        <v>24.7</v>
       </c>
       <c r="P6" t="n">
-        <v>72.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="n">
         <v>43.2</v>
       </c>
       <c r="R6" t="n">
-        <v>71.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>61.2</v>
+        <v>60.6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>389.1</v>
+        <v>393.505</v>
       </c>
       <c r="X6" t="n">
-        <v>6.47</v>
+        <v>5.51</v>
       </c>
       <c r="Y6" t="n">
-        <v>-6.21</v>
+        <v>-7.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>-13.37</v>
+        <v>-15.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>-22.47</v>
+        <v>-22.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.63</v>
+        <v>6.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.35</v>
+        <v>24.33</v>
       </c>
       <c r="AD6" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>399.2192</v>
+        <v>398.4657</v>
       </c>
       <c r="AG6" t="n">
-        <v>434.7485</v>
+        <v>433.4133</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,19 +1610,19 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27.7</v>
+        <v>24.7</v>
       </c>
       <c r="AK6" t="n">
         <v>43.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>71.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>368.57</v>
+        <v>373.02</v>
       </c>
       <c r="AO6" t="n">
         <v>352.83</v>
@@ -1634,10 +1634,10 @@
         <v>460.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>-2.53</v>
+        <v>-1.23</v>
       </c>
       <c r="AS6" t="n">
-        <v>-10.5</v>
+        <v>-9.19</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>56</v>
+        <v>55.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.5%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.2%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1507493412864</v>
+        <v>1506757312512</v>
       </c>
       <c r="G7" t="n">
-        <v>21.6</v>
+        <v>21.58</v>
       </c>
       <c r="H7" t="n">
-        <v>16.05</v>
+        <v>16.04</v>
       </c>
       <c r="I7" t="n">
         <v>32.84</v>
@@ -1742,7 +1742,7 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>27.2</v>
+        <v>21.5</v>
       </c>
       <c r="P7" t="n">
         <v>80.2</v>
@@ -1751,10 +1751,10 @@
         <v>28.2</v>
       </c>
       <c r="R7" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>58.6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1768,25 +1768,25 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>593.87</v>
+        <v>593.64</v>
       </c>
       <c r="X7" t="n">
-        <v>6.49</v>
+        <v>7.89</v>
       </c>
       <c r="Y7" t="n">
-        <v>-9.82</v>
+        <v>-12.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>-8.140000000000001</v>
+        <v>-11.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>-16.5</v>
+        <v>-16.43</v>
       </c>
       <c r="AB7" t="n">
-        <v>22.75</v>
+        <v>22.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>37.08</v>
+        <v>37.03</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.15</v>
@@ -1795,10 +1795,10 @@
         <v>0.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>605.8007</v>
+        <v>604.899</v>
       </c>
       <c r="AG7" t="n">
-        <v>637.1151</v>
+        <v>635.9232</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,19 +1809,19 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27.2</v>
+        <v>21.5</v>
       </c>
       <c r="AK7" t="n">
         <v>28.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
-        <v>550.25</v>
+        <v>563.29</v>
       </c>
       <c r="AO7" t="n">
         <v>542.87</v>
@@ -1833,10 +1833,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.97</v>
+        <v>-1.86</v>
       </c>
       <c r="AS7" t="n">
-        <v>-6.79</v>
+        <v>-6.65</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>41.4</v>
+        <v>40</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.0%.</t>
+          <t>META: scenario base Hold / Monitor, score 58.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.9%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2489087688704</v>
+        <v>2485107556352</v>
       </c>
       <c r="G8" t="n">
-        <v>27.68</v>
+        <v>27.67</v>
       </c>
       <c r="H8" t="n">
-        <v>23.33</v>
+        <v>23.29</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>36.6</v>
+        <v>31.9</v>
       </c>
       <c r="P8" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="Q8" t="n">
         <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>64.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>54.6</v>
+        <v>53.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,25 +1965,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>231.39</v>
+        <v>231</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.23</v>
+        <v>-0.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.289999999999999</v>
+        <v>-11.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.26</v>
+        <v>-3.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>-0.19</v>
       </c>
       <c r="AB8" t="n">
-        <v>20.69</v>
+        <v>20.56</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.29</v>
+        <v>31.25</v>
       </c>
       <c r="AD8" t="n">
         <v>-30.88</v>
@@ -1992,10 +1992,10 @@
         <v>0.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>249.2088</v>
+        <v>247.724</v>
       </c>
       <c r="AG8" t="n">
-        <v>234.5846</v>
+        <v>234.6652</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,19 +2006,19 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36.6</v>
+        <v>31.9</v>
       </c>
       <c r="AK8" t="n">
         <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>64.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
-        <v>231.39</v>
+        <v>231</v>
       </c>
       <c r="AO8" t="n">
         <v>227.01</v>
@@ -2030,10 +2030,10 @@
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-7.15</v>
+        <v>-6.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>-1.36</v>
+        <v>-1.56</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>51.9</v>
+        <v>50.8</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Avoid for Now, score 54.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
+          <t>AMZN: scenario base Avoid for Now, score 53.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.8%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1221279088640</v>
+        <v>1211227439104</v>
       </c>
       <c r="G10" t="n">
-        <v>281.11</v>
+        <v>283.96</v>
       </c>
       <c r="H10" t="n">
-        <v>139.31</v>
+        <v>137.93</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
         <v>24.6</v>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>309.22</v>
+        <v>306.65</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.66</v>
+        <v>-19.24</v>
       </c>
       <c r="Y10" t="n">
-        <v>-17.26</v>
+        <v>-19.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>-31.19</v>
+        <v>-29.54</v>
       </c>
       <c r="AA10" t="n">
-        <v>-7.02</v>
+        <v>-2.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.13</v>
+        <v>4.82</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.58</v>
+        <v>58.49</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>402.4818</v>
+        <v>397.104</v>
       </c>
       <c r="AG10" t="n">
-        <v>414.689</v>
+        <v>413.4285</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,22 +2350,22 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="AM10" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AN10" t="n">
-        <v>309.22</v>
+        <v>306.65</v>
       </c>
       <c r="AO10" t="n">
-        <v>309.22</v>
+        <v>306.65</v>
       </c>
       <c r="AP10" t="n">
         <v>425.3</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-23.17</v>
+        <v>-22.78</v>
       </c>
       <c r="AS10" t="n">
-        <v>-25.43</v>
+        <v>-25.83</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 23.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 22.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 24.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -23.2%.</t>
+          <t>TSLA: scenario base High Risk, score 24.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -22.8%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 309.22 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 306.65 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5000016691200</v>
+        <v>4988707274752</v>
       </c>
       <c r="G2" t="n">
-        <v>41.26</v>
+        <v>41.12</v>
       </c>
       <c r="H2" t="n">
-        <v>35.29</v>
+        <v>35.17</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
       <c r="Q2" t="n">
         <v>41.3</v>
       </c>
       <c r="R2" t="n">
-        <v>56.4</v>
+        <v>58.5</v>
       </c>
       <c r="S2" t="n">
-        <v>72.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>340.4325</v>
+        <v>339.64</v>
       </c>
       <c r="X2" t="n">
-        <v>19.96</v>
+        <v>20.55</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.33</v>
+        <v>25.58</v>
       </c>
       <c r="Z2" t="n">
-        <v>33.54</v>
+        <v>31.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>59.8</v>
+        <v>59.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.92</v>
+        <v>20.7</v>
       </c>
       <c r="AC2" t="n">
         <v>26.68</v>
@@ -800,10 +800,10 @@
         <v>0.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>307.8367</v>
+        <v>308.6178</v>
       </c>
       <c r="AG2" t="n">
-        <v>276.4847</v>
+        <v>276.9145</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,28 +820,28 @@
         <v>41.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>56.4</v>
+        <v>58.5</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
       </c>
       <c r="AN2" t="n">
-        <v>289.36</v>
+        <v>294.38</v>
       </c>
       <c r="AO2" t="n">
         <v>275.15</v>
       </c>
       <c r="AP2" t="n">
-        <v>340.43</v>
+        <v>340.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>340.43</v>
+        <v>340.08</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.59</v>
+        <v>10.05</v>
       </c>
       <c r="AS2" t="n">
-        <v>23.13</v>
+        <v>22.65</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 10.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>61.4</v>
+        <v>63</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,12 +868,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 340.43 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 340.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4081251516416</v>
+        <v>4110787018752</v>
       </c>
       <c r="G3" t="n">
-        <v>16.75</v>
+        <v>16.87</v>
       </c>
       <c r="H3" t="n">
-        <v>22.67</v>
+        <v>22.84</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>61.9</v>
+        <v>63.7</v>
       </c>
       <c r="P3" t="n">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q3" t="n">
         <v>40</v>
       </c>
       <c r="R3" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>71.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>333.71</v>
+        <v>336.13</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.09</v>
+        <v>-4.95</v>
       </c>
       <c r="Y3" t="n">
-        <v>-4.69</v>
+        <v>-3.85</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>73.23999999999999</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>36.66</v>
+        <v>36.94</v>
       </c>
       <c r="AC3" t="n">
         <v>30.16</v>
@@ -999,10 +999,10 @@
         <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>361.767</v>
+        <v>360.5588</v>
       </c>
       <c r="AG3" t="n">
-        <v>324.4482</v>
+        <v>324.9235</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>61.9</v>
+        <v>63.7</v>
       </c>
       <c r="AK3" t="n">
         <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
@@ -1037,10 +1037,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>-7.76</v>
+        <v>-6.78</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 7.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>64.3</v>
+        <v>65.2</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 71.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.8%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 71.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>533284454400</v>
+        <v>523221008384</v>
       </c>
       <c r="G4" t="n">
-        <v>54.55</v>
+        <v>53.61</v>
       </c>
       <c r="H4" t="n">
-        <v>27.27</v>
+        <v>26.75</v>
       </c>
       <c r="I4" t="n">
         <v>30.11</v>
@@ -1148,13 +1148,13 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>25.9</v>
+        <v>27.7</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
       </c>
       <c r="R4" t="n">
-        <v>65.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="S4" t="n">
         <v>67.40000000000001</v>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1388.4</v>
+        <v>1362.2</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.77</v>
+        <v>-20.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.56</v>
+        <v>11.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.8</v>
+        <v>14.82</v>
       </c>
       <c r="AA4" t="n">
-        <v>127.94</v>
+        <v>130.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>29.37</v>
+        <v>28.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.28</v>
+        <v>39.3</v>
       </c>
       <c r="AD4" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="AF4" t="n">
-        <v>1532.5183</v>
+        <v>1533.1344</v>
       </c>
       <c r="AG4" t="n">
-        <v>1195.9567</v>
+        <v>1198.5622</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1218,28 +1218,28 @@
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>65.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="AM4" t="n">
         <v>765</v>
       </c>
       <c r="AN4" t="n">
-        <v>1388.4</v>
+        <v>1362.2</v>
       </c>
       <c r="AO4" t="n">
         <v>1247.4977</v>
       </c>
       <c r="AP4" t="n">
-        <v>1639.6254</v>
+        <v>1632.4341</v>
       </c>
       <c r="AQ4" t="n">
         <v>1719.3295</v>
       </c>
       <c r="AR4" t="n">
-        <v>-9.4</v>
+        <v>-11.15</v>
       </c>
       <c r="AS4" t="n">
-        <v>16.09</v>
+        <v>13.65</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 11.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>52.3</v>
+        <v>51.6</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -9.4%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -11.2%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1313,50 +1313,50 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4778318888960</v>
+        <v>2913952071680</v>
       </c>
       <c r="G5" t="n">
-        <v>30.26</v>
+        <v>23.35</v>
       </c>
       <c r="H5" t="n">
-        <v>15.33</v>
+        <v>20.24</v>
       </c>
       <c r="I5" t="n">
-        <v>62.97</v>
+        <v>39.34</v>
       </c>
       <c r="J5" t="n">
-        <v>114.29</v>
+        <v>34.01</v>
       </c>
       <c r="K5" t="n">
-        <v>85.2</v>
+        <v>18.3</v>
       </c>
       <c r="L5" t="n">
-        <v>6.55</v>
+        <v>30.27</v>
       </c>
       <c r="M5" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>44.7</v>
+        <v>21.7</v>
       </c>
       <c r="P5" t="n">
-        <v>71.2</v>
+        <v>72.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>43.2</v>
       </c>
       <c r="R5" t="n">
-        <v>72.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>61.8</v>
+        <v>59.8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,98 +1365,98 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>197.3</v>
+        <v>392.27</v>
       </c>
       <c r="X5" t="n">
-        <v>2.48</v>
+        <v>6.43</v>
       </c>
       <c r="Y5" t="n">
-        <v>-8.81</v>
+        <v>-8.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.94</v>
+        <v>-18.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.87</v>
+        <v>-22.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>62.12</v>
+        <v>6.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>47.06</v>
+        <v>24.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>-36.88</v>
+        <v>-34.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.32</v>
+        <v>0.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>207.763</v>
+        <v>397.8878</v>
       </c>
       <c r="AG5" t="n">
-        <v>192.8171</v>
+        <v>432.7784</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AJ5" t="n">
-        <v>44.7</v>
+        <v>21.7</v>
       </c>
       <c r="AK5" t="n">
-        <v>14</v>
+        <v>43.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>72.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AM5" t="n">
         <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>194.83</v>
+        <v>381.58</v>
       </c>
       <c r="AO5" t="n">
-        <v>192.53</v>
+        <v>352.83</v>
       </c>
       <c r="AP5" t="n">
-        <v>212.5</v>
+        <v>402.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>235.4656</v>
+        <v>460.52</v>
       </c>
       <c r="AR5" t="n">
-        <v>-5.04</v>
+        <v>-1.41</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.32</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 5.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>42.7</v>
+        <v>54.9</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 61.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 59.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.4%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 192.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1512,50 +1512,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2923609194496</v>
+        <v>4643650273280</v>
       </c>
       <c r="G6" t="n">
-        <v>23.41</v>
+        <v>29.4</v>
       </c>
       <c r="H6" t="n">
-        <v>20.3</v>
+        <v>14.9</v>
       </c>
       <c r="I6" t="n">
-        <v>39.34</v>
+        <v>62.97</v>
       </c>
       <c r="J6" t="n">
-        <v>34.01</v>
+        <v>114.29</v>
       </c>
       <c r="K6" t="n">
-        <v>18.3</v>
+        <v>85.2</v>
       </c>
       <c r="L6" t="n">
-        <v>30.27</v>
+        <v>6.55</v>
       </c>
       <c r="M6" t="n">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>24.7</v>
+        <v>39.3</v>
       </c>
       <c r="P6" t="n">
-        <v>72</v>
+        <v>72.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.2</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>73.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>60.6</v>
+        <v>58.5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1564,42 +1564,42 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>393.505</v>
+        <v>191.72</v>
       </c>
       <c r="X6" t="n">
-        <v>5.51</v>
+        <v>-1.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>-7.17</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>-15.95</v>
+        <v>1.82</v>
       </c>
       <c r="AA6" t="n">
-        <v>-22.79</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.02</v>
+        <v>60.59</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.33</v>
+        <v>47.09</v>
       </c>
       <c r="AD6" t="n">
-        <v>-34.5</v>
+        <v>-36.88</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF6" t="n">
-        <v>398.4657</v>
+        <v>207.0905</v>
       </c>
       <c r="AG6" t="n">
-        <v>433.4133</v>
+        <v>192.8126</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1610,34 +1610,34 @@
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24.7</v>
+        <v>39.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>43.2</v>
+        <v>14</v>
       </c>
       <c r="AL6" t="n">
-        <v>73.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AM6" t="n">
         <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>373.02</v>
+        <v>191.72</v>
       </c>
       <c r="AO6" t="n">
-        <v>352.83</v>
+        <v>191.72</v>
       </c>
       <c r="AP6" t="n">
-        <v>402.29</v>
+        <v>212.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>460.52</v>
+        <v>235.4656</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.23</v>
+        <v>-7.42</v>
       </c>
       <c r="AS6" t="n">
-        <v>-9.19</v>
+        <v>-0.57</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1646,16 +1646,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 7.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>55.8</v>
+        <v>38.3</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.2%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 58.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 191.72 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1506757312512</v>
+        <v>1483162648576</v>
       </c>
       <c r="G7" t="n">
-        <v>21.58</v>
+        <v>21.27</v>
       </c>
       <c r="H7" t="n">
-        <v>16.04</v>
+        <v>15.79</v>
       </c>
       <c r="I7" t="n">
         <v>32.84</v>
@@ -1742,19 +1742,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>21.5</v>
+        <v>19.6</v>
       </c>
       <c r="P7" t="n">
-        <v>80.2</v>
+        <v>81</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="R7" t="n">
-        <v>72.5</v>
+        <v>70.3</v>
       </c>
       <c r="S7" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1768,37 +1768,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>593.64</v>
+        <v>584.285</v>
       </c>
       <c r="X7" t="n">
-        <v>7.89</v>
+        <v>3.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>-12.44</v>
+        <v>-12.89</v>
       </c>
       <c r="Z7" t="n">
-        <v>-11.55</v>
+        <v>-13.02</v>
       </c>
       <c r="AA7" t="n">
-        <v>-16.43</v>
+        <v>-18.31</v>
       </c>
       <c r="AB7" t="n">
-        <v>22.67</v>
+        <v>22.89</v>
       </c>
       <c r="AC7" t="n">
-        <v>37.03</v>
+        <v>37.02</v>
       </c>
       <c r="AD7" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>604.899</v>
+        <v>604.3069</v>
       </c>
       <c r="AG7" t="n">
-        <v>635.9232</v>
+        <v>635.1855</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1809,19 +1809,19 @@
         <v>35</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21.5</v>
+        <v>19.6</v>
       </c>
       <c r="AK7" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>72.5</v>
+        <v>70.3</v>
       </c>
       <c r="AM7" t="n">
         <v>752</v>
       </c>
       <c r="AN7" t="n">
-        <v>563.29</v>
+        <v>582.9</v>
       </c>
       <c r="AO7" t="n">
         <v>542.87</v>
@@ -1833,10 +1833,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.86</v>
+        <v>-3.31</v>
       </c>
       <c r="AS7" t="n">
-        <v>-6.65</v>
+        <v>-8.01</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 58.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.9%.</t>
+          <t>META: scenario base Hold / Monitor, score 58.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.3%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2485107556352</v>
+        <v>2448156786688</v>
       </c>
       <c r="G8" t="n">
-        <v>27.67</v>
+        <v>27.22</v>
       </c>
       <c r="H8" t="n">
-        <v>23.29</v>
+        <v>22.94</v>
       </c>
       <c r="I8" t="n">
         <v>12.22</v>
@@ -1939,19 +1939,19 @@
         <v>78.2</v>
       </c>
       <c r="O8" t="n">
-        <v>31.9</v>
+        <v>27.9</v>
       </c>
       <c r="P8" t="n">
-        <v>62.8</v>
+        <v>63.8</v>
       </c>
       <c r="Q8" t="n">
         <v>37.8</v>
       </c>
       <c r="R8" t="n">
-        <v>65.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="S8" t="n">
-        <v>53.5</v>
+        <v>52.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>231</v>
+        <v>227.59</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.73</v>
+        <v>-5.23</v>
       </c>
       <c r="Y8" t="n">
-        <v>-11.53</v>
+        <v>-12.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>-3.11</v>
+        <v>-6.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.19</v>
+        <v>-2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>20.56</v>
+        <v>19.52</v>
       </c>
       <c r="AC8" t="n">
         <v>31.25</v>
@@ -1989,13 +1989,13 @@
         <v>-30.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>247.724</v>
+        <v>246.9902</v>
       </c>
       <c r="AG8" t="n">
-        <v>234.6652</v>
+        <v>234.6637</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,19 +2006,19 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>31.9</v>
+        <v>27.9</v>
       </c>
       <c r="AK8" t="n">
         <v>37.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>65.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
       </c>
       <c r="AN8" t="n">
-        <v>231</v>
+        <v>227.585</v>
       </c>
       <c r="AO8" t="n">
         <v>227.01</v>
@@ -2030,10 +2030,10 @@
         <v>274.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>-6.75</v>
+        <v>-7.86</v>
       </c>
       <c r="AS8" t="n">
-        <v>-1.56</v>
+        <v>-3.02</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 6.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>50.8</v>
+        <v>49.4</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Avoid for Now, score 53.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.8%.</t>
+          <t>AMZN: scenario base Avoid for Now, score 52.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.9%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1211227439104</v>
+        <v>1177695813632</v>
       </c>
       <c r="G10" t="n">
-        <v>283.96</v>
+        <v>276.1</v>
       </c>
       <c r="H10" t="n">
-        <v>137.93</v>
+        <v>134.47</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>38.7</v>
       </c>
       <c r="S10" t="n">
-        <v>24.6</v>
+        <v>23.2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>306.65</v>
+        <v>298.375</v>
       </c>
       <c r="X10" t="n">
-        <v>-19.24</v>
+        <v>-27.55</v>
       </c>
       <c r="Y10" t="n">
-        <v>-19.02</v>
+        <v>-20.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>-29.54</v>
+        <v>-30.76</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.98</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.82</v>
+        <v>3.74</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.49</v>
+        <v>58.51</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>397.104</v>
+        <v>394.6425</v>
       </c>
       <c r="AG10" t="n">
-        <v>413.4285</v>
+        <v>412.7466</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,22 +2350,22 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>41.1</v>
+        <v>38.7</v>
       </c>
       <c r="AM10" t="n">
         <v>752</v>
       </c>
       <c r="AN10" t="n">
-        <v>306.65</v>
+        <v>298.15</v>
       </c>
       <c r="AO10" t="n">
-        <v>306.65</v>
+        <v>298.15</v>
       </c>
       <c r="AP10" t="n">
         <v>425.3</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-22.78</v>
+        <v>-24.45</v>
       </c>
       <c r="AS10" t="n">
-        <v>-25.83</v>
+        <v>-27.76</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 22.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 24.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>10.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 24.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -22.8%.</t>
+          <t>TSLA: scenario base High Risk, score 23.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -24.4%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 306.65 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 298.15 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4988707274752</v>
+        <v>4903226834944</v>
       </c>
       <c r="G2" t="n">
-        <v>41.12</v>
+        <v>40.47</v>
       </c>
       <c r="H2" t="n">
-        <v>35.17</v>
+        <v>34.57</v>
       </c>
       <c r="I2" t="n">
         <v>27.15</v>
@@ -750,16 +750,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>30.2</v>
+        <v>31.8</v>
       </c>
       <c r="Q2" t="n">
         <v>41.3</v>
       </c>
       <c r="R2" t="n">
-        <v>58.5</v>
+        <v>67</v>
       </c>
       <c r="S2" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>339.64</v>
+        <v>333.84</v>
       </c>
       <c r="X2" t="n">
-        <v>20.55</v>
+        <v>15.37</v>
       </c>
       <c r="Y2" t="n">
-        <v>25.58</v>
+        <v>23.68</v>
       </c>
       <c r="Z2" t="n">
-        <v>31.75</v>
+        <v>30.42</v>
       </c>
       <c r="AA2" t="n">
-        <v>59.3</v>
+        <v>58.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.7</v>
+        <v>19.98</v>
       </c>
       <c r="AC2" t="n">
         <v>26.68</v>
@@ -797,13 +797,13 @@
         <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>308.6178</v>
+        <v>309.3088</v>
       </c>
       <c r="AG2" t="n">
-        <v>276.9145</v>
+        <v>277.3536</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
         <v>41.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>58.5</v>
+        <v>67</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
-        <v>294.38</v>
+        <v>308.63</v>
       </c>
       <c r="AO2" t="n">
         <v>275.15</v>
@@ -838,10 +838,10 @@
         <v>340.08</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.05</v>
+        <v>7.94</v>
       </c>
       <c r="AS2" t="n">
-        <v>22.65</v>
+        <v>20.38</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 10.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>63</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4110787018752</v>
+        <v>4080640196608</v>
       </c>
       <c r="G3" t="n">
-        <v>16.87</v>
+        <v>16.74</v>
       </c>
       <c r="H3" t="n">
-        <v>22.84</v>
+        <v>22.64</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -940,25 +940,25 @@
         <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>63.7</v>
+        <v>61</v>
       </c>
       <c r="P3" t="n">
-        <v>76</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>40</v>
       </c>
       <c r="R3" t="n">
-        <v>69.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="S3" t="n">
-        <v>71.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>336.13</v>
+        <v>333.66</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.95</v>
+        <v>-6.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3.85</v>
+        <v>-4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6</v>
+        <v>-0.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>75.04000000000001</v>
+        <v>70.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>36.94</v>
+        <v>36.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.16</v>
+        <v>30.15</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>360.5588</v>
+        <v>359.3095</v>
       </c>
       <c r="AG3" t="n">
-        <v>324.9235</v>
+        <v>325.4142</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63.7</v>
+        <v>61</v>
       </c>
       <c r="AK3" t="n">
         <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>69.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
         <v>317.69</v>
@@ -1037,10 +1037,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>-6.78</v>
+        <v>-7.12</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>65.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 71.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 71.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>523221008384</v>
+        <v>553103982592</v>
       </c>
       <c r="G4" t="n">
-        <v>53.61</v>
+        <v>56.54</v>
       </c>
       <c r="H4" t="n">
-        <v>26.75</v>
+        <v>28.19</v>
       </c>
       <c r="I4" t="n">
         <v>30.11</v>
@@ -1139,7 +1139,7 @@
         <v>9.09</v>
       </c>
       <c r="M4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -1148,16 +1148,16 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>27.7</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="R4" t="n">
-        <v>63</v>
+        <v>70.5</v>
       </c>
       <c r="S4" t="n">
-        <v>67.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1362.2</v>
+        <v>1440</v>
       </c>
       <c r="X4" t="n">
-        <v>-20.77</v>
+        <v>-12.18</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.57</v>
+        <v>21.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.82</v>
+        <v>19.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>130.44</v>
+        <v>140.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.61</v>
+        <v>30.94</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="AD4" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="AF4" t="n">
-        <v>1533.1344</v>
+        <v>1535.0628</v>
       </c>
       <c r="AG4" t="n">
-        <v>1198.5622</v>
+        <v>1201.4256</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1215,13 +1215,13 @@
         <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="AL4" t="n">
-        <v>63</v>
+        <v>70.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AN4" t="n">
         <v>1362.2</v>
@@ -1236,10 +1236,10 @@
         <v>1719.3295</v>
       </c>
       <c r="AR4" t="n">
-        <v>-11.15</v>
+        <v>-6.19</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.65</v>
+        <v>19.86</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 11.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>51.6</v>
+        <v>53.5</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -11.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.2%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2913952071680</v>
+        <v>3354532511744</v>
       </c>
       <c r="G5" t="n">
-        <v>23.35</v>
+        <v>27.07</v>
       </c>
       <c r="H5" t="n">
-        <v>20.24</v>
+        <v>19.64</v>
       </c>
       <c r="I5" t="n">
         <v>39.34</v>
@@ -1344,19 +1344,19 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>21.7</v>
+        <v>53</v>
       </c>
       <c r="P5" t="n">
-        <v>72.2</v>
+        <v>68.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>43.2</v>
+        <v>41.3</v>
       </c>
       <c r="R5" t="n">
-        <v>73.09999999999999</v>
+        <v>45.4</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,62 +1365,62 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>392.27</v>
+        <v>451.58</v>
       </c>
       <c r="X5" t="n">
-        <v>6.43</v>
+        <v>21.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>-8.42</v>
+        <v>6.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>-18.01</v>
+        <v>-5.82</v>
       </c>
       <c r="AA5" t="n">
-        <v>-22.85</v>
+        <v>-11.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.16</v>
+        <v>11.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>24.33</v>
+        <v>25.93</v>
       </c>
       <c r="AD5" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>397.8878</v>
+        <v>398.4324</v>
       </c>
       <c r="AG5" t="n">
-        <v>432.7784</v>
+        <v>432.4889</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21.7</v>
+        <v>53</v>
       </c>
       <c r="AK5" t="n">
-        <v>43.2</v>
+        <v>41.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>73.09999999999999</v>
+        <v>45.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
         <v>381.58</v>
@@ -1429,20 +1429,20 @@
         <v>352.83</v>
       </c>
       <c r="AP5" t="n">
-        <v>402.29</v>
+        <v>451.58</v>
       </c>
       <c r="AQ5" t="n">
         <v>460.52</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.41</v>
+        <v>13.34</v>
       </c>
       <c r="AS5" t="n">
-        <v>-9.359999999999999</v>
+        <v>4.41</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 13.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>54.9</v>
+        <v>44</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 59.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.4%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 66.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.3%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4643650273280</v>
+        <v>4726849011712</v>
       </c>
       <c r="G6" t="n">
-        <v>29.4</v>
+        <v>29.84</v>
       </c>
       <c r="H6" t="n">
-        <v>14.9</v>
+        <v>15.16</v>
       </c>
       <c r="I6" t="n">
         <v>62.97</v>
@@ -1537,25 +1537,25 @@
         <v>6.55</v>
       </c>
       <c r="M6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>39.3</v>
+        <v>44.8</v>
       </c>
       <c r="P6" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>64.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="S6" t="n">
-        <v>58.5</v>
+        <v>61.9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,63 +1569,63 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>191.72</v>
+        <v>195.15</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.67</v>
+        <v>-2.47</v>
       </c>
       <c r="Y6" t="n">
-        <v>-9.960000000000001</v>
+        <v>-6.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.609999999999999</v>
+        <v>11.34</v>
       </c>
       <c r="AB6" t="n">
-        <v>60.59</v>
+        <v>61.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>47.09</v>
+        <v>47.1</v>
       </c>
       <c r="AD6" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>207.0905</v>
+        <v>206.5181</v>
       </c>
       <c r="AG6" t="n">
-        <v>192.8126</v>
+        <v>192.8652</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>39.3</v>
+        <v>44.8</v>
       </c>
       <c r="AK6" t="n">
         <v>14</v>
       </c>
       <c r="AL6" t="n">
-        <v>64.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN6" t="n">
-        <v>191.72</v>
+        <v>190.01</v>
       </c>
       <c r="AO6" t="n">
-        <v>191.72</v>
+        <v>190.01</v>
       </c>
       <c r="AP6" t="n">
         <v>212.5</v>
@@ -1634,14 +1634,14 @@
         <v>235.4656</v>
       </c>
       <c r="AR6" t="n">
-        <v>-7.42</v>
+        <v>-5.49</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.57</v>
+        <v>1.2</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 7.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>38.3</v>
+        <v>42.6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 58.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 61.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 191.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1691,12 +1691,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1706,55 +1706,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1483162648576</v>
+        <v>2534805340160</v>
       </c>
       <c r="G7" t="n">
-        <v>21.27</v>
+        <v>28.19</v>
       </c>
       <c r="H7" t="n">
-        <v>15.79</v>
+        <v>23.73</v>
       </c>
       <c r="I7" t="n">
-        <v>32.84</v>
+        <v>12.22</v>
       </c>
       <c r="J7" t="n">
-        <v>32.93</v>
+        <v>24.29</v>
       </c>
       <c r="K7" t="n">
-        <v>33.1</v>
+        <v>16.6</v>
       </c>
       <c r="L7" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="M7" t="n">
-        <v>35</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="O7" t="n">
-        <v>19.6</v>
+        <v>34.1</v>
       </c>
       <c r="P7" t="n">
-        <v>81</v>
+        <v>61.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.3</v>
+        <v>37.7</v>
       </c>
       <c r="R7" t="n">
-        <v>70.3</v>
+        <v>73.2</v>
       </c>
       <c r="S7" t="n">
-        <v>58.1</v>
+        <v>56.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1763,98 +1761,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>584.285</v>
+        <v>235.66</v>
       </c>
       <c r="X7" t="n">
-        <v>3.85</v>
+        <v>-1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>-12.89</v>
+        <v>-10.41</v>
       </c>
       <c r="Z7" t="n">
-        <v>-13.02</v>
+        <v>-3.02</v>
       </c>
       <c r="AA7" t="n">
-        <v>-18.31</v>
+        <v>2.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>22.89</v>
+        <v>20.89</v>
       </c>
       <c r="AC7" t="n">
-        <v>37.02</v>
+        <v>31.32</v>
       </c>
       <c r="AD7" t="n">
-        <v>-34.15</v>
+        <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>604.3069</v>
+        <v>246.3874</v>
       </c>
       <c r="AG7" t="n">
-        <v>635.1855</v>
+        <v>234.7555</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19.6</v>
+        <v>34.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>28.3</v>
+        <v>37.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>70.3</v>
+        <v>73.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
-        <v>582.9</v>
+        <v>226.65</v>
       </c>
       <c r="AO7" t="n">
-        <v>542.87</v>
+        <v>226.65</v>
       </c>
       <c r="AP7" t="n">
-        <v>681.3099999999999</v>
+        <v>254.96</v>
       </c>
       <c r="AQ7" t="n">
-        <v>681.3099999999999</v>
+        <v>274.99</v>
       </c>
       <c r="AR7" t="n">
-        <v>-3.31</v>
+        <v>-4.36</v>
       </c>
       <c r="AS7" t="n">
-        <v>-8.01</v>
+        <v>0.38</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>38.9</v>
+        <v>54.3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1863,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 58.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.3%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 56.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.4%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 681.31 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1883,19 +1881,19 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1905,97 +1903,99 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2448156786688</v>
+        <v>1369860210688</v>
       </c>
       <c r="G8" t="n">
-        <v>27.22</v>
+        <v>20.34</v>
       </c>
       <c r="H8" t="n">
-        <v>22.94</v>
+        <v>14.73</v>
       </c>
       <c r="I8" t="n">
-        <v>12.22</v>
+        <v>32.84</v>
       </c>
       <c r="J8" t="n">
-        <v>24.29</v>
+        <v>32.93</v>
       </c>
       <c r="K8" t="n">
-        <v>16.6</v>
+        <v>33.1</v>
       </c>
       <c r="L8" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>35.61</v>
+      </c>
+      <c r="M8" t="n">
+        <v>35</v>
+      </c>
       <c r="N8" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="Q8" t="n">
         <v>27.9</v>
       </c>
-      <c r="P8" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>37.8</v>
-      </c>
       <c r="R8" t="n">
-        <v>63.5</v>
+        <v>59.5</v>
       </c>
       <c r="S8" t="n">
-        <v>52.5</v>
+        <v>53.9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>227.59</v>
+        <v>539.625</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.23</v>
+        <v>-4.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>-12.36</v>
+        <v>-19.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>-6.98</v>
+        <v>-19.16</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2.23</v>
+        <v>-22.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.52</v>
+        <v>19.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.25</v>
+        <v>37.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>-30.88</v>
+        <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="AF8" t="n">
-        <v>246.9902</v>
+        <v>602.913</v>
       </c>
       <c r="AG8" t="n">
-        <v>234.6637</v>
+        <v>634.3729</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,34 +2006,34 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AK8" t="n">
         <v>27.9</v>
       </c>
-      <c r="AK8" t="n">
-        <v>37.8</v>
-      </c>
       <c r="AL8" t="n">
-        <v>63.5</v>
+        <v>59.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
-        <v>227.585</v>
+        <v>539.65</v>
       </c>
       <c r="AO8" t="n">
-        <v>227.01</v>
+        <v>539.65</v>
       </c>
       <c r="AP8" t="n">
-        <v>254.96</v>
+        <v>681.3099999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>274.99</v>
+        <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-7.86</v>
+        <v>-10.49</v>
       </c>
       <c r="AS8" t="n">
-        <v>-3.02</v>
+        <v>-14.93</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2042,16 +2042,16 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 7.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>49.4</v>
+        <v>32.2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Avoid for Now, score 52.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.9%.</t>
+          <t>META: scenario base High Risk, score 53.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.5%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 681.31 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 227.01 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 539.65 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1177695813632</v>
+        <v>1220106125312</v>
       </c>
       <c r="G10" t="n">
-        <v>276.1</v>
+        <v>288.71</v>
       </c>
       <c r="H10" t="n">
-        <v>134.47</v>
+        <v>139.31</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>38.7</v>
+        <v>43.3</v>
       </c>
       <c r="S10" t="n">
-        <v>23.2</v>
+        <v>25.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,22 +2309,22 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>298.375</v>
+        <v>308.9253</v>
       </c>
       <c r="X10" t="n">
-        <v>-27.55</v>
+        <v>-26.55</v>
       </c>
       <c r="Y10" t="n">
-        <v>-20.65</v>
+        <v>-17.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>-30.76</v>
+        <v>-28.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>-8.359999999999999</v>
+        <v>-3.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.74</v>
+        <v>4.95</v>
       </c>
       <c r="AC10" t="n">
         <v>58.51</v>
@@ -2333,13 +2333,13 @@
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>394.6425</v>
+        <v>392.6201</v>
       </c>
       <c r="AG10" t="n">
-        <v>412.7466</v>
+        <v>412.2235</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,34 +2350,34 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>38.7</v>
+        <v>43.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN10" t="n">
-        <v>298.15</v>
+        <v>298.32</v>
       </c>
       <c r="AO10" t="n">
-        <v>298.15</v>
+        <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>425.3</v>
+        <v>419.77</v>
       </c>
       <c r="AQ10" t="n">
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-24.45</v>
+        <v>-21.32</v>
       </c>
       <c r="AS10" t="n">
-        <v>-27.76</v>
+        <v>-25.06</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 24.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 21.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 23.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -24.4%.</t>
+          <t>TSLA: scenario base High Risk, score 25.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -21.3%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 298.15 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 298.32 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,25 +720,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4903226834944</v>
+        <v>4550436585472</v>
       </c>
       <c r="G2" t="n">
-        <v>40.47</v>
+        <v>35.45</v>
       </c>
       <c r="H2" t="n">
-        <v>34.57</v>
+        <v>32.35</v>
       </c>
       <c r="I2" t="n">
-        <v>27.15</v>
+        <v>27.62</v>
       </c>
       <c r="J2" t="n">
-        <v>141.47</v>
+        <v>148.75</v>
       </c>
       <c r="K2" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="L2" t="n">
-        <v>79.55</v>
+        <v>78.44</v>
       </c>
       <c r="M2" t="n">
         <v>32</v>
@@ -747,19 +747,19 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="P2" t="n">
-        <v>31.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.3</v>
+        <v>40.9</v>
       </c>
       <c r="R2" t="n">
-        <v>67</v>
+        <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>73.7</v>
+        <v>75.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>333.84</v>
+        <v>310.075</v>
       </c>
       <c r="X2" t="n">
-        <v>15.37</v>
+        <v>5.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.68</v>
+        <v>14.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>30.42</v>
+        <v>20.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>58.64</v>
+        <v>48.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.98</v>
+        <v>17.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.68</v>
+        <v>26.97</v>
       </c>
       <c r="AD2" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AF2" t="n">
-        <v>309.3088</v>
+        <v>309.5227</v>
       </c>
       <c r="AG2" t="n">
-        <v>277.3536</v>
+        <v>277.6671</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,19 +814,19 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>41.3</v>
+        <v>40.9</v>
       </c>
       <c r="AL2" t="n">
-        <v>67</v>
+        <v>82.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN2" t="n">
-        <v>308.63</v>
+        <v>310.08</v>
       </c>
       <c r="AO2" t="n">
         <v>275.15</v>
@@ -838,10 +838,10 @@
         <v>340.08</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.94</v>
+        <v>0.18</v>
       </c>
       <c r="AS2" t="n">
-        <v>20.38</v>
+        <v>11.67</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>69.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.2%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4080640196608</v>
+        <v>4354346319872</v>
       </c>
       <c r="G3" t="n">
-        <v>16.74</v>
+        <v>17.87</v>
       </c>
       <c r="H3" t="n">
-        <v>22.64</v>
+        <v>24.16</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>61</v>
+        <v>63.5</v>
       </c>
       <c r="P3" t="n">
-        <v>76.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>39.7</v>
       </c>
       <c r="R3" t="n">
-        <v>69</v>
+        <v>78.8</v>
       </c>
       <c r="S3" t="n">
-        <v>71</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>333.66</v>
+        <v>356.34</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.63</v>
+        <v>-1.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>-4.6</v>
+        <v>-7.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.57</v>
+        <v>5.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>70.94</v>
+        <v>81.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>36.54</v>
+        <v>39.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.15</v>
+        <v>30.37</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>359.3095</v>
+        <v>358.6877</v>
       </c>
       <c r="AG3" t="n">
-        <v>325.4142</v>
+        <v>325.9775</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>61</v>
+        <v>63.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>39.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>69</v>
+        <v>78.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN3" t="n">
         <v>317.69</v>
@@ -1037,10 +1037,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR3" t="n">
-        <v>-7.12</v>
+        <v>-0.66</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.55</v>
+        <v>9.31</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>64.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 71.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 71.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,150 +1114,150 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>553103982592</v>
+        <v>3454475173888</v>
       </c>
       <c r="G4" t="n">
-        <v>56.54</v>
+        <v>25.92</v>
       </c>
       <c r="H4" t="n">
-        <v>28.19</v>
+        <v>20.02</v>
       </c>
       <c r="I4" t="n">
-        <v>30.11</v>
+        <v>40.3</v>
       </c>
       <c r="J4" t="n">
-        <v>53.94</v>
+        <v>34.04</v>
       </c>
       <c r="K4" t="n">
-        <v>21.3</v>
+        <v>17.7</v>
       </c>
       <c r="L4" t="n">
-        <v>9.09</v>
+        <v>29.12</v>
       </c>
       <c r="M4" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>69.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.9</v>
+        <v>41.3</v>
       </c>
       <c r="R4" t="n">
-        <v>70.5</v>
+        <v>32.6</v>
       </c>
       <c r="S4" t="n">
-        <v>67.5</v>
+        <v>70.2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1440</v>
+        <v>465.47</v>
       </c>
       <c r="X4" t="n">
-        <v>-12.18</v>
+        <v>21.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>21.42</v>
+        <v>14.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.02</v>
+        <v>7.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>140.61</v>
+        <v>-8.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>30.94</v>
+        <v>12.39</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.4</v>
+        <v>25.96</v>
       </c>
       <c r="AD4" t="n">
-        <v>-44.77</v>
+        <v>-34.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
       <c r="AF4" t="n">
-        <v>1535.0628</v>
+        <v>399.4018</v>
       </c>
       <c r="AG4" t="n">
-        <v>1201.4256</v>
+        <v>432.2598</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.9</v>
+        <v>41.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>70.5</v>
+        <v>32.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="AN4" t="n">
-        <v>1362.2</v>
+        <v>381.58</v>
       </c>
       <c r="AO4" t="n">
-        <v>1247.4977</v>
+        <v>352.83</v>
       </c>
       <c r="AP4" t="n">
-        <v>1632.4341</v>
+        <v>465.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1719.3295</v>
+        <v>465.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>-6.19</v>
+        <v>16.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>19.86</v>
+        <v>7.69</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 16.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>53.5</v>
+        <v>39.7</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.2%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.6%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 465.50 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1247.50 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1313,50 +1313,50 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3354532511744</v>
+        <v>550876217344</v>
       </c>
       <c r="G5" t="n">
-        <v>27.07</v>
+        <v>56.6</v>
       </c>
       <c r="H5" t="n">
-        <v>19.64</v>
+        <v>28.07</v>
       </c>
       <c r="I5" t="n">
-        <v>39.34</v>
+        <v>30.11</v>
       </c>
       <c r="J5" t="n">
-        <v>34.01</v>
+        <v>53.94</v>
       </c>
       <c r="K5" t="n">
-        <v>18.3</v>
+        <v>21.3</v>
       </c>
       <c r="L5" t="n">
-        <v>30.27</v>
+        <v>9.09</v>
       </c>
       <c r="M5" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>68.7</v>
+        <v>24.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.3</v>
+        <v>16.9</v>
       </c>
       <c r="R5" t="n">
-        <v>45.4</v>
+        <v>69.8</v>
       </c>
       <c r="S5" t="n">
-        <v>66.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,98 +1365,98 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>451.58</v>
+        <v>1434.2</v>
       </c>
       <c r="X5" t="n">
-        <v>21.06</v>
+        <v>-8.99</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.62</v>
+        <v>16.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>-5.82</v>
+        <v>17.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>-11.2</v>
+        <v>141.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.28</v>
+        <v>30.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>25.93</v>
+        <v>39.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>-34.5</v>
+        <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.43</v>
+        <v>0.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>398.4324</v>
+        <v>1535.6006</v>
       </c>
       <c r="AG5" t="n">
-        <v>432.4889</v>
+        <v>1204.238</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>41.3</v>
+        <v>16.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>45.4</v>
+        <v>69.8</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="AN5" t="n">
-        <v>381.58</v>
+        <v>1362.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>352.83</v>
+        <v>1247.4977</v>
       </c>
       <c r="AP5" t="n">
-        <v>451.58</v>
+        <v>1626.4414</v>
       </c>
       <c r="AQ5" t="n">
-        <v>460.52</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.34</v>
+        <v>-6.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.41</v>
+        <v>19.1</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 13.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 6.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>44</v>
+        <v>53.4</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 66.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.3%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.6%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1247.50 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,55 +1507,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4726849011712</v>
+        <v>2918457540608</v>
       </c>
       <c r="G6" t="n">
-        <v>29.84</v>
+        <v>21.83</v>
       </c>
       <c r="H6" t="n">
-        <v>15.16</v>
+        <v>26.71</v>
       </c>
       <c r="I6" t="n">
-        <v>62.97</v>
+        <v>17.44</v>
       </c>
       <c r="J6" t="n">
-        <v>114.29</v>
+        <v>30.56</v>
       </c>
       <c r="K6" t="n">
-        <v>85.2</v>
+        <v>19.6</v>
       </c>
       <c r="L6" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="M6" t="n">
-        <v>53</v>
-      </c>
+        <v>40.47</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>44.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>71.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>36.3</v>
       </c>
       <c r="R6" t="n">
-        <v>71.5</v>
+        <v>58.1</v>
       </c>
       <c r="S6" t="n">
-        <v>61.9</v>
+        <v>65.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1564,80 +1562,80 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>195.15</v>
+        <v>271.67</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.47</v>
+        <v>12.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>-6.63</v>
+        <v>2.49</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>12.39</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.34</v>
+        <v>18.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>61.45</v>
+        <v>26.74</v>
       </c>
       <c r="AC6" t="n">
-        <v>47.1</v>
+        <v>32.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>-36.88</v>
+        <v>-30.88</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.3</v>
+        <v>0.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>206.5181</v>
+        <v>246.6308</v>
       </c>
       <c r="AG6" t="n">
-        <v>192.8652</v>
+        <v>235.0127</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>14</v>
+        <v>36.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>71.5</v>
+        <v>58.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN6" t="n">
-        <v>190.01</v>
+        <v>226.65</v>
       </c>
       <c r="AO6" t="n">
-        <v>190.01</v>
+        <v>226.65</v>
       </c>
       <c r="AP6" t="n">
-        <v>212.5</v>
+        <v>271.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>235.4656</v>
+        <v>274.99</v>
       </c>
       <c r="AR6" t="n">
-        <v>-5.49</v>
+        <v>10.14</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.2</v>
+        <v>15.59</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1646,16 +1644,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 5.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>42.6</v>
+        <v>53.7</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 61.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.5%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1684,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1706,53 +1704,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2534805340160</v>
+        <v>4875929255936</v>
       </c>
       <c r="G7" t="n">
-        <v>28.19</v>
+        <v>30.83</v>
       </c>
       <c r="H7" t="n">
-        <v>23.73</v>
+        <v>15.64</v>
       </c>
       <c r="I7" t="n">
-        <v>12.22</v>
+        <v>62.97</v>
       </c>
       <c r="J7" t="n">
-        <v>24.29</v>
+        <v>114.29</v>
       </c>
       <c r="K7" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="L7" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>6.55</v>
+      </c>
+      <c r="M7" t="n">
+        <v>51</v>
+      </c>
       <c r="N7" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>34.1</v>
+        <v>57.4</v>
       </c>
       <c r="P7" t="n">
-        <v>61.6</v>
+        <v>70</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.7</v>
+        <v>14</v>
       </c>
       <c r="R7" t="n">
-        <v>73.2</v>
+        <v>76.3</v>
       </c>
       <c r="S7" t="n">
-        <v>56.1</v>
+        <v>65.2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,42 +1761,42 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>235.66</v>
+        <v>201.39</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.12</v>
+        <v>1.93</v>
       </c>
       <c r="Y7" t="n">
-        <v>-10.41</v>
+        <v>1.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>-3.02</v>
+        <v>4.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.01</v>
+        <v>12.49</v>
       </c>
       <c r="AB7" t="n">
-        <v>20.89</v>
+        <v>63.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>31.32</v>
+        <v>47.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>-30.88</v>
+        <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.67</v>
+        <v>1.34</v>
       </c>
       <c r="AF7" t="n">
-        <v>246.3874</v>
+        <v>206.1366</v>
       </c>
       <c r="AG7" t="n">
-        <v>234.7555</v>
+        <v>192.9312</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,34 +1807,34 @@
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34.1</v>
+        <v>57.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>37.7</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
-        <v>73.2</v>
+        <v>76.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN7" t="n">
-        <v>226.65</v>
+        <v>190.01</v>
       </c>
       <c r="AO7" t="n">
-        <v>226.65</v>
+        <v>190.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>254.96</v>
+        <v>212.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>274.99</v>
+        <v>235.4656</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.36</v>
+        <v>-2.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.38</v>
+        <v>4.39</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1843,16 +1843,16 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 4.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>54.3</v>
+        <v>47.1</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 56.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.4%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 65.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.3%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1912,50 +1912,50 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1369860210688</v>
+        <v>1417508814848</v>
       </c>
       <c r="G8" t="n">
-        <v>20.34</v>
+        <v>20.94</v>
       </c>
       <c r="H8" t="n">
-        <v>14.73</v>
+        <v>15.65</v>
       </c>
       <c r="I8" t="n">
-        <v>32.84</v>
+        <v>29.83</v>
       </c>
       <c r="J8" t="n">
-        <v>32.93</v>
+        <v>29.85</v>
       </c>
       <c r="K8" t="n">
-        <v>33.1</v>
+        <v>28</v>
       </c>
       <c r="L8" t="n">
-        <v>35.61</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>5.8</v>
+        <v>17.8</v>
       </c>
       <c r="P8" t="n">
-        <v>83.5</v>
+        <v>81.5</v>
       </c>
       <c r="Q8" t="n">
         <v>27.9</v>
       </c>
       <c r="R8" t="n">
-        <v>59.5</v>
+        <v>63.9</v>
       </c>
       <c r="S8" t="n">
-        <v>53.9</v>
+        <v>57</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>539.625</v>
+        <v>556.45</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.2</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>-19.28</v>
+        <v>-8.98</v>
       </c>
       <c r="Z8" t="n">
-        <v>-19.16</v>
+        <v>-24.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>-22.66</v>
+        <v>-19.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.63</v>
+        <v>20.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.28</v>
+        <v>37.3</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AF8" t="n">
-        <v>602.913</v>
+        <v>601.9891</v>
       </c>
       <c r="AG8" t="n">
-        <v>634.3729</v>
+        <v>633.5829</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,22 +2006,22 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5.8</v>
+        <v>17.8</v>
       </c>
       <c r="AK8" t="n">
         <v>27.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>59.5</v>
+        <v>63.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN8" t="n">
-        <v>539.65</v>
+        <v>539.03</v>
       </c>
       <c r="AO8" t="n">
-        <v>539.65</v>
+        <v>539.03</v>
       </c>
       <c r="AP8" t="n">
         <v>681.3099999999999</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-10.49</v>
+        <v>-7.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>-14.93</v>
+        <v>-12.18</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 10.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>32.2</v>
+        <v>36.5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base High Risk, score 53.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 57.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 539.65 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 539.03 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1220106125312</v>
+        <v>1228960956416</v>
       </c>
       <c r="G10" t="n">
-        <v>288.71</v>
+        <v>288.12</v>
       </c>
       <c r="H10" t="n">
-        <v>139.31</v>
+        <v>139.84</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>43.3</v>
+        <v>44.8</v>
       </c>
       <c r="S10" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>308.9253</v>
+        <v>311.415</v>
       </c>
       <c r="X10" t="n">
-        <v>-26.55</v>
+        <v>-26.78</v>
       </c>
       <c r="Y10" t="n">
-        <v>-17.13</v>
+        <v>-18.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>-28.4</v>
+        <v>-25.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.82</v>
+        <v>-2.39</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.95</v>
+        <v>5.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.51</v>
+        <v>58.47</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>392.6201</v>
+        <v>390.7647</v>
       </c>
       <c r="AG10" t="n">
-        <v>412.2235</v>
+        <v>411.6007</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>43.3</v>
+        <v>44.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-21.32</v>
+        <v>-20.31</v>
       </c>
       <c r="AS10" t="n">
-        <v>-25.06</v>
+        <v>-24.34</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 21.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 20.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 25.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -21.3%.</t>
+          <t>TSLA: scenario base High Risk, score 25.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -20.3%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -696,12 +696,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -711,55 +711,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4550436585472</v>
+        <v>4568003379200</v>
       </c>
       <c r="G2" t="n">
-        <v>35.45</v>
+        <v>18.73</v>
       </c>
       <c r="H2" t="n">
-        <v>32.35</v>
+        <v>25.35</v>
       </c>
       <c r="I2" t="n">
-        <v>27.62</v>
+        <v>54.77</v>
       </c>
       <c r="J2" t="n">
-        <v>148.75</v>
+        <v>48.68</v>
       </c>
       <c r="K2" t="n">
-        <v>16.4</v>
+        <v>24.2</v>
       </c>
       <c r="L2" t="n">
-        <v>78.44</v>
+        <v>18.86</v>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>94.5</v>
+        <v>75.8</v>
       </c>
       <c r="P2" t="n">
-        <v>40.8</v>
+        <v>70.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.9</v>
+        <v>39.5</v>
       </c>
       <c r="R2" t="n">
-        <v>82.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>75.5</v>
+        <v>75.7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,42 +768,42 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>310.075</v>
+        <v>373.51</v>
       </c>
       <c r="X2" t="n">
-        <v>5.33</v>
+        <v>3.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.38</v>
+        <v>-3.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.28</v>
+        <v>10.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>48.91</v>
+        <v>95.19</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.02</v>
+        <v>43.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.97</v>
+        <v>30.51</v>
       </c>
       <c r="AD2" t="n">
-        <v>-33.36</v>
+        <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.63</v>
+        <v>1.43</v>
       </c>
       <c r="AF2" t="n">
-        <v>309.5227</v>
+        <v>358.3802</v>
       </c>
       <c r="AG2" t="n">
-        <v>277.6671</v>
+        <v>326.6192</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,34 +814,34 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>94.5</v>
+        <v>75.8</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.9</v>
+        <v>39.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>82.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN2" t="n">
-        <v>310.08</v>
+        <v>317.69</v>
       </c>
       <c r="AO2" t="n">
-        <v>275.15</v>
+        <v>317.69</v>
       </c>
       <c r="AP2" t="n">
-        <v>340.08</v>
+        <v>373.51</v>
       </c>
       <c r="AQ2" t="n">
-        <v>340.08</v>
+        <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.18</v>
+        <v>4.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.67</v>
+        <v>14.36</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>75</v>
+        <v>71.8</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,17 +868,17 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.2%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 340.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 275.15 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -888,19 +888,19 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -910,55 +910,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4354346319872</v>
+        <v>4456437514240</v>
       </c>
       <c r="G3" t="n">
-        <v>17.87</v>
+        <v>34.84</v>
       </c>
       <c r="H3" t="n">
-        <v>24.16</v>
+        <v>31.9</v>
       </c>
       <c r="I3" t="n">
-        <v>54.77</v>
+        <v>27.62</v>
       </c>
       <c r="J3" t="n">
-        <v>48.68</v>
+        <v>148.75</v>
       </c>
       <c r="K3" t="n">
-        <v>24.2</v>
+        <v>16.4</v>
       </c>
       <c r="L3" t="n">
-        <v>18.86</v>
+        <v>78.44</v>
       </c>
       <c r="M3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>63.5</v>
+        <v>83.8</v>
       </c>
       <c r="P3" t="n">
-        <v>72.90000000000001</v>
+        <v>42.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.7</v>
+        <v>41</v>
       </c>
       <c r="R3" t="n">
-        <v>78.8</v>
+        <v>76.8</v>
       </c>
       <c r="S3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>356.34</v>
+        <v>303.42</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.35</v>
+        <v>-1.69</v>
       </c>
       <c r="Y3" t="n">
-        <v>-7.34</v>
+        <v>8.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.49</v>
+        <v>17.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>81.83</v>
+        <v>46.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.52</v>
+        <v>19.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.37</v>
+        <v>26.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>-29.81</v>
+        <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.3</v>
+        <v>0.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>358.6877</v>
+        <v>309.5228</v>
       </c>
       <c r="AG3" t="n">
-        <v>325.9775</v>
+        <v>277.943</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,34 +1013,34 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63.5</v>
+        <v>83.8</v>
       </c>
       <c r="AK3" t="n">
-        <v>39.7</v>
+        <v>41</v>
       </c>
       <c r="AL3" t="n">
-        <v>78.8</v>
+        <v>76.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN3" t="n">
-        <v>317.69</v>
+        <v>303.42</v>
       </c>
       <c r="AO3" t="n">
-        <v>317.69</v>
+        <v>275.15</v>
       </c>
       <c r="AP3" t="n">
-        <v>370.92</v>
+        <v>340.08</v>
       </c>
       <c r="AQ3" t="n">
-        <v>402.3797</v>
+        <v>340.08</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.66</v>
+        <v>-1.97</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.31</v>
+        <v>9.17</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 71.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 71.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.0%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 340.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 275.15 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3454475173888</v>
+        <v>3621067423744</v>
       </c>
       <c r="G4" t="n">
-        <v>25.92</v>
+        <v>27.18</v>
       </c>
       <c r="H4" t="n">
-        <v>20.02</v>
+        <v>20.78</v>
       </c>
       <c r="I4" t="n">
         <v>40.3</v>
@@ -1139,25 +1139,25 @@
         <v>29.12</v>
       </c>
       <c r="M4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>72.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>69.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="R4" t="n">
-        <v>32.6</v>
+        <v>12</v>
       </c>
       <c r="S4" t="n">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>465.47</v>
+        <v>487.65</v>
       </c>
       <c r="X4" t="n">
-        <v>21.13</v>
+        <v>24.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.39</v>
+        <v>17.92</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.85</v>
+        <v>13.84</v>
       </c>
       <c r="AA4" t="n">
-        <v>-8.58</v>
+        <v>-7.86</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.39</v>
+        <v>15.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>25.96</v>
+        <v>26.11</v>
       </c>
       <c r="AD4" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="AF4" t="n">
-        <v>399.4018</v>
+        <v>400.7368</v>
       </c>
       <c r="AG4" t="n">
-        <v>432.2598</v>
+        <v>432.1426</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,16 +1212,16 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>72.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>32.6</v>
+        <v>12</v>
       </c>
       <c r="AM4" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN4" t="n">
         <v>381.58</v>
@@ -1230,16 +1230,16 @@
         <v>352.83</v>
       </c>
       <c r="AP4" t="n">
-        <v>465.5</v>
+        <v>487.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>465.5</v>
+        <v>487.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.55</v>
+        <v>21.69</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.69</v>
+        <v>12.84</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 16.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 21.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>39.7</v>
+        <v>26.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.6%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 69.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.7%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 465.50 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 487.65 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1313,54 +1313,54 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>550876217344</v>
+        <v>5005027311616</v>
       </c>
       <c r="G5" t="n">
-        <v>56.6</v>
+        <v>31.69</v>
       </c>
       <c r="H5" t="n">
-        <v>28.07</v>
+        <v>16.03</v>
       </c>
       <c r="I5" t="n">
-        <v>30.11</v>
+        <v>62.97</v>
       </c>
       <c r="J5" t="n">
-        <v>53.94</v>
+        <v>114.29</v>
       </c>
       <c r="K5" t="n">
-        <v>21.3</v>
+        <v>85.2</v>
       </c>
       <c r="L5" t="n">
-        <v>9.09</v>
+        <v>6.55</v>
       </c>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P5" t="n">
-        <v>24.2</v>
+        <v>68.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.9</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>69.8</v>
+        <v>82.8</v>
       </c>
       <c r="S5" t="n">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1370,75 +1370,75 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1434.2</v>
+        <v>206.64</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.99</v>
+        <v>6.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.84</v>
+        <v>4.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.65</v>
+        <v>8.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>141.76</v>
+        <v>16.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>30.72</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.38</v>
+        <v>47.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>-44.77</v>
+        <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.78</v>
+        <v>1.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>1535.6006</v>
+        <v>205.7924</v>
       </c>
       <c r="AG5" t="n">
-        <v>1204.238</v>
+        <v>193.0622</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>65</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>100</v>
-      </c>
       <c r="AK5" t="n">
-        <v>16.9</v>
+        <v>14</v>
       </c>
       <c r="AL5" t="n">
-        <v>69.8</v>
+        <v>82.8</v>
       </c>
       <c r="AM5" t="n">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="AN5" t="n">
-        <v>1362.2</v>
+        <v>190.01</v>
       </c>
       <c r="AO5" t="n">
-        <v>1247.4977</v>
+        <v>190.01</v>
       </c>
       <c r="AP5" t="n">
-        <v>1626.4414</v>
+        <v>212.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1719.3295</v>
+        <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>-6.6</v>
+        <v>0.41</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.1</v>
+        <v>7.03</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 6.6% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1247.50 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,53 +1507,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2918457540608</v>
+        <v>545268334592</v>
       </c>
       <c r="G6" t="n">
-        <v>21.83</v>
+        <v>55.91</v>
       </c>
       <c r="H6" t="n">
-        <v>26.71</v>
+        <v>27.79</v>
       </c>
       <c r="I6" t="n">
-        <v>17.44</v>
+        <v>30.11</v>
       </c>
       <c r="J6" t="n">
-        <v>30.56</v>
+        <v>53.94</v>
       </c>
       <c r="K6" t="n">
-        <v>19.6</v>
+        <v>21.3</v>
       </c>
       <c r="L6" t="n">
-        <v>40.47</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>9.09</v>
+      </c>
+      <c r="M6" t="n">
+        <v>54</v>
+      </c>
       <c r="N6" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>65.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>64.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.3</v>
+        <v>16.9</v>
       </c>
       <c r="R6" t="n">
-        <v>58.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>65.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,80 +1564,80 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>271.67</v>
+        <v>1419.6</v>
       </c>
       <c r="X6" t="n">
-        <v>12.4</v>
+        <v>-13.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.49</v>
+        <v>8.91</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.39</v>
+        <v>19.82</v>
       </c>
       <c r="AA6" t="n">
-        <v>18.02</v>
+        <v>141</v>
       </c>
       <c r="AB6" t="n">
-        <v>26.74</v>
+        <v>32.51</v>
       </c>
       <c r="AC6" t="n">
-        <v>32.52</v>
+        <v>39.39</v>
       </c>
       <c r="AD6" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>246.6308</v>
+        <v>1535.4151</v>
       </c>
       <c r="AG6" t="n">
-        <v>235.0127</v>
+        <v>1206.986</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>36.3</v>
+        <v>16.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>58.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="AN6" t="n">
-        <v>226.65</v>
+        <v>1362.2</v>
       </c>
       <c r="AO6" t="n">
-        <v>226.65</v>
+        <v>1247.4977</v>
       </c>
       <c r="AP6" t="n">
-        <v>271.64</v>
+        <v>1600.8722</v>
       </c>
       <c r="AQ6" t="n">
-        <v>274.99</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.14</v>
+        <v>-7.54</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.59</v>
+        <v>17.62</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1644,16 +1646,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 7.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>53.7</v>
+        <v>53</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1664,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1247.50 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1684,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1704,55 +1706,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4875929255936</v>
+        <v>3055234318336</v>
       </c>
       <c r="G7" t="n">
-        <v>30.83</v>
+        <v>22.83</v>
       </c>
       <c r="H7" t="n">
-        <v>15.64</v>
+        <v>27.53</v>
       </c>
       <c r="I7" t="n">
-        <v>62.97</v>
+        <v>17.44</v>
       </c>
       <c r="J7" t="n">
-        <v>114.29</v>
+        <v>30.56</v>
       </c>
       <c r="K7" t="n">
-        <v>85.2</v>
+        <v>19.6</v>
       </c>
       <c r="L7" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="M7" t="n">
-        <v>51</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>57.4</v>
+        <v>74.8</v>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>62.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>36.6</v>
       </c>
       <c r="R7" t="n">
-        <v>76.3</v>
+        <v>38.8</v>
       </c>
       <c r="S7" t="n">
-        <v>65.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,98 +1761,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>201.39</v>
+        <v>284.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.93</v>
+        <v>17.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.03</v>
+        <v>5.87</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.74</v>
+        <v>18.69</v>
       </c>
       <c r="AA7" t="n">
-        <v>12.49</v>
+        <v>21.32</v>
       </c>
       <c r="AB7" t="n">
-        <v>63.05</v>
+        <v>26.92</v>
       </c>
       <c r="AC7" t="n">
-        <v>47.1</v>
+        <v>32.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>-36.88</v>
+        <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.34</v>
+        <v>0.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>206.1366</v>
+        <v>247.0092</v>
       </c>
       <c r="AG7" t="n">
-        <v>192.9312</v>
+        <v>235.3503</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>57.4</v>
+        <v>74.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>14</v>
+        <v>36.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>76.3</v>
+        <v>38.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN7" t="n">
-        <v>190.01</v>
+        <v>226.65</v>
       </c>
       <c r="AO7" t="n">
-        <v>190.01</v>
+        <v>226.65</v>
       </c>
       <c r="AP7" t="n">
-        <v>212.5</v>
+        <v>284.02</v>
       </c>
       <c r="AQ7" t="n">
-        <v>235.4656</v>
+        <v>284.02</v>
       </c>
       <c r="AR7" t="n">
-        <v>-2.3</v>
+        <v>14.98</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.39</v>
+        <v>20.68</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 15.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>47.1</v>
+        <v>41.7</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 65.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.3%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1417508814848</v>
+        <v>1503640027136</v>
       </c>
       <c r="G8" t="n">
-        <v>20.94</v>
+        <v>22.22</v>
       </c>
       <c r="H8" t="n">
-        <v>15.65</v>
+        <v>16.91</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,25 +1933,25 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>17.8</v>
+        <v>29.5</v>
       </c>
       <c r="P8" t="n">
-        <v>81.5</v>
+        <v>78.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>63.9</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>57</v>
+        <v>60.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>556.45</v>
+        <v>590.24</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.210000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.98</v>
+        <v>-2.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>-24.5</v>
+        <v>-17.47</v>
       </c>
       <c r="AA8" t="n">
-        <v>-19.7</v>
+        <v>-23.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>20.84</v>
+        <v>24.39</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.3</v>
+        <v>37.49</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>601.9891</v>
+        <v>601.7091</v>
       </c>
       <c r="AG8" t="n">
-        <v>633.5829</v>
+        <v>633.0014</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17.8</v>
+        <v>29.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>63.9</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-7.57</v>
+        <v>-1.91</v>
       </c>
       <c r="AS8" t="n">
-        <v>-12.18</v>
+        <v>-6.76</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 7.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>36.5</v>
+        <v>41.8</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 57.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.9%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1228960956416</v>
+        <v>1272070275072</v>
       </c>
       <c r="G10" t="n">
-        <v>288.12</v>
+        <v>295.49</v>
       </c>
       <c r="H10" t="n">
-        <v>139.84</v>
+        <v>145.13</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>44.8</v>
+        <v>49.5</v>
       </c>
       <c r="S10" t="n">
-        <v>25.8</v>
+        <v>27</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>311.415</v>
+        <v>322.08</v>
       </c>
       <c r="X10" t="n">
-        <v>-26.78</v>
+        <v>-18.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>-18.4</v>
+        <v>-17.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>-25.24</v>
+        <v>-25.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.39</v>
+        <v>4.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.22</v>
+        <v>8.31</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.47</v>
+        <v>58.56</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>390.7647</v>
+        <v>388.857</v>
       </c>
       <c r="AG10" t="n">
-        <v>411.6007</v>
+        <v>411.0639</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>44.8</v>
+        <v>49.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>419.77</v>
+        <v>407.76</v>
       </c>
       <c r="AQ10" t="n">
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-20.31</v>
+        <v>-17.17</v>
       </c>
       <c r="AS10" t="n">
-        <v>-24.34</v>
+        <v>-21.65</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 20.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 17.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>12.1</v>
+        <v>14.2</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 25.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -20.3%.</t>
+          <t>TSLA: scenario base High Risk, score 27.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -17.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4568003379200</v>
+        <v>4618634919936</v>
       </c>
       <c r="G2" t="n">
-        <v>18.73</v>
+        <v>18.93</v>
       </c>
       <c r="H2" t="n">
-        <v>25.35</v>
+        <v>25.63</v>
       </c>
       <c r="I2" t="n">
         <v>54.77</v>
@@ -741,25 +741,25 @@
         <v>18.86</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>75.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>70.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="R2" t="n">
-        <v>81.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="S2" t="n">
-        <v>75.7</v>
+        <v>76</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>373.51</v>
+        <v>377.65</v>
       </c>
       <c r="X2" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.1</v>
+        <v>-1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.65</v>
+        <v>10.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>95.19</v>
+        <v>100.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.62</v>
+        <v>42.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>30.51</v>
+        <v>30.48</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AF2" t="n">
-        <v>358.3802</v>
+        <v>358.1846</v>
       </c>
       <c r="AG2" t="n">
-        <v>326.6192</v>
+        <v>327.2547</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,13 +814,13 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>81.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="AM2" t="n">
         <v>751</v>
@@ -832,16 +832,16 @@
         <v>317.69</v>
       </c>
       <c r="AP2" t="n">
-        <v>373.51</v>
+        <v>377.65</v>
       </c>
       <c r="AQ2" t="n">
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.22</v>
+        <v>5.43</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.36</v>
+        <v>15.4</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>71.8</v>
+        <v>71.3</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.2%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.4%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4456437514240</v>
+        <v>4515147284480</v>
       </c>
       <c r="G3" t="n">
-        <v>34.84</v>
+        <v>35.52</v>
       </c>
       <c r="H3" t="n">
-        <v>31.9</v>
+        <v>32.52</v>
       </c>
       <c r="I3" t="n">
         <v>27.62</v>
@@ -940,25 +940,25 @@
         <v>78.44</v>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>83.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>42.2</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
         <v>41</v>
       </c>
       <c r="R3" t="n">
-        <v>76.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>71.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,27 +967,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>303.42</v>
+        <v>309.38</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.69</v>
+        <v>-1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.41</v>
+        <v>11.86</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.15</v>
+        <v>14.79</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.76</v>
+        <v>53.48</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.27</v>
+        <v>20.75</v>
       </c>
       <c r="AC3" t="n">
         <v>26.91</v>
@@ -996,13 +996,13 @@
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>309.5228</v>
+        <v>309.6106</v>
       </c>
       <c r="AG3" t="n">
-        <v>277.943</v>
+        <v>278.2467</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>83.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>41</v>
       </c>
       <c r="AL3" t="n">
-        <v>76.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AM3" t="n">
         <v>751</v>
@@ -1037,10 +1037,10 @@
         <v>340.08</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.97</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.17</v>
+        <v>11.19</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>70</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 71.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.0%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.1%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3621067423744</v>
+        <v>3659383177216</v>
       </c>
       <c r="G4" t="n">
-        <v>27.18</v>
+        <v>27.47</v>
       </c>
       <c r="H4" t="n">
-        <v>20.78</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
         <v>40.3</v>
@@ -1139,25 +1139,25 @@
         <v>29.12</v>
       </c>
       <c r="M4" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>81.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="P4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="Q4" t="n">
         <v>41.1</v>
       </c>
       <c r="R4" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="S4" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>487.65</v>
+        <v>492.81</v>
       </c>
       <c r="X4" t="n">
-        <v>24.88</v>
+        <v>27.43</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.92</v>
+        <v>19.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.84</v>
+        <v>16.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>-7.86</v>
+        <v>-5.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.16</v>
+        <v>15.29</v>
       </c>
       <c r="AC4" t="n">
         <v>26.11</v>
@@ -1195,13 +1195,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>400.7368</v>
+        <v>402.2112</v>
       </c>
       <c r="AG4" t="n">
-        <v>432.1426</v>
+        <v>432.0556</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,13 +1212,13 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="AK4" t="n">
         <v>41.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AM4" t="n">
         <v>751</v>
@@ -1230,16 +1230,16 @@
         <v>352.83</v>
       </c>
       <c r="AP4" t="n">
-        <v>487.65</v>
+        <v>492.81</v>
       </c>
       <c r="AQ4" t="n">
-        <v>487.65</v>
+        <v>492.81</v>
       </c>
       <c r="AR4" t="n">
-        <v>21.69</v>
+        <v>22.53</v>
       </c>
       <c r="AS4" t="n">
-        <v>12.84</v>
+        <v>14.06</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 21.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 22.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>26.3</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 69.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.7%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 70.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 22.5%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 487.65 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 492.81 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5005027311616</v>
+        <v>5133398704128</v>
       </c>
       <c r="G5" t="n">
-        <v>31.69</v>
+        <v>32.51</v>
       </c>
       <c r="H5" t="n">
-        <v>16.03</v>
+        <v>16.44</v>
       </c>
       <c r="I5" t="n">
         <v>62.97</v>
@@ -1344,19 +1344,19 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>65</v>
+        <v>73.8</v>
       </c>
       <c r="P5" t="n">
-        <v>68.5</v>
+        <v>67</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="R5" t="n">
         <v>82.8</v>
       </c>
       <c r="S5" t="n">
-        <v>68.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>206.64</v>
+        <v>211.94</v>
       </c>
       <c r="X5" t="n">
-        <v>6.06</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.25</v>
+        <v>6.91</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.25</v>
+        <v>14.32</v>
       </c>
       <c r="AA5" t="n">
-        <v>16.33</v>
+        <v>22.16</v>
       </c>
       <c r="AB5" t="n">
-        <v>67.29000000000001</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>47.12</v>
+        <v>47.13</v>
       </c>
       <c r="AD5" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>205.7924</v>
+        <v>205.6461</v>
       </c>
       <c r="AG5" t="n">
-        <v>193.0622</v>
+        <v>193.2239</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>65</v>
+        <v>73.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="AL5" t="n">
         <v>82.8</v>
@@ -1435,10 +1435,10 @@
         <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.41</v>
+        <v>3.06</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.03</v>
+        <v>9.69</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>51.4</v>
+        <v>53.5</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 70.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>545268334592</v>
+        <v>565625618432</v>
       </c>
       <c r="G6" t="n">
-        <v>55.91</v>
+        <v>57.95</v>
       </c>
       <c r="H6" t="n">
-        <v>27.79</v>
+        <v>28.82</v>
       </c>
       <c r="I6" t="n">
         <v>30.11</v>
@@ -1537,7 +1537,7 @@
         <v>9.09</v>
       </c>
       <c r="M6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1546,16 +1546,16 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>24.6</v>
+        <v>23.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="R6" t="n">
-        <v>68.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="S6" t="n">
-        <v>67.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1419.6</v>
+        <v>1472.6</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.04</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.91</v>
+        <v>13.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.82</v>
+        <v>29.72</v>
       </c>
       <c r="AA6" t="n">
-        <v>141</v>
+        <v>142.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>32.51</v>
+        <v>34</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.39</v>
+        <v>39.45</v>
       </c>
       <c r="AD6" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AF6" t="n">
-        <v>1535.4151</v>
+        <v>1537.1045</v>
       </c>
       <c r="AG6" t="n">
-        <v>1206.986</v>
+        <v>1209.8832</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>68.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="AM6" t="n">
         <v>765</v>
@@ -1634,10 +1634,10 @@
         <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>-7.54</v>
+        <v>-4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>17.62</v>
+        <v>21.71</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 7.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>53</v>
+        <v>54.3</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.5%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.2%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3055234318336</v>
+        <v>2992339156992</v>
       </c>
       <c r="G7" t="n">
-        <v>22.83</v>
+        <v>22.3</v>
       </c>
       <c r="H7" t="n">
-        <v>27.53</v>
+        <v>26.89</v>
       </c>
       <c r="I7" t="n">
         <v>17.44</v>
@@ -1740,19 +1740,19 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>74.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>62.4</v>
+        <v>63.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="R7" t="n">
-        <v>38.8</v>
+        <v>49.8</v>
       </c>
       <c r="S7" t="n">
-        <v>65.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>284.02</v>
+        <v>277.42</v>
       </c>
       <c r="X7" t="n">
-        <v>17.04</v>
+        <v>13.62</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.87</v>
+        <v>1.97</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.69</v>
+        <v>14.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.32</v>
+        <v>29.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>26.92</v>
+        <v>25.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="AD7" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>247.0092</v>
+        <v>247.1884</v>
       </c>
       <c r="AG7" t="n">
-        <v>235.3503</v>
+        <v>235.6596</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,13 +1807,13 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>74.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AK7" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>38.8</v>
+        <v>49.8</v>
       </c>
       <c r="AM7" t="n">
         <v>751</v>
@@ -1831,10 +1831,10 @@
         <v>284.02</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.98</v>
+        <v>12.23</v>
       </c>
       <c r="AS7" t="n">
-        <v>20.68</v>
+        <v>17.72</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 15.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 12.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>41.7</v>
+        <v>48.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.7, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1503640027136</v>
+        <v>1497780846592</v>
       </c>
       <c r="G8" t="n">
-        <v>22.22</v>
+        <v>22.14</v>
       </c>
       <c r="H8" t="n">
-        <v>16.91</v>
+        <v>16.85</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,22 +1933,22 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="P8" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>72.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="S8" t="n">
         <v>60.2</v>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>590.24</v>
+        <v>587.9400000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>1.26</v>
+        <v>-2.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.95</v>
+        <v>-3.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>-17.47</v>
+        <v>-16.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.44</v>
+        <v>-21.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.39</v>
+        <v>23.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.49</v>
+        <v>37.48</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>601.7091</v>
+        <v>601.3315</v>
       </c>
       <c r="AG8" t="n">
-        <v>633.0014</v>
+        <v>632.3626</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="AK8" t="n">
         <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>72.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AM8" t="n">
         <v>751</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.91</v>
+        <v>-2.23</v>
       </c>
       <c r="AS8" t="n">
-        <v>-6.76</v>
+        <v>-7.02</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.9%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.2%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1272070275072</v>
+        <v>1292884377600</v>
       </c>
       <c r="G10" t="n">
-        <v>295.49</v>
+        <v>297.59</v>
       </c>
       <c r="H10" t="n">
-        <v>145.13</v>
+        <v>147.51</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>11.4</v>
+        <v>15.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>49.5</v>
+        <v>52.1</v>
       </c>
       <c r="S10" t="n">
-        <v>27</v>
+        <v>28.3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,22 +2309,22 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>322.08</v>
+        <v>327.35</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.14</v>
+        <v>-22.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>-17.59</v>
+        <v>-16.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>-25.17</v>
+        <v>-22.39</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.48</v>
+        <v>8.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.31</v>
+        <v>9.25</v>
       </c>
       <c r="AC10" t="n">
         <v>58.56</v>
@@ -2333,13 +2333,13 @@
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>388.857</v>
+        <v>387.047</v>
       </c>
       <c r="AG10" t="n">
-        <v>411.0639</v>
+        <v>410.5249</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11.4</v>
+        <v>15.4</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>49.5</v>
+        <v>52.1</v>
       </c>
       <c r="AM10" t="n">
         <v>751</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-17.17</v>
+        <v>-15.42</v>
       </c>
       <c r="AS10" t="n">
-        <v>-21.65</v>
+        <v>-20.26</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 17.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 15.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>14.2</v>
+        <v>16.1</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 27.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -17.2%.</t>
+          <t>TSLA: scenario base High Risk, score 28.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -15.4%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4618634919936</v>
+        <v>4432495378432</v>
       </c>
       <c r="G2" t="n">
-        <v>18.93</v>
+        <v>18.18</v>
       </c>
       <c r="H2" t="n">
-        <v>25.63</v>
+        <v>24.6</v>
       </c>
       <c r="I2" t="n">
         <v>54.77</v>
@@ -741,25 +741,25 @@
         <v>18.86</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>79.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>69.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="R2" t="n">
-        <v>77</v>
+        <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>76</v>
+        <v>73.8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>377.65</v>
+        <v>362.43</v>
       </c>
       <c r="X2" t="n">
-        <v>3.05</v>
+        <v>-1.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.4</v>
+        <v>-6.64</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.02</v>
+        <v>6.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>100.25</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>42.89</v>
+        <v>40.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>30.48</v>
+        <v>30.56</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AF2" t="n">
-        <v>358.1846</v>
+        <v>357.7784</v>
       </c>
       <c r="AG2" t="n">
-        <v>327.2547</v>
+        <v>327.812</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>79.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>77</v>
+        <v>82.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
         <v>317.69</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.4</v>
+        <v>10.56</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>71.3</v>
+        <v>69.8</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.4%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 73.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.3%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4515147284480</v>
+        <v>4538790051840</v>
       </c>
       <c r="G3" t="n">
-        <v>35.52</v>
+        <v>35.67</v>
       </c>
       <c r="H3" t="n">
-        <v>32.52</v>
+        <v>32.69</v>
       </c>
       <c r="I3" t="n">
         <v>27.62</v>
@@ -940,25 +940,25 @@
         <v>78.44</v>
       </c>
       <c r="M3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>40.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q3" t="n">
         <v>41</v>
       </c>
       <c r="R3" t="n">
-        <v>79.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>72.7</v>
+        <v>73.2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,57 +972,57 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>309.38</v>
+        <v>311</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.05</v>
+        <v>0.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.86</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.79</v>
+        <v>15.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>53.48</v>
+        <v>53.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.75</v>
+        <v>20.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.91</v>
+        <v>26.89</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>309.6106</v>
+        <v>309.6542</v>
       </c>
       <c r="AG3" t="n">
-        <v>278.2467</v>
+        <v>278.568</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AK3" t="n">
         <v>41</v>
       </c>
       <c r="AL3" t="n">
-        <v>79.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>303.42</v>
@@ -1037,10 +1037,10 @@
         <v>340.08</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.19</v>
+        <v>11.64</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>72.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.1%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3659383177216</v>
+        <v>5309727768576</v>
       </c>
       <c r="G4" t="n">
-        <v>27.47</v>
+        <v>33.57</v>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>17.01</v>
       </c>
       <c r="I4" t="n">
-        <v>40.3</v>
+        <v>62.97</v>
       </c>
       <c r="J4" t="n">
-        <v>34.04</v>
+        <v>114.29</v>
       </c>
       <c r="K4" t="n">
-        <v>17.7</v>
+        <v>85.2</v>
       </c>
       <c r="L4" t="n">
-        <v>29.12</v>
+        <v>6.55</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>86</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>66.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.1</v>
+        <v>13.9</v>
       </c>
       <c r="R4" t="n">
-        <v>8.6</v>
+        <v>72.5</v>
       </c>
       <c r="S4" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,42 +1166,42 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>492.81</v>
+        <v>219.22</v>
       </c>
       <c r="X4" t="n">
-        <v>27.43</v>
+        <v>11.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.4</v>
+        <v>11.69</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.92</v>
+        <v>21.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>-5.22</v>
+        <v>21.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.29</v>
+        <v>69.58</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.11</v>
+        <v>47.13</v>
       </c>
       <c r="AD4" t="n">
-        <v>-34.5</v>
+        <v>-36.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.59</v>
+        <v>1.48</v>
       </c>
       <c r="AF4" t="n">
-        <v>402.2112</v>
+        <v>205.7289</v>
       </c>
       <c r="AG4" t="n">
-        <v>432.0556</v>
+        <v>193.4121</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,52 +1212,52 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>86</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>41.1</v>
+        <v>13.9</v>
       </c>
       <c r="AL4" t="n">
-        <v>8.6</v>
+        <v>72.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>381.58</v>
+        <v>190.01</v>
       </c>
       <c r="AO4" t="n">
-        <v>352.83</v>
+        <v>190.01</v>
       </c>
       <c r="AP4" t="n">
-        <v>492.81</v>
+        <v>219.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>492.81</v>
+        <v>235.4656</v>
       </c>
       <c r="AR4" t="n">
-        <v>22.53</v>
+        <v>6.56</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.06</v>
+        <v>13.34</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 22.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>53.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 70.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 22.5%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.6%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 492.81 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1313,50 +1313,50 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5133398704128</v>
+        <v>3619656564736</v>
       </c>
       <c r="G5" t="n">
-        <v>32.51</v>
+        <v>25.9</v>
       </c>
       <c r="H5" t="n">
-        <v>16.44</v>
+        <v>20.77</v>
       </c>
       <c r="I5" t="n">
-        <v>62.97</v>
+        <v>40.3</v>
       </c>
       <c r="J5" t="n">
-        <v>114.29</v>
+        <v>34.04</v>
       </c>
       <c r="K5" t="n">
-        <v>85.2</v>
+        <v>17.7</v>
       </c>
       <c r="L5" t="n">
-        <v>6.55</v>
+        <v>29.12</v>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>73.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>67</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.9</v>
+        <v>41.1</v>
       </c>
       <c r="R5" t="n">
-        <v>82.8</v>
+        <v>15.6</v>
       </c>
       <c r="S5" t="n">
-        <v>70.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,42 +1365,42 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>211.94</v>
+        <v>487.46</v>
       </c>
       <c r="X5" t="n">
-        <v>8.380000000000001</v>
+        <v>25.36</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.91</v>
+        <v>18.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.32</v>
+        <v>19.07</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.16</v>
+        <v>-8.27</v>
       </c>
       <c r="AB5" t="n">
-        <v>67.79000000000001</v>
+        <v>14.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>47.13</v>
+        <v>26.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>-36.88</v>
+        <v>-34.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.44</v>
+        <v>0.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>205.6461</v>
+        <v>403.589</v>
       </c>
       <c r="AG5" t="n">
-        <v>193.2239</v>
+        <v>431.951</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,52 +1411,52 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>73.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.9</v>
+        <v>41.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>82.8</v>
+        <v>15.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>190.01</v>
+        <v>381.58</v>
       </c>
       <c r="AO5" t="n">
-        <v>190.01</v>
+        <v>352.83</v>
       </c>
       <c r="AP5" t="n">
-        <v>212.5</v>
+        <v>492.81</v>
       </c>
       <c r="AQ5" t="n">
-        <v>235.4656</v>
+        <v>492.81</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.06</v>
+        <v>20.78</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.69</v>
+        <v>12.85</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 20.8% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>53.5</v>
+        <v>30.3</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 70.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.1%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 71.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.8%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 492.81 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>565625618432</v>
+        <v>563013812224</v>
       </c>
       <c r="G6" t="n">
-        <v>57.95</v>
+        <v>57.53</v>
       </c>
       <c r="H6" t="n">
-        <v>28.82</v>
+        <v>28.69</v>
       </c>
       <c r="I6" t="n">
         <v>30.11</v>
@@ -1537,7 +1537,7 @@
         <v>9.09</v>
       </c>
       <c r="M6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1546,13 +1546,13 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q6" t="n">
         <v>16.8</v>
       </c>
       <c r="R6" t="n">
-        <v>73.5</v>
+        <v>72.7</v>
       </c>
       <c r="S6" t="n">
         <v>67.59999999999999</v>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1472.6</v>
+        <v>1465.8</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.41</v>
+        <v>12.89</v>
       </c>
       <c r="Z6" t="n">
-        <v>29.72</v>
+        <v>29.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>142.71</v>
+        <v>141.59</v>
       </c>
       <c r="AB6" t="n">
-        <v>34</v>
+        <v>33.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.45</v>
+        <v>39.47</v>
       </c>
       <c r="AD6" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1537.1045</v>
+        <v>1537.7365</v>
       </c>
       <c r="AG6" t="n">
-        <v>1209.8832</v>
+        <v>1210.0412</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         <v>16.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>73.5</v>
+        <v>72.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AN6" t="n">
         <v>1362.2</v>
@@ -1634,10 +1634,10 @@
         <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.2</v>
+        <v>-4.68</v>
       </c>
       <c r="AS6" t="n">
-        <v>21.71</v>
+        <v>21.14</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 4.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.7% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.7%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2992339156992</v>
+        <v>2940888154112</v>
       </c>
       <c r="G7" t="n">
-        <v>22.3</v>
+        <v>21.93</v>
       </c>
       <c r="H7" t="n">
-        <v>26.89</v>
+        <v>26.34</v>
       </c>
       <c r="I7" t="n">
         <v>17.44</v>
@@ -1740,19 +1740,19 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>68.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="P7" t="n">
-        <v>63.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>36.5</v>
       </c>
       <c r="R7" t="n">
-        <v>49.8</v>
+        <v>57.8</v>
       </c>
       <c r="S7" t="n">
-        <v>65.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>277.42</v>
+        <v>272.65</v>
       </c>
       <c r="X7" t="n">
-        <v>13.62</v>
+        <v>10.84</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.97</v>
+        <v>-0.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.18</v>
+        <v>14.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>29.18</v>
+        <v>28.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>25.13</v>
+        <v>24.37</v>
       </c>
       <c r="AC7" t="n">
-        <v>32.3</v>
+        <v>32.29</v>
       </c>
       <c r="AD7" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>247.1884</v>
+        <v>247.315</v>
       </c>
       <c r="AG7" t="n">
-        <v>235.6596</v>
+        <v>235.9505</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>68.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="AK7" t="n">
         <v>36.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>49.8</v>
+        <v>57.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
         <v>226.65</v>
@@ -1831,14 +1831,14 @@
         <v>284.02</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.23</v>
+        <v>10.24</v>
       </c>
       <c r="AS7" t="n">
-        <v>17.72</v>
+        <v>15.55</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 12.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>48.4</v>
+        <v>53.5</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.7, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1497780846592</v>
+        <v>1499895300096</v>
       </c>
       <c r="G8" t="n">
-        <v>22.14</v>
+        <v>22.16</v>
       </c>
       <c r="H8" t="n">
-        <v>16.85</v>
+        <v>16.76</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,25 +1933,25 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>29.7</v>
+        <v>31.6</v>
       </c>
       <c r="P8" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="Q8" t="n">
         <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="S8" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,25 +1965,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>587.9400000000001</v>
+        <v>588.77</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.06</v>
+        <v>-4.36</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.59</v>
+        <v>-2.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>-16.62</v>
+        <v>-14.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>-21.35</v>
+        <v>-23.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>23.45</v>
+        <v>23.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.48</v>
+        <v>37.45</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
@@ -1992,10 +1992,10 @@
         <v>0.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>601.3315</v>
+        <v>600.913</v>
       </c>
       <c r="AG8" t="n">
-        <v>632.3626</v>
+        <v>631.7554</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>29.7</v>
+        <v>31.6</v>
       </c>
       <c r="AK8" t="n">
         <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.23</v>
+        <v>-2.02</v>
       </c>
       <c r="AS8" t="n">
-        <v>-7.02</v>
+        <v>-6.8</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>41.7</v>
+        <v>42.3</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.0%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1292884377600</v>
+        <v>1269976924160</v>
       </c>
       <c r="G10" t="n">
-        <v>297.59</v>
+        <v>297.73</v>
       </c>
       <c r="H10" t="n">
-        <v>147.51</v>
+        <v>144.89</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>15.4</v>
+        <v>12.3</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
       <c r="S10" t="n">
-        <v>28.3</v>
+        <v>27.3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>327.35</v>
+        <v>321.55</v>
       </c>
       <c r="X10" t="n">
-        <v>-22.02</v>
+        <v>-20.19</v>
       </c>
       <c r="Y10" t="n">
-        <v>-16.6</v>
+        <v>-17.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>-22.39</v>
+        <v>-23.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.17</v>
+        <v>3.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.25</v>
+        <v>8.59</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.56</v>
+        <v>58.53</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>387.047</v>
+        <v>384.9578</v>
       </c>
       <c r="AG10" t="n">
-        <v>410.5249</v>
+        <v>409.9889</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.4</v>
+        <v>12.3</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-15.42</v>
+        <v>-16.47</v>
       </c>
       <c r="AS10" t="n">
-        <v>-20.26</v>
+        <v>-21.57</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 15.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 16.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>16.1</v>
+        <v>14.8</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 28.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -15.4%.</t>
+          <t>TSLA: scenario base High Risk, score 27.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -16.5%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4432495378432</v>
+        <v>4375259381760</v>
       </c>
       <c r="G2" t="n">
-        <v>18.18</v>
+        <v>17.95</v>
       </c>
       <c r="H2" t="n">
-        <v>24.6</v>
+        <v>24.28</v>
       </c>
       <c r="I2" t="n">
         <v>54.77</v>
@@ -741,16 +741,16 @@
         <v>18.86</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>66.40000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="P2" t="n">
-        <v>72</v>
+        <v>72.7</v>
       </c>
       <c r="Q2" t="n">
         <v>39.5</v>
@@ -759,7 +759,7 @@
         <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>73.8</v>
+        <v>72.7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>362.43</v>
+        <v>357.75</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.25</v>
+        <v>-1.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>-6.64</v>
+        <v>-10.07</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.83</v>
+        <v>7.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>86.34999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>40.86</v>
+        <v>40.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>30.56</v>
+        <v>30.55</v>
       </c>
       <c r="AD2" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AF2" t="n">
-        <v>357.7784</v>
+        <v>357.1604</v>
       </c>
       <c r="AG2" t="n">
-        <v>327.812</v>
+        <v>328.3367</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>66.40000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="AK2" t="n">
         <v>39.5</v>
@@ -823,7 +823,7 @@
         <v>82.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
         <v>317.69</v>
@@ -838,10 +838,10 @@
         <v>402.3797</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.3</v>
+        <v>0.17</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.56</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>69.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 73.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.3%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.2%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4538790051840</v>
+        <v>4559367831552</v>
       </c>
       <c r="G3" t="n">
-        <v>35.67</v>
+        <v>35.87</v>
       </c>
       <c r="H3" t="n">
-        <v>32.69</v>
+        <v>32.84</v>
       </c>
       <c r="I3" t="n">
         <v>27.62</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>86.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="P3" t="n">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="R3" t="n">
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>73.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,25 +972,25 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>311</v>
+        <v>312.41</v>
       </c>
       <c r="X3" t="n">
-        <v>0.11</v>
+        <v>-0.31</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.539999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.62</v>
+        <v>13.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>53.55</v>
+        <v>54.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.93</v>
+        <v>21.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.89</v>
+        <v>26.88</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
@@ -999,10 +999,10 @@
         <v>0.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>309.6542</v>
+        <v>309.7358</v>
       </c>
       <c r="AG3" t="n">
-        <v>278.568</v>
+        <v>278.8721</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>86.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AK3" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="AL3" t="n">
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
         <v>303.42</v>
@@ -1037,10 +1037,10 @@
         <v>340.08</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.64</v>
+        <v>12.03</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>72.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.9%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5309727768576</v>
+        <v>3711733071872</v>
       </c>
       <c r="G4" t="n">
-        <v>33.57</v>
+        <v>27.86</v>
       </c>
       <c r="H4" t="n">
-        <v>17.01</v>
+        <v>21.3</v>
       </c>
       <c r="I4" t="n">
-        <v>62.97</v>
+        <v>40.3</v>
       </c>
       <c r="J4" t="n">
-        <v>114.29</v>
+        <v>34.04</v>
       </c>
       <c r="K4" t="n">
-        <v>85.2</v>
+        <v>17.7</v>
       </c>
       <c r="L4" t="n">
-        <v>6.55</v>
+        <v>29.12</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>84.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="P4" t="n">
-        <v>64.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.9</v>
+        <v>41.1</v>
       </c>
       <c r="R4" t="n">
-        <v>72.5</v>
+        <v>5.4</v>
       </c>
       <c r="S4" t="n">
-        <v>71.8</v>
+        <v>71.3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,42 +1166,42 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>219.22</v>
+        <v>499.86</v>
       </c>
       <c r="X4" t="n">
-        <v>11.32</v>
+        <v>30.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.69</v>
+        <v>21.01</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.71</v>
+        <v>21.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.95</v>
+        <v>-4.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>69.58</v>
+        <v>15.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>47.13</v>
+        <v>26.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>-36.88</v>
+        <v>-34.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.48</v>
+        <v>0.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>205.7289</v>
+        <v>405.2656</v>
       </c>
       <c r="AG4" t="n">
-        <v>193.4121</v>
+        <v>431.8985</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,52 +1212,52 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>84.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="AK4" t="n">
-        <v>13.9</v>
+        <v>41.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>72.5</v>
+        <v>5.4</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN4" t="n">
-        <v>190.01</v>
+        <v>381.58</v>
       </c>
       <c r="AO4" t="n">
-        <v>190.01</v>
+        <v>352.83</v>
       </c>
       <c r="AP4" t="n">
-        <v>219.22</v>
+        <v>499.86</v>
       </c>
       <c r="AQ4" t="n">
-        <v>235.4656</v>
+        <v>499.86</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.56</v>
+        <v>23.34</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.34</v>
+        <v>15.74</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 23.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>53.3</v>
+        <v>23.8</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.6%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 71.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 499.86 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1313,50 +1313,50 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3619656564736</v>
+        <v>5304156684288</v>
       </c>
       <c r="G5" t="n">
-        <v>25.9</v>
+        <v>33.54</v>
       </c>
       <c r="H5" t="n">
-        <v>20.77</v>
+        <v>16.99</v>
       </c>
       <c r="I5" t="n">
-        <v>40.3</v>
+        <v>62.97</v>
       </c>
       <c r="J5" t="n">
-        <v>34.04</v>
+        <v>114.29</v>
       </c>
       <c r="K5" t="n">
-        <v>17.7</v>
+        <v>85.2</v>
       </c>
       <c r="L5" t="n">
-        <v>29.12</v>
+        <v>6.55</v>
       </c>
       <c r="M5" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>85.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="P5" t="n">
-        <v>68.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.1</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>15.6</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>71.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,42 +1365,42 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>487.46</v>
+        <v>218.99</v>
       </c>
       <c r="X5" t="n">
-        <v>25.36</v>
+        <v>7.28</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.75</v>
+        <v>5.49</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.07</v>
+        <v>25.87</v>
       </c>
       <c r="AA5" t="n">
-        <v>-8.27</v>
+        <v>23.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.85</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>26.1</v>
+        <v>47.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>-34.5</v>
+        <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.57</v>
+        <v>1.47</v>
       </c>
       <c r="AF5" t="n">
-        <v>403.589</v>
+        <v>205.8165</v>
       </c>
       <c r="AG5" t="n">
-        <v>431.951</v>
+        <v>193.5921</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,52 +1411,52 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>85.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="AK5" t="n">
-        <v>41.1</v>
+        <v>14</v>
       </c>
       <c r="AL5" t="n">
-        <v>15.6</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
-        <v>381.58</v>
+        <v>190.01</v>
       </c>
       <c r="AO5" t="n">
-        <v>352.83</v>
+        <v>190.01</v>
       </c>
       <c r="AP5" t="n">
-        <v>492.81</v>
+        <v>219.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>492.81</v>
+        <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>20.78</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>12.85</v>
+        <v>13.12</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 20.8% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>30.3</v>
+        <v>51.9</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 71.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.8%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 70.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 492.81 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>563013812224</v>
+        <v>573845405696</v>
       </c>
       <c r="G6" t="n">
-        <v>57.53</v>
+        <v>58.91</v>
       </c>
       <c r="H6" t="n">
-        <v>28.69</v>
+        <v>29.05</v>
       </c>
       <c r="I6" t="n">
         <v>30.11</v>
@@ -1537,7 +1537,7 @@
         <v>9.09</v>
       </c>
       <c r="M6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1546,7 +1546,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q6" t="n">
         <v>16.8</v>
@@ -1555,7 +1555,7 @@
         <v>72.7</v>
       </c>
       <c r="S6" t="n">
-        <v>67.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.7%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.7%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2940888154112</v>
+        <v>2936681791488</v>
       </c>
       <c r="G7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="H7" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
       <c r="I7" t="n">
         <v>17.44</v>
@@ -1740,19 +1740,19 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>65.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="P7" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="R7" t="n">
-        <v>57.8</v>
+        <v>58.7</v>
       </c>
       <c r="S7" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,25 +1766,25 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>272.65</v>
+        <v>272.26</v>
       </c>
       <c r="X7" t="n">
-        <v>10.84</v>
+        <v>11.76</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.33</v>
+        <v>-0.99</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.26</v>
+        <v>16.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>28.82</v>
+        <v>27.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.37</v>
+        <v>24.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>32.29</v>
+        <v>32.27</v>
       </c>
       <c r="AD7" t="n">
         <v>-30.88</v>
@@ -1793,10 +1793,10 @@
         <v>0.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>247.315</v>
+        <v>247.4544</v>
       </c>
       <c r="AG7" t="n">
-        <v>235.9505</v>
+        <v>236.2466</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AK7" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>57.8</v>
+        <v>58.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
         <v>226.65</v>
@@ -1831,10 +1831,10 @@
         <v>284.02</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.24</v>
+        <v>10.02</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.55</v>
+        <v>15.24</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 10.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.0% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>53.5</v>
+        <v>54.3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1499895300096</v>
+        <v>1502773903360</v>
       </c>
       <c r="G8" t="n">
-        <v>22.16</v>
+        <v>22.22</v>
       </c>
       <c r="H8" t="n">
-        <v>16.76</v>
+        <v>16.79</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,25 +1933,25 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>31.6</v>
+        <v>32.3</v>
       </c>
       <c r="P8" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="R8" t="n">
-        <v>72.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>60.7</v>
+        <v>60.9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,25 +1965,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>588.77</v>
+        <v>589.9</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.36</v>
+        <v>-2.19</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.59</v>
+        <v>-3.66</v>
       </c>
       <c r="Z8" t="n">
-        <v>-14.73</v>
+        <v>-11.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.92</v>
+        <v>-22.48</v>
       </c>
       <c r="AB8" t="n">
-        <v>23.48</v>
+        <v>23.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.45</v>
+        <v>37.43</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
@@ -1992,10 +1992,10 @@
         <v>0.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>600.913</v>
+        <v>600.4756</v>
       </c>
       <c r="AG8" t="n">
-        <v>631.7554</v>
+        <v>631.1296</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>31.6</v>
+        <v>32.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>72.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.02</v>
+        <v>-1.76</v>
       </c>
       <c r="AS8" t="n">
-        <v>-6.8</v>
+        <v>-6.53</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.0%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.8%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1269976924160</v>
+        <v>1261998964736</v>
       </c>
       <c r="G10" t="n">
-        <v>297.73</v>
+        <v>293.15</v>
       </c>
       <c r="H10" t="n">
-        <v>144.89</v>
+        <v>143.98</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>12.3</v>
+        <v>10.3</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>50.5</v>
       </c>
       <c r="S10" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>321.55</v>
+        <v>319.53</v>
       </c>
       <c r="X10" t="n">
-        <v>-20.19</v>
+        <v>-18.91</v>
       </c>
       <c r="Y10" t="n">
-        <v>-17.42</v>
+        <v>-19.86</v>
       </c>
       <c r="Z10" t="n">
-        <v>-23.8</v>
+        <v>-21.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.59</v>
+        <v>8.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.53</v>
+        <v>58.49</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>384.9578</v>
+        <v>382.6766</v>
       </c>
       <c r="AG10" t="n">
-        <v>409.9889</v>
+        <v>409.39</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12.3</v>
+        <v>10.3</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>50.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2374,10 +2374,10 @@
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-16.47</v>
+        <v>-16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>-21.57</v>
+        <v>-21.95</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 27.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -16.5%.</t>
+          <t>TSLA: scenario base High Risk, score 26.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -16.5%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -696,12 +696,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -711,55 +711,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4375259381760</v>
+        <v>4572283666432</v>
       </c>
       <c r="G2" t="n">
-        <v>17.95</v>
+        <v>35.93</v>
       </c>
       <c r="H2" t="n">
-        <v>24.28</v>
+        <v>32.93</v>
       </c>
       <c r="I2" t="n">
-        <v>54.77</v>
+        <v>27.62</v>
       </c>
       <c r="J2" t="n">
-        <v>48.68</v>
+        <v>148.75</v>
       </c>
       <c r="K2" t="n">
-        <v>24.2</v>
+        <v>16.4</v>
       </c>
       <c r="L2" t="n">
-        <v>18.86</v>
+        <v>78.44</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>61.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>72.7</v>
+        <v>39.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.5</v>
+        <v>41.1</v>
       </c>
       <c r="R2" t="n">
         <v>82.8</v>
       </c>
       <c r="S2" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,42 +768,42 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>357.75</v>
+        <v>313.2801</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.15</v>
+        <v>-0.93</v>
       </c>
       <c r="Y2" t="n">
-        <v>-10.07</v>
+        <v>9.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.56</v>
+        <v>13.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>84.3</v>
+        <v>47.49</v>
       </c>
       <c r="AB2" t="n">
-        <v>40.19</v>
+        <v>21.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>30.55</v>
+        <v>26.86</v>
       </c>
       <c r="AD2" t="n">
-        <v>-29.81</v>
+        <v>-33.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.32</v>
+        <v>0.79</v>
       </c>
       <c r="AF2" t="n">
-        <v>357.1604</v>
+        <v>309.7844</v>
       </c>
       <c r="AG2" t="n">
-        <v>328.3367</v>
+        <v>279.131</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,34 +814,34 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>61.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>39.5</v>
+        <v>41.1</v>
       </c>
       <c r="AL2" t="n">
         <v>82.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN2" t="n">
-        <v>317.69</v>
+        <v>303.42</v>
       </c>
       <c r="AO2" t="n">
-        <v>317.69</v>
+        <v>275.15</v>
       </c>
       <c r="AP2" t="n">
-        <v>377.65</v>
+        <v>340.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>402.3797</v>
+        <v>340.08</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.17</v>
+        <v>1.13</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.960000000000001</v>
+        <v>12.24</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>68.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,17 +868,17 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.2%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 340.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 275.15 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -888,19 +888,19 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,50 +915,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4559367831552</v>
+        <v>3726213120000</v>
       </c>
       <c r="G3" t="n">
-        <v>35.87</v>
+        <v>27.97</v>
       </c>
       <c r="H3" t="n">
-        <v>32.84</v>
+        <v>21.38</v>
       </c>
       <c r="I3" t="n">
-        <v>27.62</v>
+        <v>40.3</v>
       </c>
       <c r="J3" t="n">
-        <v>148.75</v>
+        <v>34.04</v>
       </c>
       <c r="K3" t="n">
-        <v>16.4</v>
+        <v>17.7</v>
       </c>
       <c r="L3" t="n">
-        <v>78.44</v>
+        <v>29.12</v>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>83.8</v>
+        <v>93.2</v>
       </c>
       <c r="P3" t="n">
-        <v>39.6</v>
+        <v>65.2</v>
       </c>
       <c r="Q3" t="n">
         <v>41.1</v>
       </c>
       <c r="R3" t="n">
-        <v>82.8</v>
+        <v>5.6</v>
       </c>
       <c r="S3" t="n">
-        <v>72.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -967,42 +967,42 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>312.41</v>
+        <v>501.81</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.31</v>
+        <v>30.56</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.76</v>
+        <v>19.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.2</v>
+        <v>28.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>54.57</v>
+        <v>-3.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>21.09</v>
+        <v>15.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.88</v>
+        <v>26.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33.36</v>
+        <v>-34.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="AF3" t="n">
-        <v>309.7358</v>
+        <v>407.0484</v>
       </c>
       <c r="AG3" t="n">
-        <v>278.8721</v>
+        <v>431.8399</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,38 +1013,38 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>83.8</v>
+        <v>93.2</v>
       </c>
       <c r="AK3" t="n">
         <v>41.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>82.8</v>
+        <v>5.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN3" t="n">
-        <v>303.42</v>
+        <v>381.58</v>
       </c>
       <c r="AO3" t="n">
-        <v>275.15</v>
+        <v>352.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>340.08</v>
+        <v>501.81</v>
       </c>
       <c r="AQ3" t="n">
-        <v>340.08</v>
+        <v>501.81</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.86</v>
+        <v>23.28</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.03</v>
+        <v>16.2</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 23.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>72.09999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.9%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 71.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.3%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 340.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 501.81 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 275.15 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,55 +1109,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3711733071872</v>
+        <v>4342238412800</v>
       </c>
       <c r="G4" t="n">
-        <v>27.86</v>
+        <v>17.81</v>
       </c>
       <c r="H4" t="n">
-        <v>21.3</v>
+        <v>24.1</v>
       </c>
       <c r="I4" t="n">
-        <v>40.3</v>
+        <v>54.77</v>
       </c>
       <c r="J4" t="n">
-        <v>34.04</v>
+        <v>48.68</v>
       </c>
       <c r="K4" t="n">
-        <v>17.7</v>
+        <v>24.2</v>
       </c>
       <c r="L4" t="n">
-        <v>29.12</v>
+        <v>18.86</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>91</v>
+        <v>59.7</v>
       </c>
       <c r="P4" t="n">
-        <v>65.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="R4" t="n">
-        <v>5.4</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>71.3</v>
+        <v>71</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,79 +1171,79 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>499.86</v>
+        <v>355.03</v>
       </c>
       <c r="X4" t="n">
-        <v>30.4</v>
+        <v>-1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>21.01</v>
+        <v>-10.74</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.22</v>
+        <v>7.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4.53</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.8</v>
+        <v>39.77</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.12</v>
+        <v>30.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>-34.5</v>
+        <v>-29.81</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>405.2656</v>
+        <v>356.4891</v>
       </c>
       <c r="AG4" t="n">
-        <v>431.8985</v>
+        <v>328.8316</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91</v>
+        <v>59.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.4</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN4" t="n">
-        <v>381.58</v>
+        <v>317.69</v>
       </c>
       <c r="AO4" t="n">
-        <v>352.83</v>
+        <v>317.69</v>
       </c>
       <c r="AP4" t="n">
-        <v>499.86</v>
+        <v>377.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>499.86</v>
+        <v>402.3797</v>
       </c>
       <c r="AR4" t="n">
-        <v>23.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.74</v>
+        <v>7.97</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1253,11 +1253,11 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 23.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>23.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 71.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.3%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 71.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.4%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 499.86 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5304156684288</v>
+        <v>5396438712320</v>
       </c>
       <c r="G5" t="n">
-        <v>33.54</v>
+        <v>34.12</v>
       </c>
       <c r="H5" t="n">
-        <v>16.99</v>
+        <v>17.28</v>
       </c>
       <c r="I5" t="n">
         <v>62.97</v>
@@ -1344,19 +1344,19 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>79</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>65</v>
+        <v>63.9</v>
       </c>
       <c r="Q5" t="n">
         <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>73.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="S5" t="n">
-        <v>70.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>218.99</v>
+        <v>222.8102</v>
       </c>
       <c r="X5" t="n">
-        <v>7.28</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>25.87</v>
+        <v>29.79</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.01</v>
+        <v>24.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>69.40000000000001</v>
+        <v>70.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>47.1</v>
+        <v>47.08</v>
       </c>
       <c r="AD5" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AF5" t="n">
-        <v>205.8165</v>
+        <v>206.0257</v>
       </c>
       <c r="AG5" t="n">
-        <v>193.5921</v>
+        <v>193.7941</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,16 +1411,16 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>79</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AK5" t="n">
         <v>14</v>
       </c>
       <c r="AL5" t="n">
-        <v>73.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN5" t="n">
         <v>190.01</v>
@@ -1429,16 +1429,16 @@
         <v>190.01</v>
       </c>
       <c r="AP5" t="n">
-        <v>219.22</v>
+        <v>222.795</v>
       </c>
       <c r="AQ5" t="n">
         <v>235.4656</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.4</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>13.12</v>
+        <v>14.96</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1452,11 +1452,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>51.9</v>
+        <v>48.4</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 70.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 70.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>573845405696</v>
+        <v>575765872640</v>
       </c>
       <c r="G6" t="n">
-        <v>58.91</v>
+        <v>59.02</v>
       </c>
       <c r="H6" t="n">
-        <v>29.05</v>
+        <v>29.15</v>
       </c>
       <c r="I6" t="n">
         <v>30.11</v>
@@ -1537,7 +1537,7 @@
         <v>9.09</v>
       </c>
       <c r="M6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1546,16 +1546,16 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="R6" t="n">
-        <v>72.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1465.8</v>
+        <v>1499</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.880000000000001</v>
+        <v>-6.36</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.89</v>
+        <v>18.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>29.12</v>
+        <v>24.84</v>
       </c>
       <c r="AA6" t="n">
-        <v>141.59</v>
+        <v>138.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>33.55</v>
+        <v>34.39</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.47</v>
+        <v>39.41</v>
       </c>
       <c r="AD6" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="AF6" t="n">
-        <v>1537.7365</v>
+        <v>1543.3364</v>
       </c>
       <c r="AG6" t="n">
-        <v>1210.0412</v>
+        <v>1219.0252</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>72.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="AN6" t="n">
         <v>1362.2</v>
@@ -1628,16 +1628,16 @@
         <v>1247.4977</v>
       </c>
       <c r="AP6" t="n">
-        <v>1600.8722</v>
+        <v>1596.4774</v>
       </c>
       <c r="AQ6" t="n">
         <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.68</v>
+        <v>-2.87</v>
       </c>
       <c r="AS6" t="n">
-        <v>21.14</v>
+        <v>22.97</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>prezzo 4.7% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.1</v>
+        <v>54.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.7%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.9%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2936681791488</v>
+        <v>2962460770304</v>
       </c>
       <c r="G7" t="n">
-        <v>21.9</v>
+        <v>22.08</v>
       </c>
       <c r="H7" t="n">
-        <v>26.36</v>
+        <v>26.59</v>
       </c>
       <c r="I7" t="n">
         <v>17.44</v>
@@ -1740,19 +1740,19 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>65.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="P7" t="n">
-        <v>65.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>36.6</v>
       </c>
       <c r="R7" t="n">
-        <v>58.7</v>
+        <v>54.9</v>
       </c>
       <c r="S7" t="n">
-        <v>66.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>272.26</v>
+        <v>274.65</v>
       </c>
       <c r="X7" t="n">
-        <v>11.76</v>
+        <v>11.18</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.99</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.85</v>
+        <v>23.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>27.37</v>
+        <v>23.54</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.27</v>
+        <v>24.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>32.27</v>
+        <v>32.25</v>
       </c>
       <c r="AD7" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AF7" t="n">
-        <v>247.4544</v>
+        <v>247.5104</v>
       </c>
       <c r="AG7" t="n">
-        <v>236.2466</v>
+        <v>236.5375</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AK7" t="n">
         <v>36.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>58.7</v>
+        <v>54.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN7" t="n">
         <v>226.65</v>
@@ -1831,14 +1831,14 @@
         <v>284.02</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.02</v>
+        <v>10.97</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.24</v>
+        <v>16.11</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 10.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 11.0% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>54.3</v>
+        <v>53</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 67.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1502773903360</v>
+        <v>1510391152640</v>
       </c>
       <c r="G8" t="n">
-        <v>22.22</v>
+        <v>22.33</v>
       </c>
       <c r="H8" t="n">
-        <v>16.79</v>
+        <v>16.87</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1939,16 +1939,16 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="P8" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="Q8" t="n">
         <v>27.8</v>
       </c>
       <c r="R8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>60.9</v>
@@ -1965,25 +1965,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>589.9</v>
+        <v>592.8901</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.19</v>
+        <v>-6.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.66</v>
+        <v>-3.79</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11.67</v>
+        <v>-11.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>-22.48</v>
+        <v>-22.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>23.52</v>
+        <v>23.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.43</v>
+        <v>37.4</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
@@ -1992,10 +1992,10 @@
         <v>0.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>600.4756</v>
+        <v>599.6399</v>
       </c>
       <c r="AG8" t="n">
-        <v>631.1296</v>
+        <v>630.4426999999999</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="AK8" t="n">
         <v>27.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.76</v>
+        <v>-1.13</v>
       </c>
       <c r="AS8" t="n">
-        <v>-6.53</v>
+        <v>-5.96</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.1%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1261998964736</v>
+        <v>1297663262720</v>
       </c>
       <c r="G10" t="n">
-        <v>293.15</v>
+        <v>301.43</v>
       </c>
       <c r="H10" t="n">
-        <v>143.98</v>
+        <v>148.05</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>50.5</v>
+        <v>54.8</v>
       </c>
       <c r="S10" t="n">
-        <v>26.8</v>
+        <v>27.7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>319.53</v>
+        <v>328.56</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.91</v>
+        <v>-19.18</v>
       </c>
       <c r="Y10" t="n">
-        <v>-19.86</v>
+        <v>-20.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>-21.3</v>
+        <v>-17.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.35</v>
+        <v>9.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.49</v>
+        <v>58.48</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>382.6766</v>
+        <v>380.4406</v>
       </c>
       <c r="AG10" t="n">
-        <v>409.39</v>
+        <v>408.7957</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>50.5</v>
+        <v>54.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>407.76</v>
+        <v>396.18</v>
       </c>
       <c r="AQ10" t="n">
         <v>445.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-16.5</v>
+        <v>-13.64</v>
       </c>
       <c r="AS10" t="n">
-        <v>-21.95</v>
+        <v>-19.63</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 16.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 13.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 26.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -16.5%.</t>
+          <t>TSLA: scenario base High Risk, score 27.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -13.6%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -696,12 +696,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -716,47 +716,47 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4572283666432</v>
+        <v>3749863489536</v>
       </c>
       <c r="G2" t="n">
-        <v>35.93</v>
+        <v>28.13</v>
       </c>
       <c r="H2" t="n">
-        <v>32.93</v>
+        <v>21.51</v>
       </c>
       <c r="I2" t="n">
-        <v>27.62</v>
+        <v>40.3</v>
       </c>
       <c r="J2" t="n">
-        <v>148.75</v>
+        <v>34.04</v>
       </c>
       <c r="K2" t="n">
-        <v>16.4</v>
+        <v>17.7</v>
       </c>
       <c r="L2" t="n">
-        <v>78.44</v>
+        <v>29.12</v>
       </c>
       <c r="M2" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>82.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="P2" t="n">
-        <v>39.4</v>
+        <v>64.8</v>
       </c>
       <c r="Q2" t="n">
         <v>41.1</v>
       </c>
       <c r="R2" t="n">
-        <v>82.8</v>
+        <v>4.4</v>
       </c>
       <c r="S2" t="n">
         <v>72.3</v>
@@ -768,42 +768,42 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>313.2801</v>
+        <v>504.995</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.93</v>
+        <v>31.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.09</v>
+        <v>21.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.76</v>
+        <v>26.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>47.49</v>
+        <v>-2.27</v>
       </c>
       <c r="AB2" t="n">
-        <v>21.17</v>
+        <v>17.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.86</v>
+        <v>26.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>-33.36</v>
+        <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="AF2" t="n">
-        <v>309.7844</v>
+        <v>408.5721</v>
       </c>
       <c r="AG2" t="n">
-        <v>279.131</v>
+        <v>431.7838</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,38 +814,38 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>82.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="AK2" t="n">
         <v>41.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>82.8</v>
+        <v>4.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
-        <v>303.42</v>
+        <v>381.58</v>
       </c>
       <c r="AO2" t="n">
-        <v>275.15</v>
+        <v>352.83</v>
       </c>
       <c r="AP2" t="n">
-        <v>340.08</v>
+        <v>504.995</v>
       </c>
       <c r="AQ2" t="n">
-        <v>340.08</v>
+        <v>504.995</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.13</v>
+        <v>23.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.24</v>
+        <v>16.96</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>71.8</v>
+        <v>24.3</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,17 +868,17 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 340.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 505.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 275.15 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -910,55 +910,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3726213120000</v>
+        <v>4346763804672</v>
       </c>
       <c r="G3" t="n">
-        <v>27.97</v>
+        <v>17.82</v>
       </c>
       <c r="H3" t="n">
-        <v>21.38</v>
+        <v>24.12</v>
       </c>
       <c r="I3" t="n">
-        <v>40.3</v>
+        <v>54.77</v>
       </c>
       <c r="J3" t="n">
-        <v>34.04</v>
+        <v>48.68</v>
       </c>
       <c r="K3" t="n">
-        <v>17.7</v>
+        <v>24.2</v>
       </c>
       <c r="L3" t="n">
-        <v>29.12</v>
+        <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>93.2</v>
+        <v>60.7</v>
       </c>
       <c r="P3" t="n">
-        <v>65.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>5.6</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>71.8</v>
+        <v>71.3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,79 +972,79 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>501.81</v>
+        <v>355.43</v>
       </c>
       <c r="X3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-11.27</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="AC3" t="n">
         <v>30.56</v>
       </c>
-      <c r="Y3" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-3.64</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>15.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>26.11</v>
-      </c>
       <c r="AD3" t="n">
-        <v>-34.5</v>
+        <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.61</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>407.0484</v>
+        <v>355.7851</v>
       </c>
       <c r="AG3" t="n">
-        <v>431.8399</v>
+        <v>329.3553</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>93.2</v>
+        <v>60.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.6</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
-        <v>381.58</v>
+        <v>317.69</v>
       </c>
       <c r="AO3" t="n">
-        <v>352.83</v>
+        <v>317.69</v>
       </c>
       <c r="AP3" t="n">
-        <v>501.81</v>
+        <v>377.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>501.81</v>
+        <v>400.8306</v>
       </c>
       <c r="AR3" t="n">
-        <v>23.28</v>
+        <v>-0.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.2</v>
+        <v>7.91</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>prezzo 23.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>24.6</v>
+        <v>67</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 71.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.3%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 71.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.1%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 501.81 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 400.83 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,55 +1109,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4342238412800</v>
+        <v>4488148025344</v>
       </c>
       <c r="G4" t="n">
-        <v>17.81</v>
+        <v>35.31</v>
       </c>
       <c r="H4" t="n">
-        <v>24.1</v>
+        <v>32.33</v>
       </c>
       <c r="I4" t="n">
-        <v>54.77</v>
+        <v>27.62</v>
       </c>
       <c r="J4" t="n">
-        <v>48.68</v>
+        <v>148.75</v>
       </c>
       <c r="K4" t="n">
-        <v>24.2</v>
+        <v>16.4</v>
       </c>
       <c r="L4" t="n">
-        <v>18.86</v>
+        <v>78.44</v>
       </c>
       <c r="M4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>59.7</v>
+        <v>73.5</v>
       </c>
       <c r="P4" t="n">
-        <v>73.09999999999999</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.5</v>
+        <v>41</v>
       </c>
       <c r="R4" t="n">
-        <v>79.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="S4" t="n">
-        <v>71</v>
+        <v>68.8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355.03</v>
+        <v>307.52</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.08</v>
+        <v>-2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>-10.74</v>
+        <v>4.94</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.32</v>
+        <v>10.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>81.56999999999999</v>
+        <v>40.32</v>
       </c>
       <c r="AB4" t="n">
-        <v>39.77</v>
+        <v>20.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>30.53</v>
+        <v>26.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>-29.81</v>
+        <v>-33.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.3</v>
+        <v>0.77</v>
       </c>
       <c r="AF4" t="n">
-        <v>356.4891</v>
+        <v>309.6856</v>
       </c>
       <c r="AG4" t="n">
-        <v>328.8316</v>
+        <v>279.3587</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,34 +1212,34 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>59.7</v>
+        <v>73.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>39.5</v>
+        <v>41</v>
       </c>
       <c r="AL4" t="n">
-        <v>79.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="AM4" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>317.69</v>
+        <v>303.42</v>
       </c>
       <c r="AO4" t="n">
-        <v>317.69</v>
+        <v>275.15</v>
       </c>
       <c r="AP4" t="n">
-        <v>377.65</v>
+        <v>340.08</v>
       </c>
       <c r="AQ4" t="n">
-        <v>402.3797</v>
+        <v>340.08</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.97</v>
+        <v>10.08</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>66.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 71.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.4%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 68.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 340.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 275.15 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,55 +1308,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5396438712320</v>
+        <v>2988186271744</v>
       </c>
       <c r="G5" t="n">
-        <v>34.12</v>
+        <v>22.29</v>
       </c>
       <c r="H5" t="n">
-        <v>17.28</v>
+        <v>26.82</v>
       </c>
       <c r="I5" t="n">
-        <v>62.97</v>
+        <v>17.44</v>
       </c>
       <c r="J5" t="n">
-        <v>114.29</v>
+        <v>30.56</v>
       </c>
       <c r="K5" t="n">
-        <v>85.2</v>
+        <v>19.6</v>
       </c>
       <c r="L5" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="M5" t="n">
-        <v>46</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>81.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="P5" t="n">
-        <v>63.9</v>
+        <v>64</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>36.6</v>
       </c>
       <c r="R5" t="n">
-        <v>66.2</v>
+        <v>51.1</v>
       </c>
       <c r="S5" t="n">
-        <v>70.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1365,42 +1363,42 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>222.8102</v>
+        <v>277.035</v>
       </c>
       <c r="X5" t="n">
-        <v>9.880000000000001</v>
+        <v>12.92</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.47</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.79</v>
+        <v>31.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.35</v>
+        <v>24.16</v>
       </c>
       <c r="AB5" t="n">
-        <v>70.27</v>
+        <v>26.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>47.08</v>
+        <v>32.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>-36.88</v>
+        <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AF5" t="n">
-        <v>206.0257</v>
+        <v>247.5677</v>
       </c>
       <c r="AG5" t="n">
-        <v>193.7941</v>
+        <v>236.8116</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1411,52 +1409,52 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>81.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>14</v>
+        <v>36.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>66.2</v>
+        <v>51.1</v>
       </c>
       <c r="AM5" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>190.01</v>
+        <v>226.65</v>
       </c>
       <c r="AO5" t="n">
-        <v>190.01</v>
+        <v>226.65</v>
       </c>
       <c r="AP5" t="n">
-        <v>222.795</v>
+        <v>284.02</v>
       </c>
       <c r="AQ5" t="n">
-        <v>235.4656</v>
+        <v>284.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.140000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.96</v>
+        <v>16.99</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>48.4</v>
+        <v>51.6</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1465,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 70.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 68.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1485,19 +1483,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1512,50 +1510,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>575765872640</v>
+        <v>5308031696896</v>
       </c>
       <c r="G6" t="n">
-        <v>59.02</v>
+        <v>33.51</v>
       </c>
       <c r="H6" t="n">
-        <v>29.15</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>30.11</v>
+        <v>62.97</v>
       </c>
       <c r="J6" t="n">
-        <v>53.94</v>
+        <v>114.29</v>
       </c>
       <c r="K6" t="n">
-        <v>21.3</v>
+        <v>85.2</v>
       </c>
       <c r="L6" t="n">
-        <v>9.09</v>
+        <v>6.55</v>
       </c>
       <c r="M6" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>22.6</v>
+        <v>65</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.9</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>75.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="S6" t="n">
-        <v>67.7</v>
+        <v>68</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1569,75 +1567,75 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1499</v>
+        <v>219.15</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.36</v>
+        <v>3.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.57</v>
+        <v>1.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>24.84</v>
+        <v>18.34</v>
       </c>
       <c r="AA6" t="n">
-        <v>138.02</v>
+        <v>21.39</v>
       </c>
       <c r="AB6" t="n">
-        <v>34.39</v>
+        <v>73.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.41</v>
+        <v>47.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>-44.77</v>
+        <v>-36.88</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.87</v>
+        <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>1543.3364</v>
+        <v>206.1517</v>
       </c>
       <c r="AG6" t="n">
-        <v>1219.0252</v>
+        <v>193.991</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>100</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.9</v>
+        <v>14</v>
       </c>
       <c r="AL6" t="n">
-        <v>75.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>1362.2</v>
+        <v>190.01</v>
       </c>
       <c r="AO6" t="n">
-        <v>1247.4977</v>
+        <v>190.01</v>
       </c>
       <c r="AP6" t="n">
-        <v>1596.4774</v>
+        <v>223.96</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1719.3295</v>
+        <v>235.4656</v>
       </c>
       <c r="AR6" t="n">
-        <v>-2.87</v>
+        <v>6.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>22.97</v>
+        <v>12.96</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1655,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.8</v>
+        <v>49.4</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1664,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.9%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 68.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.3%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1247.50 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1684,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1706,53 +1704,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2962460770304</v>
+        <v>581450596352</v>
       </c>
       <c r="G7" t="n">
-        <v>22.08</v>
+        <v>59.41</v>
       </c>
       <c r="H7" t="n">
-        <v>26.59</v>
+        <v>29.44</v>
       </c>
       <c r="I7" t="n">
-        <v>17.44</v>
+        <v>30.11</v>
       </c>
       <c r="J7" t="n">
-        <v>30.56</v>
+        <v>53.94</v>
       </c>
       <c r="K7" t="n">
-        <v>19.6</v>
+        <v>21.3</v>
       </c>
       <c r="L7" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>9.09</v>
+      </c>
+      <c r="M7" t="n">
+        <v>52</v>
+      </c>
       <c r="N7" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>64.59999999999999</v>
+        <v>22.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.6</v>
+        <v>16.9</v>
       </c>
       <c r="R7" t="n">
-        <v>54.9</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>67.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1761,98 +1761,98 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>274.65</v>
+        <v>1513.8</v>
       </c>
       <c r="X7" t="n">
-        <v>11.18</v>
+        <v>-3.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>14.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.33</v>
+        <v>27.32</v>
       </c>
       <c r="AA7" t="n">
-        <v>23.54</v>
+        <v>137.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.6</v>
+        <v>35</v>
       </c>
       <c r="AC7" t="n">
-        <v>32.25</v>
+        <v>39.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>247.5104</v>
+        <v>1545.7659</v>
       </c>
       <c r="AG7" t="n">
-        <v>236.5375</v>
+        <v>1222.1512</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>36.6</v>
+        <v>16.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>54.9</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AM7" t="n">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="AN7" t="n">
-        <v>226.65</v>
+        <v>1362.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>226.65</v>
+        <v>1247.4977</v>
       </c>
       <c r="AP7" t="n">
-        <v>284.02</v>
+        <v>1596.4774</v>
       </c>
       <c r="AQ7" t="n">
-        <v>284.02</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.97</v>
+        <v>-2.07</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.11</v>
+        <v>23.86</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 11.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>53</v>
+        <v>55.2</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 67.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.1%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1247.50 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1510391152640</v>
+        <v>1509499207680</v>
       </c>
       <c r="G8" t="n">
         <v>22.33</v>
       </c>
       <c r="H8" t="n">
-        <v>16.87</v>
+        <v>16.86</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,13 +1933,13 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>32.1</v>
+        <v>34.6</v>
       </c>
       <c r="P8" t="n">
         <v>78.2</v>
@@ -1948,10 +1948,10 @@
         <v>27.8</v>
       </c>
       <c r="R8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="S8" t="n">
-        <v>60.9</v>
+        <v>61.6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>592.8901</v>
+        <v>592.54</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.11</v>
+        <v>-11.46</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.79</v>
+        <v>-2.71</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11.38</v>
+        <v>-10.26</v>
       </c>
       <c r="AA8" t="n">
-        <v>-22.95</v>
+        <v>-21.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>23.69</v>
+        <v>25.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.4</v>
+        <v>37.42</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>599.6399</v>
+        <v>598.7809</v>
       </c>
       <c r="AG8" t="n">
-        <v>630.4426999999999</v>
+        <v>629.7446</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32.1</v>
+        <v>34.6</v>
       </c>
       <c r="AK8" t="n">
         <v>27.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.13</v>
+        <v>-1.04</v>
       </c>
       <c r="AS8" t="n">
-        <v>-5.96</v>
+        <v>-5.91</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>42.8</v>
+        <v>43.5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.1%.</t>
+          <t>META: scenario base Hold / Monitor, score 61.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.0%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1297663262720</v>
+        <v>1301336424448</v>
       </c>
       <c r="G10" t="n">
-        <v>301.43</v>
+        <v>305.08</v>
       </c>
       <c r="H10" t="n">
-        <v>148.05</v>
+        <v>148.47</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>54.8</v>
+        <v>55.9</v>
       </c>
       <c r="S10" t="n">
-        <v>27.7</v>
+        <v>26.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>328.56</v>
+        <v>329.515</v>
       </c>
       <c r="X10" t="n">
-        <v>-19.18</v>
+        <v>-19.19</v>
       </c>
       <c r="Y10" t="n">
-        <v>-20.21</v>
+        <v>-23.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>-17.28</v>
+        <v>-19.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.35</v>
+        <v>10.39</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.48</v>
+        <v>58.52</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>380.4406</v>
+        <v>378.1893</v>
       </c>
       <c r="AG10" t="n">
-        <v>408.7957</v>
+        <v>408.2303</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>54.8</v>
+        <v>55.9</v>
       </c>
       <c r="AM10" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2371,13 +2371,13 @@
         <v>396.18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>445.27</v>
+        <v>443.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>-13.64</v>
+        <v>-12.88</v>
       </c>
       <c r="AS10" t="n">
-        <v>-19.63</v>
+        <v>-19.29</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 13.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 12.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>16</v>
+        <v>14.8</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 27.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -13.6%.</t>
+          <t>TSLA: scenario base High Risk, score 26.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -12.9%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 443.30 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3749863489536</v>
+        <v>3735197843456</v>
       </c>
       <c r="G2" t="n">
-        <v>28.13</v>
+        <v>27.99</v>
       </c>
       <c r="H2" t="n">
-        <v>21.51</v>
+        <v>21.36</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -741,25 +741,25 @@
         <v>29.12</v>
       </c>
       <c r="M2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>96</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>64.8</v>
+        <v>65.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="S2" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>504.995</v>
+        <v>503.03</v>
       </c>
       <c r="X2" t="n">
-        <v>31.13</v>
+        <v>28.66</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.91</v>
+        <v>22.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.45</v>
+        <v>22.16</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2.27</v>
+        <v>-2.87</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.08</v>
+        <v>17.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.12</v>
+        <v>26.13</v>
       </c>
       <c r="AD2" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AF2" t="n">
-        <v>408.5721</v>
+        <v>409.6492</v>
       </c>
       <c r="AG2" t="n">
-        <v>431.7838</v>
+        <v>431.7179</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,13 +814,13 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>96</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
@@ -832,16 +832,16 @@
         <v>352.83</v>
       </c>
       <c r="AP2" t="n">
-        <v>504.995</v>
+        <v>506.06</v>
       </c>
       <c r="AQ2" t="n">
-        <v>504.995</v>
+        <v>506.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.96</v>
+        <v>16.52</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 22.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>24.3</v>
+        <v>26.1</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,12 +868,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 72.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 22.8%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 505.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 506.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4346763804672</v>
+        <v>4207587098624</v>
       </c>
       <c r="G3" t="n">
-        <v>17.82</v>
+        <v>17.28</v>
       </c>
       <c r="H3" t="n">
-        <v>24.12</v>
+        <v>23.34</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>60.7</v>
+        <v>55.6</v>
       </c>
       <c r="P3" t="n">
-        <v>73.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="R3" t="n">
-        <v>79.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>71.3</v>
+        <v>69.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>355.43</v>
+        <v>344.04</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.49</v>
+        <v>-2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>-11.27</v>
+        <v>-11.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.23</v>
+        <v>6.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>81.38</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>40.61</v>
+        <v>39.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.56</v>
+        <v>30.65</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>355.7851</v>
+        <v>355.1055</v>
       </c>
       <c r="AG3" t="n">
-        <v>329.3553</v>
+        <v>329.8299</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>60.7</v>
+        <v>55.6</v>
       </c>
       <c r="AK3" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>79.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
@@ -1034,13 +1034,13 @@
         <v>377.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>400.8306</v>
+        <v>396.7031</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.1</v>
+        <v>-3.12</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.91</v>
+        <v>4.31</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>67</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 71.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.1%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 69.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 400.83 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 396.70 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1114,50 +1114,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4488148025344</v>
+        <v>596891402240</v>
       </c>
       <c r="G4" t="n">
-        <v>35.31</v>
+        <v>61.11</v>
       </c>
       <c r="H4" t="n">
-        <v>32.33</v>
+        <v>30.22</v>
       </c>
       <c r="I4" t="n">
-        <v>27.62</v>
+        <v>30.11</v>
       </c>
       <c r="J4" t="n">
-        <v>148.75</v>
+        <v>53.94</v>
       </c>
       <c r="K4" t="n">
-        <v>16.4</v>
+        <v>21.3</v>
       </c>
       <c r="L4" t="n">
-        <v>78.44</v>
+        <v>9.09</v>
       </c>
       <c r="M4" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>73.5</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>21.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>16.9</v>
       </c>
       <c r="R4" t="n">
-        <v>78.7</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,80 +1166,80 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>307.52</v>
+        <v>1554</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.47</v>
+        <v>0.98</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.94</v>
+        <v>13.82</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.78</v>
+        <v>29.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>40.32</v>
+        <v>143.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>20.68</v>
+        <v>37.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.91</v>
+        <v>39.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>-33.36</v>
+        <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.77</v>
+        <v>0.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>309.6856</v>
+        <v>1547.6451</v>
       </c>
       <c r="AG4" t="n">
-        <v>279.3587</v>
+        <v>1225.4102</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>73.5</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>41</v>
+        <v>16.9</v>
       </c>
       <c r="AL4" t="n">
-        <v>78.7</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="AN4" t="n">
-        <v>303.42</v>
+        <v>1362.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>275.15</v>
+        <v>1331.3966</v>
       </c>
       <c r="AP4" t="n">
-        <v>340.08</v>
+        <v>1596.4774</v>
       </c>
       <c r="AQ4" t="n">
-        <v>340.08</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.7</v>
+        <v>0.41</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.08</v>
+        <v>26.81</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>67.8</v>
+        <v>57.4</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 68.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 69.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 340.08 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 275.15 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1331.40 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2988186271744</v>
+        <v>2941643390976</v>
       </c>
       <c r="G5" t="n">
-        <v>22.29</v>
+        <v>21.94</v>
       </c>
       <c r="H5" t="n">
-        <v>26.82</v>
+        <v>26.4</v>
       </c>
       <c r="I5" t="n">
         <v>17.44</v>
@@ -1342,19 +1342,19 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>77.3</v>
+        <v>76</v>
       </c>
       <c r="P5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="R5" t="n">
-        <v>51.1</v>
+        <v>58.2</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>277.035</v>
+        <v>272.74</v>
       </c>
       <c r="X5" t="n">
-        <v>12.92</v>
+        <v>10.28</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>31.72</v>
+        <v>30.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.16</v>
+        <v>22.48</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.13</v>
+        <v>25.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>32.27</v>
+        <v>32.3</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>247.5677</v>
+        <v>247.6308</v>
       </c>
       <c r="AG5" t="n">
-        <v>236.8116</v>
+        <v>237.0909</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>77.3</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>51.1</v>
+        <v>58.2</v>
       </c>
       <c r="AM5" t="n">
         <v>752</v>
@@ -1433,14 +1433,14 @@
         <v>284.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.9</v>
+        <v>10.13</v>
       </c>
       <c r="AS5" t="n">
-        <v>16.99</v>
+        <v>15.03</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 11.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>51.6</v>
+        <v>56.7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 68.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1510,132 +1510,132 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5308031696896</v>
+        <v>4447649398784</v>
       </c>
       <c r="G6" t="n">
-        <v>33.51</v>
+        <v>34.95</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>32.05</v>
       </c>
       <c r="I6" t="n">
-        <v>62.97</v>
+        <v>27.62</v>
       </c>
       <c r="J6" t="n">
-        <v>114.29</v>
+        <v>148.75</v>
       </c>
       <c r="K6" t="n">
-        <v>85.2</v>
+        <v>16.4</v>
       </c>
       <c r="L6" t="n">
-        <v>6.55</v>
+        <v>78.44</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>69.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="P6" t="n">
-        <v>65</v>
+        <v>41.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="R6" t="n">
-        <v>73.5</v>
+        <v>77.5</v>
       </c>
       <c r="S6" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>219.15</v>
+        <v>304.7423</v>
       </c>
       <c r="X6" t="n">
-        <v>3.88</v>
+        <v>-3.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.95</v>
+        <v>4.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.34</v>
+        <v>11.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.39</v>
+        <v>33.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>73.53</v>
+        <v>20.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>47.07</v>
+        <v>26.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>-36.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.56</v>
+        <v>0.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>206.1517</v>
+        <v>309.2979</v>
       </c>
       <c r="AG6" t="n">
-        <v>193.991</v>
+        <v>279.3593</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>69.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="AK6" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="AL6" t="n">
-        <v>73.5</v>
+        <v>77.5</v>
       </c>
       <c r="AM6" t="n">
         <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>190.01</v>
+        <v>303.1586</v>
       </c>
       <c r="AO6" t="n">
-        <v>190.01</v>
+        <v>274.9129</v>
       </c>
       <c r="AP6" t="n">
-        <v>223.96</v>
+        <v>339.7869</v>
       </c>
       <c r="AQ6" t="n">
-        <v>235.4656</v>
+        <v>339.7869</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.3</v>
+        <v>-1.47</v>
       </c>
       <c r="AS6" t="n">
-        <v>12.96</v>
+        <v>9.09</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>49.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 68.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.3%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 68.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,19 +1682,19 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1709,50 +1709,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>581450596352</v>
+        <v>5277755637760</v>
       </c>
       <c r="G7" t="n">
-        <v>59.41</v>
+        <v>33.37</v>
       </c>
       <c r="H7" t="n">
-        <v>29.44</v>
+        <v>16.9</v>
       </c>
       <c r="I7" t="n">
-        <v>30.11</v>
+        <v>62.97</v>
       </c>
       <c r="J7" t="n">
-        <v>53.94</v>
+        <v>114.29</v>
       </c>
       <c r="K7" t="n">
-        <v>21.3</v>
+        <v>85.2</v>
       </c>
       <c r="L7" t="n">
-        <v>9.09</v>
+        <v>6.55</v>
       </c>
       <c r="M7" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>62.9</v>
       </c>
       <c r="P7" t="n">
-        <v>22.2</v>
+        <v>65.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.9</v>
+        <v>14.1</v>
       </c>
       <c r="R7" t="n">
-        <v>76.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="S7" t="n">
-        <v>67.8</v>
+        <v>66.7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,75 +1766,75 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>1513.8</v>
+        <v>217.9031</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.4</v>
+        <v>7.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.21</v>
+        <v>-0.58</v>
       </c>
       <c r="Z7" t="n">
-        <v>27.32</v>
+        <v>14.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>137.85</v>
+        <v>19.43</v>
       </c>
       <c r="AB7" t="n">
-        <v>35</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>39.44</v>
+        <v>47.03</v>
       </c>
       <c r="AD7" t="n">
-        <v>-44.77</v>
+        <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.89</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>1545.7659</v>
+        <v>206.2598</v>
       </c>
       <c r="AG7" t="n">
-        <v>1222.1512</v>
+        <v>194.1722</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>100</v>
+        <v>62.9</v>
       </c>
       <c r="AK7" t="n">
-        <v>16.9</v>
+        <v>14.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>76.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
-        <v>1362.2</v>
+        <v>190.01</v>
       </c>
       <c r="AO7" t="n">
-        <v>1247.4977</v>
+        <v>190.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>1596.4774</v>
+        <v>223.96</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1719.3295</v>
+        <v>225.0577</v>
       </c>
       <c r="AR7" t="n">
-        <v>-2.07</v>
+        <v>5.64</v>
       </c>
       <c r="AS7" t="n">
-        <v>23.86</v>
+        <v>12.22</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>55.2</v>
+        <v>48.6</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.1%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 66.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.6%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 225.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1247.50 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 190.01 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1509499207680</v>
+        <v>1532668936192</v>
       </c>
       <c r="G8" t="n">
-        <v>22.33</v>
+        <v>22.68</v>
       </c>
       <c r="H8" t="n">
-        <v>16.86</v>
+        <v>17.25</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>34.6</v>
+        <v>38.8</v>
       </c>
       <c r="P8" t="n">
-        <v>78.2</v>
+        <v>77.2</v>
       </c>
       <c r="Q8" t="n">
         <v>27.8</v>
       </c>
       <c r="R8" t="n">
-        <v>73.7</v>
+        <v>78.2</v>
       </c>
       <c r="S8" t="n">
-        <v>61.6</v>
+        <v>63.9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,54 +1965,54 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>592.54</v>
+        <v>601.635</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.46</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>-10.26</v>
+        <v>-11</v>
       </c>
       <c r="AA8" t="n">
-        <v>-21.97</v>
+        <v>-21.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>25.19</v>
+        <v>26.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.42</v>
+        <v>37.41</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AF8" t="n">
-        <v>598.7809</v>
+        <v>598.2227</v>
       </c>
       <c r="AG8" t="n">
-        <v>629.7446</v>
+        <v>629.1070999999999</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34.6</v>
+        <v>38.8</v>
       </c>
       <c r="AK8" t="n">
         <v>27.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>73.7</v>
+        <v>78.2</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
@@ -2030,14 +2030,14 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.04</v>
+        <v>0.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>-5.91</v>
+        <v>-4.37</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>43.5</v>
+        <v>46.3</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 61.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.0%.</t>
+          <t>META: scenario base Hold / Monitor, score 63.9, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1301336424448</v>
+        <v>1312098877440</v>
       </c>
       <c r="G10" t="n">
-        <v>305.08</v>
+        <v>304.78</v>
       </c>
       <c r="H10" t="n">
-        <v>148.47</v>
+        <v>149.7</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>55.9</v>
+        <v>57.7</v>
       </c>
       <c r="S10" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,22 +2309,22 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>329.515</v>
+        <v>332.215</v>
       </c>
       <c r="X10" t="n">
-        <v>-19.19</v>
+        <v>-15.84</v>
       </c>
       <c r="Y10" t="n">
-        <v>-23.07</v>
+        <v>-25.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>-19.85</v>
+        <v>-20.39</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.25</v>
+        <v>0.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.39</v>
+        <v>11.1</v>
       </c>
       <c r="AC10" t="n">
         <v>58.52</v>
@@ -2333,13 +2333,13 @@
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>378.1893</v>
+        <v>376.1451</v>
       </c>
       <c r="AG10" t="n">
-        <v>408.2303</v>
+        <v>407.7034</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>55.9</v>
+        <v>57.7</v>
       </c>
       <c r="AM10" t="n">
         <v>752</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>396.18</v>
+        <v>394.46</v>
       </c>
       <c r="AQ10" t="n">
-        <v>443.3</v>
+        <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-12.88</v>
+        <v>-11.68</v>
       </c>
       <c r="AS10" t="n">
-        <v>-19.29</v>
+        <v>-18.52</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 12.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 11.7% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 26.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -12.9%.</t>
+          <t>TSLA: scenario base High Risk, score 25.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.7%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 443.30 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 442.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3735197843456</v>
+        <v>3669036367872</v>
       </c>
       <c r="G2" t="n">
-        <v>27.99</v>
+        <v>27.54</v>
       </c>
       <c r="H2" t="n">
-        <v>21.36</v>
+        <v>20.98</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -747,19 +747,19 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>93.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>65.2</v>
+        <v>66.2</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>7.6</v>
+        <v>17.1</v>
       </c>
       <c r="S2" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>503.03</v>
+        <v>494.11</v>
       </c>
       <c r="X2" t="n">
-        <v>28.66</v>
+        <v>28.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.16</v>
+        <v>21.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.16</v>
+        <v>20.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2.87</v>
+        <v>-4.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.16</v>
+        <v>16.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.13</v>
+        <v>26.15</v>
       </c>
       <c r="AD2" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>409.6492</v>
+        <v>410.3366</v>
       </c>
       <c r="AG2" t="n">
-        <v>431.7179</v>
+        <v>431.6059</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,13 +814,13 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>93.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.6</v>
+        <v>17.1</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
@@ -838,10 +838,10 @@
         <v>506.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>22.8</v>
+        <v>20.42</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.52</v>
+        <v>14.49</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 22.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 20.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>26.1</v>
+        <v>32.6</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 72.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 22.8%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 72.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.4%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4207587098624</v>
+        <v>4205996933120</v>
       </c>
       <c r="G3" t="n">
-        <v>17.28</v>
+        <v>17.25</v>
       </c>
       <c r="H3" t="n">
-        <v>23.34</v>
+        <v>23.33</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -940,25 +940,25 @@
         <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="P3" t="n">
-        <v>74.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>39.4</v>
       </c>
       <c r="R3" t="n">
-        <v>75.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="S3" t="n">
-        <v>69.8</v>
+        <v>70.2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>344.04</v>
+        <v>343.89</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4</v>
+        <v>-4.34</v>
       </c>
       <c r="Y3" t="n">
-        <v>-11.42</v>
+        <v>-11.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.22</v>
+        <v>8.09</v>
       </c>
       <c r="AA3" t="n">
-        <v>71.29000000000001</v>
+        <v>71.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.13</v>
+        <v>38.48</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.65</v>
+        <v>30.64</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF3" t="n">
-        <v>355.1055</v>
+        <v>354.4555</v>
       </c>
       <c r="AG3" t="n">
-        <v>329.8299</v>
+        <v>330.2853</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="AK3" t="n">
         <v>39.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>75.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
@@ -1037,10 +1037,10 @@
         <v>396.7031</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3.12</v>
+        <v>-2.98</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.31</v>
+        <v>4.12</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>64.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 69.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 70.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.0%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,55 +1109,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>596891402240</v>
+        <v>2899738361856</v>
       </c>
       <c r="G4" t="n">
-        <v>61.11</v>
+        <v>21.61</v>
       </c>
       <c r="H4" t="n">
-        <v>30.22</v>
+        <v>26.02</v>
       </c>
       <c r="I4" t="n">
-        <v>30.11</v>
+        <v>17.44</v>
       </c>
       <c r="J4" t="n">
-        <v>53.94</v>
+        <v>30.56</v>
       </c>
       <c r="K4" t="n">
-        <v>21.3</v>
+        <v>19.6</v>
       </c>
       <c r="L4" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="M4" t="n">
-        <v>51</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>21.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.9</v>
+        <v>36.5</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>64.7</v>
       </c>
       <c r="S4" t="n">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,42 +1164,42 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1554</v>
+        <v>268.835</v>
       </c>
       <c r="X4" t="n">
-        <v>0.98</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.82</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>29.1</v>
+        <v>29.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>143.3</v>
+        <v>21.48</v>
       </c>
       <c r="AB4" t="n">
-        <v>37.52</v>
+        <v>24.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.42</v>
+        <v>32.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>-44.77</v>
+        <v>-30.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1547.6451</v>
+        <v>247.7729</v>
       </c>
       <c r="AG4" t="n">
-        <v>1225.4102</v>
+        <v>237.3272</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,34 +1210,34 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.9</v>
+        <v>36.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>64.7</v>
       </c>
       <c r="AM4" t="n">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>1362.2</v>
+        <v>226.65</v>
       </c>
       <c r="AO4" t="n">
-        <v>1331.3966</v>
+        <v>226.65</v>
       </c>
       <c r="AP4" t="n">
-        <v>1596.4774</v>
+        <v>284.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1719.3295</v>
+        <v>284.02</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.41</v>
+        <v>8.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>26.81</v>
+        <v>13.28</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1248,16 +1246,16 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>57.4</v>
+        <v>61.3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1264,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 69.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.5%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1331.40 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1284,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,53 +1306,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2941643390976</v>
+        <v>601884721152</v>
       </c>
       <c r="G5" t="n">
-        <v>21.94</v>
+        <v>61.48</v>
       </c>
       <c r="H5" t="n">
-        <v>26.4</v>
+        <v>30.47</v>
       </c>
       <c r="I5" t="n">
-        <v>17.44</v>
+        <v>30.11</v>
       </c>
       <c r="J5" t="n">
-        <v>30.56</v>
+        <v>53.94</v>
       </c>
       <c r="K5" t="n">
-        <v>19.6</v>
+        <v>21.3</v>
       </c>
       <c r="L5" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>9.09</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50</v>
+      </c>
       <c r="N5" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>65</v>
+        <v>20.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.5</v>
+        <v>16.9</v>
       </c>
       <c r="R5" t="n">
-        <v>58.2</v>
+        <v>82.8</v>
       </c>
       <c r="S5" t="n">
-        <v>68.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1363,42 +1363,42 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>272.74</v>
+        <v>1567</v>
       </c>
       <c r="X5" t="n">
-        <v>10.28</v>
+        <v>-0.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>18.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>30.67</v>
+        <v>31.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.48</v>
+        <v>146.21</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.52</v>
+        <v>38.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>32.3</v>
+        <v>39.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.79</v>
+        <v>0.96</v>
       </c>
       <c r="AF5" t="n">
-        <v>247.6308</v>
+        <v>1549.1225</v>
       </c>
       <c r="AG5" t="n">
-        <v>237.0909</v>
+        <v>1222.9904</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,34 +1409,34 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>36.5</v>
+        <v>16.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>58.2</v>
+        <v>82.8</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="AN5" t="n">
-        <v>226.65</v>
+        <v>1362.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>226.65</v>
+        <v>1343.5819</v>
       </c>
       <c r="AP5" t="n">
-        <v>284.02</v>
+        <v>1596.4774</v>
       </c>
       <c r="AQ5" t="n">
-        <v>284.02</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.13</v>
+        <v>1.14</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.03</v>
+        <v>27.53</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>56.7</v>
+        <v>57.3</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1343.58 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4447649398784</v>
+        <v>4405253373952</v>
       </c>
       <c r="G6" t="n">
-        <v>34.95</v>
+        <v>34.62</v>
       </c>
       <c r="H6" t="n">
-        <v>32.05</v>
+        <v>31.75</v>
       </c>
       <c r="I6" t="n">
         <v>27.62</v>
@@ -1541,23 +1541,23 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>71</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>41.8</v>
+        <v>42.6</v>
       </c>
       <c r="Q6" t="n">
         <v>41</v>
       </c>
       <c r="R6" t="n">
-        <v>77.5</v>
+        <v>76.2</v>
       </c>
       <c r="S6" t="n">
-        <v>68.2</v>
+        <v>67.5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>304.7423</v>
+        <v>301.85</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.88</v>
+        <v>-4.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.21</v>
+        <v>2.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.17</v>
+        <v>10.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>33.51</v>
+        <v>33.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.33</v>
+        <v>19.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>26.91</v>
+        <v>26.92</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>309.2979</v>
+        <v>309.2173</v>
       </c>
       <c r="AG6" t="n">
-        <v>279.3593</v>
+        <v>279.5762</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,19 +1608,19 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>71</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK6" t="n">
         <v>41</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.5</v>
+        <v>76.2</v>
       </c>
       <c r="AM6" t="n">
         <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>303.1586</v>
+        <v>301.85</v>
       </c>
       <c r="AO6" t="n">
         <v>274.9129</v>
@@ -1632,10 +1632,10 @@
         <v>339.7869</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.47</v>
+        <v>-2.38</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.09</v>
+        <v>7.97</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>66.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 68.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.5%.</t>
+          <t>AAPL: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.4%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5277755637760</v>
+        <v>5392442064896</v>
       </c>
       <c r="G7" t="n">
-        <v>33.37</v>
+        <v>34.15</v>
       </c>
       <c r="H7" t="n">
-        <v>16.9</v>
+        <v>17.27</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1740,19 +1740,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>62.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>65.3</v>
+        <v>63.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="R7" t="n">
-        <v>76.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>66.7</v>
+        <v>66.8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>217.9031</v>
+        <v>222.63</v>
       </c>
       <c r="X7" t="n">
-        <v>7.06</v>
+        <v>5.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.58</v>
+        <v>0.96</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.8</v>
+        <v>18.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.43</v>
+        <v>22.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>75.34999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>47.03</v>
+        <v>46.88</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF7" t="n">
-        <v>206.2598</v>
+        <v>206.2224</v>
       </c>
       <c r="AG7" t="n">
-        <v>194.1722</v>
+        <v>194.3737</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,13 +1807,13 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>62.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>76.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AM7" t="n">
         <v>752</v>
@@ -1828,13 +1828,13 @@
         <v>223.96</v>
       </c>
       <c r="AQ7" t="n">
-        <v>225.0577</v>
+        <v>224.0988</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.64</v>
+        <v>7.96</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.22</v>
+        <v>14.54</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>48.6</v>
+        <v>45.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 66.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.6%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 225.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 224.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1532668936192</v>
+        <v>1477910331392</v>
       </c>
       <c r="G8" t="n">
-        <v>22.68</v>
+        <v>21.86</v>
       </c>
       <c r="H8" t="n">
-        <v>17.25</v>
+        <v>16.63</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>38.8</v>
+        <v>30.8</v>
       </c>
       <c r="P8" t="n">
-        <v>77.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>78.2</v>
+        <v>70.8</v>
       </c>
       <c r="S8" t="n">
-        <v>63.9</v>
+        <v>60.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,54 +1965,54 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>601.635</v>
+        <v>580.14</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.390000000000001</v>
+        <v>-12.24</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5600000000000001</v>
+        <v>-3.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11</v>
+        <v>-13.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>-21.54</v>
+        <v>-24</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.4</v>
+        <v>24.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.41</v>
+        <v>37.45</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>598.2227</v>
+        <v>597.7769</v>
       </c>
       <c r="AG8" t="n">
-        <v>629.1070999999999</v>
+        <v>628.3348</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38.8</v>
+        <v>30.8</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>78.2</v>
+        <v>70.8</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
@@ -2024,20 +2024,20 @@
         <v>539.03</v>
       </c>
       <c r="AP8" t="n">
-        <v>681.3099999999999</v>
+        <v>664.54</v>
       </c>
       <c r="AQ8" t="n">
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.57</v>
+        <v>-2.95</v>
       </c>
       <c r="AS8" t="n">
-        <v>-4.37</v>
+        <v>-7.67</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>46.3</v>
+        <v>41.7</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 63.9, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.0%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1312098877440</v>
+        <v>1293910802432</v>
       </c>
       <c r="G10" t="n">
-        <v>304.78</v>
+        <v>309.07</v>
       </c>
       <c r="H10" t="n">
-        <v>149.7</v>
+        <v>147.62</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>57.7</v>
+        <v>56.5</v>
       </c>
       <c r="S10" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,22 +2309,22 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>332.215</v>
+        <v>327.5808</v>
       </c>
       <c r="X10" t="n">
-        <v>-15.84</v>
+        <v>-17.32</v>
       </c>
       <c r="Y10" t="n">
-        <v>-25.34</v>
+        <v>-24.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>-20.39</v>
+        <v>-22.96</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.78</v>
+        <v>-3.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.1</v>
+        <v>11.03</v>
       </c>
       <c r="AC10" t="n">
         <v>58.52</v>
@@ -2336,10 +2336,10 @@
         <v>0.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>376.1451</v>
+        <v>374.391</v>
       </c>
       <c r="AG10" t="n">
-        <v>407.7034</v>
+        <v>407.0994</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>57.7</v>
+        <v>56.5</v>
       </c>
       <c r="AM10" t="n">
         <v>752</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>394.46</v>
+        <v>391.06</v>
       </c>
       <c r="AQ10" t="n">
         <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-11.68</v>
+        <v>-12.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>-18.52</v>
+        <v>-19.53</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sotto MA50: attendere recupero</t>
+          <t>prezzo 12.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 25.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.7%.</t>
+          <t>TSLA: scenario base High Risk, score 25.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -12.5%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Watchlist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3669036367872</v>
+        <v>3696436445184</v>
       </c>
       <c r="G2" t="n">
-        <v>27.54</v>
+        <v>27.7</v>
       </c>
       <c r="H2" t="n">
-        <v>20.98</v>
+        <v>21.12</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -747,19 +747,19 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>90.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="P2" t="n">
-        <v>66.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>17.1</v>
+        <v>14.8</v>
       </c>
       <c r="S2" t="n">
-        <v>72.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>494.11</v>
+        <v>497.8</v>
       </c>
       <c r="X2" t="n">
-        <v>28.36</v>
+        <v>25.82</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.44</v>
+        <v>23.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.09</v>
+        <v>23.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>-4.54</v>
+        <v>-5.19</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.09</v>
+        <v>16.36</v>
       </c>
       <c r="AC2" t="n">
         <v>26.15</v>
@@ -797,13 +797,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AF2" t="n">
-        <v>410.3366</v>
+        <v>411.4328</v>
       </c>
       <c r="AG2" t="n">
-        <v>431.6059</v>
+        <v>431.485</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AK2" t="n">
         <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>17.1</v>
+        <v>14.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
         <v>381.58</v>
@@ -838,10 +838,10 @@
         <v>506.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>20.42</v>
+        <v>20.99</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.49</v>
+        <v>15.37</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 20.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 21.0% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 72.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.4%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 73.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.0%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4205996933120</v>
+        <v>4235715674112</v>
       </c>
       <c r="G3" t="n">
-        <v>17.25</v>
+        <v>17.38</v>
       </c>
       <c r="H3" t="n">
-        <v>23.33</v>
+        <v>23.5</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>57.1</v>
+        <v>55.1</v>
       </c>
       <c r="P3" t="n">
-        <v>74.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="Q3" t="n">
         <v>39.4</v>
       </c>
       <c r="R3" t="n">
-        <v>75.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>343.89</v>
+        <v>346.34</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.34</v>
+        <v>-6.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>-11.17</v>
+        <v>-13.93</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.09</v>
+        <v>11.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>71.58</v>
+        <v>70.81</v>
       </c>
       <c r="AB3" t="n">
-        <v>38.48</v>
+        <v>38.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.64</v>
+        <v>30.63</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>354.4555</v>
+        <v>354.1427</v>
       </c>
       <c r="AG3" t="n">
-        <v>330.2853</v>
+        <v>330.7181</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>57.1</v>
+        <v>55.1</v>
       </c>
       <c r="AK3" t="n">
         <v>39.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>75.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
         <v>317.69</v>
@@ -1034,13 +1034,13 @@
         <v>377.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>396.7031</v>
+        <v>389.8971</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2.98</v>
+        <v>-2.21</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.12</v>
+        <v>4.72</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 70.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.0%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 69.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.2%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 396.70 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 389.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,53 +1109,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2899738361856</v>
+        <v>618170548224</v>
       </c>
       <c r="G4" t="n">
-        <v>21.61</v>
+        <v>63.39</v>
       </c>
       <c r="H4" t="n">
-        <v>26.02</v>
+        <v>31.3</v>
       </c>
       <c r="I4" t="n">
-        <v>17.44</v>
+        <v>30.11</v>
       </c>
       <c r="J4" t="n">
-        <v>30.56</v>
+        <v>53.94</v>
       </c>
       <c r="K4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P4" t="n">
         <v>19.6</v>
       </c>
-      <c r="L4" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="O4" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="P4" t="n">
-        <v>65.90000000000001</v>
-      </c>
       <c r="Q4" t="n">
-        <v>36.5</v>
+        <v>16.8</v>
       </c>
       <c r="R4" t="n">
-        <v>64.7</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1164,42 +1166,42 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>268.835</v>
+        <v>1609.4</v>
       </c>
       <c r="X4" t="n">
-        <v>8.619999999999999</v>
+        <v>3.57</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>23.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>29.9</v>
+        <v>36.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.48</v>
+        <v>154.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.27</v>
+        <v>39.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>32.3</v>
+        <v>39.46</v>
       </c>
       <c r="AD4" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="AF4" t="n">
-        <v>247.7729</v>
+        <v>1552.8208</v>
       </c>
       <c r="AG4" t="n">
-        <v>237.3272</v>
+        <v>1229.6057</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1210,34 +1212,34 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>74.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>36.5</v>
+        <v>16.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>64.7</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="AN4" t="n">
-        <v>226.65</v>
+        <v>1362.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>226.65</v>
+        <v>1343.5819</v>
       </c>
       <c r="AP4" t="n">
-        <v>284.02</v>
+        <v>1609.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>284.02</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.5</v>
+        <v>3.64</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.28</v>
+        <v>30.89</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1246,16 +1248,16 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo 8.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>61.3</v>
+        <v>57.2</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.5%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1343.58 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1284,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1306,55 +1308,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>601884721152</v>
+        <v>2863280685056</v>
       </c>
       <c r="G5" t="n">
-        <v>61.48</v>
+        <v>21.36</v>
       </c>
       <c r="H5" t="n">
-        <v>30.47</v>
+        <v>25.57</v>
       </c>
       <c r="I5" t="n">
-        <v>30.11</v>
+        <v>17.44</v>
       </c>
       <c r="J5" t="n">
-        <v>53.94</v>
+        <v>30.56</v>
       </c>
       <c r="K5" t="n">
-        <v>21.3</v>
+        <v>19.6</v>
       </c>
       <c r="L5" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="M5" t="n">
-        <v>50</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>20.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.9</v>
+        <v>36.6</v>
       </c>
       <c r="R5" t="n">
-        <v>82.8</v>
+        <v>70.5</v>
       </c>
       <c r="S5" t="n">
-        <v>69.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1363,42 +1363,42 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1567</v>
+        <v>265.455</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01</v>
+        <v>4.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.23</v>
+        <v>-1.73</v>
       </c>
       <c r="Z5" t="n">
-        <v>31.8</v>
+        <v>30.07</v>
       </c>
       <c r="AA5" t="n">
-        <v>146.21</v>
+        <v>19.86</v>
       </c>
       <c r="AB5" t="n">
-        <v>38.06</v>
+        <v>23.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.44</v>
+        <v>32.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>-44.77</v>
+        <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>1549.1225</v>
+        <v>247.9205</v>
       </c>
       <c r="AG5" t="n">
-        <v>1222.9904</v>
+        <v>237.5257</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,34 +1409,34 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.9</v>
+        <v>36.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>82.8</v>
+        <v>70.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
-        <v>1362.2</v>
+        <v>226.65</v>
       </c>
       <c r="AO5" t="n">
-        <v>1343.5819</v>
+        <v>226.65</v>
       </c>
       <c r="AP5" t="n">
-        <v>1596.4774</v>
+        <v>284.02</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1719.3295</v>
+        <v>284.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.14</v>
+        <v>7.07</v>
       </c>
       <c r="AS5" t="n">
-        <v>27.53</v>
+        <v>11.76</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>57.3</v>
+        <v>64.5</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1343.58 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4405253373952</v>
+        <v>4442468384768</v>
       </c>
       <c r="G6" t="n">
-        <v>34.62</v>
+        <v>35.23</v>
       </c>
       <c r="H6" t="n">
-        <v>31.75</v>
+        <v>32.02</v>
       </c>
       <c r="I6" t="n">
         <v>27.62</v>
@@ -1541,19 +1541,19 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>68.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q6" t="n">
         <v>41</v>
       </c>
       <c r="R6" t="n">
-        <v>76.2</v>
+        <v>77.5</v>
       </c>
       <c r="S6" t="n">
-        <v>67.5</v>
+        <v>67.3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>301.85</v>
+        <v>304.4</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.05</v>
+        <v>-6.97</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.48</v>
+        <v>1.94</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.49</v>
+        <v>10.69</v>
       </c>
       <c r="AA6" t="n">
-        <v>33.36</v>
+        <v>33.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.57</v>
+        <v>19.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>26.92</v>
+        <v>26.9</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AF6" t="n">
-        <v>309.2173</v>
+        <v>309.0147</v>
       </c>
       <c r="AG6" t="n">
-        <v>279.5762</v>
+        <v>279.791</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,19 +1608,19 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>68.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AK6" t="n">
         <v>41</v>
       </c>
       <c r="AL6" t="n">
-        <v>76.2</v>
+        <v>77.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN6" t="n">
-        <v>301.85</v>
+        <v>302.25</v>
       </c>
       <c r="AO6" t="n">
         <v>274.9129</v>
@@ -1632,10 +1632,10 @@
         <v>339.7869</v>
       </c>
       <c r="AR6" t="n">
-        <v>-2.38</v>
+        <v>-1.48</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.97</v>
+        <v>8.81</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Hold / Monitor, score 67.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.4%.</t>
+          <t>AAPL: scenario base Hold / Monitor, score 67.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5392442064896</v>
+        <v>5470072864768</v>
       </c>
       <c r="G7" t="n">
-        <v>34.15</v>
+        <v>34.64</v>
       </c>
       <c r="H7" t="n">
-        <v>17.27</v>
+        <v>17.62</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1740,19 +1740,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>67.90000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>63.9</v>
+        <v>62.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="R7" t="n">
-        <v>66.90000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="S7" t="n">
-        <v>66.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>222.63</v>
+        <v>225.8401</v>
       </c>
       <c r="X7" t="n">
-        <v>5.11</v>
+        <v>6.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.96</v>
+        <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.23</v>
+        <v>18.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.45</v>
+        <v>23.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>72.61</v>
+        <v>73.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>206.2224</v>
+        <v>206.3172</v>
       </c>
       <c r="AG7" t="n">
-        <v>194.3737</v>
+        <v>194.5801</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>67.90000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>66.90000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
         <v>190.01</v>
@@ -1825,16 +1825,16 @@
         <v>190.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>223.96</v>
+        <v>225.8401</v>
       </c>
       <c r="AQ7" t="n">
-        <v>224.0988</v>
+        <v>225.8401</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.96</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.54</v>
+        <v>16.07</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>45.4</v>
+        <v>40.7</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 224.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 225.84 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1477910331392</v>
+        <v>1516237488128</v>
       </c>
       <c r="G8" t="n">
-        <v>21.86</v>
+        <v>22.4</v>
       </c>
       <c r="H8" t="n">
-        <v>16.63</v>
+        <v>17.06</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>30.8</v>
+        <v>32.7</v>
       </c>
       <c r="P8" t="n">
-        <v>79.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Q8" t="n">
         <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>70.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>60.5</v>
+        <v>61.1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>580.14</v>
+        <v>595.1900000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-12.24</v>
+        <v>-12.64</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.7</v>
+        <v>-3.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.35</v>
+        <v>-10.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>-24</v>
+        <v>-24.41</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.24</v>
+        <v>25.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.45</v>
+        <v>37.46</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>597.7769</v>
+        <v>597.7134</v>
       </c>
       <c r="AG8" t="n">
-        <v>628.3348</v>
+        <v>627.622</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30.8</v>
+        <v>32.7</v>
       </c>
       <c r="AK8" t="n">
         <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>70.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2024,16 +2024,16 @@
         <v>539.03</v>
       </c>
       <c r="AP8" t="n">
-        <v>664.54</v>
+        <v>646.01</v>
       </c>
       <c r="AQ8" t="n">
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.95</v>
+        <v>-0.42</v>
       </c>
       <c r="AS8" t="n">
-        <v>-7.67</v>
+        <v>-5.17</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>41.7</v>
+        <v>43.2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.0%.</t>
+          <t>META: scenario base Hold / Monitor, score 61.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.4%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1293910802432</v>
+        <v>1338324025344</v>
       </c>
       <c r="G10" t="n">
-        <v>309.07</v>
+        <v>313.75</v>
       </c>
       <c r="H10" t="n">
-        <v>147.62</v>
+        <v>155.47</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>56.5</v>
+        <v>61.6</v>
       </c>
       <c r="S10" t="n">
-        <v>25.2</v>
+        <v>26.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,22 +2309,22 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>327.5808</v>
+        <v>338.855</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.32</v>
+        <v>-14.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>-24.42</v>
+        <v>-23.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>-22.96</v>
+        <v>-20.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.38</v>
+        <v>-0.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.03</v>
+        <v>12.27</v>
       </c>
       <c r="AC10" t="n">
         <v>58.52</v>
@@ -2333,13 +2333,13 @@
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="AF10" t="n">
-        <v>374.391</v>
+        <v>372.6919</v>
       </c>
       <c r="AG10" t="n">
-        <v>407.0994</v>
+        <v>406.6247</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>56.5</v>
+        <v>61.6</v>
       </c>
       <c r="AM10" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>391.06</v>
+        <v>380.84</v>
       </c>
       <c r="AQ10" t="n">
         <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-12.5</v>
+        <v>-9.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>-19.53</v>
+        <v>-16.67</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 12.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>13.6</v>
+        <v>15.9</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 25.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -12.5%.</t>
+          <t>TSLA: scenario base High Risk, score 26.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3696436445184</v>
+        <v>3677204512768</v>
       </c>
       <c r="G2" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="H2" t="n">
-        <v>21.12</v>
+        <v>21.01</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -741,25 +741,25 @@
         <v>29.12</v>
       </c>
       <c r="M2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>95.3</v>
+        <v>93</v>
       </c>
       <c r="P2" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>14.8</v>
+        <v>18.8</v>
       </c>
       <c r="S2" t="n">
-        <v>73.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>497.8</v>
+        <v>495.235</v>
       </c>
       <c r="X2" t="n">
-        <v>25.82</v>
+        <v>23.47</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.12</v>
+        <v>21.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>23.65</v>
+        <v>23.79</v>
       </c>
       <c r="AA2" t="n">
-        <v>-5.19</v>
+        <v>-4.11</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.36</v>
+        <v>16.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.15</v>
+        <v>26.13</v>
       </c>
       <c r="AD2" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>411.4328</v>
+        <v>412.7723</v>
       </c>
       <c r="AG2" t="n">
-        <v>431.485</v>
+        <v>431.3157</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>95.3</v>
+        <v>93</v>
       </c>
       <c r="AK2" t="n">
         <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>14.8</v>
+        <v>18.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN2" t="n">
         <v>381.58</v>
@@ -838,10 +838,10 @@
         <v>506.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>20.99</v>
+        <v>19.97</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.37</v>
+        <v>14.81</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 21.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 20.0% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>34.4</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 73.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.0%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 73.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.0%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4235715674112</v>
+        <v>4225919614976</v>
       </c>
       <c r="G3" t="n">
-        <v>17.38</v>
+        <v>17.35</v>
       </c>
       <c r="H3" t="n">
-        <v>23.5</v>
+        <v>23.44</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>55.1</v>
+        <v>55.8</v>
       </c>
       <c r="P3" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q3" t="n">
         <v>39.4</v>
       </c>
       <c r="R3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="S3" t="n">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>346.34</v>
+        <v>345.539</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.63</v>
+        <v>-2.52</v>
       </c>
       <c r="Y3" t="n">
-        <v>-13.93</v>
+        <v>-13.79</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.52</v>
+        <v>11.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>70.81</v>
+        <v>71.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>38.75</v>
+        <v>38.58</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.63</v>
+        <v>30.61</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF3" t="n">
-        <v>354.1427</v>
+        <v>353.8783</v>
       </c>
       <c r="AG3" t="n">
-        <v>330.7181</v>
+        <v>331.1022</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55.1</v>
+        <v>55.8</v>
       </c>
       <c r="AK3" t="n">
         <v>39.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN3" t="n">
         <v>317.69</v>
@@ -1037,10 +1037,10 @@
         <v>389.8971</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2.21</v>
+        <v>-2.36</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.72</v>
+        <v>4.36</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 69.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.2%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 69.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.4%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,55 +1109,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>618170548224</v>
+        <v>2840683347968</v>
       </c>
       <c r="G4" t="n">
-        <v>63.39</v>
+        <v>21.19</v>
       </c>
       <c r="H4" t="n">
-        <v>31.3</v>
+        <v>25.37</v>
       </c>
       <c r="I4" t="n">
-        <v>30.11</v>
+        <v>17.44</v>
       </c>
       <c r="J4" t="n">
-        <v>53.94</v>
+        <v>30.56</v>
       </c>
       <c r="K4" t="n">
-        <v>21.3</v>
+        <v>19.6</v>
       </c>
       <c r="L4" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="M4" t="n">
-        <v>50</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>71.5</v>
       </c>
       <c r="P4" t="n">
-        <v>19.6</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.8</v>
+        <v>36.6</v>
       </c>
       <c r="R4" t="n">
-        <v>82.8</v>
+        <v>74.3</v>
       </c>
       <c r="S4" t="n">
-        <v>68.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1166,42 +1164,42 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1609.4</v>
+        <v>263.36</v>
       </c>
       <c r="X4" t="n">
-        <v>3.57</v>
+        <v>5.39</v>
       </c>
       <c r="Y4" t="n">
-        <v>23.32</v>
+        <v>-1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.88</v>
+        <v>31.94</v>
       </c>
       <c r="AA4" t="n">
-        <v>154.42</v>
+        <v>17.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>39.16</v>
+        <v>23.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>39.46</v>
+        <v>32.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>-44.77</v>
+        <v>-30.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.99</v>
+        <v>0.72</v>
       </c>
       <c r="AF4" t="n">
-        <v>1552.8208</v>
+        <v>248.1808</v>
       </c>
       <c r="AG4" t="n">
-        <v>1229.6057</v>
+        <v>237.706</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,34 +1210,34 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>71.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.8</v>
+        <v>36.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>82.8</v>
+        <v>74.3</v>
       </c>
       <c r="AM4" t="n">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="AN4" t="n">
-        <v>1362.2</v>
+        <v>226.65</v>
       </c>
       <c r="AO4" t="n">
-        <v>1343.5819</v>
+        <v>226.65</v>
       </c>
       <c r="AP4" t="n">
-        <v>1609.4</v>
+        <v>284.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1719.3295</v>
+        <v>284.02</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.64</v>
+        <v>6.12</v>
       </c>
       <c r="AS4" t="n">
-        <v>30.89</v>
+        <v>10.79</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1248,16 +1246,16 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>57.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1264,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 69.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.1%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1343.58 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1284,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,53 +1306,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2863280685056</v>
+        <v>606724358144</v>
       </c>
       <c r="G5" t="n">
-        <v>21.36</v>
+        <v>62.12</v>
       </c>
       <c r="H5" t="n">
-        <v>25.57</v>
+        <v>30.72</v>
       </c>
       <c r="I5" t="n">
-        <v>17.44</v>
+        <v>30.11</v>
       </c>
       <c r="J5" t="n">
-        <v>30.56</v>
+        <v>53.94</v>
       </c>
       <c r="K5" t="n">
-        <v>19.6</v>
+        <v>21.3</v>
       </c>
       <c r="L5" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>9.09</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50</v>
+      </c>
       <c r="N5" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>70.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>66.90000000000001</v>
+        <v>20.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.6</v>
+        <v>16.8</v>
       </c>
       <c r="R5" t="n">
-        <v>70.5</v>
+        <v>82.8</v>
       </c>
       <c r="S5" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1363,42 +1363,42 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>265.455</v>
+        <v>1579.6</v>
       </c>
       <c r="X5" t="n">
-        <v>4.12</v>
+        <v>2.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.73</v>
+        <v>25.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>30.07</v>
+        <v>33.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.86</v>
+        <v>148.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.71</v>
+        <v>38.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>32.29</v>
+        <v>39.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="AF5" t="n">
-        <v>247.9205</v>
+        <v>1554.4888</v>
       </c>
       <c r="AG5" t="n">
-        <v>237.5257</v>
+        <v>1232.9285</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,34 +1409,34 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>70.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>36.6</v>
+        <v>16.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>70.5</v>
+        <v>82.8</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="AN5" t="n">
-        <v>226.65</v>
+        <v>1362.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>226.65</v>
+        <v>1362.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>284.02</v>
+        <v>1609.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>284.02</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.07</v>
+        <v>1.62</v>
       </c>
       <c r="AS5" t="n">
-        <v>11.76</v>
+        <v>28.12</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>64.5</v>
+        <v>57.3</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.1%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1362.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4442468384768</v>
+        <v>4459543920640</v>
       </c>
       <c r="G6" t="n">
-        <v>35.23</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
-        <v>32.02</v>
+        <v>32.14</v>
       </c>
       <c r="I6" t="n">
         <v>27.62</v>
@@ -1535,29 +1535,29 @@
         <v>78.44</v>
       </c>
       <c r="M6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>67.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="R6" t="n">
-        <v>77.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>67.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1567,25 +1567,25 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>304.4</v>
+        <v>305.57</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.97</v>
+        <v>-8.23</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.94</v>
+        <v>2.56</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.69</v>
+        <v>16.96</v>
       </c>
       <c r="AA6" t="n">
-        <v>33.04</v>
+        <v>31.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.88</v>
+        <v>20.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>26.9</v>
+        <v>26.88</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.36</v>
@@ -1594,10 +1594,10 @@
         <v>0.74</v>
       </c>
       <c r="AF6" t="n">
-        <v>309.0147</v>
+        <v>308.9435</v>
       </c>
       <c r="AG6" t="n">
-        <v>279.791</v>
+        <v>279.984</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,16 +1608,16 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>67.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AK6" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN6" t="n">
         <v>302.25</v>
@@ -1632,10 +1632,10 @@
         <v>339.7869</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.48</v>
+        <v>-1.09</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.81</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>65.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Hold / Monitor, score 67.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.5%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 68.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.1%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5470072864768</v>
+        <v>5452631375872</v>
       </c>
       <c r="G7" t="n">
-        <v>34.64</v>
+        <v>34.47</v>
       </c>
       <c r="H7" t="n">
-        <v>17.62</v>
+        <v>17.56</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1734,25 +1734,25 @@
         <v>6.55</v>
       </c>
       <c r="M7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>67.40000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="P7" t="n">
-        <v>62.8</v>
+        <v>63.1</v>
       </c>
       <c r="Q7" t="n">
         <v>14.3</v>
       </c>
       <c r="R7" t="n">
-        <v>60.9</v>
+        <v>62.7</v>
       </c>
       <c r="S7" t="n">
-        <v>65.90000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,25 +1766,25 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>225.8401</v>
+        <v>225.12</v>
       </c>
       <c r="X7" t="n">
-        <v>6.28</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.12</v>
+        <v>-4.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.98</v>
+        <v>20.57</v>
       </c>
       <c r="AA7" t="n">
-        <v>23.47</v>
+        <v>24.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>73.31</v>
+        <v>73</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.86</v>
+        <v>46.83</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
@@ -1793,10 +1793,10 @@
         <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>206.3172</v>
+        <v>206.5188</v>
       </c>
       <c r="AG7" t="n">
-        <v>194.5801</v>
+        <v>194.7468</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>67.40000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="AK7" t="n">
         <v>14.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>60.9</v>
+        <v>62.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN7" t="n">
         <v>190.01</v>
@@ -1825,16 +1825,16 @@
         <v>190.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>225.8401</v>
+        <v>225.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>225.8401</v>
+        <v>225.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.460000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.07</v>
+        <v>15.6</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 9.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 65.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 64.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 225.84 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 225.30 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1516237488128</v>
+        <v>1506072985600</v>
       </c>
       <c r="G8" t="n">
-        <v>22.4</v>
+        <v>22.28</v>
       </c>
       <c r="H8" t="n">
-        <v>17.06</v>
+        <v>16.95</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,7 +1933,7 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1942,13 +1942,13 @@
         <v>32.7</v>
       </c>
       <c r="P8" t="n">
-        <v>77.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="R8" t="n">
-        <v>74.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="S8" t="n">
         <v>61.1</v>
@@ -1965,25 +1965,25 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>595.1900000000001</v>
+        <v>591.1950000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-12.64</v>
+        <v>-11.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.39</v>
+        <v>-4.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>-10.83</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>-24.41</v>
+        <v>-23.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>25.28</v>
+        <v>24.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.46</v>
+        <v>37.44</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
@@ -1992,10 +1992,10 @@
         <v>0.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>597.7134</v>
+        <v>597.0848</v>
       </c>
       <c r="AG8" t="n">
-        <v>627.622</v>
+        <v>626.8326</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2009,13 +2009,13 @@
         <v>32.7</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>74.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2024,16 +2024,16 @@
         <v>539.03</v>
       </c>
       <c r="AP8" t="n">
-        <v>646.01</v>
+        <v>645.85</v>
       </c>
       <c r="AQ8" t="n">
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.42</v>
+        <v>-0.99</v>
       </c>
       <c r="AS8" t="n">
-        <v>-5.17</v>
+        <v>-5.69</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 61.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.4%.</t>
+          <t>META: scenario base Hold / Monitor, score 61.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.0%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1338324025344</v>
+        <v>1349402361856</v>
       </c>
       <c r="G10" t="n">
-        <v>313.75</v>
+        <v>305.05</v>
       </c>
       <c r="H10" t="n">
-        <v>155.47</v>
+        <v>156.76</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>61.6</v>
+        <v>63.4</v>
       </c>
       <c r="S10" t="n">
-        <v>26.4</v>
+        <v>27.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,25 +2309,25 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>338.855</v>
+        <v>341.67</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.1</v>
+        <v>-12.63</v>
       </c>
       <c r="Y10" t="n">
-        <v>-23.9</v>
+        <v>-22.93</v>
       </c>
       <c r="Z10" t="n">
-        <v>-20.88</v>
+        <v>-18.08</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.27</v>
+        <v>12.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.52</v>
+        <v>58.48</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
@@ -2336,10 +2336,10 @@
         <v>0.21</v>
       </c>
       <c r="AF10" t="n">
-        <v>372.6919</v>
+        <v>371.0734</v>
       </c>
       <c r="AG10" t="n">
-        <v>406.6247</v>
+        <v>406.0765</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>61.6</v>
+        <v>63.4</v>
       </c>
       <c r="AM10" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>380.84</v>
+        <v>378.93</v>
       </c>
       <c r="AQ10" t="n">
         <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-9.08</v>
+        <v>-7.92</v>
       </c>
       <c r="AS10" t="n">
-        <v>-16.67</v>
+        <v>-15.86</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>15.9</v>
+        <v>17.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 26.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
+          <t>TSLA: scenario base High Risk, score 27.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.9%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3677204512768</v>
+        <v>3566489567232</v>
       </c>
       <c r="G2" t="n">
-        <v>27.6</v>
+        <v>26.79</v>
       </c>
       <c r="H2" t="n">
-        <v>21.01</v>
+        <v>20.37</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -741,25 +741,25 @@
         <v>29.12</v>
       </c>
       <c r="M2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>66.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="Q2" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="R2" t="n">
-        <v>18.8</v>
+        <v>34.4</v>
       </c>
       <c r="S2" t="n">
-        <v>73.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>495.235</v>
+        <v>480.35</v>
       </c>
       <c r="X2" t="n">
-        <v>23.47</v>
+        <v>21.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.22</v>
+        <v>14.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>23.79</v>
+        <v>20.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>-4.11</v>
+        <v>-7.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.13</v>
+        <v>15.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.13</v>
+        <v>26.21</v>
       </c>
       <c r="AD2" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>412.7723</v>
+        <v>413.8216</v>
       </c>
       <c r="AG2" t="n">
-        <v>431.3157</v>
+        <v>431.025</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="AL2" t="n">
-        <v>18.8</v>
+        <v>34.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
         <v>381.58</v>
@@ -838,10 +838,10 @@
         <v>506.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>19.97</v>
+        <v>16.06</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.81</v>
+        <v>11.43</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 20.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 16.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>34.4</v>
+        <v>42.8</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 73.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.0%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.1%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4225919614976</v>
+        <v>4205018349568</v>
       </c>
       <c r="G3" t="n">
-        <v>17.35</v>
+        <v>17.26</v>
       </c>
       <c r="H3" t="n">
-        <v>23.44</v>
+        <v>23.32</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -940,25 +940,25 @@
         <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>55.8</v>
+        <v>56.4</v>
       </c>
       <c r="P3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>39.4</v>
       </c>
       <c r="R3" t="n">
-        <v>76.2</v>
+        <v>75.7</v>
       </c>
       <c r="S3" t="n">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>345.539</v>
+        <v>343.83</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.52</v>
+        <v>-0.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>-13.79</v>
+        <v>-13.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.97</v>
+        <v>12.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>71.58</v>
+        <v>69.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>38.58</v>
+        <v>38.97</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.61</v>
+        <v>30.63</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>353.8783</v>
+        <v>353.3228</v>
       </c>
       <c r="AG3" t="n">
-        <v>331.1022</v>
+        <v>331.4884</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55.8</v>
+        <v>56.4</v>
       </c>
       <c r="AK3" t="n">
         <v>39.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>76.2</v>
+        <v>75.7</v>
       </c>
       <c r="AM3" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
         <v>317.69</v>
@@ -1037,10 +1037,10 @@
         <v>389.8971</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2.36</v>
+        <v>-2.69</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.36</v>
+        <v>3.72</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 69.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.4%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 70.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2840683347968</v>
+        <v>2804117929984</v>
       </c>
       <c r="G4" t="n">
-        <v>21.19</v>
+        <v>20.93</v>
       </c>
       <c r="H4" t="n">
-        <v>25.37</v>
+        <v>24.99</v>
       </c>
       <c r="I4" t="n">
         <v>17.44</v>
@@ -1143,19 +1143,19 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>71.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>67.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="Q4" t="n">
         <v>36.6</v>
       </c>
       <c r="R4" t="n">
-        <v>74.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1169,22 +1169,22 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>263.36</v>
+        <v>259.97</v>
       </c>
       <c r="X4" t="n">
-        <v>5.39</v>
+        <v>5.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.44</v>
+        <v>-1.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>31.94</v>
+        <v>30.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.28</v>
+        <v>12.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>23.35</v>
+        <v>24.87</v>
       </c>
       <c r="AC4" t="n">
         <v>32.27</v>
@@ -1193,13 +1193,13 @@
         <v>-30.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="AF4" t="n">
-        <v>248.1808</v>
+        <v>248.2902</v>
       </c>
       <c r="AG4" t="n">
-        <v>237.706</v>
+        <v>237.8561</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1210,16 +1210,16 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>71.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AK4" t="n">
         <v>36.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>74.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
         <v>226.65</v>
@@ -1234,10 +1234,10 @@
         <v>284.02</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.12</v>
+        <v>4.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.79</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>66.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 69.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.1%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 69.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>606724358144</v>
+        <v>622702886912</v>
       </c>
       <c r="G5" t="n">
-        <v>62.12</v>
+        <v>63.75</v>
       </c>
       <c r="H5" t="n">
-        <v>30.72</v>
+        <v>31.53</v>
       </c>
       <c r="I5" t="n">
         <v>30.11</v>
@@ -1336,7 +1336,7 @@
         <v>9.09</v>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -1345,16 +1345,16 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>20.4</v>
+        <v>19.2</v>
       </c>
       <c r="Q5" t="n">
         <v>16.8</v>
       </c>
       <c r="R5" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="S5" t="n">
-        <v>69.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1579.6</v>
+        <v>1621.2</v>
       </c>
       <c r="X5" t="n">
-        <v>2.07</v>
+        <v>5.61</v>
       </c>
       <c r="Y5" t="n">
-        <v>25.08</v>
+        <v>21.77</v>
       </c>
       <c r="Z5" t="n">
-        <v>33.15</v>
+        <v>35.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>148.93</v>
+        <v>155.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>38.25</v>
+        <v>40.46</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.45</v>
+        <v>39.48</v>
       </c>
       <c r="AD5" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1554.4888</v>
+        <v>1556.1325</v>
       </c>
       <c r="AG5" t="n">
-        <v>1232.9285</v>
+        <v>1238.9715</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>16.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="AM5" t="n">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AN5" t="n">
         <v>1362.2</v>
@@ -1427,16 +1427,16 @@
         <v>1362.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>1609.4</v>
+        <v>1621.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>1719.3295</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.62</v>
+        <v>4.18</v>
       </c>
       <c r="AS5" t="n">
-        <v>28.12</v>
+        <v>30.85</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>57.3</v>
+        <v>57</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>ASML.AS: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4459543920640</v>
+        <v>4461036568576</v>
       </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>35.05</v>
       </c>
       <c r="H6" t="n">
-        <v>32.14</v>
+        <v>32.15</v>
       </c>
       <c r="I6" t="n">
         <v>27.62</v>
@@ -1535,25 +1535,25 @@
         <v>78.44</v>
       </c>
       <c r="M6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>71.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="P6" t="n">
         <v>41.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="R6" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="S6" t="n">
-        <v>68.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>305.57</v>
+        <v>305.68</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.23</v>
+        <v>-8.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.96</v>
+        <v>19.72</v>
       </c>
       <c r="AA6" t="n">
-        <v>31.44</v>
+        <v>31.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.01</v>
+        <v>21.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>26.88</v>
+        <v>26.89</v>
       </c>
       <c r="AD6" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>308.9435</v>
+        <v>308.845</v>
       </c>
       <c r="AG6" t="n">
-        <v>279.984</v>
+        <v>280.1742</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,16 +1608,16 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>71.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="AL6" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
         <v>302.25</v>
@@ -1632,10 +1632,10 @@
         <v>339.7869</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.09</v>
+        <v>-1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.140000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 68.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.1%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 68.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.0%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5452631375872</v>
+        <v>5463288578048</v>
       </c>
       <c r="G7" t="n">
-        <v>34.47</v>
+        <v>34.54</v>
       </c>
       <c r="H7" t="n">
-        <v>17.56</v>
+        <v>17.62</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1734,25 +1734,25 @@
         <v>6.55</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="R7" t="n">
         <v>62.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>62.7</v>
-      </c>
       <c r="S7" t="n">
-        <v>64.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>225.12</v>
+        <v>225.56</v>
       </c>
       <c r="X7" t="n">
-        <v>8.539999999999999</v>
+        <v>11.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.39</v>
+        <v>0.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.57</v>
+        <v>23.54</v>
       </c>
       <c r="AA7" t="n">
-        <v>24.14</v>
+        <v>24.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>73</v>
+        <v>73.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.83</v>
+        <v>46.88</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AF7" t="n">
-        <v>206.5188</v>
+        <v>206.6576</v>
       </c>
       <c r="AG7" t="n">
-        <v>194.7468</v>
+        <v>194.8709</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AL7" t="n">
         <v>62.2</v>
       </c>
-      <c r="AK7" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>62.7</v>
-      </c>
       <c r="AM7" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
         <v>190.01</v>
@@ -1825,16 +1825,16 @@
         <v>190.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>225.3</v>
+        <v>225.56</v>
       </c>
       <c r="AQ7" t="n">
-        <v>225.3</v>
+        <v>225.56</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.01</v>
+        <v>9.15</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.6</v>
+        <v>15.75</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 9.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>40.7</v>
+        <v>42.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 64.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 225.30 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 225.56 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1506072985600</v>
+        <v>1447467548672</v>
       </c>
       <c r="G8" t="n">
-        <v>22.28</v>
+        <v>21.41</v>
       </c>
       <c r="H8" t="n">
-        <v>16.95</v>
+        <v>16.29</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>32.7</v>
+        <v>26.2</v>
       </c>
       <c r="P8" t="n">
-        <v>78.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>73.8</v>
+        <v>68.3</v>
       </c>
       <c r="S8" t="n">
-        <v>61.1</v>
+        <v>59.3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>591.1950000000001</v>
+        <v>568.1900000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.04</v>
+        <v>-12.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>-4.32</v>
+        <v>-7.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>-8.859999999999999</v>
+        <v>-11.03</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.97</v>
+        <v>-27.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.96</v>
+        <v>26.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.44</v>
+        <v>37.47</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>597.0848</v>
+        <v>595.8819</v>
       </c>
       <c r="AG8" t="n">
-        <v>626.8326</v>
+        <v>625.9193</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32.7</v>
+        <v>26.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>73.8</v>
+        <v>68.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2024,16 +2024,16 @@
         <v>539.03</v>
       </c>
       <c r="AP8" t="n">
-        <v>645.85</v>
+        <v>643.8099999999999</v>
       </c>
       <c r="AQ8" t="n">
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.99</v>
+        <v>-4.64</v>
       </c>
       <c r="AS8" t="n">
-        <v>-5.69</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>43</v>
+        <v>39.8</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 61.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.0%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1349402361856</v>
+        <v>1346242740224</v>
       </c>
       <c r="G10" t="n">
-        <v>305.05</v>
+        <v>309.87</v>
       </c>
       <c r="H10" t="n">
-        <v>156.76</v>
+        <v>156.72</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>7.2</v>
+        <v>12.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
       <c r="S10" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,22 +2309,22 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>341.67</v>
+        <v>340.8601</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.63</v>
+        <v>-10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>-22.93</v>
+        <v>-19.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>-18.08</v>
+        <v>-18.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.57</v>
+        <v>15.94</v>
       </c>
       <c r="AC10" t="n">
         <v>58.48</v>
@@ -2333,13 +2333,13 @@
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="AF10" t="n">
-        <v>371.0734</v>
+        <v>369.5336</v>
       </c>
       <c r="AG10" t="n">
-        <v>406.0765</v>
+        <v>405.481</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7.2</v>
+        <v>12.4</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
       <c r="AM10" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2374,10 +2374,10 @@
         <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-7.92</v>
+        <v>-7.76</v>
       </c>
       <c r="AS10" t="n">
-        <v>-15.86</v>
+        <v>-15.94</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 7.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>17.3</v>
+        <v>18.7</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 27.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.9%.</t>
+          <t>TSLA: scenario base High Risk, score 28.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.8%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3566489567232</v>
+        <v>3584756547584</v>
       </c>
       <c r="G2" t="n">
-        <v>26.79</v>
+        <v>26.86</v>
       </c>
       <c r="H2" t="n">
-        <v>20.37</v>
+        <v>20.48</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -741,25 +741,25 @@
         <v>29.12</v>
       </c>
       <c r="M2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>80</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>68</v>
+        <v>67.7</v>
       </c>
       <c r="Q2" t="n">
         <v>40.9</v>
       </c>
       <c r="R2" t="n">
-        <v>34.4</v>
+        <v>33.6</v>
       </c>
       <c r="S2" t="n">
-        <v>71.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>480.35</v>
+        <v>482.76</v>
       </c>
       <c r="X2" t="n">
-        <v>21.97</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.1</v>
+        <v>14.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.23</v>
+        <v>22.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>-7.33</v>
+        <v>-6.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.78</v>
+        <v>16.02</v>
       </c>
       <c r="AC2" t="n">
         <v>26.21</v>
@@ -797,13 +797,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>413.8216</v>
+        <v>415.1434</v>
       </c>
       <c r="AG2" t="n">
-        <v>431.025</v>
+        <v>430.748</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,13 +814,13 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>40.9</v>
       </c>
       <c r="AL2" t="n">
-        <v>34.4</v>
+        <v>33.6</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
@@ -838,10 +838,10 @@
         <v>506.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.06</v>
+        <v>16.28</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.43</v>
+        <v>12.07</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 16.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 16.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.1%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 72.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.3%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -910,55 +910,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4205018349568</v>
+        <v>4526676901888</v>
       </c>
       <c r="G3" t="n">
-        <v>17.26</v>
+        <v>35.61</v>
       </c>
       <c r="H3" t="n">
-        <v>23.32</v>
+        <v>32.62</v>
       </c>
       <c r="I3" t="n">
-        <v>54.77</v>
+        <v>27.62</v>
       </c>
       <c r="J3" t="n">
-        <v>48.68</v>
+        <v>148.75</v>
       </c>
       <c r="K3" t="n">
-        <v>24.2</v>
+        <v>16.4</v>
       </c>
       <c r="L3" t="n">
-        <v>18.86</v>
+        <v>78.44</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>56.4</v>
+        <v>75.2</v>
       </c>
       <c r="P3" t="n">
-        <v>74.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.4</v>
+        <v>41</v>
       </c>
       <c r="R3" t="n">
-        <v>75.7</v>
+        <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,75 +972,75 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>343.83</v>
+        <v>310.17</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.85</v>
+        <v>-4.95</v>
       </c>
       <c r="Y3" t="n">
-        <v>-13.29</v>
+        <v>4.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.61</v>
+        <v>17.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>69.91</v>
+        <v>34.43</v>
       </c>
       <c r="AB3" t="n">
-        <v>38.97</v>
+        <v>21.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.63</v>
+        <v>26.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>-29.81</v>
+        <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.27</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>353.3228</v>
+        <v>308.9051</v>
       </c>
       <c r="AG3" t="n">
-        <v>331.4884</v>
+        <v>280.381</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>56.4</v>
+        <v>75.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>39.4</v>
+        <v>41</v>
       </c>
       <c r="AL3" t="n">
-        <v>75.7</v>
+        <v>82.8</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
       </c>
       <c r="AN3" t="n">
-        <v>317.69</v>
+        <v>302.25</v>
       </c>
       <c r="AO3" t="n">
-        <v>317.69</v>
+        <v>274.9129</v>
       </c>
       <c r="AP3" t="n">
-        <v>377.65</v>
+        <v>339.7869</v>
       </c>
       <c r="AQ3" t="n">
-        <v>389.8971</v>
+        <v>339.7869</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2.69</v>
+        <v>0.41</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.72</v>
+        <v>10.62</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>64.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 70.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 70.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 389.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,53 +1109,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2804117929984</v>
+        <v>4193277706240</v>
       </c>
       <c r="G4" t="n">
-        <v>20.93</v>
+        <v>17.21</v>
       </c>
       <c r="H4" t="n">
-        <v>24.99</v>
+        <v>23.25</v>
       </c>
       <c r="I4" t="n">
-        <v>17.44</v>
+        <v>54.77</v>
       </c>
       <c r="J4" t="n">
-        <v>30.56</v>
+        <v>48.68</v>
       </c>
       <c r="K4" t="n">
-        <v>19.6</v>
+        <v>24.2</v>
       </c>
       <c r="L4" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>18.86</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26</v>
+      </c>
       <c r="N4" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>69.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="P4" t="n">
-        <v>68.2</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="n">
-        <v>36.6</v>
+        <v>39.4</v>
       </c>
       <c r="R4" t="n">
-        <v>79.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="S4" t="n">
-        <v>69.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1169,75 +1171,75 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>259.97</v>
+        <v>342.87</v>
       </c>
       <c r="X4" t="n">
-        <v>5.15</v>
+        <v>-2.59</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.58</v>
+        <v>-13.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>30.78</v>
+        <v>13.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.55</v>
+        <v>68.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.87</v>
+        <v>39.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>32.27</v>
+        <v>30.61</v>
       </c>
       <c r="AD4" t="n">
-        <v>-30.88</v>
+        <v>-29.81</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.77</v>
+        <v>1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>248.2902</v>
+        <v>352.8174</v>
       </c>
       <c r="AG4" t="n">
-        <v>237.8561</v>
+        <v>331.8335</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>69.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="AK4" t="n">
-        <v>36.6</v>
+        <v>39.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>79.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="AM4" t="n">
         <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>226.65</v>
+        <v>317.69</v>
       </c>
       <c r="AO4" t="n">
-        <v>226.65</v>
+        <v>317.69</v>
       </c>
       <c r="AP4" t="n">
-        <v>284.02</v>
+        <v>377.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>284.02</v>
+        <v>389.8971</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.7</v>
+        <v>-2.82</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.300000000000001</v>
+        <v>3.33</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1255,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>67.2</v>
+        <v>64.8</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 69.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 70.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 389.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1284,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1306,55 +1308,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>622702886912</v>
+        <v>2809025527808</v>
       </c>
       <c r="G5" t="n">
-        <v>63.75</v>
+        <v>20.93</v>
       </c>
       <c r="H5" t="n">
-        <v>31.53</v>
+        <v>25.03</v>
       </c>
       <c r="I5" t="n">
-        <v>30.11</v>
+        <v>17.44</v>
       </c>
       <c r="J5" t="n">
-        <v>53.94</v>
+        <v>30.56</v>
       </c>
       <c r="K5" t="n">
-        <v>21.3</v>
+        <v>19.6</v>
       </c>
       <c r="L5" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="M5" t="n">
-        <v>49</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>68.5</v>
       </c>
       <c r="P5" t="n">
-        <v>19.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.8</v>
+        <v>36.6</v>
       </c>
       <c r="R5" t="n">
-        <v>82</v>
+        <v>79.7</v>
       </c>
       <c r="S5" t="n">
-        <v>68.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1363,42 +1363,42 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1621.2</v>
+        <v>260.425</v>
       </c>
       <c r="X5" t="n">
-        <v>5.61</v>
+        <v>4.17</v>
       </c>
       <c r="Y5" t="n">
-        <v>21.77</v>
+        <v>-1.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.65</v>
+        <v>29.47</v>
       </c>
       <c r="AA5" t="n">
-        <v>155.69</v>
+        <v>12.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>40.46</v>
+        <v>25.19</v>
       </c>
       <c r="AC5" t="n">
-        <v>39.48</v>
+        <v>32.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>-44.77</v>
+        <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>1556.1325</v>
+        <v>248.6049</v>
       </c>
       <c r="AG5" t="n">
-        <v>1238.9715</v>
+        <v>238.0134</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,34 +1409,34 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>68.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.8</v>
+        <v>36.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>82</v>
+        <v>79.7</v>
       </c>
       <c r="AM5" t="n">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>1362.2</v>
+        <v>226.65</v>
       </c>
       <c r="AO5" t="n">
-        <v>1362.2</v>
+        <v>226.65</v>
       </c>
       <c r="AP5" t="n">
-        <v>1621.2</v>
+        <v>284.02</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1719.3295</v>
+        <v>284.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.18</v>
+        <v>4.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>30.85</v>
+        <v>9.42</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>57</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.2%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.8%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1362.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,19 +1483,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1510,94 +1510,94 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4461036568576</v>
+        <v>592205381632</v>
       </c>
       <c r="G6" t="n">
-        <v>35.05</v>
+        <v>60.58</v>
       </c>
       <c r="H6" t="n">
-        <v>32.15</v>
+        <v>29.98</v>
       </c>
       <c r="I6" t="n">
-        <v>27.62</v>
+        <v>30.11</v>
       </c>
       <c r="J6" t="n">
-        <v>148.75</v>
+        <v>53.94</v>
       </c>
       <c r="K6" t="n">
-        <v>16.4</v>
+        <v>21.3</v>
       </c>
       <c r="L6" t="n">
-        <v>78.44</v>
+        <v>9.09</v>
       </c>
       <c r="M6" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>41.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>16.6</v>
       </c>
       <c r="R6" t="n">
         <v>78.2</v>
       </c>
       <c r="S6" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>305.68</v>
+        <v>1541.8</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.33</v>
+        <v>0.43</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.9</v>
+        <v>15.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.72</v>
+        <v>29.01</v>
       </c>
       <c r="AA6" t="n">
-        <v>31.8</v>
+        <v>143.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>21.33</v>
+        <v>37.79</v>
       </c>
       <c r="AC6" t="n">
-        <v>26.89</v>
+        <v>39.61</v>
       </c>
       <c r="AD6" t="n">
-        <v>-33.36</v>
+        <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>308.845</v>
+        <v>1558.2845</v>
       </c>
       <c r="AG6" t="n">
-        <v>280.1742</v>
+        <v>1239.5095</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,34 +1608,34 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>41</v>
+        <v>16.6</v>
       </c>
       <c r="AL6" t="n">
         <v>78.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="AN6" t="n">
-        <v>302.25</v>
+        <v>1362.2</v>
       </c>
       <c r="AO6" t="n">
-        <v>274.9129</v>
+        <v>1362.2</v>
       </c>
       <c r="AP6" t="n">
-        <v>339.7869</v>
+        <v>1621.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>339.7869</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.03</v>
+        <v>-1.06</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.1</v>
+        <v>24.39</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>67.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 68.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.1%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1362.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5463288578048</v>
+        <v>5324502204416</v>
       </c>
       <c r="G7" t="n">
-        <v>34.54</v>
+        <v>33.66</v>
       </c>
       <c r="H7" t="n">
-        <v>17.62</v>
+        <v>17.13</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1740,19 +1740,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>70.5</v>
+        <v>65.5</v>
       </c>
       <c r="P7" t="n">
-        <v>62.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>14.2</v>
       </c>
       <c r="R7" t="n">
-        <v>62.2</v>
+        <v>73.8</v>
       </c>
       <c r="S7" t="n">
-        <v>66.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>225.56</v>
+        <v>219.83</v>
       </c>
       <c r="X7" t="n">
-        <v>11.22</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.22</v>
+        <v>-1</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.54</v>
+        <v>18.99</v>
       </c>
       <c r="AA7" t="n">
-        <v>24.09</v>
+        <v>21.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>73.91</v>
+        <v>72.48</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.88</v>
+        <v>46.9</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AF7" t="n">
-        <v>206.6576</v>
+        <v>206.9412</v>
       </c>
       <c r="AG7" t="n">
-        <v>194.8709</v>
+        <v>194.9334</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,13 +1807,13 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70.5</v>
+        <v>65.5</v>
       </c>
       <c r="AK7" t="n">
         <v>14.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>62.2</v>
+        <v>73.8</v>
       </c>
       <c r="AM7" t="n">
         <v>752</v>
@@ -1825,16 +1825,16 @@
         <v>190.01</v>
       </c>
       <c r="AP7" t="n">
-        <v>225.56</v>
+        <v>225.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>225.56</v>
+        <v>225.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.15</v>
+        <v>6.23</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.75</v>
+        <v>12.77</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>42.4</v>
+        <v>48.6</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.2%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 67.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.2%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 225.56 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 225.30 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1447467548672</v>
+        <v>1387550081024</v>
       </c>
       <c r="G8" t="n">
-        <v>21.41</v>
+        <v>20.5</v>
       </c>
       <c r="H8" t="n">
-        <v>16.29</v>
+        <v>15.61</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,25 +1933,25 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>26.2</v>
+        <v>18.5</v>
       </c>
       <c r="P8" t="n">
-        <v>80.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="R8" t="n">
-        <v>68.3</v>
+        <v>62.6</v>
       </c>
       <c r="S8" t="n">
-        <v>59.3</v>
+        <v>57.1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>568.1900000000001</v>
+        <v>544.6849999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-12.05</v>
+        <v>-15.66</v>
       </c>
       <c r="Y8" t="n">
-        <v>-7.41</v>
+        <v>-10.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11.03</v>
+        <v>-14.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>-27.12</v>
+        <v>-30.41</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.37</v>
+        <v>24.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.47</v>
+        <v>37.55</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>595.8819</v>
+        <v>594.9422</v>
       </c>
       <c r="AG8" t="n">
-        <v>625.9193</v>
+        <v>624.898</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26.2</v>
+        <v>18.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>68.3</v>
+        <v>62.6</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
@@ -2024,16 +2024,16 @@
         <v>539.03</v>
       </c>
       <c r="AP8" t="n">
-        <v>643.8099999999999</v>
+        <v>627.17</v>
       </c>
       <c r="AQ8" t="n">
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-4.64</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>-9.220000000000001</v>
+        <v>-12.84</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>39.8</v>
+        <v>36.3</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 57.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.4%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1346242740224</v>
+        <v>1326534492160</v>
       </c>
       <c r="G10" t="n">
-        <v>309.87</v>
+        <v>308.14</v>
       </c>
       <c r="H10" t="n">
-        <v>156.72</v>
+        <v>154.42</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>12.4</v>
+        <v>14.2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>63.6</v>
+        <v>62</v>
       </c>
       <c r="S10" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,22 +2309,22 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>340.8601</v>
+        <v>335.87</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.5</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>-19.27</v>
+        <v>-18.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>-18.35</v>
+        <v>-18.21</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.94</v>
+        <v>16.04</v>
       </c>
       <c r="AC10" t="n">
         <v>58.48</v>
@@ -2336,10 +2336,10 @@
         <v>0.27</v>
       </c>
       <c r="AF10" t="n">
-        <v>369.5336</v>
+        <v>368.3998</v>
       </c>
       <c r="AG10" t="n">
-        <v>405.481</v>
+        <v>404.845</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12.4</v>
+        <v>14.2</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>63.6</v>
+        <v>62</v>
       </c>
       <c r="AM10" t="n">
         <v>752</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>378.93</v>
+        <v>374.01</v>
       </c>
       <c r="AQ10" t="n">
         <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-7.76</v>
+        <v>-8.83</v>
       </c>
       <c r="AS10" t="n">
-        <v>-15.94</v>
+        <v>-17.04</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 7.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 28.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.8%.</t>
+          <t>TSLA: scenario base High Risk, score 29.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3584756547584</v>
+        <v>3592144814080</v>
       </c>
       <c r="G2" t="n">
-        <v>26.86</v>
+        <v>26.94</v>
       </c>
       <c r="H2" t="n">
-        <v>20.48</v>
+        <v>20.52</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -747,19 +747,19 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>81.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="S2" t="n">
-        <v>72.2</v>
+        <v>72.8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>482.76</v>
+        <v>483.755</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>21.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.23</v>
+        <v>16.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.19</v>
+        <v>21.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6.45</v>
+        <v>-5.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.02</v>
+        <v>15.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.21</v>
+        <v>26.19</v>
       </c>
       <c r="AD2" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="AF2" t="n">
-        <v>415.1434</v>
+        <v>416.5611</v>
       </c>
       <c r="AG2" t="n">
-        <v>430.748</v>
+        <v>430.5489</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,13 +814,13 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>81.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
@@ -838,10 +838,10 @@
         <v>506.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.28</v>
+        <v>16.13</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.07</v>
+        <v>12.36</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 16.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 16.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>42.6</v>
+        <v>43.6</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 72.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.3%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.1%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4526676901888</v>
+        <v>4596509966336</v>
       </c>
       <c r="G3" t="n">
-        <v>35.61</v>
+        <v>36.16</v>
       </c>
       <c r="H3" t="n">
-        <v>32.62</v>
+        <v>33.02</v>
       </c>
       <c r="I3" t="n">
         <v>27.62</v>
@@ -946,10 +946,10 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>75.2</v>
+        <v>78.5</v>
       </c>
       <c r="P3" t="n">
-        <v>40.2</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="n">
         <v>41</v>
@@ -958,7 +958,7 @@
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>70.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>310.17</v>
+        <v>314.955</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.95</v>
+        <v>-3.82</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.23</v>
+        <v>5.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.75</v>
+        <v>19.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>34.43</v>
+        <v>36.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>21.81</v>
+        <v>22.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.91</v>
+        <v>26.92</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>308.9051</v>
+        <v>309.1758</v>
       </c>
       <c r="AG3" t="n">
-        <v>280.381</v>
+        <v>280.6031</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75.2</v>
+        <v>78.5</v>
       </c>
       <c r="AK3" t="n">
         <v>41</v>
@@ -1037,10 +1037,10 @@
         <v>339.7869</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.41</v>
+        <v>1.87</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.62</v>
+        <v>12.24</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>69.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 70.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.9%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4193277706240</v>
+        <v>4211867648000</v>
       </c>
       <c r="G4" t="n">
-        <v>17.21</v>
+        <v>17.28</v>
       </c>
       <c r="H4" t="n">
-        <v>23.25</v>
+        <v>23.35</v>
       </c>
       <c r="I4" t="n">
         <v>54.77</v>
@@ -1145,19 +1145,19 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>56.4</v>
+        <v>60.1</v>
       </c>
       <c r="P4" t="n">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="Q4" t="n">
         <v>39.4</v>
       </c>
       <c r="R4" t="n">
-        <v>75.5</v>
+        <v>76.3</v>
       </c>
       <c r="S4" t="n">
-        <v>70.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>342.87</v>
+        <v>344.39</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.59</v>
+        <v>-0.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>-13.57</v>
+        <v>-11.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.67</v>
+        <v>13.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>68.64</v>
+        <v>69.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>39.73</v>
+        <v>39.61</v>
       </c>
       <c r="AC4" t="n">
         <v>30.61</v>
@@ -1195,13 +1195,13 @@
         <v>-29.81</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF4" t="n">
-        <v>352.8174</v>
+        <v>352.4656</v>
       </c>
       <c r="AG4" t="n">
-        <v>331.8335</v>
+        <v>332.1574</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,13 +1212,13 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>56.4</v>
+        <v>60.1</v>
       </c>
       <c r="AK4" t="n">
         <v>39.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>75.5</v>
+        <v>76.3</v>
       </c>
       <c r="AM4" t="n">
         <v>752</v>
@@ -1236,10 +1236,10 @@
         <v>389.8971</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2.82</v>
+        <v>-2.29</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.33</v>
+        <v>3.68</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>64.8</v>
+        <v>66</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 70.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 71.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2809025527808</v>
+        <v>2849204600832</v>
       </c>
       <c r="G5" t="n">
-        <v>20.93</v>
+        <v>21.25</v>
       </c>
       <c r="H5" t="n">
-        <v>25.03</v>
+        <v>25.39</v>
       </c>
       <c r="I5" t="n">
         <v>17.44</v>
@@ -1342,19 +1342,19 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>68.5</v>
+        <v>73.5</v>
       </c>
       <c r="P5" t="n">
-        <v>68.09999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="Q5" t="n">
         <v>36.6</v>
       </c>
       <c r="R5" t="n">
-        <v>79.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>69.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,25 +1368,25 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>260.425</v>
+        <v>264.15</v>
       </c>
       <c r="X5" t="n">
-        <v>4.17</v>
+        <v>6.71</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.47</v>
+        <v>28.99</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.72</v>
+        <v>14.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.19</v>
+        <v>25.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>32.27</v>
+        <v>32.28</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
@@ -1395,10 +1395,10 @@
         <v>0.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>248.6049</v>
+        <v>248.964</v>
       </c>
       <c r="AG5" t="n">
-        <v>238.0134</v>
+        <v>238.215</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>68.5</v>
+        <v>73.5</v>
       </c>
       <c r="AK5" t="n">
         <v>36.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>79.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AM5" t="n">
         <v>752</v>
@@ -1433,10 +1433,10 @@
         <v>284.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.75</v>
+        <v>6.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.42</v>
+        <v>10.89</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.8%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 70.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>592205381632</v>
+        <v>579069149184</v>
       </c>
       <c r="G6" t="n">
-        <v>60.58</v>
+        <v>59.26</v>
       </c>
       <c r="H6" t="n">
-        <v>29.98</v>
+        <v>29.32</v>
       </c>
       <c r="I6" t="n">
         <v>30.11</v>
@@ -1535,7 +1535,7 @@
         <v>9.09</v>
       </c>
       <c r="M6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1544,16 +1544,16 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q6" t="n">
         <v>16.6</v>
       </c>
       <c r="R6" t="n">
-        <v>78.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>67.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1541.8</v>
+        <v>1507.6</v>
       </c>
       <c r="X6" t="n">
-        <v>0.43</v>
+        <v>-1.79</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.8</v>
+        <v>13.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>29.01</v>
+        <v>26.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>143.17</v>
+        <v>137.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>37.79</v>
+        <v>36.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.61</v>
+        <v>39.62</v>
       </c>
       <c r="AD6" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AF6" t="n">
-        <v>1558.2845</v>
+        <v>1558.057</v>
       </c>
       <c r="AG6" t="n">
-        <v>1239.5095</v>
+        <v>1239.4527</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
         <v>16.6</v>
       </c>
       <c r="AL6" t="n">
-        <v>78.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AN6" t="n">
         <v>1362.2</v>
@@ -1632,10 +1632,10 @@
         <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.06</v>
+        <v>-3.24</v>
       </c>
       <c r="AS6" t="n">
-        <v>24.39</v>
+        <v>21.63</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>55.6</v>
+        <v>54.6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.1%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.2%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5324502204416</v>
+        <v>5315298328576</v>
       </c>
       <c r="G7" t="n">
-        <v>33.66</v>
+        <v>33.61</v>
       </c>
       <c r="H7" t="n">
-        <v>17.13</v>
+        <v>17.1</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1734,22 +1734,22 @@
         <v>6.55</v>
       </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>65.5</v>
+        <v>64.8</v>
       </c>
       <c r="P7" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="R7" t="n">
-        <v>73.8</v>
+        <v>75</v>
       </c>
       <c r="S7" t="n">
         <v>67.09999999999999</v>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>219.83</v>
+        <v>219.4684</v>
       </c>
       <c r="X7" t="n">
-        <v>8.140000000000001</v>
+        <v>5.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.99</v>
+        <v>16.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.99</v>
+        <v>20.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>72.48</v>
+        <v>67.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.9</v>
+        <v>46.66</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>206.9412</v>
+        <v>207.156</v>
       </c>
       <c r="AG7" t="n">
-        <v>194.9334</v>
+        <v>195.0172</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,13 +1807,13 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65.5</v>
+        <v>64.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>73.8</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
         <v>752</v>
@@ -1831,10 +1831,10 @@
         <v>225.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.23</v>
+        <v>5.94</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.77</v>
+        <v>12.54</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 67.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.2%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 67.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.9%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1387550081024</v>
+        <v>1404453126144</v>
       </c>
       <c r="G8" t="n">
-        <v>20.5</v>
+        <v>20.78</v>
       </c>
       <c r="H8" t="n">
-        <v>15.61</v>
+        <v>15.89</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,25 +1933,25 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>18.5</v>
+        <v>22.7</v>
       </c>
       <c r="P8" t="n">
-        <v>82.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>27.6</v>
       </c>
       <c r="R8" t="n">
-        <v>62.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>544.6849999999999</v>
+        <v>551.3051</v>
       </c>
       <c r="X8" t="n">
-        <v>-15.66</v>
+        <v>-14.37</v>
       </c>
       <c r="Y8" t="n">
-        <v>-10.8</v>
+        <v>-8.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>-14.65</v>
+        <v>-14.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>-30.41</v>
+        <v>-27.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.86</v>
+        <v>24.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.55</v>
+        <v>37.54</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>594.9422</v>
+        <v>594.2511</v>
       </c>
       <c r="AG8" t="n">
-        <v>624.898</v>
+        <v>624.3258</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18.5</v>
+        <v>22.7</v>
       </c>
       <c r="AK8" t="n">
         <v>27.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>62.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
@@ -2024,16 +2024,16 @@
         <v>539.03</v>
       </c>
       <c r="AP8" t="n">
-        <v>627.17</v>
+        <v>606.1</v>
       </c>
       <c r="AQ8" t="n">
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-8.449999999999999</v>
+        <v>-7.23</v>
       </c>
       <c r="AS8" t="n">
-        <v>-12.84</v>
+        <v>-11.7</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 8.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>36.3</v>
+        <v>37.8</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 57.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.4%.</t>
+          <t>META: scenario base Hold / Monitor, score 58.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1326534492160</v>
+        <v>1375587926016</v>
       </c>
       <c r="G10" t="n">
-        <v>308.14</v>
+        <v>322.49</v>
       </c>
       <c r="H10" t="n">
-        <v>154.42</v>
+        <v>160.13</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>62</v>
+        <v>67.5</v>
       </c>
       <c r="S10" t="n">
-        <v>29</v>
+        <v>31.6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>335.87</v>
+        <v>348.295</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.119999999999999</v>
+        <v>-8.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>-18.08</v>
+        <v>-13.81</v>
       </c>
       <c r="Z10" t="n">
-        <v>-18.21</v>
+        <v>-15.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>3.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.04</v>
+        <v>14.71</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.48</v>
+        <v>58.36</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>368.3998</v>
+        <v>367.2067</v>
       </c>
       <c r="AG10" t="n">
-        <v>404.845</v>
+        <v>404.391</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>62</v>
+        <v>67.5</v>
       </c>
       <c r="AM10" t="n">
         <v>752</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>374.01</v>
+        <v>348.29</v>
       </c>
       <c r="AQ10" t="n">
         <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-8.83</v>
+        <v>-5.15</v>
       </c>
       <c r="AS10" t="n">
-        <v>-17.04</v>
+        <v>-13.87</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.2% sotto MA50: attendere recupero; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>18.7</v>
+        <v>22.5</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 29.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
+          <t>TSLA: scenario base High Risk, score 31.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3592144814080</v>
+        <v>3580078325760</v>
       </c>
       <c r="G2" t="n">
-        <v>26.94</v>
+        <v>26.83</v>
       </c>
       <c r="H2" t="n">
-        <v>20.52</v>
+        <v>20.45</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -741,25 +741,25 @@
         <v>29.12</v>
       </c>
       <c r="M2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>84.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="P2" t="n">
-        <v>67.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>34.2</v>
+        <v>37.5</v>
       </c>
       <c r="S2" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>483.755</v>
+        <v>482.13</v>
       </c>
       <c r="X2" t="n">
-        <v>21.62</v>
+        <v>23.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.14</v>
+        <v>14.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.6</v>
+        <v>21.26</v>
       </c>
       <c r="AA2" t="n">
-        <v>-5.7</v>
+        <v>-4.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.45</v>
+        <v>15.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.19</v>
+        <v>26.18</v>
       </c>
       <c r="AD2" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="AF2" t="n">
-        <v>416.5611</v>
+        <v>418.1466</v>
       </c>
       <c r="AG2" t="n">
-        <v>430.5489</v>
+        <v>430.3896</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,19 +814,19 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>84.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AK2" t="n">
         <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>34.2</v>
+        <v>37.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN2" t="n">
-        <v>381.58</v>
+        <v>381.7</v>
       </c>
       <c r="AO2" t="n">
         <v>352.83</v>
@@ -838,10 +838,10 @@
         <v>506.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.13</v>
+        <v>15.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.36</v>
+        <v>12.02</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 16.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 15.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>43.6</v>
+        <v>45.6</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.1%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.3%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4596509966336</v>
+        <v>4596729118720</v>
       </c>
       <c r="G3" t="n">
         <v>36.16</v>
@@ -940,13 +940,13 @@
         <v>78.44</v>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>78.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="P3" t="n">
         <v>39</v>
@@ -958,7 +958,7 @@
         <v>82.8</v>
       </c>
       <c r="S3" t="n">
-        <v>71.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,25 +972,25 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>314.955</v>
+        <v>314.95</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.82</v>
+        <v>-3.27</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.44</v>
+        <v>4.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.36</v>
+        <v>21.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>36.91</v>
+        <v>37.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>22.12</v>
+        <v>22.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.92</v>
+        <v>26.91</v>
       </c>
       <c r="AD3" t="n">
         <v>-33.36</v>
@@ -999,10 +999,10 @@
         <v>0.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>309.1758</v>
+        <v>309.7063</v>
       </c>
       <c r="AG3" t="n">
-        <v>280.6031</v>
+        <v>280.8403</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>41</v>
@@ -1022,7 +1022,7 @@
         <v>82.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN3" t="n">
         <v>302.25</v>
@@ -1037,10 +1037,10 @@
         <v>339.7869</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.24</v>
+        <v>12.15</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 71.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 71.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.7%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4211867648000</v>
+        <v>4161602322432</v>
       </c>
       <c r="G4" t="n">
-        <v>17.28</v>
+        <v>17.08</v>
       </c>
       <c r="H4" t="n">
-        <v>23.35</v>
+        <v>22.98</v>
       </c>
       <c r="I4" t="n">
         <v>54.77</v>
@@ -1145,19 +1145,19 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>60.1</v>
+        <v>57.4</v>
       </c>
       <c r="P4" t="n">
-        <v>74.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>39.4</v>
       </c>
       <c r="R4" t="n">
-        <v>76.3</v>
+        <v>74.8</v>
       </c>
       <c r="S4" t="n">
-        <v>71.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>344.39</v>
+        <v>340.28</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8</v>
+        <v>-0.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>-11.11</v>
+        <v>-12.45</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.68</v>
+        <v>12.51</v>
       </c>
       <c r="AA4" t="n">
-        <v>69.72</v>
+        <v>69.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>39.61</v>
+        <v>38.99</v>
       </c>
       <c r="AC4" t="n">
-        <v>30.61</v>
+        <v>30.6</v>
       </c>
       <c r="AD4" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>352.4656</v>
+        <v>351.9926</v>
       </c>
       <c r="AG4" t="n">
-        <v>332.1574</v>
+        <v>332.4573</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60.1</v>
+        <v>57.4</v>
       </c>
       <c r="AK4" t="n">
         <v>39.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>76.3</v>
+        <v>74.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN4" t="n">
-        <v>317.69</v>
+        <v>319.74</v>
       </c>
       <c r="AO4" t="n">
         <v>317.69</v>
@@ -1236,10 +1236,10 @@
         <v>389.8971</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2.29</v>
+        <v>-3.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.68</v>
+        <v>2.35</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>66</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 71.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.3%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 70.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.3%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2849204600832</v>
+        <v>2815281856512</v>
       </c>
       <c r="G5" t="n">
-        <v>21.25</v>
+        <v>20.98</v>
       </c>
       <c r="H5" t="n">
-        <v>25.39</v>
+        <v>25.15</v>
       </c>
       <c r="I5" t="n">
         <v>17.44</v>
@@ -1342,19 +1342,19 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>73.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>67.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="R5" t="n">
-        <v>74.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="S5" t="n">
-        <v>70</v>
+        <v>69.3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>264.15</v>
+        <v>261.005</v>
       </c>
       <c r="X5" t="n">
-        <v>6.71</v>
+        <v>6.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>-1.51</v>
       </c>
       <c r="Z5" t="n">
-        <v>28.99</v>
+        <v>27.41</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.11</v>
+        <v>14.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.32</v>
+        <v>24.79</v>
       </c>
       <c r="AC5" t="n">
-        <v>32.28</v>
+        <v>32.29</v>
       </c>
       <c r="AD5" t="n">
         <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AF5" t="n">
-        <v>248.964</v>
+        <v>249.3341</v>
       </c>
       <c r="AG5" t="n">
-        <v>238.215</v>
+        <v>238.3073</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1409,16 +1409,16 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>73.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>74.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN5" t="n">
         <v>226.65</v>
@@ -1433,10 +1433,10 @@
         <v>284.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.1</v>
+        <v>4.68</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.89</v>
+        <v>9.52</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>66.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 70.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.1%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 69.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>579069149184</v>
+        <v>578224128000</v>
       </c>
       <c r="G6" t="n">
-        <v>59.26</v>
+        <v>59.08</v>
       </c>
       <c r="H6" t="n">
-        <v>29.32</v>
+        <v>29.27</v>
       </c>
       <c r="I6" t="n">
         <v>30.11</v>
@@ -1535,7 +1535,7 @@
         <v>9.09</v>
       </c>
       <c r="M6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1544,13 +1544,13 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="R6" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="S6" t="n">
         <v>67.59999999999999</v>
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1507.6</v>
+        <v>1505.4</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.79</v>
+        <v>-5.41</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.23</v>
+        <v>12.04</v>
       </c>
       <c r="Z6" t="n">
-        <v>26.15</v>
+        <v>21.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>137.77</v>
+        <v>138.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>36.72</v>
+        <v>36.59</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.62</v>
+        <v>39.59</v>
       </c>
       <c r="AD6" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>1558.057</v>
+        <v>1558.0333</v>
       </c>
       <c r="AG6" t="n">
-        <v>1239.4527</v>
+        <v>1242.3692</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AN6" t="n">
         <v>1362.2</v>
@@ -1632,10 +1632,10 @@
         <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>-3.24</v>
+        <v>-3.38</v>
       </c>
       <c r="AS6" t="n">
-        <v>21.63</v>
+        <v>21.17</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5315298328576</v>
+        <v>5254261243904</v>
       </c>
       <c r="G7" t="n">
-        <v>33.61</v>
+        <v>33.22</v>
       </c>
       <c r="H7" t="n">
-        <v>17.1</v>
+        <v>16.69</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1740,19 +1740,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>64.8</v>
+        <v>61.3</v>
       </c>
       <c r="P7" t="n">
-        <v>64.7</v>
+        <v>65.8</v>
       </c>
       <c r="Q7" t="n">
         <v>14.5</v>
       </c>
       <c r="R7" t="n">
-        <v>75</v>
+        <v>80.2</v>
       </c>
       <c r="S7" t="n">
-        <v>67.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>219.4684</v>
+        <v>216.93</v>
       </c>
       <c r="X7" t="n">
-        <v>5.88</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.4</v>
+        <v>-2.81</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.89</v>
+        <v>15.59</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.74</v>
+        <v>23.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>67.75</v>
+        <v>66.98</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.66</v>
+        <v>46.64</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>207.156</v>
+        <v>207.2926</v>
       </c>
       <c r="AG7" t="n">
-        <v>195.0172</v>
+        <v>195.0811</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>64.8</v>
+        <v>61.3</v>
       </c>
       <c r="AK7" t="n">
         <v>14.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>80.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN7" t="n">
         <v>190.01</v>
@@ -1831,10 +1831,10 @@
         <v>225.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.94</v>
+        <v>4.66</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.54</v>
+        <v>11.21</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>48.8</v>
+        <v>49.5</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 67.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.9%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 66.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1404453126144</v>
+        <v>1378506506240</v>
       </c>
       <c r="G8" t="n">
-        <v>20.78</v>
+        <v>20.39</v>
       </c>
       <c r="H8" t="n">
-        <v>15.89</v>
+        <v>15.59</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1933,25 +1933,25 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>22.7</v>
+        <v>18.8</v>
       </c>
       <c r="P8" t="n">
-        <v>81.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>64.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="S8" t="n">
-        <v>58.2</v>
+        <v>57.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>551.3051</v>
+        <v>541.12</v>
       </c>
       <c r="X8" t="n">
-        <v>-14.37</v>
+        <v>-13.72</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.43</v>
+        <v>-10.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>-14.14</v>
+        <v>-15.93</v>
       </c>
       <c r="AA8" t="n">
-        <v>-27.92</v>
+        <v>-27.76</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.4</v>
+        <v>23.59</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.54</v>
+        <v>37.51</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>594.2511</v>
+        <v>593.287</v>
       </c>
       <c r="AG8" t="n">
-        <v>624.3258</v>
+        <v>623.7717</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22.7</v>
+        <v>18.8</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>64.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2024,16 +2024,16 @@
         <v>539.03</v>
       </c>
       <c r="AP8" t="n">
-        <v>606.1</v>
+        <v>599.12</v>
       </c>
       <c r="AQ8" t="n">
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-7.23</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>-11.7</v>
+        <v>-13.25</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>37.8</v>
+        <v>36.2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 58.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 57.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1375587926016</v>
+        <v>1355287232512</v>
       </c>
       <c r="G10" t="n">
-        <v>322.49</v>
+        <v>314.82</v>
       </c>
       <c r="H10" t="n">
-        <v>160.13</v>
+        <v>157.77</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>22.4</v>
+        <v>16.2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>67.5</v>
+        <v>65.8</v>
       </c>
       <c r="S10" t="n">
-        <v>31.6</v>
+        <v>29.8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>348.295</v>
+        <v>343.15</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.08</v>
+        <v>-8.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>-13.81</v>
+        <v>-17.76</v>
       </c>
       <c r="Z10" t="n">
-        <v>-15.32</v>
+        <v>-16.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.71</v>
+        <v>14.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.36</v>
+        <v>58.35</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>367.2067</v>
+        <v>366.1926</v>
       </c>
       <c r="AG10" t="n">
-        <v>404.391</v>
+        <v>403.838</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22.4</v>
+        <v>16.2</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>67.5</v>
+        <v>65.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>348.29</v>
+        <v>351.12</v>
       </c>
       <c r="AQ10" t="n">
         <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-5.15</v>
+        <v>-6.29</v>
       </c>
       <c r="AS10" t="n">
-        <v>-13.87</v>
+        <v>-15.03</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 5.2% sotto MA50: attendere recupero; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 6.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 31.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.2%.</t>
+          <t>TSLA: scenario base High Risk, score 29.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.3%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3580078325760</v>
+        <v>3586167406592</v>
       </c>
       <c r="G2" t="n">
-        <v>26.83</v>
+        <v>26.91</v>
       </c>
       <c r="H2" t="n">
-        <v>20.45</v>
+        <v>20.49</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -741,25 +741,25 @@
         <v>29.12</v>
       </c>
       <c r="M2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>82.2</v>
+        <v>84</v>
       </c>
       <c r="P2" t="n">
-        <v>67.8</v>
+        <v>67.7</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>37.5</v>
+        <v>37.8</v>
       </c>
       <c r="S2" t="n">
-        <v>72.7</v>
+        <v>73.2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,37 +773,37 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>482.13</v>
+        <v>482.95</v>
       </c>
       <c r="X2" t="n">
-        <v>23.52</v>
+        <v>26.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.75</v>
+        <v>15.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.26</v>
+        <v>22.07</v>
       </c>
       <c r="AA2" t="n">
-        <v>-4.67</v>
+        <v>-3.56</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.3</v>
+        <v>15.41</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.18</v>
+        <v>26.16</v>
       </c>
       <c r="AD2" t="n">
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="AF2" t="n">
-        <v>418.1466</v>
+        <v>419.0862</v>
       </c>
       <c r="AG2" t="n">
-        <v>430.3896</v>
+        <v>429.4312</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,34 +814,34 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>82.2</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="n">
         <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>37.5</v>
+        <v>37.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN2" t="n">
-        <v>381.7</v>
+        <v>388.3689</v>
       </c>
       <c r="AO2" t="n">
-        <v>352.83</v>
+        <v>352.167</v>
       </c>
       <c r="AP2" t="n">
-        <v>506.06</v>
+        <v>505.1091</v>
       </c>
       <c r="AQ2" t="n">
-        <v>506.06</v>
+        <v>505.1091</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.3</v>
+        <v>15.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.02</v>
+        <v>12.44</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 15.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 15.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>45.6</v>
+        <v>46.3</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,17 +868,17 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.3%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.2%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 506.06 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 505.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.17 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -910,55 +910,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4596729118720</v>
+        <v>4222446206976</v>
       </c>
       <c r="G3" t="n">
-        <v>36.16</v>
+        <v>17.32</v>
       </c>
       <c r="H3" t="n">
-        <v>33.02</v>
+        <v>23.31</v>
       </c>
       <c r="I3" t="n">
-        <v>27.62</v>
+        <v>54.77</v>
       </c>
       <c r="J3" t="n">
-        <v>148.75</v>
+        <v>48.68</v>
       </c>
       <c r="K3" t="n">
-        <v>16.4</v>
+        <v>24.2</v>
       </c>
       <c r="L3" t="n">
-        <v>78.44</v>
+        <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>77.90000000000001</v>
+        <v>59</v>
       </c>
       <c r="P3" t="n">
-        <v>39</v>
+        <v>74.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>82.8</v>
+        <v>77</v>
       </c>
       <c r="S3" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,75 +972,75 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>314.95</v>
+        <v>345.255</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.27</v>
+        <v>8.68</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.29</v>
+        <v>-10.89</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.08</v>
+        <v>9.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>37.11</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>22.09</v>
+        <v>39.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.91</v>
+        <v>30.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33.36</v>
+        <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.82</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>309.7063</v>
+        <v>351.7779</v>
       </c>
       <c r="AG3" t="n">
-        <v>280.8403</v>
+        <v>332.7697</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>77.90000000000001</v>
+        <v>59</v>
       </c>
       <c r="AK3" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>82.8</v>
+        <v>77</v>
       </c>
       <c r="AM3" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN3" t="n">
-        <v>302.25</v>
+        <v>326.56</v>
       </c>
       <c r="AO3" t="n">
-        <v>274.9129</v>
+        <v>317.69</v>
       </c>
       <c r="AP3" t="n">
-        <v>339.7869</v>
+        <v>377.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>339.7869</v>
+        <v>389.8971</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.69</v>
+        <v>-1.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.15</v>
+        <v>3.75</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>70.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 71.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.7%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 70.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.9%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 389.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,55 +1109,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4161602322432</v>
+        <v>2797214367744</v>
       </c>
       <c r="G4" t="n">
-        <v>17.08</v>
+        <v>20.86</v>
       </c>
       <c r="H4" t="n">
-        <v>22.98</v>
+        <v>24.96</v>
       </c>
       <c r="I4" t="n">
-        <v>54.77</v>
+        <v>17.44</v>
       </c>
       <c r="J4" t="n">
-        <v>48.68</v>
+        <v>30.56</v>
       </c>
       <c r="K4" t="n">
-        <v>24.2</v>
+        <v>19.6</v>
       </c>
       <c r="L4" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="M4" t="n">
-        <v>26</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>57.4</v>
+        <v>63.3</v>
       </c>
       <c r="P4" t="n">
-        <v>75.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.4</v>
+        <v>36.6</v>
       </c>
       <c r="R4" t="n">
-        <v>74.8</v>
+        <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>70.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,75 +1169,75 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>340.28</v>
+        <v>259.33</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.53</v>
+        <v>10.99</v>
       </c>
       <c r="Y4" t="n">
-        <v>-12.45</v>
+        <v>-3.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.51</v>
+        <v>23.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>69.3</v>
+        <v>15.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>38.99</v>
+        <v>24.48</v>
       </c>
       <c r="AC4" t="n">
-        <v>30.6</v>
+        <v>32.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>-29.81</v>
+        <v>-30.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.27</v>
+        <v>0.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>351.9926</v>
+        <v>249.7428</v>
       </c>
       <c r="AG4" t="n">
-        <v>332.4573</v>
+        <v>238.3295</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>57.4</v>
+        <v>63.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>39.4</v>
+        <v>36.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>74.8</v>
+        <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN4" t="n">
-        <v>319.74</v>
+        <v>226.65</v>
       </c>
       <c r="AO4" t="n">
-        <v>317.69</v>
+        <v>226.65</v>
       </c>
       <c r="AP4" t="n">
-        <v>377.65</v>
+        <v>284.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>389.8971</v>
+        <v>284.02</v>
       </c>
       <c r="AR4" t="n">
-        <v>-3.33</v>
+        <v>3.84</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.35</v>
+        <v>8.81</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1255,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>64.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1264,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 70.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.3%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 389.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 317.69 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1284,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,53 +1306,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2815281856512</v>
+        <v>4502742106112</v>
       </c>
       <c r="G5" t="n">
-        <v>20.98</v>
+        <v>35.38</v>
       </c>
       <c r="H5" t="n">
-        <v>25.15</v>
+        <v>32.35</v>
       </c>
       <c r="I5" t="n">
-        <v>17.44</v>
+        <v>27.62</v>
       </c>
       <c r="J5" t="n">
-        <v>30.56</v>
+        <v>148.75</v>
       </c>
       <c r="K5" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="L5" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>78.44</v>
+      </c>
+      <c r="M5" t="n">
+        <v>35</v>
+      </c>
       <c r="N5" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>67.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>67.90000000000001</v>
+        <v>40.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.5</v>
+        <v>41</v>
       </c>
       <c r="R5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S5" t="n">
-        <v>69.3</v>
+        <v>68.3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,75 +1368,75 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>261.005</v>
+        <v>308.5</v>
       </c>
       <c r="X5" t="n">
-        <v>6.6</v>
+        <v>-4.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.51</v>
+        <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.41</v>
+        <v>16.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.47</v>
+        <v>37</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.79</v>
+        <v>21.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>32.29</v>
+        <v>26.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>-30.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>249.3341</v>
+        <v>309.9768</v>
       </c>
       <c r="AG5" t="n">
-        <v>238.3073</v>
+        <v>281.0243</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>67.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>36.5</v>
+        <v>41</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM5" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN5" t="n">
-        <v>226.65</v>
+        <v>302.25</v>
       </c>
       <c r="AO5" t="n">
-        <v>226.65</v>
+        <v>274.9129</v>
       </c>
       <c r="AP5" t="n">
-        <v>284.02</v>
+        <v>339.7869</v>
       </c>
       <c r="AQ5" t="n">
-        <v>284.02</v>
+        <v>339.7869</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.68</v>
+        <v>-0.48</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.52</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 69.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 68.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.5%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>578224128000</v>
+        <v>578454618112</v>
       </c>
       <c r="G6" t="n">
-        <v>59.08</v>
+        <v>59.2</v>
       </c>
       <c r="H6" t="n">
-        <v>29.27</v>
+        <v>29.14</v>
       </c>
       <c r="I6" t="n">
         <v>30.11</v>
@@ -1544,16 +1544,16 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q6" t="n">
         <v>16.7</v>
       </c>
       <c r="R6" t="n">
-        <v>74.7</v>
+        <v>75.2</v>
       </c>
       <c r="S6" t="n">
-        <v>67.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1567,25 +1567,25 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1505.4</v>
+        <v>1506</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.41</v>
+        <v>-4.52</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.04</v>
+        <v>8.49</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.35</v>
+        <v>20.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>138.81</v>
+        <v>132.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>36.59</v>
+        <v>36.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.59</v>
+        <v>39.56</v>
       </c>
       <c r="AD6" t="n">
         <v>-44.77</v>
@@ -1594,10 +1594,10 @@
         <v>0.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>1558.0333</v>
+        <v>1553.0741</v>
       </c>
       <c r="AG6" t="n">
-        <v>1242.3692</v>
+        <v>1251.13</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
         <v>16.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>74.7</v>
+        <v>75.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="AN6" t="n">
         <v>1362.2</v>
@@ -1632,10 +1632,10 @@
         <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>-3.38</v>
+        <v>-3.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>21.17</v>
+        <v>20.37</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.6</v>
+        <v>54.8</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.0%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5254261243904</v>
+        <v>5216476332032</v>
       </c>
       <c r="G7" t="n">
-        <v>33.22</v>
+        <v>32.98</v>
       </c>
       <c r="H7" t="n">
-        <v>16.69</v>
+        <v>16.53</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1740,19 +1740,19 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
       <c r="P7" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="R7" t="n">
-        <v>80.2</v>
+        <v>82.8</v>
       </c>
       <c r="S7" t="n">
-        <v>66.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>216.93</v>
+        <v>215.37</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>3.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.81</v>
+        <v>-1.77</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.59</v>
+        <v>13.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>23.67</v>
+        <v>22.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>66.98</v>
+        <v>66.47</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.64</v>
+        <v>46.61</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF7" t="n">
-        <v>207.2926</v>
+        <v>207.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>195.0811</v>
+        <v>195.1245</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>80.2</v>
+        <v>82.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN7" t="n">
         <v>190.01</v>
@@ -1831,10 +1831,10 @@
         <v>225.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.66</v>
+        <v>3.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.21</v>
+        <v>10.38</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>49.5</v>
+        <v>50.4</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 66.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 67.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1378506506240</v>
+        <v>1402491240448</v>
       </c>
       <c r="G8" t="n">
-        <v>20.39</v>
+        <v>20.75</v>
       </c>
       <c r="H8" t="n">
-        <v>15.59</v>
+        <v>15.86</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>18.8</v>
+        <v>21</v>
       </c>
       <c r="P8" t="n">
-        <v>82.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>62.1</v>
+        <v>64.5</v>
       </c>
       <c r="S8" t="n">
-        <v>57.2</v>
+        <v>57.8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>541.12</v>
+        <v>550.535</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.72</v>
+        <v>-9.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>-10.48</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>-15.93</v>
+        <v>-15.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>-27.76</v>
+        <v>-26.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>23.59</v>
+        <v>24.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>37.51</v>
+        <v>37.49</v>
       </c>
       <c r="AD8" t="n">
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>593.287</v>
+        <v>592.9829</v>
       </c>
       <c r="AG8" t="n">
-        <v>623.7717</v>
+        <v>623.3676</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18.8</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
         <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>62.1</v>
+        <v>64.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-8.789999999999999</v>
+        <v>-7.16</v>
       </c>
       <c r="AS8" t="n">
-        <v>-13.25</v>
+        <v>-11.68</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 8.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>36.2</v>
+        <v>37.4</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 57.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 57.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1355287232512</v>
+        <v>1441979826176</v>
       </c>
       <c r="G10" t="n">
-        <v>314.82</v>
+        <v>341.21</v>
       </c>
       <c r="H10" t="n">
-        <v>157.77</v>
+        <v>167.86</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>16.2</v>
+        <v>28.7</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>65.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>29.8</v>
+        <v>33.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>343.15</v>
+        <v>365.1</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.25</v>
+        <v>14.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>-17.76</v>
+        <v>-12.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>-16.65</v>
+        <v>-11.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>12.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.12</v>
+        <v>16.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.35</v>
+        <v>58.4</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>366.1926</v>
+        <v>365.9024</v>
       </c>
       <c r="AG10" t="n">
-        <v>403.838</v>
+        <v>403.3316</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16.2</v>
+        <v>28.7</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>65.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AM10" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>351.12</v>
+        <v>365.1</v>
       </c>
       <c r="AQ10" t="n">
         <v>442.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-6.29</v>
+        <v>-0.22</v>
       </c>
       <c r="AS10" t="n">
-        <v>-15.03</v>
+        <v>-9.48</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 6.3% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>20.3</v>
+        <v>26.3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 29.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.3%.</t>
+          <t>TSLA: scenario base High Risk, score 33.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.2%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3586167406592</v>
+        <v>3620101947392</v>
       </c>
       <c r="G2" t="n">
-        <v>26.91</v>
+        <v>27.19</v>
       </c>
       <c r="H2" t="n">
-        <v>20.49</v>
+        <v>20.68</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -741,25 +741,25 @@
         <v>29.12</v>
       </c>
       <c r="M2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>84</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>67.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="S2" t="n">
-        <v>73.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>482.95</v>
+        <v>487.52</v>
       </c>
       <c r="X2" t="n">
-        <v>26.8</v>
+        <v>27.96</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.45</v>
+        <v>16.69</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.07</v>
+        <v>27.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>-3.56</v>
+        <v>-2.52</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.41</v>
+        <v>16.05</v>
       </c>
       <c r="AC2" t="n">
         <v>26.16</v>
@@ -797,13 +797,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>419.0862</v>
+        <v>421.0502</v>
       </c>
       <c r="AG2" t="n">
-        <v>429.4312</v>
+        <v>429.3196</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,19 +814,19 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>84</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="AM2" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN2" t="n">
-        <v>388.3689</v>
+        <v>389.8062</v>
       </c>
       <c r="AO2" t="n">
         <v>352.167</v>
@@ -838,10 +838,10 @@
         <v>505.1091</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.22</v>
+        <v>15.79</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.44</v>
+        <v>13.56</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 15.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 15.8% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.2%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.8%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4222446206976</v>
+        <v>4263966670848</v>
       </c>
       <c r="G3" t="n">
-        <v>17.32</v>
+        <v>17.49</v>
       </c>
       <c r="H3" t="n">
-        <v>23.31</v>
+        <v>23.54</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>59</v>
+        <v>63.5</v>
       </c>
       <c r="P3" t="n">
-        <v>74.8</v>
+        <v>74.3</v>
       </c>
       <c r="Q3" t="n">
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>77</v>
+        <v>78.5</v>
       </c>
       <c r="S3" t="n">
-        <v>70.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>345.255</v>
+        <v>348.6501</v>
       </c>
       <c r="X3" t="n">
-        <v>8.68</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>-10.89</v>
+        <v>-8.91</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.75</v>
+        <v>12.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>73.70999999999999</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.6</v>
+        <v>39.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.58</v>
+        <v>30.57</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>351.7779</v>
+        <v>351.5868</v>
       </c>
       <c r="AG3" t="n">
-        <v>332.7697</v>
+        <v>333.1257</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>59</v>
+        <v>63.5</v>
       </c>
       <c r="AK3" t="n">
         <v>39.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>77</v>
+        <v>78.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN3" t="n">
-        <v>326.56</v>
+        <v>333.66</v>
       </c>
       <c r="AO3" t="n">
         <v>317.69</v>
@@ -1034,13 +1034,13 @@
         <v>377.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>389.8971</v>
+        <v>380.1129</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.85</v>
+        <v>-0.84</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.75</v>
+        <v>4.66</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>65.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 70.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.9%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 72.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 389.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 380.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,53 +1109,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2797214367744</v>
+        <v>4547108929536</v>
       </c>
       <c r="G4" t="n">
-        <v>20.86</v>
+        <v>35.73</v>
       </c>
       <c r="H4" t="n">
-        <v>24.96</v>
+        <v>32.66</v>
       </c>
       <c r="I4" t="n">
-        <v>17.44</v>
+        <v>27.62</v>
       </c>
       <c r="J4" t="n">
-        <v>30.56</v>
+        <v>148.75</v>
       </c>
       <c r="K4" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="L4" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>78.44</v>
+      </c>
+      <c r="M4" t="n">
+        <v>35</v>
+      </c>
       <c r="N4" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>63.3</v>
+        <v>71.5</v>
       </c>
       <c r="P4" t="n">
-        <v>68.3</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="n">
-        <v>36.6</v>
+        <v>41.1</v>
       </c>
       <c r="R4" t="n">
         <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1169,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>259.33</v>
+        <v>311.56</v>
       </c>
       <c r="X4" t="n">
-        <v>10.99</v>
+        <v>-6.36</v>
       </c>
       <c r="Y4" t="n">
-        <v>-3.4</v>
+        <v>0.97</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.43</v>
+        <v>17.26</v>
       </c>
       <c r="AA4" t="n">
-        <v>15.87</v>
+        <v>39.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.48</v>
+        <v>21.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>32.28</v>
+        <v>26.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>-30.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>249.7428</v>
+        <v>310.3175</v>
       </c>
       <c r="AG4" t="n">
-        <v>238.3295</v>
+        <v>281.2411</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1210,34 +1212,34 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>63.3</v>
+        <v>71.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>36.6</v>
+        <v>41.1</v>
       </c>
       <c r="AL4" t="n">
         <v>82.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>226.65</v>
+        <v>302.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>226.65</v>
+        <v>274.9129</v>
       </c>
       <c r="AP4" t="n">
-        <v>284.02</v>
+        <v>339.7869</v>
       </c>
       <c r="AQ4" t="n">
-        <v>284.02</v>
+        <v>339.7869</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.84</v>
+        <v>0.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.81</v>
+        <v>10.78</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1255,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>66.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 69.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1284,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1306,55 +1308,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4502742106112</v>
+        <v>2823749107712</v>
       </c>
       <c r="G5" t="n">
-        <v>35.38</v>
+        <v>21.04</v>
       </c>
       <c r="H5" t="n">
-        <v>32.35</v>
+        <v>25.2</v>
       </c>
       <c r="I5" t="n">
-        <v>27.62</v>
+        <v>17.44</v>
       </c>
       <c r="J5" t="n">
-        <v>148.75</v>
+        <v>30.56</v>
       </c>
       <c r="K5" t="n">
-        <v>16.4</v>
+        <v>19.6</v>
       </c>
       <c r="L5" t="n">
-        <v>78.44</v>
-      </c>
-      <c r="M5" t="n">
-        <v>35</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>71.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>40.9</v>
+        <v>67.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="R5" t="n">
-        <v>79</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>68.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1368,75 +1368,75 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>308.5</v>
+        <v>261.79</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.01</v>
+        <v>12.79</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.24</v>
+        <v>-1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.81</v>
+        <v>27.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>37</v>
+        <v>17.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>21.21</v>
+        <v>25.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>26.92</v>
+        <v>32.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>-33.36</v>
+        <v>-30.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>309.9768</v>
+        <v>250.1344</v>
       </c>
       <c r="AG5" t="n">
-        <v>281.0243</v>
+        <v>238.3883</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>71.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>79</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN5" t="n">
-        <v>302.25</v>
+        <v>226.65</v>
       </c>
       <c r="AO5" t="n">
-        <v>274.9129</v>
+        <v>226.65</v>
       </c>
       <c r="AP5" t="n">
-        <v>339.7869</v>
+        <v>284.02</v>
       </c>
       <c r="AQ5" t="n">
-        <v>339.7869</v>
+        <v>284.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.48</v>
+        <v>4.66</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 68.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.5%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>578454618112</v>
+        <v>572232171520</v>
       </c>
       <c r="G6" t="n">
-        <v>59.2</v>
+        <v>58.54</v>
       </c>
       <c r="H6" t="n">
-        <v>29.14</v>
+        <v>28.82</v>
       </c>
       <c r="I6" t="n">
         <v>30.11</v>
@@ -1544,13 +1544,13 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="R6" t="n">
-        <v>75.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="S6" t="n">
         <v>67.7</v>
@@ -1567,37 +1567,37 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1506</v>
+        <v>1489.8</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.52</v>
+        <v>-4.57</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.49</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.97</v>
+        <v>18.32</v>
       </c>
       <c r="AA6" t="n">
-        <v>132.99</v>
+        <v>127.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>36.45</v>
+        <v>35.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.56</v>
+        <v>39.52</v>
       </c>
       <c r="AD6" t="n">
         <v>-44.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>1553.0741</v>
+        <v>1550.4651</v>
       </c>
       <c r="AG6" t="n">
-        <v>1251.13</v>
+        <v>1254.2456</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>75.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AN6" t="n">
         <v>1362.2</v>
@@ -1632,10 +1632,10 @@
         <v>1719.3295</v>
       </c>
       <c r="AR6" t="n">
-        <v>-3.03</v>
+        <v>-3.91</v>
       </c>
       <c r="AS6" t="n">
-        <v>20.37</v>
+        <v>18.78</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.8</v>
+        <v>54.5</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.9%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5216476332032</v>
+        <v>5071756591104</v>
       </c>
       <c r="G7" t="n">
-        <v>32.98</v>
+        <v>32.07</v>
       </c>
       <c r="H7" t="n">
-        <v>16.53</v>
+        <v>16.06</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1734,25 +1734,25 @@
         <v>6.55</v>
       </c>
       <c r="M7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>61.4</v>
+        <v>56.9</v>
       </c>
       <c r="P7" t="n">
-        <v>66.3</v>
+        <v>68</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="R7" t="n">
         <v>82.8</v>
       </c>
       <c r="S7" t="n">
-        <v>67.3</v>
+        <v>66.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>215.37</v>
+        <v>209.395</v>
       </c>
       <c r="X7" t="n">
-        <v>3.17</v>
+        <v>1.24</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.77</v>
+        <v>-2.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.95</v>
+        <v>19.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>66.47</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.61</v>
+        <v>46.64</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AF7" t="n">
-        <v>207.59</v>
+        <v>207.6675</v>
       </c>
       <c r="AG7" t="n">
-        <v>195.1245</v>
+        <v>195.176</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>61.4</v>
+        <v>56.9</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="AL7" t="n">
         <v>82.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN7" t="n">
         <v>190.01</v>
@@ -1831,10 +1831,10 @@
         <v>225.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.75</v>
+        <v>0.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.38</v>
+        <v>7.29</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>50.4</v>
+        <v>49.3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 67.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 66.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1402491240448</v>
+        <v>1426246729728</v>
       </c>
       <c r="G8" t="n">
-        <v>20.75</v>
+        <v>21.08</v>
       </c>
       <c r="H8" t="n">
-        <v>15.86</v>
+        <v>16.13</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>21</v>
+        <v>25.4</v>
       </c>
       <c r="P8" t="n">
-        <v>81.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="Q8" t="n">
         <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>64.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>57.8</v>
+        <v>59</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>550.535</v>
+        <v>559.86</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.17</v>
+        <v>-5.94</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.279999999999999</v>
+        <v>-8.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>-15.88</v>
+        <v>-11.99</v>
       </c>
       <c r="AA8" t="n">
-        <v>-26.13</v>
+        <v>-24</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.27</v>
+        <v>25.5</v>
       </c>
       <c r="AC8" t="n">
         <v>37.49</v>
@@ -1989,13 +1989,13 @@
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="AF8" t="n">
-        <v>592.9829</v>
+        <v>592.8093</v>
       </c>
       <c r="AG8" t="n">
-        <v>623.3676</v>
+        <v>623.0353</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,16 +2006,16 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>25.4</v>
       </c>
       <c r="AK8" t="n">
         <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>64.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN8" t="n">
         <v>539.03</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-7.16</v>
+        <v>-5.56</v>
       </c>
       <c r="AS8" t="n">
-        <v>-11.68</v>
+        <v>-10.14</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>37.4</v>
+        <v>39.2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 57.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1441979826176</v>
+        <v>1379199352832</v>
       </c>
       <c r="G10" t="n">
-        <v>341.21</v>
+        <v>320.37</v>
       </c>
       <c r="H10" t="n">
-        <v>167.86</v>
+        <v>161.78</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>28.7</v>
+        <v>19.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>74.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="S10" t="n">
-        <v>33.9</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>365.1</v>
+        <v>349.225</v>
       </c>
       <c r="X10" t="n">
-        <v>14.2</v>
+        <v>11.56</v>
       </c>
       <c r="Y10" t="n">
-        <v>-12.62</v>
+        <v>-18.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>-11.34</v>
+        <v>-12.66</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.72</v>
+        <v>9.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.48</v>
+        <v>15.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.4</v>
+        <v>58.47</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>365.9024</v>
+        <v>364.8591</v>
       </c>
       <c r="AG10" t="n">
-        <v>403.3316</v>
+        <v>402.8452</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>28.7</v>
+        <v>19.4</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>74.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN10" t="n">
         <v>298.32</v>
@@ -2368,16 +2368,16 @@
         <v>298.32</v>
       </c>
       <c r="AP10" t="n">
-        <v>365.1</v>
+        <v>362.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>442.1</v>
+        <v>435.79</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.22</v>
+        <v>-4.28</v>
       </c>
       <c r="AS10" t="n">
-        <v>-9.48</v>
+        <v>-13.31</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 4.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>26.3</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 33.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.2%.</t>
+          <t>TSLA: scenario base High Risk, score 30.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.3%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 442.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 435.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3620101947392</v>
+        <v>3641636290560</v>
       </c>
       <c r="G2" t="n">
-        <v>27.19</v>
+        <v>27.35</v>
       </c>
       <c r="H2" t="n">
-        <v>20.68</v>
+        <v>20.8</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -747,19 +747,19 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>89.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="P2" t="n">
-        <v>67.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="S2" t="n">
-        <v>74.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>487.52</v>
+        <v>490.42</v>
       </c>
       <c r="X2" t="n">
-        <v>27.96</v>
+        <v>26.28</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.69</v>
+        <v>18.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.32</v>
+        <v>26.58</v>
       </c>
       <c r="AA2" t="n">
         <v>-2.52</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.05</v>
+        <v>15.92</v>
       </c>
       <c r="AC2" t="n">
         <v>26.16</v>
@@ -800,10 +800,10 @@
         <v>0.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>421.0502</v>
+        <v>423.0543</v>
       </c>
       <c r="AG2" t="n">
-        <v>429.3196</v>
+        <v>429.2555</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,13 +814,13 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>89.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="AK2" t="n">
         <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
@@ -838,10 +838,10 @@
         <v>505.1091</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.79</v>
+        <v>15.92</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.56</v>
+        <v>14.25</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 15.8% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 15.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.8%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 74.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.9%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4263966670848</v>
+        <v>4234858463232</v>
       </c>
       <c r="G3" t="n">
-        <v>17.49</v>
+        <v>17.37</v>
       </c>
       <c r="H3" t="n">
-        <v>23.54</v>
+        <v>23.38</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -940,25 +940,25 @@
         <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>63.5</v>
+        <v>58.8</v>
       </c>
       <c r="P3" t="n">
-        <v>74.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q3" t="n">
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>78.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>72.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,22 +972,22 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>348.6501</v>
+        <v>346.2699</v>
       </c>
       <c r="X3" t="n">
-        <v>9.039999999999999</v>
+        <v>6.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>-8.91</v>
+        <v>-10.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.08</v>
+        <v>11.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>75.04000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.67</v>
+        <v>39.31</v>
       </c>
       <c r="AC3" t="n">
         <v>30.57</v>
@@ -996,13 +996,13 @@
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>351.5868</v>
+        <v>351.3068</v>
       </c>
       <c r="AG3" t="n">
-        <v>333.1257</v>
+        <v>333.4354</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63.5</v>
+        <v>58.8</v>
       </c>
       <c r="AK3" t="n">
         <v>39.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>78.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
@@ -1034,13 +1034,13 @@
         <v>377.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>380.1129</v>
+        <v>377.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.84</v>
+        <v>-1.43</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.66</v>
+        <v>3.85</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>67.5</v>
+        <v>66</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 72.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 70.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.4%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 380.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 377.65 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,55 +1109,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4547108929536</v>
+        <v>2810675986432</v>
       </c>
       <c r="G4" t="n">
-        <v>35.73</v>
+        <v>20.98</v>
       </c>
       <c r="H4" t="n">
-        <v>32.66</v>
+        <v>25.08</v>
       </c>
       <c r="I4" t="n">
-        <v>27.62</v>
+        <v>17.44</v>
       </c>
       <c r="J4" t="n">
-        <v>148.75</v>
+        <v>30.56</v>
       </c>
       <c r="K4" t="n">
-        <v>16.4</v>
+        <v>19.6</v>
       </c>
       <c r="L4" t="n">
-        <v>78.44</v>
-      </c>
-      <c r="M4" t="n">
-        <v>35</v>
-      </c>
+        <v>45.62</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>71.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.1</v>
+        <v>36.6</v>
       </c>
       <c r="R4" t="n">
         <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1171,37 +1169,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>311.56</v>
+        <v>260.578</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.36</v>
+        <v>12.61</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.97</v>
+        <v>-1.78</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.26</v>
+        <v>24.94</v>
       </c>
       <c r="AA4" t="n">
-        <v>39.04</v>
+        <v>13.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>21.55</v>
+        <v>25.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.88</v>
+        <v>32.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>-33.36</v>
+        <v>-30.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>310.3175</v>
+        <v>250.5806</v>
       </c>
       <c r="AG4" t="n">
-        <v>281.2411</v>
+        <v>238.4416</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1212,10 +1210,10 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>71.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>41.1</v>
+        <v>36.6</v>
       </c>
       <c r="AL4" t="n">
         <v>82.8</v>
@@ -1224,22 +1222,22 @@
         <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>302.25</v>
+        <v>226.65</v>
       </c>
       <c r="AO4" t="n">
-        <v>274.9129</v>
+        <v>226.65</v>
       </c>
       <c r="AP4" t="n">
-        <v>339.7869</v>
+        <v>284.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>339.7869</v>
+        <v>284.02</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.4</v>
+        <v>3.99</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.78</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1257,7 +1255,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>68.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1266,17 +1264,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 69.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.4%.</t>
+          <t>AMZN: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1286,19 +1284,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1308,135 +1306,137 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2823749107712</v>
+        <v>576534085632</v>
       </c>
       <c r="G5" t="n">
-        <v>21.04</v>
+        <v>58.91</v>
       </c>
       <c r="H5" t="n">
-        <v>25.2</v>
+        <v>29.04</v>
       </c>
       <c r="I5" t="n">
-        <v>17.44</v>
+        <v>30.11</v>
       </c>
       <c r="J5" t="n">
-        <v>30.56</v>
+        <v>53.94</v>
       </c>
       <c r="K5" t="n">
-        <v>19.6</v>
+        <v>21.3</v>
       </c>
       <c r="L5" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>9.09</v>
+      </c>
+      <c r="M5" t="n">
+        <v>52</v>
+      </c>
       <c r="N5" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>68.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>67.8</v>
+        <v>22.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.6</v>
+        <v>16.8</v>
       </c>
       <c r="R5" t="n">
-        <v>80.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>69.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>261.79</v>
+        <v>1501</v>
       </c>
       <c r="X5" t="n">
-        <v>12.79</v>
+        <v>4.98</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.7</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.53</v>
+        <v>16.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.95</v>
+        <v>130.91</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.84</v>
+        <v>36.82</v>
       </c>
       <c r="AC5" t="n">
-        <v>32.28</v>
+        <v>39.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>-30.88</v>
+        <v>-44.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="AF5" t="n">
-        <v>250.1344</v>
+        <v>1548.6994</v>
       </c>
       <c r="AG5" t="n">
-        <v>238.3883</v>
+        <v>1257.3382</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>68.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>36.6</v>
+        <v>16.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>80.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="AN5" t="n">
-        <v>226.65</v>
+        <v>1362.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>226.65</v>
+        <v>1362.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>284.02</v>
+        <v>1621.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>284.02</v>
+        <v>1719.3295</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.66</v>
+        <v>-3.08</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.82</v>
+        <v>19.38</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>67</v>
+        <v>54.8</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.7%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.1%.</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 1362.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1483,19 +1483,19 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1510,50 +1510,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>572232171520</v>
+        <v>4501284585472</v>
       </c>
       <c r="G6" t="n">
-        <v>58.54</v>
+        <v>35.37</v>
       </c>
       <c r="H6" t="n">
-        <v>28.82</v>
+        <v>32.34</v>
       </c>
       <c r="I6" t="n">
-        <v>30.11</v>
+        <v>27.62</v>
       </c>
       <c r="J6" t="n">
-        <v>53.94</v>
+        <v>148.75</v>
       </c>
       <c r="K6" t="n">
-        <v>21.3</v>
+        <v>16.4</v>
       </c>
       <c r="L6" t="n">
-        <v>9.09</v>
+        <v>78.44</v>
       </c>
       <c r="M6" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>67.3</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>40.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.8</v>
+        <v>41.1</v>
       </c>
       <c r="R6" t="n">
-        <v>73.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="S6" t="n">
-        <v>67.7</v>
+        <v>67.3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1562,42 +1562,42 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1489.8</v>
+        <v>308.45</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.57</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.369999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.32</v>
+        <v>13.54</v>
       </c>
       <c r="AA6" t="n">
-        <v>127.13</v>
+        <v>35.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>35.78</v>
+        <v>20.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>39.52</v>
+        <v>26.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>-44.77</v>
+        <v>-33.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="AF6" t="n">
-        <v>1550.4651</v>
+        <v>310.6445</v>
       </c>
       <c r="AG6" t="n">
-        <v>1254.2456</v>
+        <v>281.4315</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1608,34 +1608,34 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>100</v>
+        <v>67.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.8</v>
+        <v>41.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>73.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="AN6" t="n">
-        <v>1362.2</v>
+        <v>302.25</v>
       </c>
       <c r="AO6" t="n">
-        <v>1362.2</v>
+        <v>274.9129</v>
       </c>
       <c r="AP6" t="n">
-        <v>1621.2</v>
+        <v>337.8986</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1719.3295</v>
+        <v>339.7869</v>
       </c>
       <c r="AR6" t="n">
-        <v>-3.91</v>
+        <v>-0.71</v>
       </c>
       <c r="AS6" t="n">
-        <v>18.78</v>
+        <v>9.6</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>54.5</v>
+        <v>66.2</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 67.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.9%.</t>
+          <t>AAPL: scenario base Hold / Monitor, score 67.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1719.33 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1362.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5071756591104</v>
+        <v>5152775864320</v>
       </c>
       <c r="G7" t="n">
-        <v>32.07</v>
+        <v>32.58</v>
       </c>
       <c r="H7" t="n">
-        <v>16.06</v>
+        <v>16.31</v>
       </c>
       <c r="I7" t="n">
         <v>62.97</v>
@@ -1734,16 +1734,16 @@
         <v>6.55</v>
       </c>
       <c r="M7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>56.9</v>
+        <v>60</v>
       </c>
       <c r="P7" t="n">
-        <v>68</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>14.5</v>
@@ -1752,7 +1752,7 @@
         <v>82.8</v>
       </c>
       <c r="S7" t="n">
-        <v>66.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>209.395</v>
+        <v>212.75</v>
       </c>
       <c r="X7" t="n">
-        <v>1.24</v>
+        <v>8.26</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.64</v>
+        <v>-0.87</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.449999999999999</v>
+        <v>10.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.83</v>
+        <v>19.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>64.90000000000001</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>46.64</v>
+        <v>46.63</v>
       </c>
       <c r="AD7" t="n">
         <v>-36.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>207.6675</v>
+        <v>207.8004</v>
       </c>
       <c r="AG7" t="n">
-        <v>195.176</v>
+        <v>195.2604</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>56.9</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
         <v>14.5</v>
@@ -1831,10 +1831,10 @@
         <v>225.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.83</v>
+        <v>2.38</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.29</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>49.3</v>
+        <v>50.1</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Hold / Monitor, score 66.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>NVDA: scenario base Hold / Monitor, score 67.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1426246729728</v>
+        <v>1442767306752</v>
       </c>
       <c r="G8" t="n">
-        <v>21.08</v>
+        <v>21.33</v>
       </c>
       <c r="H8" t="n">
-        <v>16.13</v>
+        <v>16.32</v>
       </c>
       <c r="I8" t="n">
         <v>29.83</v>
@@ -1939,19 +1939,19 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>25.4</v>
+        <v>26.7</v>
       </c>
       <c r="P8" t="n">
-        <v>80.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>27.7</v>
       </c>
       <c r="R8" t="n">
-        <v>66.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>559.86</v>
+        <v>566.355</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.94</v>
+        <v>-4.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.17</v>
+        <v>-7.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11.99</v>
+        <v>-11.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>-24</v>
+        <v>-24.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>25.5</v>
+        <v>26.17</v>
       </c>
       <c r="AC8" t="n">
         <v>37.49</v>
@@ -1989,13 +1989,13 @@
         <v>-34.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>592.8093</v>
+        <v>592.7905</v>
       </c>
       <c r="AG8" t="n">
-        <v>623.0353</v>
+        <v>622.6914</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25.4</v>
+        <v>26.7</v>
       </c>
       <c r="AK8" t="n">
         <v>27.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>66.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AM8" t="n">
         <v>752</v>
@@ -2030,10 +2030,10 @@
         <v>681.3099999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>-5.56</v>
+        <v>-4.46</v>
       </c>
       <c r="AS8" t="n">
-        <v>-10.14</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>prezzo 5.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 4.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>39.2</v>
+        <v>40</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.5%.</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1379199352832</v>
+        <v>1393400348672</v>
       </c>
       <c r="G10" t="n">
-        <v>320.37</v>
+        <v>326.67</v>
       </c>
       <c r="H10" t="n">
-        <v>161.78</v>
+        <v>163.44</v>
       </c>
       <c r="I10" t="n">
         <v>3.67</v>
@@ -2283,7 +2283,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>68.8</v>
+        <v>70.7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.9</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2309,37 +2309,37 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>349.225</v>
+        <v>352.8</v>
       </c>
       <c r="X10" t="n">
-        <v>11.56</v>
+        <v>14.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>-18.02</v>
+        <v>-18.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>-12.66</v>
+        <v>-13.82</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.1</v>
+        <v>3.76</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.02</v>
+        <v>14.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.47</v>
+        <v>58.44</v>
       </c>
       <c r="AD10" t="n">
         <v>-53.77</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>364.8591</v>
+        <v>363.781</v>
       </c>
       <c r="AG10" t="n">
-        <v>402.8452</v>
+        <v>402.2975</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>68.8</v>
+        <v>70.7</v>
       </c>
       <c r="AM10" t="n">
         <v>752</v>
@@ -2371,13 +2371,13 @@
         <v>362.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>435.79</v>
+        <v>425.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>-4.28</v>
+        <v>-3.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>-13.31</v>
+        <v>-12.29</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>prezzo 4.3% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 30.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.3%.</t>
+          <t>TSLA: scenario base High Risk, score 30.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.0%.</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 435.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 425.30 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">

--- a/AlphaForge_Watchlist.xlsx
+++ b/AlphaForge_Watchlist.xlsx
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3641636290560</v>
+        <v>3685818040320</v>
       </c>
       <c r="G2" t="n">
-        <v>27.35</v>
+        <v>27.65</v>
       </c>
       <c r="H2" t="n">
-        <v>20.8</v>
+        <v>21.06</v>
       </c>
       <c r="I2" t="n">
         <v>40.3</v>
@@ -747,19 +747,19 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>90.7</v>
+        <v>93.2</v>
       </c>
       <c r="P2" t="n">
-        <v>66.7</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="S2" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>490.42</v>
+        <v>496.37</v>
       </c>
       <c r="X2" t="n">
-        <v>26.28</v>
+        <v>26.43</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.1</v>
+        <v>20.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.58</v>
+        <v>24.41</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2.52</v>
+        <v>-0.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.92</v>
+        <v>16.3</v>
       </c>
       <c r="AC2" t="n">
         <v>26.16</v>
@@ -797,13 +797,13 @@
         <v>-34.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>423.0543</v>
+        <v>425.0273</v>
       </c>
       <c r="AG2" t="n">
-        <v>429.2555</v>
+        <v>429.2786</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -814,19 +814,19 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90.7</v>
+        <v>93.2</v>
       </c>
       <c r="AK2" t="n">
         <v>41</v>
       </c>
       <c r="AL2" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="AM2" t="n">
         <v>752</v>
       </c>
       <c r="AN2" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="AO2" t="n">
         <v>352.167</v>
@@ -838,10 +838,10 @@
         <v>505.1091</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.92</v>
+        <v>16.79</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.25</v>
+        <v>15.63</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>prezzo 15.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 16.8% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="AW2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Accumulate Carefully, score 74.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 15.9%.</t>
+          <t>MSFT: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.8%.</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4234858463232</v>
+        <v>4182637805568</v>
       </c>
       <c r="G3" t="n">
-        <v>17.37</v>
+        <v>17.17</v>
       </c>
       <c r="H3" t="n">
-        <v>23.38</v>
+        <v>23.09</v>
       </c>
       <c r="I3" t="n">
         <v>54.77</v>
@@ -946,19 +946,19 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>58.8</v>
+        <v>55</v>
       </c>
       <c r="P3" t="n">
-        <v>74.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="Q3" t="n">
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>77.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="S3" t="n">
-        <v>70.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -972,37 +972,37 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>346.2699</v>
+        <v>342</v>
       </c>
       <c r="X3" t="n">
-        <v>6.04</v>
+        <v>2.48</v>
       </c>
       <c r="Y3" t="n">
-        <v>-10.9</v>
+        <v>-11.99</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.52</v>
+        <v>9.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>68.5</v>
+        <v>64.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.31</v>
+        <v>38.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.57</v>
+        <v>30.58</v>
       </c>
       <c r="AD3" t="n">
         <v>-29.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>351.3068</v>
+        <v>350.7736</v>
       </c>
       <c r="AG3" t="n">
-        <v>333.4354</v>
+        <v>333.7279</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>58.8</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
         <v>39.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>77.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="AM3" t="n">
         <v>752</v>
@@ -1037,10 +1037,10 @@
         <v>377.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.43</v>
+        <v>-2.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.85</v>
+        <v>2.48</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>66</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Accumulate Carefully, score 70.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.4%.</t>
+          <t>GOOGL: scenario base Accumulate Carefully, score 69.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1109,53 +1109,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2810675986432</v>
+        <v>4574545969152</v>
       </c>
       <c r="G4" t="n">
-        <v>20.98</v>
+        <v>35.99</v>
       </c>
       <c r="H4" t="n">
-        <v>25.08</v>
+        <v>32.86</v>
       </c>
       <c r="I4" t="n">
-        <v>17.44</v>
+        <v>27.62</v>
       </c>
       <c r="J4" t="n">
-        <v>30.56</v>
+        <v>148.75</v>
       </c>
       <c r="K4" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="L4" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>78.44</v>
+      </c>
+      <c r="M4" t="n">
+        <v>35</v>
+      </c>
       <c r="N4" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>65.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>68</v>
+        <v>39.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>36.6</v>
+        <v>41.1</v>
       </c>
       <c r="R4" t="n">
         <v>82.8</v>
       </c>
       <c r="S4" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1169,37 +1171,37 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>260.578</v>
+        <v>313.45</v>
       </c>
       <c r="X4" t="n">
-        <v>12.61</v>
+        <v>-7.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.78</v>
+        <v>0.92</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.94</v>
+        <v>14.51</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.87</v>
+        <v>38.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>25.2</v>
+        <v>20.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>32.28</v>
+        <v>26.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>-30.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AE4" t="n">
         <v>0.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>250.5806</v>
+        <v>311.0192</v>
       </c>
       <c r="AG4" t="n">
-        <v>238.4416</v>
+        <v>281.6621</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1210,10 +1212,10 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>36.6</v>
+        <v>41.1</v>
       </c>
       <c r="AL4" t="n">
         <v>82.8</v>
@@ -1222,22 +1224,22 @@
         <v>752</v>
       </c>
       <c r="AN4" t="n">
-        <v>226.65</v>
+        <v>302.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>226.65</v>
+        <v>274.9129</v>
       </c>
       <c r="AP4" t="n">
-        <v>284.02</v>
+        <v>333.1427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>284.02</v>
+        <v>339.7869</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.99</v>
+        <v>0.78</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.279999999999999</v>
+        <v>11.29</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1255,7 +1257,7 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>67.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1264,17 +1266,17 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.0%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 284.02 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 339.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 226.65 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 274.91 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1284,19 +1286,19 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1306,137 +1308,135 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>576534085632</v>
+        <v>2807461576704</v>
       </c>
       <c r="G5" t="n">
-        <v>58.91</v>
+        <v>20.94</v>
       </c>
       <c r="H5" t="n">
-        <v>29.04</v>
+        <v>